--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1303,16 +1303,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1328,7 +1320,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1336,30 +1328,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1659,70 +1633,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1763,10 +1737,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>41754</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1778,7 +1752,7 @@
       <c r="T2" t="s">
         <v>147</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="1">
         <v>46170</v>
       </c>
     </row>
@@ -1819,10 +1793,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>44709</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1869,10 +1843,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>44348</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -1919,10 +1893,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>46059</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -1934,7 +1908,7 @@
       <c r="T5" t="s">
         <v>148</v>
       </c>
-      <c r="U5" s="2">
+      <c r="U5" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -1972,10 +1946,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>46149</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -2022,10 +1996,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>43731</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -2037,7 +2011,7 @@
       <c r="T7" t="s">
         <v>149</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U7" s="1">
         <v>43507</v>
       </c>
     </row>
@@ -2078,10 +2052,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45511</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2128,10 +2102,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45716</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2143,7 +2117,7 @@
       <c r="T9" t="s">
         <v>150</v>
       </c>
-      <c r="U9" s="2">
+      <c r="U9" s="1">
         <v>44665</v>
       </c>
     </row>
@@ -2184,10 +2158,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>45064</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2228,10 +2202,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>46135</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2243,7 +2217,7 @@
       <c r="T11" t="s">
         <v>151</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="1">
         <v>46203</v>
       </c>
     </row>
@@ -2281,7 +2255,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2322,10 +2296,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>46199</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2369,10 +2343,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45667</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2384,7 +2358,7 @@
       <c r="T14" t="s">
         <v>152</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" s="1">
         <v>46072</v>
       </c>
     </row>
@@ -2425,10 +2399,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>46064</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="1">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2475,10 +2449,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>44285</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="1">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2490,7 +2464,7 @@
       <c r="T16" t="s">
         <v>153</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2531,10 +2505,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45922</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2581,10 +2555,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>45930</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2596,7 +2570,7 @@
       <c r="T18" t="s">
         <v>154</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" s="1">
         <v>46198</v>
       </c>
     </row>
@@ -2637,10 +2611,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45524</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2652,7 +2626,7 @@
       <c r="T19" t="s">
         <v>122</v>
       </c>
-      <c r="U19" s="2">
+      <c r="U19" s="1">
         <v>46153</v>
       </c>
       <c r="V19">
@@ -2696,10 +2670,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>45026</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2711,7 +2685,7 @@
       <c r="T20" t="s">
         <v>155</v>
       </c>
-      <c r="U20" s="2">
+      <c r="U20" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2752,10 +2726,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>45159</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2767,7 +2741,7 @@
       <c r="T21" t="s">
         <v>124</v>
       </c>
-      <c r="U21" s="2">
+      <c r="U21" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2808,10 +2782,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2823,7 +2797,7 @@
       <c r="T22" t="s">
         <v>156</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" s="1">
         <v>45995</v>
       </c>
     </row>
@@ -2861,10 +2835,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>45713</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -2873,7 +2847,7 @@
       <c r="S23" t="s">
         <v>146</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -2914,10 +2888,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>46062</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>45925</v>
       </c>
       <c r="R24" t="s">
@@ -2964,10 +2938,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45079</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -3014,10 +2988,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>41346</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -3029,7 +3003,7 @@
       <c r="T26" t="s">
         <v>157</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>46150</v>
       </c>
     </row>
@@ -3070,10 +3044,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45579</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3120,10 +3094,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>46171</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3170,10 +3144,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44320</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3220,10 +3194,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="1">
         <v>42661</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="1">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3235,7 +3209,7 @@
       <c r="T30" t="s">
         <v>158</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>45358</v>
       </c>
     </row>
@@ -3276,10 +3250,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="1">
         <v>46064</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="1">
         <v>46064</v>
       </c>
       <c r="R31" t="s">
@@ -3326,10 +3300,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="1">
         <v>43797</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="1">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3376,10 +3350,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>42810</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3391,7 +3365,7 @@
       <c r="T33" t="s">
         <v>159</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>43802</v>
       </c>
     </row>
@@ -3432,10 +3406,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>45070</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>44910</v>
       </c>
       <c r="R34" t="s">
@@ -3482,10 +3456,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>43250</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3532,10 +3506,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45841</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3582,10 +3556,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="2">
+      <c r="P37" s="1">
         <v>45105</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="1">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3597,7 +3571,7 @@
       <c r="T37" t="s">
         <v>160</v>
       </c>
-      <c r="U37" s="2">
+      <c r="U37" s="1">
         <v>46184</v>
       </c>
     </row>
@@ -3638,10 +3612,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>45636</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>45579</v>
       </c>
       <c r="S38" t="s">
@@ -3685,10 +3659,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>45831</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3732,10 +3706,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>44287</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3756,22 +3730,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>162</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>163</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>164</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>165</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>166</v>
       </c>
     </row>
@@ -7951,91 +7925,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>226</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>227</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>228</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>229</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>230</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>231</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>232</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>233</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>234</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>235</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>236</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>237</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>238</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>239</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>240</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>241</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>242</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>243</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>244</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>245</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>246</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>247</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>248</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>249</v>
       </c>
     </row>
@@ -8049,13 +8023,13 @@
       <c r="D2" t="s">
         <v>252</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
         <v>255</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>45492</v>
       </c>
       <c r="H2" t="s">
@@ -8073,13 +8047,13 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45491</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="1">
         <v>45528</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="1">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
@@ -8117,13 +8091,13 @@
       <c r="D3" t="s">
         <v>253</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
         <v>255</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>45631</v>
       </c>
       <c r="H3" t="s">
@@ -8141,13 +8115,13 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45628</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>45632</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
@@ -8182,13 +8156,13 @@
       <c r="D4" t="s">
         <v>253</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
         <v>255</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>45716</v>
       </c>
       <c r="H4" t="s">
@@ -8206,13 +8180,13 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45716</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <v>45722</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="1">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
@@ -8247,13 +8221,13 @@
       <c r="D5" t="s">
         <v>253</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
         <v>255</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>45728</v>
       </c>
       <c r="H5" t="s">
@@ -8271,13 +8245,13 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45722</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <v>45782</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="1">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
@@ -8315,13 +8289,13 @@
       <c r="D6" t="s">
         <v>253</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
         <v>255</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>45755</v>
       </c>
       <c r="H6" t="s">
@@ -8339,13 +8313,13 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45728</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="1">
         <v>45734</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="1">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
@@ -8383,7 +8357,7 @@
       <c r="D7" t="s">
         <v>254</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
@@ -8404,10 +8378,10 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45772</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="1">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
@@ -8445,7 +8419,7 @@
       <c r="D8" t="s">
         <v>254</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
@@ -8466,10 +8440,10 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>45762</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="1">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
@@ -8507,7 +8481,7 @@
       <c r="D9" t="s">
         <v>254</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
@@ -8528,10 +8502,10 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45763</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="1">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
@@ -8569,13 +8543,13 @@
       <c r="D10" t="s">
         <v>253</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
         <v>255</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>45755</v>
       </c>
       <c r="H10" t="s">
@@ -8593,13 +8567,13 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45754</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="1">
         <v>45849</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="1">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
@@ -8634,13 +8608,13 @@
       <c r="D11" t="s">
         <v>253</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
         <v>255</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>44973</v>
       </c>
       <c r="H11" t="s">
@@ -8658,13 +8632,13 @@
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44973</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="1">
         <v>45687</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" s="1">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
@@ -8699,13 +8673,13 @@
       <c r="D12" t="s">
         <v>253</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
         <v>255</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>45358</v>
       </c>
       <c r="H12" t="s">
@@ -8723,13 +8697,13 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45358</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="1">
         <v>45517</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12" s="1">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
@@ -8764,13 +8738,13 @@
       <c r="D13" t="s">
         <v>253</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
         <v>255</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>45573</v>
       </c>
       <c r="H13" t="s">
@@ -8788,13 +8762,13 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45572</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="1">
         <v>45572</v>
       </c>
-      <c r="S13" s="2">
+      <c r="S13" s="1">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
@@ -8832,13 +8806,13 @@
       <c r="D14" t="s">
         <v>253</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
         <v>255</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>45747</v>
       </c>
       <c r="H14" t="s">
@@ -8856,13 +8830,13 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>45736</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" s="1">
         <v>46101</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14" s="1">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
@@ -8898,70 +8872,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8999,10 +8973,10 @@
       <c r="O2" t="s">
         <v>102</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>45490</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -9046,10 +9020,10 @@
       <c r="O3" t="s">
         <v>81</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>45618</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -9093,10 +9067,10 @@
       <c r="O4" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>45539</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -9140,10 +9114,10 @@
       <c r="O5" t="s">
         <v>98</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>45567</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -9187,10 +9161,10 @@
       <c r="O6" t="s">
         <v>95</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>45568</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -9234,10 +9208,10 @@
       <c r="O7" t="s">
         <v>83</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>45831</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -9281,10 +9255,10 @@
       <c r="O8" t="s">
         <v>103</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45601</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -9328,10 +9302,10 @@
       <c r="O9" t="s">
         <v>92</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45631</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -9375,10 +9349,10 @@
       <c r="O10" t="s">
         <v>89</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>43902</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -9422,10 +9396,10 @@
       <c r="O11" t="s">
         <v>99</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>44736</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -9469,10 +9443,10 @@
       <c r="O12" t="s">
         <v>82</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>45776</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -9516,10 +9490,10 @@
       <c r="O13" t="s">
         <v>80</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>45772</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -9563,10 +9537,10 @@
       <c r="O14" t="s">
         <v>100</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45000</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -9610,7 +9584,7 @@
       <c r="O15" t="s">
         <v>94</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -9651,7 +9625,7 @@
       <c r="O16" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -9692,10 +9666,10 @@
       <c r="O17" t="s">
         <v>93</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45371</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -9739,10 +9713,10 @@
       <c r="O18" t="s">
         <v>91</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>46001</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -9786,10 +9760,10 @@
       <c r="O19" t="s">
         <v>104</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45436</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -9833,10 +9807,10 @@
       <c r="O20" t="s">
         <v>96</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>44372</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -9880,10 +9854,10 @@
       <c r="O21" t="s">
         <v>105</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>44362</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -9927,10 +9901,10 @@
       <c r="O22" t="s">
         <v>86</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -9968,10 +9942,10 @@
       <c r="O23" t="s">
         <v>356</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>40044</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -9983,7 +9957,7 @@
       <c r="T23" t="s">
         <v>396</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45775</v>
       </c>
     </row>
@@ -10021,10 +9995,10 @@
       <c r="O24" t="s">
         <v>80</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>43549</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -10036,7 +10010,7 @@
       <c r="T24" t="s">
         <v>397</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -10074,10 +10048,10 @@
       <c r="O25" t="s">
         <v>86</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45447</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -10089,7 +10063,7 @@
       <c r="T25" t="s">
         <v>398</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U25" s="1">
         <v>45937</v>
       </c>
     </row>
@@ -10127,10 +10101,10 @@
       <c r="O26" t="s">
         <v>100</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>44485</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -10142,7 +10116,7 @@
       <c r="T26" t="s">
         <v>399</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>45580</v>
       </c>
     </row>
@@ -10180,10 +10154,10 @@
       <c r="O27" t="s">
         <v>86</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45420</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -10195,7 +10169,7 @@
       <c r="T27" t="s">
         <v>400</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U27" s="1">
         <v>45588</v>
       </c>
     </row>
@@ -10233,10 +10207,10 @@
       <c r="O28" t="s">
         <v>101</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>44369</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -10248,7 +10222,7 @@
       <c r="T28" t="s">
         <v>401</v>
       </c>
-      <c r="U28" s="2">
+      <c r="U28" s="1">
         <v>45831</v>
       </c>
     </row>
@@ -10286,10 +10260,10 @@
       <c r="O29" t="s">
         <v>98</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44652</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -10301,7 +10275,7 @@
       <c r="T29" t="s">
         <v>402</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U29" s="1">
         <v>45734</v>
       </c>
     </row>
@@ -10333,7 +10307,7 @@
       <c r="T30" t="s">
         <v>403</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10365,7 +10339,7 @@
       <c r="T31" t="s">
         <v>404</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10397,7 +10371,7 @@
       <c r="T32" t="s">
         <v>405</v>
       </c>
-      <c r="U32" s="2">
+      <c r="U32" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10435,10 +10409,10 @@
       <c r="O33" t="s">
         <v>90</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>43762</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -10450,7 +10424,7 @@
       <c r="T33" t="s">
         <v>384</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>46037</v>
       </c>
     </row>
@@ -10488,16 +10462,16 @@
       <c r="O34" t="s">
         <v>357</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>40071</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>146</v>
       </c>
-      <c r="U34" s="2">
+      <c r="U34" s="1">
         <v>41023</v>
       </c>
     </row>
@@ -10529,10 +10503,10 @@
       <c r="O35" t="s">
         <v>87</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>44784</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -10541,7 +10515,7 @@
       <c r="S35" t="s">
         <v>146</v>
       </c>
-      <c r="U35" s="2">
+      <c r="U35" s="1">
         <v>45259</v>
       </c>
     </row>
@@ -10579,10 +10553,10 @@
       <c r="O36" t="s">
         <v>91</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45103</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -10591,7 +10565,7 @@
       <c r="S36" t="s">
         <v>146</v>
       </c>
-      <c r="U36" s="2">
+      <c r="U36" s="1">
         <v>46000</v>
       </c>
     </row>
@@ -10655,10 +10629,10 @@
       <c r="O38" t="s">
         <v>96</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>38511</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -10667,7 +10641,7 @@
       <c r="S38" t="s">
         <v>146</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>39068</v>
       </c>
     </row>
@@ -10705,10 +10679,10 @@
       <c r="O39" t="s">
         <v>103</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>39006</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -10720,7 +10694,7 @@
       <c r="T39" t="s">
         <v>406</v>
       </c>
-      <c r="U39" s="2">
+      <c r="U39" s="1">
         <v>40568</v>
       </c>
     </row>
@@ -10752,10 +10726,10 @@
       <c r="O40" t="s">
         <v>100</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>40836</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -10767,7 +10741,7 @@
       <c r="T40" t="s">
         <v>407</v>
       </c>
-      <c r="U40" s="2">
+      <c r="U40" s="1">
         <v>42270</v>
       </c>
     </row>
@@ -10805,10 +10779,10 @@
       <c r="O41" t="s">
         <v>95</v>
       </c>
-      <c r="P41" s="2">
+      <c r="P41" s="1">
         <v>42940</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="1">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -10820,7 +10794,7 @@
       <c r="T41" t="s">
         <v>408</v>
       </c>
-      <c r="U41" s="2">
+      <c r="U41" s="1">
         <v>44148</v>
       </c>
     </row>
@@ -10858,10 +10832,10 @@
       <c r="O42" t="s">
         <v>82</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="1">
         <v>43696</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="1">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -10873,7 +10847,7 @@
       <c r="T42" t="s">
         <v>409</v>
       </c>
-      <c r="U42" s="2">
+      <c r="U42" s="1">
         <v>43185</v>
       </c>
     </row>
@@ -10911,10 +10885,10 @@
       <c r="O43" t="s">
         <v>84</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="1">
         <v>43544</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="1">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -10926,7 +10900,7 @@
       <c r="T43" t="s">
         <v>410</v>
       </c>
-      <c r="U43" s="2">
+      <c r="U43" s="1">
         <v>42850</v>
       </c>
     </row>
@@ -10964,10 +10938,10 @@
       <c r="O44" t="s">
         <v>97</v>
       </c>
-      <c r="P44" s="2">
+      <c r="P44" s="1">
         <v>45076</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="1">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -10979,7 +10953,7 @@
       <c r="T44" t="s">
         <v>411</v>
       </c>
-      <c r="U44" s="2">
+      <c r="U44" s="1">
         <v>44404</v>
       </c>
     </row>
@@ -11017,10 +10991,10 @@
       <c r="O45" t="s">
         <v>81</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="1">
         <v>42963</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="1">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -11032,7 +11006,7 @@
       <c r="T45" t="s">
         <v>412</v>
       </c>
-      <c r="U45" s="2">
+      <c r="U45" s="1">
         <v>42698</v>
       </c>
     </row>
@@ -11070,10 +11044,10 @@
       <c r="O46" t="s">
         <v>88</v>
       </c>
-      <c r="P46" s="2">
+      <c r="P46" s="1">
         <v>45054</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="1">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -11085,7 +11059,7 @@
       <c r="T46" t="s">
         <v>413</v>
       </c>
-      <c r="U46" s="2">
+      <c r="U46" s="1">
         <v>43941</v>
       </c>
     </row>
@@ -11100,25 +11074,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>162</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>414</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>415</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>416</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>417</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>418</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -575,7 +575,7 @@
     <t>19.2</t>
   </si>
   <si>
-    <t>2.974628583</t>
+    <t>29.77939946</t>
   </si>
   <si>
     <t>5.1586629</t>
@@ -4906,13 +4906,13 @@
         <v>2729</v>
       </c>
       <c r="C68">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -11302,7 +11302,7 @@
         <v>2832.83</v>
       </c>
       <c r="D11">
-        <v>313.1666667</v>
+        <v>1167.166667</v>
       </c>
       <c r="E11">
         <v>39.70818182</v>
@@ -11311,7 +11311,7 @@
         <v>218.395</v>
       </c>
       <c r="G11">
-        <v>7.886703755</v>
+        <v>29.39360639</v>
       </c>
     </row>
     <row r="12" spans="1:7">

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="422">
   <si>
     <t>om</t>
   </si>
@@ -461,6 +461,9 @@
     <t>REMOV</t>
   </si>
   <si>
+    <t>OS OPR</t>
+  </si>
+  <si>
     <t>3810279892</t>
   </si>
   <si>
@@ -503,6 +506,9 @@
     <t>3810280182</t>
   </si>
   <si>
+    <t>MOTOR EM HSI NO OPERADOR, 17/07/2026</t>
+  </si>
+  <si>
     <t>serial</t>
   </si>
   <si>
@@ -575,7 +581,7 @@
     <t>19.2</t>
   </si>
   <si>
-    <t>29.77939946</t>
+    <t>#N/A</t>
   </si>
   <si>
     <t>5.1586629</t>
@@ -609,6 +615,9 @@
   </si>
   <si>
     <t>15.25999355</t>
+  </si>
+  <si>
+    <t>Rachadura na CT DISK, vai recolher</t>
   </si>
   <si>
     <t>22.5</t>
@@ -1750,7 +1759,7 @@
         <v>142</v>
       </c>
       <c r="T2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="U2" s="1">
         <v>46170</v>
@@ -1906,7 +1915,7 @@
         <v>142</v>
       </c>
       <c r="T5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="U5" s="1">
         <v>46210</v>
@@ -2009,7 +2018,7 @@
         <v>144</v>
       </c>
       <c r="T7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="U7" s="1">
         <v>43507</v>
@@ -2115,7 +2124,7 @@
         <v>144</v>
       </c>
       <c r="T9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="U9" s="1">
         <v>44665</v>
@@ -2215,7 +2224,7 @@
         <v>142</v>
       </c>
       <c r="T11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="U11" s="1">
         <v>46203</v>
@@ -2356,7 +2365,7 @@
         <v>142</v>
       </c>
       <c r="T14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="U14" s="1">
         <v>46072</v>
@@ -2462,7 +2471,7 @@
         <v>142</v>
       </c>
       <c r="T16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U16" s="1">
         <v>46157</v>
@@ -2568,7 +2577,7 @@
         <v>142</v>
       </c>
       <c r="T18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="U18" s="1">
         <v>46198</v>
@@ -2683,7 +2692,7 @@
         <v>142</v>
       </c>
       <c r="T20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U20" s="1">
         <v>46157</v>
@@ -2795,7 +2804,7 @@
         <v>142</v>
       </c>
       <c r="T22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="U22" s="1">
         <v>45995</v>
@@ -3001,7 +3010,7 @@
         <v>142</v>
       </c>
       <c r="T26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U26" s="1">
         <v>46150</v>
@@ -3207,7 +3216,7 @@
         <v>142</v>
       </c>
       <c r="T30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="U30" s="1">
         <v>45358</v>
@@ -3313,7 +3322,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:22">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -3363,13 +3372,13 @@
         <v>144</v>
       </c>
       <c r="T33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="U33" s="1">
         <v>43802</v>
       </c>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:22">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -3419,7 +3428,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:22">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -3469,7 +3478,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:22">
       <c r="A36" t="s">
         <v>33</v>
       </c>
@@ -3519,7 +3528,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:22">
       <c r="A37" t="s">
         <v>22</v>
       </c>
@@ -3569,13 +3578,13 @@
         <v>142</v>
       </c>
       <c r="T37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U37" s="1">
         <v>46184</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:22">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -3619,10 +3628,13 @@
         <v>45579</v>
       </c>
       <c r="S38" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21">
+        <v>147</v>
+      </c>
+      <c r="V38" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
       <c r="A39" t="s">
         <v>26</v>
       </c>
@@ -3669,7 +3681,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:22">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -3726,27 +3738,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F243"/>
+  <dimension ref="A1:F245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3763,7 +3775,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3780,7 +3792,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3797,7 +3809,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3814,7 +3826,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3831,10 +3843,10 @@
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F6" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3851,7 +3863,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3868,7 +3880,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3885,7 +3897,7 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3902,7 +3914,7 @@
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3919,7 +3931,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3936,7 +3948,7 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3953,10 +3965,10 @@
         <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3973,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3990,7 +4002,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4007,7 +4019,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4024,10 +4036,10 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4044,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4061,7 +4073,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4078,7 +4090,7 @@
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4095,7 +4107,7 @@
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4112,7 +4124,7 @@
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4129,7 +4141,7 @@
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4146,10 +4158,10 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F24" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4166,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4183,7 +4195,7 @@
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4200,7 +4212,7 @@
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4217,7 +4229,7 @@
         <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4234,7 +4246,7 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4251,7 +4263,7 @@
         <v>6</v>
       </c>
       <c r="E30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4268,7 +4280,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4285,7 +4297,7 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4302,7 +4314,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4319,7 +4331,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4336,7 +4348,7 @@
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4353,7 +4365,7 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4370,7 +4382,7 @@
         <v>6</v>
       </c>
       <c r="E37" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4387,10 +4399,10 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F38" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4407,7 +4419,7 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4424,7 +4436,7 @@
         <v>8</v>
       </c>
       <c r="E40" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4441,7 +4453,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4458,7 +4470,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4475,7 +4487,7 @@
         <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4492,7 +4504,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4509,10 +4521,10 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F45" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -4529,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4546,7 +4558,7 @@
         <v>2</v>
       </c>
       <c r="E47" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -4563,7 +4575,7 @@
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -4580,7 +4592,7 @@
         <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4597,7 +4609,7 @@
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -4614,10 +4626,10 @@
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F51" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -4634,7 +4646,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4651,7 +4663,7 @@
         <v>2</v>
       </c>
       <c r="E53" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -4668,7 +4680,7 @@
         <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -4685,7 +4697,7 @@
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -4702,7 +4714,7 @@
         <v>5</v>
       </c>
       <c r="E56" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -4719,7 +4731,7 @@
         <v>6</v>
       </c>
       <c r="E57" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -4736,7 +4748,7 @@
         <v>7</v>
       </c>
       <c r="E58" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4753,10 +4765,10 @@
         <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F59" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4773,15 +4785,15 @@
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>76</v>
       </c>
-      <c r="B61">
-        <v>2729</v>
+      <c r="B61" t="b">
+        <v>0</v>
       </c>
       <c r="C61">
         <v>2025</v>
@@ -4790,15 +4802,15 @@
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>76</v>
       </c>
-      <c r="B62">
-        <v>2729</v>
+      <c r="B62" t="b">
+        <v>0</v>
       </c>
       <c r="C62">
         <v>2025</v>
@@ -4807,15 +4819,15 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>76</v>
       </c>
-      <c r="B63">
-        <v>2729</v>
+      <c r="B63" t="b">
+        <v>0</v>
       </c>
       <c r="C63">
         <v>2025</v>
@@ -4824,15 +4836,15 @@
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>76</v>
       </c>
-      <c r="B64">
-        <v>2729</v>
+      <c r="B64" t="b">
+        <v>0</v>
       </c>
       <c r="C64">
         <v>2025</v>
@@ -4841,15 +4853,15 @@
         <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>76</v>
       </c>
-      <c r="B65">
-        <v>2729</v>
+      <c r="B65" t="b">
+        <v>0</v>
       </c>
       <c r="C65">
         <v>2026</v>
@@ -4858,15 +4870,15 @@
         <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>76</v>
       </c>
-      <c r="B66">
-        <v>2729</v>
+      <c r="B66" t="b">
+        <v>0</v>
       </c>
       <c r="C66">
         <v>2026</v>
@@ -4875,18 +4887,18 @@
         <v>6</v>
       </c>
       <c r="E66" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F66" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>76</v>
       </c>
-      <c r="B67">
-        <v>2729</v>
+      <c r="B67" t="b">
+        <v>0</v>
       </c>
       <c r="C67">
         <v>2026</v>
@@ -4895,41 +4907,41 @@
         <v>7</v>
       </c>
       <c r="E67" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>76</v>
       </c>
-      <c r="B68">
-        <v>2729</v>
+      <c r="B68" t="b">
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D68">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69">
-        <v>2703</v>
+        <v>76</v>
+      </c>
+      <c r="B69" t="b">
+        <v>0</v>
       </c>
       <c r="C69">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4943,10 +4955,10 @@
         <v>2025</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -4960,10 +4972,10 @@
         <v>2025</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4977,10 +4989,10 @@
         <v>2025</v>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -4991,13 +5003,13 @@
         <v>2703</v>
       </c>
       <c r="C73">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D73">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5008,30 +5020,30 @@
         <v>2703</v>
       </c>
       <c r="C74">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E74" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B75">
-        <v>2742</v>
+        <v>2703</v>
       </c>
       <c r="C75">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E75" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -5045,10 +5057,10 @@
         <v>2025</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -5062,10 +5074,10 @@
         <v>2025</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -5079,10 +5091,10 @@
         <v>2025</v>
       </c>
       <c r="D78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -5096,10 +5108,10 @@
         <v>2025</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E79" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -5110,13 +5122,13 @@
         <v>2742</v>
       </c>
       <c r="C80">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D80">
         <v>5</v>
       </c>
       <c r="E80" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -5130,10 +5142,10 @@
         <v>2026</v>
       </c>
       <c r="D81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E81" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -5147,10 +5159,10 @@
         <v>2026</v>
       </c>
       <c r="D82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E82" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -5161,13 +5173,13 @@
         <v>2742</v>
       </c>
       <c r="C83">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D83">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E83" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -5178,30 +5190,30 @@
         <v>2742</v>
       </c>
       <c r="C84">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="D84">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="B85">
-        <v>2704</v>
+        <v>2742</v>
       </c>
       <c r="C85">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -5215,10 +5227,10 @@
         <v>2025</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -5232,10 +5244,10 @@
         <v>2025</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -5249,10 +5261,10 @@
         <v>2025</v>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E88" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -5266,10 +5278,10 @@
         <v>2025</v>
       </c>
       <c r="D89">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -5283,10 +5295,10 @@
         <v>2025</v>
       </c>
       <c r="D90">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -5297,13 +5309,13 @@
         <v>2704</v>
       </c>
       <c r="C91">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D91">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E91" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -5314,30 +5326,30 @@
         <v>2704</v>
       </c>
       <c r="C92">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D92">
         <v>7</v>
       </c>
       <c r="E92" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B93">
-        <v>2739</v>
+        <v>2704</v>
       </c>
       <c r="C93">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E93" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -5351,10 +5363,10 @@
         <v>2025</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -5368,10 +5380,10 @@
         <v>2025</v>
       </c>
       <c r="D95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -5385,10 +5397,10 @@
         <v>2025</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E96" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -5399,13 +5411,13 @@
         <v>2739</v>
       </c>
       <c r="C97">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -5419,10 +5431,10 @@
         <v>2026</v>
       </c>
       <c r="D98">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E98" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -5436,10 +5448,10 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E99" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -5450,30 +5462,30 @@
         <v>2739</v>
       </c>
       <c r="C100">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D100">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B101">
-        <v>2720</v>
+        <v>2739</v>
       </c>
       <c r="C101">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E101" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -5487,10 +5499,10 @@
         <v>2025</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5504,10 +5516,10 @@
         <v>2025</v>
       </c>
       <c r="D103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5521,10 +5533,10 @@
         <v>2025</v>
       </c>
       <c r="D104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E104" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5538,10 +5550,10 @@
         <v>2025</v>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5555,10 +5567,10 @@
         <v>2025</v>
       </c>
       <c r="D106">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E106" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5569,13 +5581,13 @@
         <v>2720</v>
       </c>
       <c r="C107">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D107">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E107" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5586,30 +5598,30 @@
         <v>2720</v>
       </c>
       <c r="C108">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D108">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E108" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B109">
-        <v>2733</v>
+        <v>2720</v>
       </c>
       <c r="C109">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5623,10 +5635,10 @@
         <v>2025</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5640,10 +5652,10 @@
         <v>2025</v>
       </c>
       <c r="D111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5657,10 +5669,10 @@
         <v>2025</v>
       </c>
       <c r="D112">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E112" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -5671,16 +5683,13 @@
         <v>2733</v>
       </c>
       <c r="C113">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D113">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E113" t="s">
-        <v>194</v>
-      </c>
-      <c r="F113" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -5694,10 +5703,13 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>195</v>
+        <v>196</v>
+      </c>
+      <c r="F114" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -5708,33 +5720,33 @@
         <v>2733</v>
       </c>
       <c r="C115">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D115">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E115" t="s">
-        <v>169</v>
-      </c>
-      <c r="F115" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B116">
-        <v>2741</v>
+        <v>2733</v>
       </c>
       <c r="C116">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E116" t="s">
-        <v>167</v>
+        <v>171</v>
+      </c>
+      <c r="F116" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -5748,10 +5760,10 @@
         <v>2025</v>
       </c>
       <c r="D117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -5765,10 +5777,10 @@
         <v>2025</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -5782,10 +5794,10 @@
         <v>2025</v>
       </c>
       <c r="D119">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E119" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -5799,10 +5811,10 @@
         <v>2025</v>
       </c>
       <c r="D120">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -5813,13 +5825,13 @@
         <v>2741</v>
       </c>
       <c r="C121">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D121">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E121" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -5830,47 +5842,47 @@
         <v>2741</v>
       </c>
       <c r="C122">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D122">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E122" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B123">
-        <v>2708</v>
+        <v>2741</v>
       </c>
       <c r="C123">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E123" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B124">
-        <v>2708</v>
+        <v>2741</v>
       </c>
       <c r="C124">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D124">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E124" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -5884,10 +5896,10 @@
         <v>2025</v>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5901,10 +5913,10 @@
         <v>2025</v>
       </c>
       <c r="D126">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E126" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -5915,13 +5927,13 @@
         <v>2708</v>
       </c>
       <c r="C127">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E127" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5932,13 +5944,13 @@
         <v>2708</v>
       </c>
       <c r="C128">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D128">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E128" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -5952,10 +5964,10 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E129" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -5966,13 +5978,13 @@
         <v>2708</v>
       </c>
       <c r="C130">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E130" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -5983,47 +5995,47 @@
         <v>2708</v>
       </c>
       <c r="C131">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="D131">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E131" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B132">
-        <v>2737</v>
+        <v>2708</v>
       </c>
       <c r="C132">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E132" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="B133">
-        <v>2737</v>
+        <v>2708</v>
       </c>
       <c r="C133">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E133" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -6037,10 +6049,10 @@
         <v>2025</v>
       </c>
       <c r="D134">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -6054,10 +6066,10 @@
         <v>2025</v>
       </c>
       <c r="D135">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -6071,10 +6083,10 @@
         <v>2025</v>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -6085,13 +6097,13 @@
         <v>2737</v>
       </c>
       <c r="C137">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D137">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E137" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -6102,13 +6114,13 @@
         <v>2737</v>
       </c>
       <c r="C138">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D138">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E138" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -6119,64 +6131,64 @@
         <v>2737</v>
       </c>
       <c r="C139">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D139">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E139" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>43</v>
-      </c>
-      <c r="B140" t="b">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="B140">
+        <v>2737</v>
       </c>
       <c r="C140">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D140">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E140" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>56</v>
-      </c>
-      <c r="B141" t="b">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="B141">
+        <v>2737</v>
       </c>
       <c r="C141">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D141">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E141" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B142" t="b">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D142">
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -6190,10 +6202,10 @@
         <v>2025</v>
       </c>
       <c r="D143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -6207,10 +6219,10 @@
         <v>2025</v>
       </c>
       <c r="D144">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E144" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -6224,10 +6236,10 @@
         <v>2025</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E145" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -6241,10 +6253,10 @@
         <v>2025</v>
       </c>
       <c r="D146">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E146" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -6255,13 +6267,13 @@
         <v>0</v>
       </c>
       <c r="C147">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D147">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E147" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -6272,47 +6284,47 @@
         <v>0</v>
       </c>
       <c r="C148">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="D148">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E148" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>66</v>
-      </c>
-      <c r="B149">
-        <v>2702</v>
+        <v>56</v>
+      </c>
+      <c r="B149" t="b">
+        <v>0</v>
       </c>
       <c r="C149">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D149">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E149" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>66</v>
-      </c>
-      <c r="B150">
-        <v>2702</v>
+        <v>56</v>
+      </c>
+      <c r="B150" t="b">
+        <v>0</v>
       </c>
       <c r="C150">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E150" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -6326,10 +6338,10 @@
         <v>2025</v>
       </c>
       <c r="D151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -6343,10 +6355,10 @@
         <v>2025</v>
       </c>
       <c r="D152">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -6357,13 +6369,13 @@
         <v>2702</v>
       </c>
       <c r="C153">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D153">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E153" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -6374,13 +6386,13 @@
         <v>2702</v>
       </c>
       <c r="C154">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D154">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -6394,44 +6406,44 @@
         <v>2026</v>
       </c>
       <c r="D155">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E155" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B156">
-        <v>2738</v>
+        <v>2702</v>
       </c>
       <c r="C156">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E156" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B157">
-        <v>2738</v>
+        <v>2702</v>
       </c>
       <c r="C157">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E157" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -6445,10 +6457,10 @@
         <v>2025</v>
       </c>
       <c r="D158">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -6462,10 +6474,10 @@
         <v>2025</v>
       </c>
       <c r="D159">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E159" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -6479,10 +6491,10 @@
         <v>2025</v>
       </c>
       <c r="D160">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E160" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -6493,13 +6505,13 @@
         <v>2738</v>
       </c>
       <c r="C161">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D161">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E161" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -6510,64 +6522,64 @@
         <v>2738</v>
       </c>
       <c r="C162">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E162" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>49</v>
-      </c>
-      <c r="B163" t="b">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="B163">
+        <v>2738</v>
       </c>
       <c r="C163">
         <v>2026</v>
       </c>
       <c r="D163">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E163" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>45</v>
-      </c>
-      <c r="B164" t="b">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="B164">
+        <v>2738</v>
       </c>
       <c r="C164">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D164">
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B165" t="b">
         <v>0</v>
       </c>
       <c r="C165">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D165">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E165" t="s">
-        <v>170</v>
+        <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -6581,10 +6593,10 @@
         <v>2025</v>
       </c>
       <c r="D166">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E166" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -6598,10 +6610,10 @@
         <v>2025</v>
       </c>
       <c r="D167">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -6615,15 +6627,15 @@
         <v>2025</v>
       </c>
       <c r="D168">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E168" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B169" t="b">
         <v>0</v>
@@ -6632,15 +6644,15 @@
         <v>2025</v>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E169" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B170" t="b">
         <v>0</v>
@@ -6649,10 +6661,10 @@
         <v>2025</v>
       </c>
       <c r="D170">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E170" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -6666,10 +6678,10 @@
         <v>2025</v>
       </c>
       <c r="D171">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -6683,10 +6695,10 @@
         <v>2025</v>
       </c>
       <c r="D172">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E172" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -6700,15 +6712,15 @@
         <v>2025</v>
       </c>
       <c r="D173">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E173" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B174" t="b">
         <v>0</v>
@@ -6717,15 +6729,15 @@
         <v>2025</v>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E174" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B175" t="b">
         <v>0</v>
@@ -6734,10 +6746,10 @@
         <v>2025</v>
       </c>
       <c r="D175">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -6751,10 +6763,10 @@
         <v>2025</v>
       </c>
       <c r="D176">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -6768,13 +6780,10 @@
         <v>2025</v>
       </c>
       <c r="D177">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E177" t="s">
         <v>169</v>
-      </c>
-      <c r="F177" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -6788,10 +6797,10 @@
         <v>2025</v>
       </c>
       <c r="D178">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E178" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -6802,13 +6811,16 @@
         <v>0</v>
       </c>
       <c r="C179">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D179">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E179" t="s">
-        <v>208</v>
+        <v>171</v>
+      </c>
+      <c r="F179" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -6819,50 +6831,50 @@
         <v>0</v>
       </c>
       <c r="C180">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D180">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E180" t="s">
-        <v>169</v>
-      </c>
-      <c r="F180" t="s">
-        <v>223</v>
+        <v>180</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>50</v>
-      </c>
-      <c r="B181">
-        <v>2727</v>
+        <v>40</v>
+      </c>
+      <c r="B181" t="b">
+        <v>0</v>
       </c>
       <c r="C181">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D181">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E181" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>50</v>
-      </c>
-      <c r="B182">
-        <v>2727</v>
+        <v>40</v>
+      </c>
+      <c r="B182" t="b">
+        <v>0</v>
       </c>
       <c r="C182">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D182">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="F182" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -6876,10 +6888,10 @@
         <v>2025</v>
       </c>
       <c r="D183">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -6893,10 +6905,10 @@
         <v>2025</v>
       </c>
       <c r="D184">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -6910,10 +6922,10 @@
         <v>2025</v>
       </c>
       <c r="D185">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E185" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -6924,13 +6936,13 @@
         <v>2727</v>
       </c>
       <c r="C186">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D186">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E186" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -6941,47 +6953,47 @@
         <v>2727</v>
       </c>
       <c r="C187">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="D187">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E187" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>54</v>
-      </c>
-      <c r="B188" t="b">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="B188">
+        <v>2727</v>
       </c>
       <c r="C188">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E188" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>54</v>
-      </c>
-      <c r="B189" t="b">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="B189">
+        <v>2727</v>
       </c>
       <c r="C189">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D189">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E189" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -6995,10 +7007,10 @@
         <v>2025</v>
       </c>
       <c r="D190">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -7012,10 +7024,10 @@
         <v>2025</v>
       </c>
       <c r="D191">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -7029,15 +7041,15 @@
         <v>2025</v>
       </c>
       <c r="D192">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E192" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B193" t="b">
         <v>0</v>
@@ -7046,15 +7058,15 @@
         <v>2025</v>
       </c>
       <c r="D193">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B194" t="b">
         <v>0</v>
@@ -7063,10 +7075,10 @@
         <v>2025</v>
       </c>
       <c r="D194">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E194" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -7080,10 +7092,10 @@
         <v>2025</v>
       </c>
       <c r="D195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -7097,10 +7109,10 @@
         <v>2025</v>
       </c>
       <c r="D196">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -7114,10 +7126,10 @@
         <v>2025</v>
       </c>
       <c r="D197">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E197" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -7131,13 +7143,10 @@
         <v>2025</v>
       </c>
       <c r="D198">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E198" t="s">
-        <v>169</v>
-      </c>
-      <c r="F198" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -7151,10 +7160,10 @@
         <v>2025</v>
       </c>
       <c r="D199">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E199" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -7165,21 +7174,21 @@
         <v>0</v>
       </c>
       <c r="C200">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D200">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E200" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F200" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B201" t="b">
         <v>0</v>
@@ -7188,27 +7197,30 @@
         <v>2025</v>
       </c>
       <c r="D201">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E201" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B202" t="b">
         <v>0</v>
       </c>
       <c r="C202">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D202">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>167</v>
+        <v>171</v>
+      </c>
+      <c r="F202" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -7222,15 +7234,15 @@
         <v>2025</v>
       </c>
       <c r="D203">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B204" t="b">
         <v>0</v>
@@ -7239,15 +7251,15 @@
         <v>2025</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B205" t="b">
         <v>0</v>
@@ -7256,10 +7268,10 @@
         <v>2025</v>
       </c>
       <c r="D205">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E205" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -7273,10 +7285,10 @@
         <v>2025</v>
       </c>
       <c r="D206">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E206" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -7290,7 +7302,7 @@
         <v>2025</v>
       </c>
       <c r="D207">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E207" t="s">
         <v>169</v>
@@ -7307,7 +7319,7 @@
         <v>2025</v>
       </c>
       <c r="D208">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E208" t="s">
         <v>169</v>
@@ -7315,7 +7327,7 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B209" t="b">
         <v>0</v>
@@ -7324,15 +7336,15 @@
         <v>2025</v>
       </c>
       <c r="D209">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E209" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B210" t="b">
         <v>0</v>
@@ -7341,10 +7353,10 @@
         <v>2025</v>
       </c>
       <c r="D210">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E210" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -7358,15 +7370,15 @@
         <v>2025</v>
       </c>
       <c r="D211">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B212" t="b">
         <v>0</v>
@@ -7375,15 +7387,15 @@
         <v>2025</v>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B213" t="b">
         <v>0</v>
@@ -7392,10 +7404,10 @@
         <v>2025</v>
       </c>
       <c r="D213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E213" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -7409,10 +7421,10 @@
         <v>2025</v>
       </c>
       <c r="D214">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -7426,13 +7438,10 @@
         <v>2025</v>
       </c>
       <c r="D215">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E215" t="s">
-        <v>169</v>
-      </c>
-      <c r="F215" t="s">
-        <v>225</v>
+        <v>175</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -7446,18 +7455,15 @@
         <v>2025</v>
       </c>
       <c r="D216">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E216" t="s">
         <v>169</v>
       </c>
-      <c r="F216" t="s">
-        <v>225</v>
-      </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B217" t="b">
         <v>0</v>
@@ -7466,15 +7472,18 @@
         <v>2025</v>
       </c>
       <c r="D217">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E217" t="s">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="F217" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B218" t="b">
         <v>0</v>
@@ -7483,10 +7492,13 @@
         <v>2025</v>
       </c>
       <c r="D218">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="F218" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -7500,10 +7512,10 @@
         <v>2025</v>
       </c>
       <c r="D219">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E219" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -7517,10 +7529,10 @@
         <v>2025</v>
       </c>
       <c r="D220">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -7534,44 +7546,44 @@
         <v>2025</v>
       </c>
       <c r="D221">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E221" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>55</v>
-      </c>
-      <c r="B222">
-        <v>2731</v>
+        <v>68</v>
+      </c>
+      <c r="B222" t="b">
+        <v>0</v>
       </c>
       <c r="C222">
         <v>2025</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E222" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>55</v>
-      </c>
-      <c r="B223">
-        <v>2731</v>
+        <v>68</v>
+      </c>
+      <c r="B223" t="b">
+        <v>0</v>
       </c>
       <c r="C223">
         <v>2025</v>
       </c>
       <c r="D223">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E223" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -7585,10 +7597,10 @@
         <v>2025</v>
       </c>
       <c r="D224">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E224" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -7602,10 +7614,10 @@
         <v>2025</v>
       </c>
       <c r="D225">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E225" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -7619,10 +7631,10 @@
         <v>2025</v>
       </c>
       <c r="D226">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E226" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -7636,10 +7648,10 @@
         <v>2025</v>
       </c>
       <c r="D227">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E227" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -7650,13 +7662,13 @@
         <v>2731</v>
       </c>
       <c r="C228">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D228">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E228" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -7667,47 +7679,47 @@
         <v>2731</v>
       </c>
       <c r="C229">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="D229">
         <v>10</v>
       </c>
       <c r="E229" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>71</v>
-      </c>
-      <c r="B230" t="b">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="B230">
+        <v>2731</v>
       </c>
       <c r="C230">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D230">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E230" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>71</v>
-      </c>
-      <c r="B231" t="b">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="B231">
+        <v>2731</v>
       </c>
       <c r="C231">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="D231">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E231" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -7721,10 +7733,10 @@
         <v>2025</v>
       </c>
       <c r="D232">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -7738,10 +7750,10 @@
         <v>2025</v>
       </c>
       <c r="D233">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -7755,15 +7767,15 @@
         <v>2025</v>
       </c>
       <c r="D234">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E234" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B235" t="b">
         <v>0</v>
@@ -7772,15 +7784,15 @@
         <v>2025</v>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E235" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B236" t="b">
         <v>0</v>
@@ -7789,10 +7801,10 @@
         <v>2025</v>
       </c>
       <c r="D236">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E236" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -7806,10 +7818,10 @@
         <v>2025</v>
       </c>
       <c r="D237">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E237" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -7823,15 +7835,15 @@
         <v>2025</v>
       </c>
       <c r="D238">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="B239" t="b">
         <v>0</v>
@@ -7840,15 +7852,15 @@
         <v>2025</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E239" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="B240" t="b">
         <v>0</v>
@@ -7857,7 +7869,7 @@
         <v>2025</v>
       </c>
       <c r="D240">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E240" t="s">
         <v>170</v>
@@ -7874,10 +7886,10 @@
         <v>2025</v>
       </c>
       <c r="D241">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E241" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -7891,10 +7903,10 @@
         <v>2025</v>
       </c>
       <c r="D242">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E242" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -7908,10 +7920,44 @@
         <v>2025</v>
       </c>
       <c r="D243">
+        <v>3</v>
+      </c>
+      <c r="E243" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" t="s">
+        <v>75</v>
+      </c>
+      <c r="B244" t="b">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>2025</v>
+      </c>
+      <c r="D244">
+        <v>4</v>
+      </c>
+      <c r="E244" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" t="s">
+        <v>75</v>
+      </c>
+      <c r="B245" t="b">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>2025</v>
+      </c>
+      <c r="D245">
         <v>5</v>
       </c>
-      <c r="E243" t="s">
-        <v>170</v>
+      <c r="E245" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -7926,34 +7972,34 @@
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H1" t="s">
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="J1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
@@ -7962,55 +8008,55 @@
         <v>13</v>
       </c>
       <c r="M1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="R1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="S1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="T1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="U1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="V1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="W1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="X1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Y1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Z1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AA1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AB1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AC1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:29">
@@ -8018,16 +8064,16 @@
         <v>3810267428</v>
       </c>
       <c r="C2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E2" s="1">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G2" s="1">
         <v>45492</v>
@@ -8039,7 +8085,7 @@
         <v>198</v>
       </c>
       <c r="J2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K2" t="s">
         <v>58</v>
@@ -8057,28 +8103,28 @@
         <v>45492</v>
       </c>
       <c r="U2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="W2" t="s">
         <v>22</v>
       </c>
       <c r="X2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Y2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Z2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AA2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AB2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -8086,16 +8132,16 @@
         <v>3810269967</v>
       </c>
       <c r="C3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E3" s="1">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G3" s="1">
         <v>45631</v>
@@ -8107,7 +8153,7 @@
         <v>198</v>
       </c>
       <c r="J3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K3" t="s">
         <v>75</v>
@@ -8125,25 +8171,25 @@
         <v>45631</v>
       </c>
       <c r="U3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W3" t="s">
         <v>22</v>
       </c>
       <c r="X3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Y3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Z3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AA3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AB3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -8151,16 +8197,16 @@
         <v>3810271134</v>
       </c>
       <c r="C4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E4" s="1">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G4" s="1">
         <v>45716</v>
@@ -8172,7 +8218,7 @@
         <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K4" t="s">
         <v>54</v>
@@ -8190,25 +8236,25 @@
         <v>45716</v>
       </c>
       <c r="U4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W4" t="s">
         <v>22</v>
       </c>
       <c r="X4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Y4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Z4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AA4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AB4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -8216,16 +8262,16 @@
         <v>3810271161</v>
       </c>
       <c r="C5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E5" s="1">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G5" s="1">
         <v>45728</v>
@@ -8237,7 +8283,7 @@
         <v>198</v>
       </c>
       <c r="J5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K5" t="s">
         <v>44</v>
@@ -8255,25 +8301,25 @@
         <v>45728</v>
       </c>
       <c r="U5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W5" t="s">
         <v>22</v>
       </c>
       <c r="X5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Y5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Z5" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AA5" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AB5" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -8284,16 +8330,16 @@
         <v>3810271161</v>
       </c>
       <c r="C6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E6" s="1">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G6" s="1">
         <v>45755</v>
@@ -8305,7 +8351,7 @@
         <v>198</v>
       </c>
       <c r="J6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K6" t="s">
         <v>44</v>
@@ -8323,25 +8369,25 @@
         <v>45755</v>
       </c>
       <c r="U6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W6" t="s">
         <v>22</v>
       </c>
       <c r="X6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Y6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Z6" t="s">
         <v>22</v>
       </c>
       <c r="AA6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AB6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -8352,16 +8398,16 @@
         <v>3810272114</v>
       </c>
       <c r="C7" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E7" s="1">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H7" t="s">
         <v>36</v>
@@ -8370,7 +8416,7 @@
         <v>198</v>
       </c>
       <c r="J7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K7" t="s">
         <v>44</v>
@@ -8385,25 +8431,25 @@
         <v>45775</v>
       </c>
       <c r="U7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W7" t="s">
         <v>22</v>
       </c>
       <c r="X7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Y7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Z7" t="s">
         <v>22</v>
       </c>
       <c r="AA7" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AB7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -8414,16 +8460,16 @@
         <v>3810272114</v>
       </c>
       <c r="C8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D8" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E8" s="1">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H8" t="s">
         <v>36</v>
@@ -8432,7 +8478,7 @@
         <v>198</v>
       </c>
       <c r="J8" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K8" t="s">
         <v>44</v>
@@ -8447,25 +8493,25 @@
         <v>45770</v>
       </c>
       <c r="U8" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W8" t="s">
         <v>22</v>
       </c>
       <c r="X8" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Y8" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Z8" t="s">
         <v>22</v>
       </c>
       <c r="AA8" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AB8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -8476,16 +8522,16 @@
         <v>3810272114</v>
       </c>
       <c r="C9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E9" s="1">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H9" t="s">
         <v>36</v>
@@ -8494,7 +8540,7 @@
         <v>198</v>
       </c>
       <c r="J9" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K9" t="s">
         <v>44</v>
@@ -8509,25 +8555,25 @@
         <v>45777</v>
       </c>
       <c r="U9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W9" t="s">
         <v>22</v>
       </c>
       <c r="X9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Y9" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Z9" t="s">
         <v>22</v>
       </c>
       <c r="AA9" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AB9" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -8538,16 +8584,16 @@
         <v>3810271161</v>
       </c>
       <c r="C10" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D10" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E10" s="1">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G10" s="1">
         <v>45755</v>
@@ -8559,7 +8605,7 @@
         <v>198</v>
       </c>
       <c r="J10" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K10" t="s">
         <v>44</v>
@@ -8577,25 +8623,25 @@
         <v>45754</v>
       </c>
       <c r="U10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W10" t="s">
         <v>22</v>
       </c>
       <c r="X10" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Y10" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Z10" t="s">
         <v>22</v>
       </c>
       <c r="AA10" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AB10" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -8603,16 +8649,16 @@
         <v>3810255268</v>
       </c>
       <c r="C11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E11" s="1">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G11" s="1">
         <v>44973</v>
@@ -8624,10 +8670,10 @@
         <v>198</v>
       </c>
       <c r="J11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -8642,25 +8688,25 @@
         <v>44973</v>
       </c>
       <c r="U11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W11" t="s">
         <v>22</v>
       </c>
       <c r="X11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Y11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Z11" t="s">
         <v>22</v>
       </c>
       <c r="AA11" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AB11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -8668,16 +8714,16 @@
         <v>3810264674</v>
       </c>
       <c r="C12" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D12" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E12" s="1">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G12" s="1">
         <v>45358</v>
@@ -8689,7 +8735,7 @@
         <v>198</v>
       </c>
       <c r="J12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K12" t="s">
         <v>68</v>
@@ -8707,25 +8753,25 @@
         <v>45358</v>
       </c>
       <c r="U12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W12" t="s">
         <v>22</v>
       </c>
       <c r="X12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Y12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Z12" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AA12" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AB12" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -8733,16 +8779,16 @@
         <v>3810268863</v>
       </c>
       <c r="C13" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E13" s="1">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G13" s="1">
         <v>45573</v>
@@ -8754,7 +8800,7 @@
         <v>198</v>
       </c>
       <c r="J13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K13" t="s">
         <v>55</v>
@@ -8772,28 +8818,28 @@
         <v>45573</v>
       </c>
       <c r="U13" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="V13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="W13" t="s">
         <v>22</v>
       </c>
       <c r="X13" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Y13" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Z13" t="s">
         <v>22</v>
       </c>
       <c r="AA13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AB13" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -8801,16 +8847,16 @@
         <v>3810271550</v>
       </c>
       <c r="C14" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D14" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E14" s="1">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G14" s="1">
         <v>45747</v>
@@ -8822,7 +8868,7 @@
         <v>198</v>
       </c>
       <c r="J14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="K14" t="s">
         <v>53</v>
@@ -8840,25 +8886,25 @@
         <v>45747</v>
       </c>
       <c r="U14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="W14" t="s">
         <v>22</v>
       </c>
       <c r="X14" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Y14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Z14" t="s">
         <v>22</v>
       </c>
       <c r="AA14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AB14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -8941,22 +8987,22 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K2">
         <v>797.33</v>
@@ -8980,7 +9026,7 @@
         <v>45015</v>
       </c>
       <c r="R2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="S2" t="s">
         <v>143</v>
@@ -8988,22 +9034,22 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K3">
         <v>1001.83</v>
@@ -9027,7 +9073,7 @@
         <v>45614</v>
       </c>
       <c r="R3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="S3" t="s">
         <v>143</v>
@@ -9035,22 +9081,22 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="J4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K4">
         <v>2813.92</v>
@@ -9074,7 +9120,7 @@
         <v>45539</v>
       </c>
       <c r="R4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="S4" t="s">
         <v>143</v>
@@ -9082,22 +9128,22 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K5">
         <v>1258.5</v>
@@ -9121,7 +9167,7 @@
         <v>45490</v>
       </c>
       <c r="R5" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="S5" t="s">
         <v>143</v>
@@ -9129,22 +9175,22 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="J6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K6">
         <v>708.33</v>
@@ -9168,7 +9214,7 @@
         <v>45526</v>
       </c>
       <c r="R6" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="S6" t="s">
         <v>143</v>
@@ -9176,22 +9222,22 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="J7" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K7">
         <v>133.42</v>
@@ -9215,7 +9261,7 @@
         <v>45352</v>
       </c>
       <c r="R7" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="S7" t="s">
         <v>143</v>
@@ -9223,22 +9269,22 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E8" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I8" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J8" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K8">
         <v>224.08</v>
@@ -9262,7 +9308,7 @@
         <v>44704</v>
       </c>
       <c r="R8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="S8" t="s">
         <v>143</v>
@@ -9270,22 +9316,22 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E9" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J9" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K9">
         <v>783.42</v>
@@ -9309,7 +9355,7 @@
         <v>45628</v>
       </c>
       <c r="R9" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="S9" t="s">
         <v>143</v>
@@ -9317,22 +9363,22 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E10" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I10" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J10" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K10">
         <v>2718.58</v>
@@ -9356,7 +9402,7 @@
         <v>43549</v>
       </c>
       <c r="R10" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="S10" t="s">
         <v>143</v>
@@ -9364,22 +9410,22 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E11" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K11">
         <v>3603.17</v>
@@ -9403,7 +9449,7 @@
         <v>44735</v>
       </c>
       <c r="R11" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="S11" t="s">
         <v>143</v>
@@ -9411,22 +9457,22 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E12" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I12" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J12" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K12">
         <v>2298.67</v>
@@ -9450,7 +9496,7 @@
         <v>45776</v>
       </c>
       <c r="R12" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="S12" t="s">
         <v>143</v>
@@ -9458,22 +9504,22 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E13" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I13" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="J13" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K13">
         <v>2132.08</v>
@@ -9497,7 +9543,7 @@
         <v>45600</v>
       </c>
       <c r="R13" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="S13" t="s">
         <v>143</v>
@@ -9511,16 +9557,16 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E14" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I14" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="J14" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K14">
         <v>1013.92</v>
@@ -9544,7 +9590,7 @@
         <v>44630</v>
       </c>
       <c r="R14" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="S14" t="s">
         <v>143</v>
@@ -9552,22 +9598,22 @@
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E15" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I15" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="J15" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K15">
         <v>209.92</v>
@@ -9593,22 +9639,22 @@
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E16" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I16" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="J16" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K16">
         <v>49.33</v>
@@ -9634,22 +9680,22 @@
     </row>
     <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E17" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I17" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J17" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K17">
         <v>923.83</v>
@@ -9673,7 +9719,7 @@
         <v>45026</v>
       </c>
       <c r="R17" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="S17" t="s">
         <v>143</v>
@@ -9681,22 +9727,22 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E18" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I18" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="J18" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K18">
         <v>112.33</v>
@@ -9720,7 +9766,7 @@
         <v>45371</v>
       </c>
       <c r="R18" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="S18" t="s">
         <v>143</v>
@@ -9728,22 +9774,22 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E19" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I19" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J19" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K19">
         <v>598</v>
@@ -9767,7 +9813,7 @@
         <v>45294</v>
       </c>
       <c r="R19" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="S19" t="s">
         <v>143</v>
@@ -9781,16 +9827,16 @@
         <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E20" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I20" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="J20" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K20">
         <v>779.67</v>
@@ -9814,7 +9860,7 @@
         <v>44369</v>
       </c>
       <c r="R20" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="S20" t="s">
         <v>143</v>
@@ -9822,22 +9868,22 @@
     </row>
     <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E21" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I21" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J21" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K21">
         <v>1685.25</v>
@@ -9861,7 +9907,7 @@
         <v>43894</v>
       </c>
       <c r="R21" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="S21" t="s">
         <v>143</v>
@@ -9869,22 +9915,22 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E22" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I22" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J22" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K22">
         <v>1926.58</v>
@@ -9908,7 +9954,7 @@
         <v>45509</v>
       </c>
       <c r="R22" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="S22" t="s">
         <v>143</v>
@@ -9922,16 +9968,16 @@
         <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E23" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I23" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J23" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L23">
         <v>2562.83</v>
@@ -9940,7 +9986,7 @@
         <v>4000</v>
       </c>
       <c r="O23" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="P23" s="1">
         <v>40044</v>
@@ -9949,13 +9995,13 @@
         <v>40126</v>
       </c>
       <c r="R23" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="S23" t="s">
         <v>142</v>
       </c>
       <c r="T23" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="U23" s="1">
         <v>45775</v>
@@ -9969,16 +10015,16 @@
         <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E24" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I24" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J24" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K24">
         <v>1903.17</v>
@@ -10002,13 +10048,13 @@
         <v>45772</v>
       </c>
       <c r="R24" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="S24" t="s">
         <v>142</v>
       </c>
       <c r="T24" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="U24" s="1">
         <v>45810</v>
@@ -10022,16 +10068,16 @@
         <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E25" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I25" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J25" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K25">
         <v>835.42</v>
@@ -10055,13 +10101,13 @@
         <v>45510</v>
       </c>
       <c r="R25" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="S25" t="s">
         <v>142</v>
       </c>
       <c r="T25" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="U25" s="1">
         <v>45937</v>
@@ -10075,16 +10121,16 @@
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E26" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I26" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J26" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K26">
         <v>1657.42</v>
@@ -10108,13 +10154,13 @@
         <v>44959</v>
       </c>
       <c r="R26" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="S26" t="s">
         <v>142</v>
       </c>
       <c r="T26" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="U26" s="1">
         <v>45580</v>
@@ -10128,16 +10174,16 @@
         <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E27" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I27" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J27" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K27">
         <v>39.92</v>
@@ -10161,13 +10207,13 @@
         <v>45446</v>
       </c>
       <c r="R27" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="S27" t="s">
         <v>142</v>
       </c>
       <c r="T27" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="U27" s="1">
         <v>45588</v>
@@ -10181,16 +10227,16 @@
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E28" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I28" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J28" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K28">
         <v>4204.25</v>
@@ -10214,13 +10260,13 @@
         <v>45824</v>
       </c>
       <c r="R28" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="S28" t="s">
         <v>142</v>
       </c>
       <c r="T28" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="U28" s="1">
         <v>45831</v>
@@ -10234,16 +10280,16 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E29" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I29" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J29" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K29">
         <v>1891.33</v>
@@ -10267,13 +10313,13 @@
         <v>45567</v>
       </c>
       <c r="R29" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="S29" t="s">
         <v>142</v>
       </c>
       <c r="T29" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="U29" s="1">
         <v>45734</v>
@@ -10287,16 +10333,16 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E30" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I30" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J30" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N30">
         <v>4000</v>
@@ -10305,7 +10351,7 @@
         <v>142</v>
       </c>
       <c r="T30" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="U30" s="1">
         <v>46001</v>
@@ -10319,16 +10365,16 @@
         <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E31" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I31" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J31" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N31">
         <v>4000</v>
@@ -10337,7 +10383,7 @@
         <v>142</v>
       </c>
       <c r="T31" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="U31" s="1">
         <v>46001</v>
@@ -10351,16 +10397,16 @@
         <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E32" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I32" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J32" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N32">
         <v>4000</v>
@@ -10369,7 +10415,7 @@
         <v>142</v>
       </c>
       <c r="T32" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="U32" s="1">
         <v>46001</v>
@@ -10377,22 +10423,22 @@
     </row>
     <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E33" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I33" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J33" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K33">
         <v>3238.83</v>
@@ -10416,13 +10462,13 @@
         <v>46031</v>
       </c>
       <c r="R33" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="S33" t="s">
         <v>145</v>
       </c>
       <c r="T33" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="U33" s="1">
         <v>46037</v>
@@ -10436,16 +10482,16 @@
         <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E34" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I34" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J34" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K34">
         <v>833.58</v>
@@ -10460,7 +10506,7 @@
         <v>4000</v>
       </c>
       <c r="O34" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="P34" s="1">
         <v>40071</v>
@@ -10477,22 +10523,22 @@
     </row>
     <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E35" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I35" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J35" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L35">
         <v>6168.75</v>
@@ -10510,7 +10556,7 @@
         <v>45259</v>
       </c>
       <c r="R35" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="S35" t="s">
         <v>146</v>
@@ -10521,22 +10567,22 @@
     </row>
     <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E36" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I36" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J36" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K36">
         <v>2184.17</v>
@@ -10560,7 +10606,7 @@
         <v>46000</v>
       </c>
       <c r="R36" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="S36" t="s">
         <v>146</v>
@@ -10571,22 +10617,22 @@
     </row>
     <row r="37" spans="1:21">
       <c r="A37" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E37" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I37" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J37" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N37">
         <v>4000</v>
@@ -10597,22 +10643,22 @@
     </row>
     <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s">
         <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E38" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I38" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J38" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K38">
         <v>553.17</v>
@@ -10636,7 +10682,7 @@
         <v>39068</v>
       </c>
       <c r="R38" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="S38" t="s">
         <v>146</v>
@@ -10653,16 +10699,16 @@
         <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E39" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I39" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J39" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K39">
         <v>85.58</v>
@@ -10686,13 +10732,13 @@
         <v>40568</v>
       </c>
       <c r="R39" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="S39" t="s">
         <v>146</v>
       </c>
       <c r="T39" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="U39" s="1">
         <v>40568</v>
@@ -10706,16 +10752,16 @@
         <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E40" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I40" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J40" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K40">
         <v>796.67</v>
@@ -10733,13 +10779,13 @@
         <v>42270</v>
       </c>
       <c r="R40" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="S40" t="s">
         <v>146</v>
       </c>
       <c r="T40" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="U40" s="1">
         <v>42270</v>
@@ -10753,16 +10799,16 @@
         <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I41" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J41" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K41">
         <v>981.58</v>
@@ -10786,13 +10832,13 @@
         <v>43494</v>
       </c>
       <c r="R41" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="S41" t="s">
         <v>144</v>
       </c>
       <c r="T41" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="U41" s="1">
         <v>44148</v>
@@ -10806,16 +10852,16 @@
         <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E42" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I42" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J42" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K42">
         <v>3152</v>
@@ -10839,13 +10885,13 @@
         <v>45776</v>
       </c>
       <c r="R42" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="S42" t="s">
         <v>144</v>
       </c>
       <c r="T42" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="U42" s="1">
         <v>43185</v>
@@ -10859,16 +10905,16 @@
         <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E43" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I43" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="J43" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K43">
         <v>2787.25</v>
@@ -10892,13 +10938,13 @@
         <v>45916</v>
       </c>
       <c r="R43" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="S43" t="s">
         <v>144</v>
       </c>
       <c r="T43" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="U43" s="1">
         <v>42850</v>
@@ -10912,16 +10958,16 @@
         <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E44" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I44" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J44" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K44">
         <v>2413.42</v>
@@ -10945,13 +10991,13 @@
         <v>45539</v>
       </c>
       <c r="R44" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="S44" t="s">
         <v>144</v>
       </c>
       <c r="T44" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="U44" s="1">
         <v>44404</v>
@@ -10965,16 +11011,16 @@
         <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E45" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I45" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J45" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K45">
         <v>2266.5</v>
@@ -10998,13 +11044,13 @@
         <v>45239</v>
       </c>
       <c r="R45" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="S45" t="s">
         <v>144</v>
       </c>
       <c r="T45" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="U45" s="1">
         <v>42698</v>
@@ -11018,16 +11064,16 @@
         <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I46" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J46" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K46">
         <v>545.75</v>
@@ -11051,13 +11097,13 @@
         <v>45586</v>
       </c>
       <c r="R46" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="S46" t="s">
         <v>144</v>
       </c>
       <c r="T46" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="U46" s="1">
         <v>43941</v>
@@ -11075,25 +11121,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D1" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E1" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -11295,23 +11341,11 @@
       <c r="A11" t="s">
         <v>76</v>
       </c>
-      <c r="B11">
-        <v>2729</v>
-      </c>
       <c r="C11">
         <v>2832.83</v>
       </c>
       <c r="D11">
         <v>1167.166667</v>
-      </c>
-      <c r="E11">
-        <v>39.70818182</v>
-      </c>
-      <c r="F11">
-        <v>218.395</v>
-      </c>
-      <c r="G11">
-        <v>29.39360639</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -11776,7 +11810,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1312,8 +1312,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1329,7 +1337,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1337,12 +1345,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1642,70 +1668,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1746,10 +1772,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>41754</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1761,7 +1787,7 @@
       <c r="T2" t="s">
         <v>148</v>
       </c>
-      <c r="U2" s="1">
+      <c r="U2" s="2">
         <v>46170</v>
       </c>
     </row>
@@ -1802,10 +1828,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>44709</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1852,10 +1878,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>44348</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -1902,10 +1928,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>46059</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -1917,7 +1943,7 @@
       <c r="T5" t="s">
         <v>149</v>
       </c>
-      <c r="U5" s="1">
+      <c r="U5" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -1955,10 +1981,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>46149</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -2005,10 +2031,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>43731</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -2020,7 +2046,7 @@
       <c r="T7" t="s">
         <v>150</v>
       </c>
-      <c r="U7" s="1">
+      <c r="U7" s="2">
         <v>43507</v>
       </c>
     </row>
@@ -2061,10 +2087,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45511</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2111,10 +2137,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45716</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2126,7 +2152,7 @@
       <c r="T9" t="s">
         <v>151</v>
       </c>
-      <c r="U9" s="1">
+      <c r="U9" s="2">
         <v>44665</v>
       </c>
     </row>
@@ -2167,10 +2193,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>45064</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2211,10 +2237,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>46135</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2226,7 +2252,7 @@
       <c r="T11" t="s">
         <v>152</v>
       </c>
-      <c r="U11" s="1">
+      <c r="U11" s="2">
         <v>46203</v>
       </c>
     </row>
@@ -2264,7 +2290,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2305,10 +2331,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>46199</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2352,10 +2378,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45667</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2367,7 +2393,7 @@
       <c r="T14" t="s">
         <v>153</v>
       </c>
-      <c r="U14" s="1">
+      <c r="U14" s="2">
         <v>46072</v>
       </c>
     </row>
@@ -2408,10 +2434,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>46064</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="Q15" s="2">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2458,10 +2484,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>44285</v>
       </c>
-      <c r="Q16" s="1">
+      <c r="Q16" s="2">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2473,7 +2499,7 @@
       <c r="T16" t="s">
         <v>154</v>
       </c>
-      <c r="U16" s="1">
+      <c r="U16" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2514,10 +2540,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45922</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2564,10 +2590,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>45930</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2579,7 +2605,7 @@
       <c r="T18" t="s">
         <v>155</v>
       </c>
-      <c r="U18" s="1">
+      <c r="U18" s="2">
         <v>46198</v>
       </c>
     </row>
@@ -2620,10 +2646,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45524</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2635,7 +2661,7 @@
       <c r="T19" t="s">
         <v>122</v>
       </c>
-      <c r="U19" s="1">
+      <c r="U19" s="2">
         <v>46153</v>
       </c>
       <c r="V19">
@@ -2679,10 +2705,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>45026</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2694,7 +2720,7 @@
       <c r="T20" t="s">
         <v>156</v>
       </c>
-      <c r="U20" s="1">
+      <c r="U20" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2735,10 +2761,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>45159</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2750,7 +2776,7 @@
       <c r="T21" t="s">
         <v>124</v>
       </c>
-      <c r="U21" s="1">
+      <c r="U21" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -2791,10 +2817,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2806,7 +2832,7 @@
       <c r="T22" t="s">
         <v>157</v>
       </c>
-      <c r="U22" s="1">
+      <c r="U22" s="2">
         <v>45995</v>
       </c>
     </row>
@@ -2844,10 +2870,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>45713</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -2856,7 +2882,7 @@
       <c r="S23" t="s">
         <v>146</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -2897,10 +2923,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>46062</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>45925</v>
       </c>
       <c r="R24" t="s">
@@ -2947,10 +2973,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45079</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -2997,10 +3023,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>41346</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -3012,7 +3038,7 @@
       <c r="T26" t="s">
         <v>158</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>46150</v>
       </c>
     </row>
@@ -3053,10 +3079,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45579</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3103,10 +3129,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>46171</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3153,10 +3179,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44320</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3203,10 +3229,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="2">
         <v>42661</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="Q30" s="2">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3218,7 +3244,7 @@
       <c r="T30" t="s">
         <v>159</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="2">
         <v>45358</v>
       </c>
     </row>
@@ -3259,10 +3285,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="2">
         <v>46064</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="Q31" s="2">
         <v>46064</v>
       </c>
       <c r="R31" t="s">
@@ -3309,10 +3335,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="2">
         <v>43797</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="Q32" s="2">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3359,10 +3385,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>42810</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3374,7 +3400,7 @@
       <c r="T33" t="s">
         <v>160</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="2">
         <v>43802</v>
       </c>
     </row>
@@ -3415,10 +3441,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>45070</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>44910</v>
       </c>
       <c r="R34" t="s">
@@ -3465,10 +3491,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>43250</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3515,10 +3541,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45841</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3565,10 +3591,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="2">
         <v>45105</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="Q37" s="2">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3580,7 +3606,7 @@
       <c r="T37" t="s">
         <v>161</v>
       </c>
-      <c r="U37" s="1">
+      <c r="U37" s="2">
         <v>46184</v>
       </c>
     </row>
@@ -3621,10 +3647,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>45636</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>45579</v>
       </c>
       <c r="S38" t="s">
@@ -3671,10 +3697,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>45831</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3718,10 +3744,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>44287</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3742,22 +3768,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -7971,91 +7997,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>252</v>
       </c>
     </row>
@@ -8069,13 +8095,13 @@
       <c r="D2" t="s">
         <v>255</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
         <v>258</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>45492</v>
       </c>
       <c r="H2" t="s">
@@ -8093,13 +8119,13 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45491</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="2">
         <v>45528</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="2">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
@@ -8137,13 +8163,13 @@
       <c r="D3" t="s">
         <v>256</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
         <v>258</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="2">
         <v>45631</v>
       </c>
       <c r="H3" t="s">
@@ -8161,13 +8187,13 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>45628</v>
       </c>
-      <c r="R3" s="1">
+      <c r="R3" s="2">
         <v>45632</v>
       </c>
-      <c r="S3" s="1">
+      <c r="S3" s="2">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
@@ -8202,13 +8228,13 @@
       <c r="D4" t="s">
         <v>256</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
         <v>258</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="2">
         <v>45716</v>
       </c>
       <c r="H4" t="s">
@@ -8226,13 +8252,13 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45716</v>
       </c>
-      <c r="R4" s="1">
+      <c r="R4" s="2">
         <v>45722</v>
       </c>
-      <c r="S4" s="1">
+      <c r="S4" s="2">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
@@ -8267,13 +8293,13 @@
       <c r="D5" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <v>45728</v>
       </c>
       <c r="H5" t="s">
@@ -8291,13 +8317,13 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45722</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R5" s="2">
         <v>45782</v>
       </c>
-      <c r="S5" s="1">
+      <c r="S5" s="2">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
@@ -8335,13 +8361,13 @@
       <c r="D6" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
         <v>258</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <v>45755</v>
       </c>
       <c r="H6" t="s">
@@ -8359,13 +8385,13 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45728</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R6" s="2">
         <v>45734</v>
       </c>
-      <c r="S6" s="1">
+      <c r="S6" s="2">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
@@ -8403,7 +8429,7 @@
       <c r="D7" t="s">
         <v>257</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
@@ -8424,10 +8450,10 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45772</v>
       </c>
-      <c r="R7" s="1">
+      <c r="R7" s="2">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
@@ -8465,7 +8491,7 @@
       <c r="D8" t="s">
         <v>257</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
@@ -8486,10 +8512,10 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>45762</v>
       </c>
-      <c r="R8" s="1">
+      <c r="R8" s="2">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
@@ -8527,7 +8553,7 @@
       <c r="D9" t="s">
         <v>257</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
@@ -8548,10 +8574,10 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45763</v>
       </c>
-      <c r="R9" s="1">
+      <c r="R9" s="2">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
@@ -8589,13 +8615,13 @@
       <c r="D10" t="s">
         <v>256</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
         <v>258</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="2">
         <v>45755</v>
       </c>
       <c r="H10" t="s">
@@ -8613,13 +8639,13 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45754</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R10" s="2">
         <v>45849</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S10" s="2">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
@@ -8654,13 +8680,13 @@
       <c r="D11" t="s">
         <v>256</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
         <v>258</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="2">
         <v>44973</v>
       </c>
       <c r="H11" t="s">
@@ -8678,13 +8704,13 @@
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44973</v>
       </c>
-      <c r="R11" s="1">
+      <c r="R11" s="2">
         <v>45687</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S11" s="2">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
@@ -8719,13 +8745,13 @@
       <c r="D12" t="s">
         <v>256</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
         <v>258</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="2">
         <v>45358</v>
       </c>
       <c r="H12" t="s">
@@ -8743,13 +8769,13 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45358</v>
       </c>
-      <c r="R12" s="1">
+      <c r="R12" s="2">
         <v>45517</v>
       </c>
-      <c r="S12" s="1">
+      <c r="S12" s="2">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
@@ -8784,13 +8810,13 @@
       <c r="D13" t="s">
         <v>256</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
         <v>258</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="2">
         <v>45573</v>
       </c>
       <c r="H13" t="s">
@@ -8808,13 +8834,13 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45572</v>
       </c>
-      <c r="R13" s="1">
+      <c r="R13" s="2">
         <v>45572</v>
       </c>
-      <c r="S13" s="1">
+      <c r="S13" s="2">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
@@ -8852,13 +8878,13 @@
       <c r="D14" t="s">
         <v>256</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
         <v>258</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="2">
         <v>45747</v>
       </c>
       <c r="H14" t="s">
@@ -8876,13 +8902,13 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>45736</v>
       </c>
-      <c r="R14" s="1">
+      <c r="R14" s="2">
         <v>46101</v>
       </c>
-      <c r="S14" s="1">
+      <c r="S14" s="2">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
@@ -8918,70 +8944,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9019,10 +9045,10 @@
       <c r="O2" t="s">
         <v>102</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>45490</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -9066,10 +9092,10 @@
       <c r="O3" t="s">
         <v>81</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>45618</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -9113,10 +9139,10 @@
       <c r="O4" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>45539</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -9160,10 +9186,10 @@
       <c r="O5" t="s">
         <v>98</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>45567</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -9207,10 +9233,10 @@
       <c r="O6" t="s">
         <v>95</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>45568</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -9254,10 +9280,10 @@
       <c r="O7" t="s">
         <v>83</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>45831</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -9301,10 +9327,10 @@
       <c r="O8" t="s">
         <v>103</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45601</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -9348,10 +9374,10 @@
       <c r="O9" t="s">
         <v>92</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45631</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -9395,10 +9421,10 @@
       <c r="O10" t="s">
         <v>89</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>43902</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -9442,10 +9468,10 @@
       <c r="O11" t="s">
         <v>99</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>44736</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -9489,10 +9515,10 @@
       <c r="O12" t="s">
         <v>82</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>45776</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -9536,10 +9562,10 @@
       <c r="O13" t="s">
         <v>80</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>45772</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -9583,10 +9609,10 @@
       <c r="O14" t="s">
         <v>100</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45000</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -9630,7 +9656,7 @@
       <c r="O15" t="s">
         <v>94</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -9671,7 +9697,7 @@
       <c r="O16" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -9712,10 +9738,10 @@
       <c r="O17" t="s">
         <v>93</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45371</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -9759,10 +9785,10 @@
       <c r="O18" t="s">
         <v>91</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>46001</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -9806,10 +9832,10 @@
       <c r="O19" t="s">
         <v>104</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45436</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -9853,10 +9879,10 @@
       <c r="O20" t="s">
         <v>96</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>44372</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -9900,10 +9926,10 @@
       <c r="O21" t="s">
         <v>105</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>44362</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -9947,10 +9973,10 @@
       <c r="O22" t="s">
         <v>86</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -9988,10 +10014,10 @@
       <c r="O23" t="s">
         <v>359</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>40044</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -10003,7 +10029,7 @@
       <c r="T23" t="s">
         <v>399</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>45775</v>
       </c>
     </row>
@@ -10041,10 +10067,10 @@
       <c r="O24" t="s">
         <v>80</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>43549</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -10056,7 +10082,7 @@
       <c r="T24" t="s">
         <v>400</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -10094,10 +10120,10 @@
       <c r="O25" t="s">
         <v>86</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45447</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -10109,7 +10135,7 @@
       <c r="T25" t="s">
         <v>401</v>
       </c>
-      <c r="U25" s="1">
+      <c r="U25" s="2">
         <v>45937</v>
       </c>
     </row>
@@ -10147,10 +10173,10 @@
       <c r="O26" t="s">
         <v>100</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>44485</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -10162,7 +10188,7 @@
       <c r="T26" t="s">
         <v>402</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>45580</v>
       </c>
     </row>
@@ -10200,10 +10226,10 @@
       <c r="O27" t="s">
         <v>86</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45420</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -10215,7 +10241,7 @@
       <c r="T27" t="s">
         <v>403</v>
       </c>
-      <c r="U27" s="1">
+      <c r="U27" s="2">
         <v>45588</v>
       </c>
     </row>
@@ -10253,10 +10279,10 @@
       <c r="O28" t="s">
         <v>101</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>44369</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -10268,7 +10294,7 @@
       <c r="T28" t="s">
         <v>404</v>
       </c>
-      <c r="U28" s="1">
+      <c r="U28" s="2">
         <v>45831</v>
       </c>
     </row>
@@ -10306,10 +10332,10 @@
       <c r="O29" t="s">
         <v>98</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44652</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -10321,7 +10347,7 @@
       <c r="T29" t="s">
         <v>405</v>
       </c>
-      <c r="U29" s="1">
+      <c r="U29" s="2">
         <v>45734</v>
       </c>
     </row>
@@ -10353,7 +10379,7 @@
       <c r="T30" t="s">
         <v>406</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10385,7 +10411,7 @@
       <c r="T31" t="s">
         <v>407</v>
       </c>
-      <c r="U31" s="1">
+      <c r="U31" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10417,7 +10443,7 @@
       <c r="T32" t="s">
         <v>408</v>
       </c>
-      <c r="U32" s="1">
+      <c r="U32" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10455,10 +10481,10 @@
       <c r="O33" t="s">
         <v>90</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>43762</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -10470,7 +10496,7 @@
       <c r="T33" t="s">
         <v>387</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="2">
         <v>46037</v>
       </c>
     </row>
@@ -10508,16 +10534,16 @@
       <c r="O34" t="s">
         <v>360</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>40071</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>146</v>
       </c>
-      <c r="U34" s="1">
+      <c r="U34" s="2">
         <v>41023</v>
       </c>
     </row>
@@ -10549,10 +10575,10 @@
       <c r="O35" t="s">
         <v>87</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>44784</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -10561,7 +10587,7 @@
       <c r="S35" t="s">
         <v>146</v>
       </c>
-      <c r="U35" s="1">
+      <c r="U35" s="2">
         <v>45259</v>
       </c>
     </row>
@@ -10599,10 +10625,10 @@
       <c r="O36" t="s">
         <v>91</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45103</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -10611,7 +10637,7 @@
       <c r="S36" t="s">
         <v>146</v>
       </c>
-      <c r="U36" s="1">
+      <c r="U36" s="2">
         <v>46000</v>
       </c>
     </row>
@@ -10675,10 +10701,10 @@
       <c r="O38" t="s">
         <v>96</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>38511</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -10687,7 +10713,7 @@
       <c r="S38" t="s">
         <v>146</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="2">
         <v>39068</v>
       </c>
     </row>
@@ -10725,10 +10751,10 @@
       <c r="O39" t="s">
         <v>103</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>39006</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -10740,7 +10766,7 @@
       <c r="T39" t="s">
         <v>409</v>
       </c>
-      <c r="U39" s="1">
+      <c r="U39" s="2">
         <v>40568</v>
       </c>
     </row>
@@ -10772,10 +10798,10 @@
       <c r="O40" t="s">
         <v>100</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>40836</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -10787,7 +10813,7 @@
       <c r="T40" t="s">
         <v>410</v>
       </c>
-      <c r="U40" s="1">
+      <c r="U40" s="2">
         <v>42270</v>
       </c>
     </row>
@@ -10825,10 +10851,10 @@
       <c r="O41" t="s">
         <v>95</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P41" s="2">
         <v>42940</v>
       </c>
-      <c r="Q41" s="1">
+      <c r="Q41" s="2">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -10840,7 +10866,7 @@
       <c r="T41" t="s">
         <v>411</v>
       </c>
-      <c r="U41" s="1">
+      <c r="U41" s="2">
         <v>44148</v>
       </c>
     </row>
@@ -10878,10 +10904,10 @@
       <c r="O42" t="s">
         <v>82</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P42" s="2">
         <v>43696</v>
       </c>
-      <c r="Q42" s="1">
+      <c r="Q42" s="2">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -10893,7 +10919,7 @@
       <c r="T42" t="s">
         <v>412</v>
       </c>
-      <c r="U42" s="1">
+      <c r="U42" s="2">
         <v>43185</v>
       </c>
     </row>
@@ -10931,10 +10957,10 @@
       <c r="O43" t="s">
         <v>84</v>
       </c>
-      <c r="P43" s="1">
+      <c r="P43" s="2">
         <v>43544</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="Q43" s="2">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -10946,7 +10972,7 @@
       <c r="T43" t="s">
         <v>413</v>
       </c>
-      <c r="U43" s="1">
+      <c r="U43" s="2">
         <v>42850</v>
       </c>
     </row>
@@ -10984,10 +11010,10 @@
       <c r="O44" t="s">
         <v>97</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P44" s="2">
         <v>45076</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="Q44" s="2">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -10999,7 +11025,7 @@
       <c r="T44" t="s">
         <v>414</v>
       </c>
-      <c r="U44" s="1">
+      <c r="U44" s="2">
         <v>44404</v>
       </c>
     </row>
@@ -11037,10 +11063,10 @@
       <c r="O45" t="s">
         <v>81</v>
       </c>
-      <c r="P45" s="1">
+      <c r="P45" s="2">
         <v>42963</v>
       </c>
-      <c r="Q45" s="1">
+      <c r="Q45" s="2">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -11052,7 +11078,7 @@
       <c r="T45" t="s">
         <v>415</v>
       </c>
-      <c r="U45" s="1">
+      <c r="U45" s="2">
         <v>42698</v>
       </c>
     </row>
@@ -11090,10 +11116,10 @@
       <c r="O46" t="s">
         <v>88</v>
       </c>
-      <c r="P46" s="1">
+      <c r="P46" s="2">
         <v>45054</v>
       </c>
-      <c r="Q46" s="1">
+      <c r="Q46" s="2">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -11105,7 +11131,7 @@
       <c r="T46" t="s">
         <v>416</v>
       </c>
-      <c r="U46" s="1">
+      <c r="U46" s="2">
         <v>43941</v>
       </c>
     </row>
@@ -11120,25 +11146,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>421</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1312,16 +1312,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1337,7 +1329,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1345,30 +1337,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1668,70 +1642,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1772,10 +1746,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>41754</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1787,7 +1761,7 @@
       <c r="T2" t="s">
         <v>148</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="1">
         <v>46170</v>
       </c>
     </row>
@@ -1828,10 +1802,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>44709</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1878,10 +1852,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>44348</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -1928,10 +1902,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>46059</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -1943,7 +1917,7 @@
       <c r="T5" t="s">
         <v>149</v>
       </c>
-      <c r="U5" s="2">
+      <c r="U5" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -1981,10 +1955,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>46149</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -2031,10 +2005,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>43731</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -2046,7 +2020,7 @@
       <c r="T7" t="s">
         <v>150</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U7" s="1">
         <v>43507</v>
       </c>
     </row>
@@ -2087,10 +2061,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45511</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2137,10 +2111,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45716</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2152,7 +2126,7 @@
       <c r="T9" t="s">
         <v>151</v>
       </c>
-      <c r="U9" s="2">
+      <c r="U9" s="1">
         <v>44665</v>
       </c>
     </row>
@@ -2193,10 +2167,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>45064</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2237,10 +2211,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>46135</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2252,7 +2226,7 @@
       <c r="T11" t="s">
         <v>152</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="1">
         <v>46203</v>
       </c>
     </row>
@@ -2290,7 +2264,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2331,10 +2305,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>46199</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2378,10 +2352,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45667</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2393,7 +2367,7 @@
       <c r="T14" t="s">
         <v>153</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" s="1">
         <v>46072</v>
       </c>
     </row>
@@ -2434,10 +2408,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>46064</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="1">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2484,10 +2458,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>44285</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="1">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2499,7 +2473,7 @@
       <c r="T16" t="s">
         <v>154</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2540,10 +2514,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45922</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2590,10 +2564,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>45930</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2605,7 +2579,7 @@
       <c r="T18" t="s">
         <v>155</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" s="1">
         <v>46198</v>
       </c>
     </row>
@@ -2646,10 +2620,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45524</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2661,7 +2635,7 @@
       <c r="T19" t="s">
         <v>122</v>
       </c>
-      <c r="U19" s="2">
+      <c r="U19" s="1">
         <v>46153</v>
       </c>
       <c r="V19">
@@ -2705,10 +2679,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>45026</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2720,7 +2694,7 @@
       <c r="T20" t="s">
         <v>156</v>
       </c>
-      <c r="U20" s="2">
+      <c r="U20" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2761,10 +2735,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>45159</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2776,7 +2750,7 @@
       <c r="T21" t="s">
         <v>124</v>
       </c>
-      <c r="U21" s="2">
+      <c r="U21" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2817,10 +2791,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2832,7 +2806,7 @@
       <c r="T22" t="s">
         <v>157</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" s="1">
         <v>45995</v>
       </c>
     </row>
@@ -2870,10 +2844,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>45713</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -2882,7 +2856,7 @@
       <c r="S23" t="s">
         <v>146</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -2923,10 +2897,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>46062</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>45925</v>
       </c>
       <c r="R24" t="s">
@@ -2973,10 +2947,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45079</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -3023,10 +2997,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>41346</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -3038,7 +3012,7 @@
       <c r="T26" t="s">
         <v>158</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>46150</v>
       </c>
     </row>
@@ -3079,10 +3053,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45579</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3129,10 +3103,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>46171</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3179,10 +3153,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44320</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3229,10 +3203,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="1">
         <v>42661</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="1">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3244,7 +3218,7 @@
       <c r="T30" t="s">
         <v>159</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>45358</v>
       </c>
     </row>
@@ -3285,10 +3259,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="1">
         <v>46064</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="1">
         <v>46064</v>
       </c>
       <c r="R31" t="s">
@@ -3335,10 +3309,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="1">
         <v>43797</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="1">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3385,10 +3359,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>42810</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3400,7 +3374,7 @@
       <c r="T33" t="s">
         <v>160</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>43802</v>
       </c>
     </row>
@@ -3441,10 +3415,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>45070</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>44910</v>
       </c>
       <c r="R34" t="s">
@@ -3491,10 +3465,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>43250</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3541,10 +3515,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45841</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3591,10 +3565,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="2">
+      <c r="P37" s="1">
         <v>45105</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="1">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3606,7 +3580,7 @@
       <c r="T37" t="s">
         <v>161</v>
       </c>
-      <c r="U37" s="2">
+      <c r="U37" s="1">
         <v>46184</v>
       </c>
     </row>
@@ -3647,10 +3621,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>45636</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>45579</v>
       </c>
       <c r="S38" t="s">
@@ -3697,10 +3671,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>45831</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3744,10 +3718,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>44287</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3768,22 +3742,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>164</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>165</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>166</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>167</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -7997,91 +7971,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>230</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>231</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>232</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>233</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>234</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>235</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>236</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>237</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>238</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>239</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>240</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>241</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>242</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>243</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>244</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>245</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>246</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>247</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>248</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>249</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>250</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>251</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>252</v>
       </c>
     </row>
@@ -8095,13 +8069,13 @@
       <c r="D2" t="s">
         <v>255</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
         <v>258</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>45492</v>
       </c>
       <c r="H2" t="s">
@@ -8119,13 +8093,13 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45491</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="1">
         <v>45528</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="1">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
@@ -8163,13 +8137,13 @@
       <c r="D3" t="s">
         <v>256</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
         <v>258</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>45631</v>
       </c>
       <c r="H3" t="s">
@@ -8187,13 +8161,13 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45628</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>45632</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
@@ -8228,13 +8202,13 @@
       <c r="D4" t="s">
         <v>256</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
         <v>258</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>45716</v>
       </c>
       <c r="H4" t="s">
@@ -8252,13 +8226,13 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45716</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <v>45722</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="1">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
@@ -8293,13 +8267,13 @@
       <c r="D5" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>45728</v>
       </c>
       <c r="H5" t="s">
@@ -8317,13 +8291,13 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45722</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <v>45782</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="1">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
@@ -8361,13 +8335,13 @@
       <c r="D6" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
         <v>258</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>45755</v>
       </c>
       <c r="H6" t="s">
@@ -8385,13 +8359,13 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45728</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="1">
         <v>45734</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="1">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
@@ -8429,7 +8403,7 @@
       <c r="D7" t="s">
         <v>257</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
@@ -8450,10 +8424,10 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45772</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="1">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
@@ -8491,7 +8465,7 @@
       <c r="D8" t="s">
         <v>257</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
@@ -8512,10 +8486,10 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>45762</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="1">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
@@ -8553,7 +8527,7 @@
       <c r="D9" t="s">
         <v>257</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
@@ -8574,10 +8548,10 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45763</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="1">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
@@ -8615,13 +8589,13 @@
       <c r="D10" t="s">
         <v>256</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
         <v>258</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>45755</v>
       </c>
       <c r="H10" t="s">
@@ -8639,13 +8613,13 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45754</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="1">
         <v>45849</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="1">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
@@ -8680,13 +8654,13 @@
       <c r="D11" t="s">
         <v>256</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
         <v>258</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>44973</v>
       </c>
       <c r="H11" t="s">
@@ -8704,13 +8678,13 @@
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44973</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="1">
         <v>45687</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" s="1">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
@@ -8745,13 +8719,13 @@
       <c r="D12" t="s">
         <v>256</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
         <v>258</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>45358</v>
       </c>
       <c r="H12" t="s">
@@ -8769,13 +8743,13 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45358</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="1">
         <v>45517</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12" s="1">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
@@ -8810,13 +8784,13 @@
       <c r="D13" t="s">
         <v>256</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
         <v>258</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>45573</v>
       </c>
       <c r="H13" t="s">
@@ -8834,13 +8808,13 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45572</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="1">
         <v>45572</v>
       </c>
-      <c r="S13" s="2">
+      <c r="S13" s="1">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
@@ -8878,13 +8852,13 @@
       <c r="D14" t="s">
         <v>256</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
         <v>258</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>45747</v>
       </c>
       <c r="H14" t="s">
@@ -8902,13 +8876,13 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>45736</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" s="1">
         <v>46101</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14" s="1">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
@@ -8944,70 +8918,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9045,10 +9019,10 @@
       <c r="O2" t="s">
         <v>102</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>45490</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -9092,10 +9066,10 @@
       <c r="O3" t="s">
         <v>81</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>45618</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -9139,10 +9113,10 @@
       <c r="O4" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>45539</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -9186,10 +9160,10 @@
       <c r="O5" t="s">
         <v>98</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>45567</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -9233,10 +9207,10 @@
       <c r="O6" t="s">
         <v>95</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>45568</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -9280,10 +9254,10 @@
       <c r="O7" t="s">
         <v>83</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>45831</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -9327,10 +9301,10 @@
       <c r="O8" t="s">
         <v>103</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45601</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -9374,10 +9348,10 @@
       <c r="O9" t="s">
         <v>92</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45631</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -9421,10 +9395,10 @@
       <c r="O10" t="s">
         <v>89</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>43902</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -9468,10 +9442,10 @@
       <c r="O11" t="s">
         <v>99</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>44736</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -9515,10 +9489,10 @@
       <c r="O12" t="s">
         <v>82</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>45776</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -9562,10 +9536,10 @@
       <c r="O13" t="s">
         <v>80</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>45772</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -9609,10 +9583,10 @@
       <c r="O14" t="s">
         <v>100</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45000</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -9656,7 +9630,7 @@
       <c r="O15" t="s">
         <v>94</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -9697,7 +9671,7 @@
       <c r="O16" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -9738,10 +9712,10 @@
       <c r="O17" t="s">
         <v>93</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45371</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -9785,10 +9759,10 @@
       <c r="O18" t="s">
         <v>91</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>46001</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -9832,10 +9806,10 @@
       <c r="O19" t="s">
         <v>104</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45436</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -9879,10 +9853,10 @@
       <c r="O20" t="s">
         <v>96</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>44372</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -9926,10 +9900,10 @@
       <c r="O21" t="s">
         <v>105</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>44362</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -9973,10 +9947,10 @@
       <c r="O22" t="s">
         <v>86</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -10014,10 +9988,10 @@
       <c r="O23" t="s">
         <v>359</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>40044</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -10029,7 +10003,7 @@
       <c r="T23" t="s">
         <v>399</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45775</v>
       </c>
     </row>
@@ -10067,10 +10041,10 @@
       <c r="O24" t="s">
         <v>80</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>43549</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -10082,7 +10056,7 @@
       <c r="T24" t="s">
         <v>400</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -10120,10 +10094,10 @@
       <c r="O25" t="s">
         <v>86</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45447</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -10135,7 +10109,7 @@
       <c r="T25" t="s">
         <v>401</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U25" s="1">
         <v>45937</v>
       </c>
     </row>
@@ -10173,10 +10147,10 @@
       <c r="O26" t="s">
         <v>100</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>44485</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -10188,7 +10162,7 @@
       <c r="T26" t="s">
         <v>402</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>45580</v>
       </c>
     </row>
@@ -10226,10 +10200,10 @@
       <c r="O27" t="s">
         <v>86</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45420</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -10241,7 +10215,7 @@
       <c r="T27" t="s">
         <v>403</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U27" s="1">
         <v>45588</v>
       </c>
     </row>
@@ -10279,10 +10253,10 @@
       <c r="O28" t="s">
         <v>101</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>44369</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -10294,7 +10268,7 @@
       <c r="T28" t="s">
         <v>404</v>
       </c>
-      <c r="U28" s="2">
+      <c r="U28" s="1">
         <v>45831</v>
       </c>
     </row>
@@ -10332,10 +10306,10 @@
       <c r="O29" t="s">
         <v>98</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44652</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -10347,7 +10321,7 @@
       <c r="T29" t="s">
         <v>405</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U29" s="1">
         <v>45734</v>
       </c>
     </row>
@@ -10379,7 +10353,7 @@
       <c r="T30" t="s">
         <v>406</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10411,7 +10385,7 @@
       <c r="T31" t="s">
         <v>407</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10443,7 +10417,7 @@
       <c r="T32" t="s">
         <v>408</v>
       </c>
-      <c r="U32" s="2">
+      <c r="U32" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10481,10 +10455,10 @@
       <c r="O33" t="s">
         <v>90</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>43762</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -10496,7 +10470,7 @@
       <c r="T33" t="s">
         <v>387</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>46037</v>
       </c>
     </row>
@@ -10534,16 +10508,16 @@
       <c r="O34" t="s">
         <v>360</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>40071</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>146</v>
       </c>
-      <c r="U34" s="2">
+      <c r="U34" s="1">
         <v>41023</v>
       </c>
     </row>
@@ -10575,10 +10549,10 @@
       <c r="O35" t="s">
         <v>87</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>44784</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -10587,7 +10561,7 @@
       <c r="S35" t="s">
         <v>146</v>
       </c>
-      <c r="U35" s="2">
+      <c r="U35" s="1">
         <v>45259</v>
       </c>
     </row>
@@ -10625,10 +10599,10 @@
       <c r="O36" t="s">
         <v>91</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45103</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -10637,7 +10611,7 @@
       <c r="S36" t="s">
         <v>146</v>
       </c>
-      <c r="U36" s="2">
+      <c r="U36" s="1">
         <v>46000</v>
       </c>
     </row>
@@ -10701,10 +10675,10 @@
       <c r="O38" t="s">
         <v>96</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>38511</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -10713,7 +10687,7 @@
       <c r="S38" t="s">
         <v>146</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>39068</v>
       </c>
     </row>
@@ -10751,10 +10725,10 @@
       <c r="O39" t="s">
         <v>103</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>39006</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -10766,7 +10740,7 @@
       <c r="T39" t="s">
         <v>409</v>
       </c>
-      <c r="U39" s="2">
+      <c r="U39" s="1">
         <v>40568</v>
       </c>
     </row>
@@ -10798,10 +10772,10 @@
       <c r="O40" t="s">
         <v>100</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>40836</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -10813,7 +10787,7 @@
       <c r="T40" t="s">
         <v>410</v>
       </c>
-      <c r="U40" s="2">
+      <c r="U40" s="1">
         <v>42270</v>
       </c>
     </row>
@@ -10851,10 +10825,10 @@
       <c r="O41" t="s">
         <v>95</v>
       </c>
-      <c r="P41" s="2">
+      <c r="P41" s="1">
         <v>42940</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="1">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -10866,7 +10840,7 @@
       <c r="T41" t="s">
         <v>411</v>
       </c>
-      <c r="U41" s="2">
+      <c r="U41" s="1">
         <v>44148</v>
       </c>
     </row>
@@ -10904,10 +10878,10 @@
       <c r="O42" t="s">
         <v>82</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="1">
         <v>43696</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="1">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -10919,7 +10893,7 @@
       <c r="T42" t="s">
         <v>412</v>
       </c>
-      <c r="U42" s="2">
+      <c r="U42" s="1">
         <v>43185</v>
       </c>
     </row>
@@ -10957,10 +10931,10 @@
       <c r="O43" t="s">
         <v>84</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="1">
         <v>43544</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="1">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -10972,7 +10946,7 @@
       <c r="T43" t="s">
         <v>413</v>
       </c>
-      <c r="U43" s="2">
+      <c r="U43" s="1">
         <v>42850</v>
       </c>
     </row>
@@ -11010,10 +10984,10 @@
       <c r="O44" t="s">
         <v>97</v>
       </c>
-      <c r="P44" s="2">
+      <c r="P44" s="1">
         <v>45076</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="1">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -11025,7 +10999,7 @@
       <c r="T44" t="s">
         <v>414</v>
       </c>
-      <c r="U44" s="2">
+      <c r="U44" s="1">
         <v>44404</v>
       </c>
     </row>
@@ -11063,10 +11037,10 @@
       <c r="O45" t="s">
         <v>81</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="1">
         <v>42963</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="1">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -11078,7 +11052,7 @@
       <c r="T45" t="s">
         <v>415</v>
       </c>
-      <c r="U45" s="2">
+      <c r="U45" s="1">
         <v>42698</v>
       </c>
     </row>
@@ -11116,10 +11090,10 @@
       <c r="O46" t="s">
         <v>88</v>
       </c>
-      <c r="P46" s="2">
+      <c r="P46" s="1">
         <v>45054</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="1">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -11131,7 +11105,7 @@
       <c r="T46" t="s">
         <v>416</v>
       </c>
-      <c r="U46" s="2">
+      <c r="U46" s="1">
         <v>43941</v>
       </c>
     </row>
@@ -11146,25 +11120,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>164</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>417</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>418</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>419</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>420</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>421</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -12,13 +12,14 @@
     <sheet name="OS" sheetId="3" r:id="rId3"/>
     <sheet name="Helice" sheetId="4" r:id="rId4"/>
     <sheet name="DiagonalMeta" sheetId="5" r:id="rId5"/>
+    <sheet name="Financeiro" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="351">
   <si>
     <t>om</t>
   </si>
@@ -260,237 +261,57 @@
     <t>H - Horas de Vôo</t>
   </si>
   <si>
-    <t>2702</t>
-  </si>
-  <si>
-    <t>2703</t>
-  </si>
-  <si>
-    <t>2719</t>
-  </si>
-  <si>
-    <t>2728</t>
-  </si>
-  <si>
-    <t>2742</t>
-  </si>
-  <si>
-    <t>2734</t>
-  </si>
-  <si>
-    <t>2740</t>
-  </si>
-  <si>
-    <t>2732</t>
-  </si>
-  <si>
-    <t>2733</t>
-  </si>
-  <si>
-    <t>2727</t>
-  </si>
-  <si>
-    <t>2738</t>
-  </si>
-  <si>
-    <t>2737</t>
-  </si>
-  <si>
-    <t>2736</t>
-  </si>
-  <si>
-    <t>2731</t>
-  </si>
-  <si>
-    <t>2721</t>
-  </si>
-  <si>
-    <t>2741</t>
-  </si>
-  <si>
-    <t>2704</t>
-  </si>
-  <si>
-    <t>2739</t>
-  </si>
-  <si>
-    <t>2722</t>
-  </si>
-  <si>
-    <t>2724</t>
-  </si>
-  <si>
-    <t>2723</t>
-  </si>
-  <si>
-    <t>2743</t>
-  </si>
-  <si>
-    <t>2709</t>
-  </si>
-  <si>
-    <t>2720</t>
-  </si>
-  <si>
-    <t>2729</t>
-  </si>
-  <si>
-    <t>2708</t>
-  </si>
-  <si>
-    <t>3040093565</t>
-  </si>
-  <si>
-    <t>3040083839</t>
-  </si>
-  <si>
-    <t>2260002888</t>
-  </si>
-  <si>
-    <t>3040093881</t>
-  </si>
-  <si>
-    <t>3130007347</t>
-  </si>
-  <si>
-    <t>3810139776</t>
-  </si>
-  <si>
-    <t>3810113895</t>
-  </si>
-  <si>
-    <t>3810140243</t>
-  </si>
-  <si>
-    <t>7080005835</t>
-  </si>
-  <si>
-    <t>3040093764</t>
-  </si>
-  <si>
-    <t>3810134655</t>
-  </si>
-  <si>
-    <t>6850006787</t>
-  </si>
-  <si>
-    <t>3810135032</t>
-  </si>
-  <si>
-    <t>3810140063</t>
-  </si>
-  <si>
-    <t>3810135107</t>
-  </si>
-  <si>
-    <t>3290008824</t>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>APL</t>
+  </si>
+  <si>
+    <t>REPARA</t>
+  </si>
+  <si>
+    <t>RECOLH</t>
+  </si>
+  <si>
+    <t>REMOV</t>
+  </si>
+  <si>
+    <t>OS OPR</t>
+  </si>
+  <si>
+    <t>3810279892</t>
+  </si>
+  <si>
+    <t>3810280456</t>
+  </si>
+  <si>
+    <t>381/201900011201</t>
+  </si>
+  <si>
+    <t>708/202200008802</t>
+  </si>
+  <si>
+    <t>3810280355</t>
+  </si>
+  <si>
+    <t>3810277703</t>
+  </si>
+  <si>
+    <t>3810279578</t>
+  </si>
+  <si>
+    <t>3810280317</t>
   </si>
   <si>
     <t>6900004625</t>
   </si>
   <si>
-    <t>3810140068</t>
+    <t>3810279579</t>
   </si>
   <si>
     <t>3130008877</t>
   </si>
   <si>
-    <t>3810138909</t>
-  </si>
-  <si>
-    <t>3810138523</t>
-  </si>
-  <si>
-    <t>6890000683</t>
-  </si>
-  <si>
-    <t>3810112732</t>
-  </si>
-  <si>
-    <t>3810139780</t>
-  </si>
-  <si>
-    <t>3810126785</t>
-  </si>
-  <si>
-    <t>3860011562</t>
-  </si>
-  <si>
-    <t>3950001218</t>
-  </si>
-  <si>
-    <t>6890001058</t>
-  </si>
-  <si>
-    <t>3810118951</t>
-  </si>
-  <si>
-    <t>7080002856</t>
-  </si>
-  <si>
-    <t>3810129323</t>
-  </si>
-  <si>
-    <t>3130005802</t>
-  </si>
-  <si>
-    <t>3740026391</t>
-  </si>
-  <si>
-    <t>3290008244</t>
-  </si>
-  <si>
-    <t>3810139583</t>
-  </si>
-  <si>
-    <t>7080004330</t>
-  </si>
-  <si>
-    <t>OS</t>
-  </si>
-  <si>
-    <t>APL</t>
-  </si>
-  <si>
-    <t>REPARA</t>
-  </si>
-  <si>
-    <t>RECOLH</t>
-  </si>
-  <si>
-    <t>REMOV</t>
-  </si>
-  <si>
-    <t>OS OPR</t>
-  </si>
-  <si>
-    <t>3810279892</t>
-  </si>
-  <si>
-    <t>3810280456</t>
-  </si>
-  <si>
-    <t>381/201900011201</t>
-  </si>
-  <si>
-    <t>708/202200008802</t>
-  </si>
-  <si>
-    <t>3810280355</t>
-  </si>
-  <si>
-    <t>3810277703</t>
-  </si>
-  <si>
-    <t>3810279578</t>
-  </si>
-  <si>
-    <t>3810280317</t>
-  </si>
-  <si>
-    <t>3810279579</t>
-  </si>
-  <si>
     <t>3810276969</t>
   </si>
   <si>
@@ -579,9 +400,6 @@
   </si>
   <si>
     <t>19.2</t>
-  </si>
-  <si>
-    <t>#N/A</t>
   </si>
   <si>
     <t>5.1586629</t>
@@ -828,12 +646,6 @@
     <t>M</t>
   </si>
   <si>
-    <t>313240015920</t>
-  </si>
-  <si>
-    <t>313240016031</t>
-  </si>
-  <si>
     <t>S4J</t>
   </si>
   <si>
@@ -846,45 +658,6 @@
     <t>SEP</t>
   </si>
   <si>
-    <t>3810496453</t>
-  </si>
-  <si>
-    <t>3810499719</t>
-  </si>
-  <si>
-    <t>3810500784</t>
-  </si>
-  <si>
-    <t>3810501279</t>
-  </si>
-  <si>
-    <t>3810502614</t>
-  </si>
-  <si>
-    <t>3810504268</t>
-  </si>
-  <si>
-    <t>3810504159</t>
-  </si>
-  <si>
-    <t>3810504182</t>
-  </si>
-  <si>
-    <t>3810503807</t>
-  </si>
-  <si>
-    <t>3810481813</t>
-  </si>
-  <si>
-    <t>3810492521</t>
-  </si>
-  <si>
-    <t>3810499557</t>
-  </si>
-  <si>
-    <t>3810499086</t>
-  </si>
-  <si>
     <t>BAMN</t>
   </si>
   <si>
@@ -1116,156 +889,39 @@
     <t>H-HorasdeVôo</t>
   </si>
   <si>
-    <t>2725</t>
-  </si>
-  <si>
-    <t>2735</t>
-  </si>
-  <si>
-    <t>3130006005</t>
-  </si>
-  <si>
-    <t>6890000562</t>
-  </si>
-  <si>
-    <t>3040075245</t>
-  </si>
-  <si>
-    <t>3290007931</t>
-  </si>
-  <si>
-    <t>7090002248</t>
-  </si>
-  <si>
-    <t>3130006789</t>
-  </si>
-  <si>
-    <t>7090002894</t>
-  </si>
-  <si>
-    <t>3130005796</t>
-  </si>
-  <si>
-    <t>7100002436</t>
-  </si>
-  <si>
-    <t>3040057779</t>
-  </si>
-  <si>
-    <t>3040073019</t>
-  </si>
-  <si>
-    <t>3040090256</t>
-  </si>
-  <si>
-    <t>7090002718</t>
-  </si>
-  <si>
-    <t>3040077697</t>
-  </si>
-  <si>
-    <t>3960004903</t>
-  </si>
-  <si>
-    <t>3130006599</t>
-  </si>
-  <si>
-    <t>7090000956</t>
-  </si>
-  <si>
-    <t>7080003306</t>
-  </si>
-  <si>
-    <t>7080005315</t>
-  </si>
-  <si>
-    <t>3130007478</t>
-  </si>
-  <si>
-    <t>3040091287</t>
-  </si>
-  <si>
-    <t>3130007827</t>
-  </si>
-  <si>
-    <t>4190000750</t>
-  </si>
-  <si>
-    <t>3130007058</t>
-  </si>
-  <si>
-    <t>3040091753</t>
-  </si>
-  <si>
-    <t>6850004453</t>
+    <t>3040252386</t>
+  </si>
+  <si>
+    <t>3040253442</t>
+  </si>
+  <si>
+    <t>3040258338</t>
+  </si>
+  <si>
+    <t>3040247635</t>
+  </si>
+  <si>
+    <t>3040247803</t>
+  </si>
+  <si>
+    <t>3040254478</t>
+  </si>
+  <si>
+    <t>3040250893</t>
+  </si>
+  <si>
+    <t>3040260408</t>
+  </si>
+  <si>
+    <t>3040260405</t>
+  </si>
+  <si>
+    <t>3040260407</t>
   </si>
   <si>
     <t>3130008485</t>
   </si>
   <si>
-    <t>3130006532</t>
-  </si>
-  <si>
-    <t>6890000560</t>
-  </si>
-  <si>
-    <t>3070018395</t>
-  </si>
-  <si>
-    <t>3130002407</t>
-  </si>
-  <si>
-    <t>3040050893</t>
-  </si>
-  <si>
-    <t>3040080066</t>
-  </si>
-  <si>
-    <t>6850005706</t>
-  </si>
-  <si>
-    <t>3860010942</t>
-  </si>
-  <si>
-    <t>3960005216</t>
-  </si>
-  <si>
-    <t>3040088304</t>
-  </si>
-  <si>
-    <t>3130007348</t>
-  </si>
-  <si>
-    <t>3040252386</t>
-  </si>
-  <si>
-    <t>3040253442</t>
-  </si>
-  <si>
-    <t>3040258338</t>
-  </si>
-  <si>
-    <t>3040247635</t>
-  </si>
-  <si>
-    <t>3040247803</t>
-  </si>
-  <si>
-    <t>3040254478</t>
-  </si>
-  <si>
-    <t>3040250893</t>
-  </si>
-  <si>
-    <t>3040260408</t>
-  </si>
-  <si>
-    <t>3040260405</t>
-  </si>
-  <si>
-    <t>3040260407</t>
-  </si>
-  <si>
     <t>3040040322</t>
   </si>
   <si>
@@ -1303,6 +959,138 @@
   </si>
   <si>
     <t>mes_disp</t>
+  </si>
+  <si>
+    <t>pacote</t>
+  </si>
+  <si>
+    <t>sigla_projeto</t>
+  </si>
+  <si>
+    <t>atividade</t>
+  </si>
+  <si>
+    <t>tarefa</t>
+  </si>
+  <si>
+    <t>categoria</t>
+  </si>
+  <si>
+    <t>valor_total</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>RAP</t>
+  </si>
+  <si>
+    <t>C-98</t>
+  </si>
+  <si>
+    <t>REQUISIÇÃO PUBLICAÇÃO</t>
+  </si>
+  <si>
+    <t>CNT 048/CELOG-PAMASP/2022 - PW - Material</t>
+  </si>
+  <si>
+    <t>Requisição CABW</t>
+  </si>
+  <si>
+    <t>CNT XXX/CELOG-PAMASP/2026 - Material</t>
+  </si>
+  <si>
+    <t>REQUISIÇÃO SERVIÇO</t>
+  </si>
+  <si>
+    <t>CNT 031/CELOG-PAMASP/2022 - PW - RG</t>
+  </si>
+  <si>
+    <t>CNT XXX/CELOG-PAMASP/2026 - XXX - RG</t>
+  </si>
+  <si>
+    <t>Maintenance and Overhaul Collection PN 3077123 PT6A-34/114A</t>
+  </si>
+  <si>
+    <t>Material HSI PT6A-114A (1/2)</t>
+  </si>
+  <si>
+    <t>Material HSI PT6A-114A (2/2)</t>
+  </si>
+  <si>
+    <t>Material reparo acessórios PT6A-114A (1/3)</t>
+  </si>
+  <si>
+    <t>Material reparo acessórios PT6A-114A (2/3)</t>
+  </si>
+  <si>
+    <t>Material reparo acessórios PT6A-114A (3/3)</t>
+  </si>
+  <si>
+    <t>Material reparo PT6A-114A (1/3)</t>
+  </si>
+  <si>
+    <t>Material reparo PT6A-114A (2/3)</t>
+  </si>
+  <si>
+    <t>Material reparo PT6A-114A (3/3)</t>
+  </si>
+  <si>
+    <t>Publicações</t>
+  </si>
+  <si>
+    <t>Publicações de Acessórios PT6A-114A</t>
+  </si>
+  <si>
+    <t>Reparo de CTVR 2 EA (1/2)</t>
+  </si>
+  <si>
+    <t>Reparo de CTVR 2 EA (2/2)</t>
+  </si>
+  <si>
+    <t>Reparo de PTVR 2 EA (1/2)</t>
+  </si>
+  <si>
+    <t>Reparo de PTVR 2 EA (2/2)</t>
+  </si>
+  <si>
+    <t>Revisão Geral PT6A-114A (1/6)</t>
+  </si>
+  <si>
+    <t>Revisão Geral PT6A-114A (2/6)</t>
+  </si>
+  <si>
+    <t>Revisão Geral PT6A-114A (3/6)</t>
+  </si>
+  <si>
+    <t>Revisão Geral PT6A-114A (4/6)</t>
+  </si>
+  <si>
+    <t>Revisão Geral PT6A-114A (5/6)</t>
+  </si>
+  <si>
+    <t>Revisão Geral PT6A-114A (6/6)</t>
+  </si>
+  <si>
+    <t>RG FCU 3 EA (1/2)</t>
+  </si>
+  <si>
+    <t>RG FCU 3 EA (2/2)</t>
+  </si>
+  <si>
+    <t>RG Fuel Pump 5 EA (1/1)</t>
+  </si>
+  <si>
+    <t>RG IGNITION EXCITER 4 EA (1/1)</t>
+  </si>
+  <si>
+    <t>MOTOR</t>
   </si>
 </sst>
 </file>
@@ -1312,8 +1100,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1329,7 +1125,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1337,12 +1133,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1642,70 +1456,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1740,28 +1554,28 @@
       <c r="M2">
         <v>128.48</v>
       </c>
-      <c r="N2" t="s">
-        <v>80</v>
+      <c r="N2">
+        <v>2702</v>
       </c>
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>41754</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>46134</v>
       </c>
-      <c r="R2" t="s">
-        <v>106</v>
+      <c r="R2">
+        <v>3040093565</v>
       </c>
       <c r="S2" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T2" t="s">
-        <v>148</v>
-      </c>
-      <c r="U2" s="1">
+        <v>86</v>
+      </c>
+      <c r="U2" s="2">
         <v>46170</v>
       </c>
     </row>
@@ -1796,23 +1610,23 @@
       <c r="M3">
         <v>102.93</v>
       </c>
-      <c r="N3" t="s">
-        <v>81</v>
+      <c r="N3">
+        <v>2703</v>
       </c>
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>44709</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>44652</v>
       </c>
-      <c r="R3" t="s">
-        <v>107</v>
+      <c r="R3">
+        <v>3040083839</v>
       </c>
       <c r="S3" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1846,23 +1660,23 @@
       <c r="M4">
         <v>106.56</v>
       </c>
-      <c r="N4" t="s">
-        <v>82</v>
+      <c r="N4">
+        <v>2719</v>
       </c>
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>44348</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>44348</v>
       </c>
-      <c r="R4" t="s">
-        <v>108</v>
+      <c r="R4">
+        <v>2260002888</v>
       </c>
       <c r="S4" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1896,28 +1710,28 @@
       <c r="M5">
         <v>1.48</v>
       </c>
-      <c r="N5" t="s">
-        <v>83</v>
+      <c r="N5">
+        <v>2728</v>
       </c>
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>46059</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>46203</v>
       </c>
-      <c r="R5" t="s">
-        <v>109</v>
+      <c r="R5">
+        <v>3040093881</v>
       </c>
       <c r="S5" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T5" t="s">
-        <v>149</v>
-      </c>
-      <c r="U5" s="1">
+        <v>87</v>
+      </c>
+      <c r="U5" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -1949,23 +1763,23 @@
       <c r="M6">
         <v>18.72</v>
       </c>
-      <c r="N6" t="s">
-        <v>84</v>
+      <c r="N6">
+        <v>2742</v>
       </c>
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>46149</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45510</v>
       </c>
-      <c r="R6" t="s">
-        <v>110</v>
+      <c r="R6">
+        <v>3130007347</v>
       </c>
       <c r="S6" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1999,28 +1813,28 @@
       <c r="M7">
         <v>124.93</v>
       </c>
-      <c r="N7" t="s">
-        <v>85</v>
+      <c r="N7">
+        <v>2734</v>
       </c>
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>43731</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45301</v>
       </c>
-      <c r="R7" t="s">
-        <v>111</v>
+      <c r="R7">
+        <v>3810139776</v>
       </c>
       <c r="S7" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="T7" t="s">
-        <v>150</v>
-      </c>
-      <c r="U7" s="1">
+        <v>88</v>
+      </c>
+      <c r="U7" s="2">
         <v>43507</v>
       </c>
     </row>
@@ -2055,23 +1869,23 @@
       <c r="M8">
         <v>80.92</v>
       </c>
-      <c r="N8" t="s">
-        <v>86</v>
+      <c r="N8">
+        <v>2740</v>
       </c>
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45511</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>43725</v>
       </c>
-      <c r="R8" t="s">
-        <v>112</v>
+      <c r="R8">
+        <v>3810113895</v>
       </c>
       <c r="S8" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -2105,28 +1919,28 @@
       <c r="M9">
         <v>72.23999999999999</v>
       </c>
-      <c r="N9" t="s">
-        <v>87</v>
+      <c r="N9">
+        <v>2732</v>
       </c>
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45716</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45716</v>
       </c>
-      <c r="R9" t="s">
-        <v>113</v>
+      <c r="R9">
+        <v>3810140243</v>
       </c>
       <c r="S9" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="T9" t="s">
-        <v>151</v>
-      </c>
-      <c r="U9" s="1">
+        <v>89</v>
+      </c>
+      <c r="U9" s="2">
         <v>44665</v>
       </c>
     </row>
@@ -2161,23 +1975,23 @@
       <c r="M10">
         <v>103.29</v>
       </c>
-      <c r="N10" t="s">
-        <v>88</v>
+      <c r="N10">
+        <v>2733</v>
       </c>
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>45064</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45048</v>
       </c>
-      <c r="R10" t="s">
-        <v>114</v>
+      <c r="R10">
+        <v>7080005835</v>
       </c>
       <c r="S10" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -2205,28 +2019,28 @@
       <c r="L11">
         <v>16595</v>
       </c>
-      <c r="N11" t="s">
-        <v>80</v>
+      <c r="N11">
+        <v>2702</v>
       </c>
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>46135</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>46169</v>
       </c>
-      <c r="R11" t="s">
-        <v>115</v>
+      <c r="R11">
+        <v>3040093764</v>
       </c>
       <c r="S11" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T11" t="s">
-        <v>152</v>
-      </c>
-      <c r="U11" s="1">
+        <v>90</v>
+      </c>
+      <c r="U11" s="2">
         <v>46203</v>
       </c>
     </row>
@@ -2258,17 +2072,17 @@
       <c r="M12">
         <v>0.3</v>
       </c>
-      <c r="N12" t="s">
-        <v>89</v>
+      <c r="N12">
+        <v>2727</v>
       </c>
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2299,23 +2113,23 @@
       <c r="M13">
         <v>0.57</v>
       </c>
-      <c r="N13" t="s">
-        <v>90</v>
+      <c r="N13">
+        <v>2738</v>
       </c>
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>46199</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>41861</v>
       </c>
-      <c r="R13" t="s">
-        <v>116</v>
+      <c r="R13">
+        <v>3810134655</v>
       </c>
       <c r="S13" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2346,28 +2160,28 @@
       <c r="M14">
         <v>3.57</v>
       </c>
-      <c r="N14" t="s">
-        <v>83</v>
+      <c r="N14">
+        <v>2728</v>
       </c>
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45667</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>46059</v>
       </c>
-      <c r="R14" t="s">
-        <v>117</v>
+      <c r="R14">
+        <v>6850006787</v>
       </c>
       <c r="S14" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T14" t="s">
-        <v>153</v>
-      </c>
-      <c r="U14" s="1">
+        <v>91</v>
+      </c>
+      <c r="U14" s="2">
         <v>46072</v>
       </c>
     </row>
@@ -2402,23 +2216,23 @@
       <c r="M15">
         <v>7.31</v>
       </c>
-      <c r="N15" t="s">
-        <v>91</v>
+      <c r="N15">
+        <v>2737</v>
       </c>
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>46064</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="Q15" s="2">
         <v>43592</v>
       </c>
-      <c r="R15" t="s">
-        <v>118</v>
+      <c r="R15">
+        <v>3810135032</v>
       </c>
       <c r="S15" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2452,28 +2266,28 @@
       <c r="M16">
         <v>111.99</v>
       </c>
-      <c r="N16" t="s">
-        <v>92</v>
+      <c r="N16">
+        <v>2736</v>
       </c>
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>44285</v>
       </c>
-      <c r="Q16" s="1">
+      <c r="Q16" s="2">
         <v>45524</v>
       </c>
-      <c r="R16" t="s">
-        <v>119</v>
+      <c r="R16">
+        <v>3810140063</v>
       </c>
       <c r="S16" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T16" t="s">
-        <v>154</v>
-      </c>
-      <c r="U16" s="1">
+        <v>92</v>
+      </c>
+      <c r="U16" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2508,23 +2322,23 @@
       <c r="M17">
         <v>8.880000000000001</v>
       </c>
-      <c r="N17" t="s">
-        <v>93</v>
+      <c r="N17">
+        <v>2731</v>
       </c>
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45922</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45061</v>
       </c>
-      <c r="R17" t="s">
-        <v>120</v>
+      <c r="R17">
+        <v>3810135107</v>
       </c>
       <c r="S17" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2558,28 +2372,28 @@
       <c r="M18">
         <v>6.68</v>
       </c>
-      <c r="N18" t="s">
-        <v>94</v>
+      <c r="N18">
+        <v>2721</v>
       </c>
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>45930</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>46184</v>
       </c>
-      <c r="R18" t="s">
-        <v>121</v>
+      <c r="R18">
+        <v>3290008824</v>
       </c>
       <c r="S18" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T18" t="s">
-        <v>155</v>
-      </c>
-      <c r="U18" s="1">
+        <v>93</v>
+      </c>
+      <c r="U18" s="2">
         <v>46198</v>
       </c>
     </row>
@@ -2614,28 +2428,28 @@
       <c r="M19">
         <v>130</v>
       </c>
-      <c r="N19" t="s">
-        <v>89</v>
+      <c r="N19">
+        <v>2727</v>
       </c>
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45524</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>46014</v>
       </c>
-      <c r="R19" t="s">
-        <v>122</v>
+      <c r="R19">
+        <v>6900004625</v>
       </c>
       <c r="S19" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="T19" t="s">
-        <v>122</v>
-      </c>
-      <c r="U19" s="1">
+        <v>94</v>
+      </c>
+      <c r="U19" s="2">
         <v>46153</v>
       </c>
       <c r="V19">
@@ -2673,28 +2487,28 @@
       <c r="M20">
         <v>120.81</v>
       </c>
-      <c r="N20" t="s">
-        <v>86</v>
+      <c r="N20">
+        <v>2740</v>
       </c>
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>45026</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>45446</v>
       </c>
-      <c r="R20" t="s">
-        <v>123</v>
+      <c r="R20">
+        <v>3810140068</v>
       </c>
       <c r="S20" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T20" t="s">
-        <v>156</v>
-      </c>
-      <c r="U20" s="1">
+        <v>95</v>
+      </c>
+      <c r="U20" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2729,28 +2543,28 @@
       <c r="M21">
         <v>111.25</v>
       </c>
-      <c r="N21" t="s">
-        <v>90</v>
+      <c r="N21">
+        <v>2738</v>
       </c>
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>45159</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>46199</v>
       </c>
-      <c r="R21" t="s">
-        <v>124</v>
+      <c r="R21">
+        <v>3130008877</v>
       </c>
       <c r="S21" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="T21" t="s">
-        <v>124</v>
-      </c>
-      <c r="U21" s="1">
+        <v>96</v>
+      </c>
+      <c r="U21" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -2785,28 +2599,28 @@
       <c r="M22">
         <v>115.75</v>
       </c>
-      <c r="N22" t="s">
-        <v>93</v>
+      <c r="N22">
+        <v>2731</v>
       </c>
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45922</v>
       </c>
-      <c r="R22" t="s">
-        <v>125</v>
+      <c r="R22">
+        <v>3810138909</v>
       </c>
       <c r="S22" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T22" t="s">
-        <v>157</v>
-      </c>
-      <c r="U22" s="1">
+        <v>97</v>
+      </c>
+      <c r="U22" s="2">
         <v>45995</v>
       </c>
     </row>
@@ -2838,25 +2652,25 @@
       <c r="L23">
         <v>5094.67</v>
       </c>
-      <c r="N23" t="s">
-        <v>91</v>
+      <c r="N23">
+        <v>2737</v>
       </c>
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>45713</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>45810</v>
       </c>
-      <c r="R23" t="s">
-        <v>126</v>
+      <c r="R23">
+        <v>3810138523</v>
       </c>
       <c r="S23" t="s">
-        <v>146</v>
-      </c>
-      <c r="U23" s="1">
+        <v>84</v>
+      </c>
+      <c r="U23" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -2891,23 +2705,23 @@
       <c r="M24">
         <v>77.38</v>
       </c>
-      <c r="N24" t="s">
-        <v>95</v>
+      <c r="N24">
+        <v>2741</v>
       </c>
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>46062</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>45925</v>
       </c>
-      <c r="R24" t="s">
-        <v>127</v>
+      <c r="R24">
+        <v>6890000683</v>
       </c>
       <c r="S24" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2941,23 +2755,23 @@
       <c r="M25">
         <v>121.42</v>
       </c>
-      <c r="N25" t="s">
-        <v>96</v>
+      <c r="N25">
+        <v>2704</v>
       </c>
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45079</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45062</v>
       </c>
-      <c r="R25" t="s">
-        <v>128</v>
+      <c r="R25">
+        <v>3810112732</v>
       </c>
       <c r="S25" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2991,28 +2805,28 @@
       <c r="M26">
         <v>133.71</v>
       </c>
-      <c r="N26" t="s">
-        <v>84</v>
+      <c r="N26">
+        <v>2742</v>
       </c>
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>41346</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>45916</v>
       </c>
-      <c r="R26" t="s">
-        <v>129</v>
+      <c r="R26">
+        <v>3810139780</v>
       </c>
       <c r="S26" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T26" t="s">
-        <v>158</v>
-      </c>
-      <c r="U26" s="1">
+        <v>98</v>
+      </c>
+      <c r="U26" s="2">
         <v>46150</v>
       </c>
     </row>
@@ -3047,23 +2861,23 @@
       <c r="M27">
         <v>29.88</v>
       </c>
-      <c r="N27" t="s">
-        <v>97</v>
+      <c r="N27">
+        <v>2739</v>
       </c>
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45579</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45579</v>
       </c>
-      <c r="R27" t="s">
-        <v>130</v>
+      <c r="R27">
+        <v>3810126785</v>
       </c>
       <c r="S27" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -3097,23 +2911,23 @@
       <c r="M28">
         <v>11.92</v>
       </c>
-      <c r="N28" t="s">
-        <v>80</v>
+      <c r="N28">
+        <v>2702</v>
       </c>
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>46171</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>46149</v>
       </c>
-      <c r="R28" t="s">
-        <v>131</v>
+      <c r="R28">
+        <v>3860011562</v>
       </c>
       <c r="S28" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -3147,23 +2961,23 @@
       <c r="M29">
         <v>101.98</v>
       </c>
-      <c r="N29" t="s">
-        <v>98</v>
+      <c r="N29">
+        <v>2722</v>
       </c>
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44320</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>44320</v>
       </c>
-      <c r="R29" t="s">
-        <v>132</v>
+      <c r="R29">
+        <v>3950001218</v>
       </c>
       <c r="S29" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -3197,28 +3011,28 @@
       <c r="M30">
         <v>83.67</v>
       </c>
-      <c r="N30" t="s">
-        <v>99</v>
+      <c r="N30">
+        <v>2724</v>
       </c>
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="2">
         <v>42661</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="Q30" s="2">
         <v>45252</v>
       </c>
-      <c r="R30" t="s">
-        <v>133</v>
+      <c r="R30">
+        <v>6890001058</v>
       </c>
       <c r="S30" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T30" t="s">
-        <v>159</v>
-      </c>
-      <c r="U30" s="1">
+        <v>99</v>
+      </c>
+      <c r="U30" s="2">
         <v>45358</v>
       </c>
     </row>
@@ -3253,23 +3067,23 @@
       <c r="M31">
         <v>96.72</v>
       </c>
-      <c r="N31" t="s">
-        <v>87</v>
+      <c r="N31">
+        <v>2732</v>
       </c>
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="2">
         <v>46064</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="Q31" s="2">
         <v>46064</v>
       </c>
-      <c r="R31" t="s">
-        <v>134</v>
+      <c r="R31">
+        <v>3810118951</v>
       </c>
       <c r="S31" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3303,23 +3117,23 @@
       <c r="M32">
         <v>70.77</v>
       </c>
-      <c r="N32" t="s">
-        <v>100</v>
+      <c r="N32">
+        <v>2723</v>
       </c>
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="2">
         <v>43797</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="Q32" s="2">
         <v>43725</v>
       </c>
-      <c r="R32" t="s">
-        <v>135</v>
+      <c r="R32">
+        <v>7080002856</v>
       </c>
       <c r="S32" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3353,28 +3167,28 @@
       <c r="M33">
         <v>9.640000000000001</v>
       </c>
-      <c r="N33" t="s">
-        <v>93</v>
+      <c r="N33">
+        <v>2731</v>
       </c>
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>42810</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>43159</v>
       </c>
-      <c r="R33" t="s">
-        <v>136</v>
+      <c r="R33">
+        <v>3810129323</v>
       </c>
       <c r="S33" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="T33" t="s">
-        <v>160</v>
-      </c>
-      <c r="U33" s="1">
+        <v>100</v>
+      </c>
+      <c r="U33" s="2">
         <v>43802</v>
       </c>
     </row>
@@ -3409,23 +3223,23 @@
       <c r="M34">
         <v>108.65</v>
       </c>
-      <c r="N34" t="s">
-        <v>101</v>
+      <c r="N34">
+        <v>2743</v>
       </c>
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>45070</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>44910</v>
       </c>
-      <c r="R34" t="s">
-        <v>137</v>
+      <c r="R34">
+        <v>3130005802</v>
       </c>
       <c r="S34" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3459,23 +3273,23 @@
       <c r="M35">
         <v>68.05</v>
       </c>
-      <c r="N35" t="s">
-        <v>102</v>
+      <c r="N35">
+        <v>2709</v>
       </c>
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>43250</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>41149</v>
       </c>
-      <c r="R35" t="s">
-        <v>138</v>
+      <c r="R35">
+        <v>3740026391</v>
       </c>
       <c r="S35" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3509,23 +3323,23 @@
       <c r="M36">
         <v>79.41</v>
       </c>
-      <c r="N36" t="s">
-        <v>103</v>
+      <c r="N36">
+        <v>2720</v>
       </c>
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45841</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>45754</v>
       </c>
-      <c r="R36" t="s">
-        <v>139</v>
+      <c r="R36">
+        <v>3290008244</v>
       </c>
       <c r="S36" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3559,28 +3373,28 @@
       <c r="M37">
         <v>45.47</v>
       </c>
-      <c r="N37" t="s">
-        <v>93</v>
+      <c r="N37">
+        <v>2731</v>
       </c>
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="2">
         <v>45105</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="Q37" s="2">
         <v>45509</v>
       </c>
-      <c r="R37" t="s">
-        <v>140</v>
+      <c r="R37">
+        <v>3810139583</v>
       </c>
       <c r="S37" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T37" t="s">
-        <v>161</v>
-      </c>
-      <c r="U37" s="1">
+        <v>101</v>
+      </c>
+      <c r="U37" s="2">
         <v>46184</v>
       </c>
     </row>
@@ -3615,23 +3429,23 @@
       <c r="M38">
         <v>70.81999999999999</v>
       </c>
-      <c r="N38" t="s">
-        <v>104</v>
+      <c r="N38">
+        <v>2729</v>
       </c>
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>45636</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>45579</v>
       </c>
       <c r="S38" t="s">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="V38" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3665,20 +3479,20 @@
       <c r="M39">
         <v>97.23999999999999</v>
       </c>
-      <c r="N39" t="s">
-        <v>92</v>
+      <c r="N39">
+        <v>2736</v>
       </c>
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>45831</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3712,23 +3526,23 @@
       <c r="M40">
         <v>56.08</v>
       </c>
-      <c r="N40" t="s">
-        <v>105</v>
+      <c r="N40">
+        <v>2708</v>
       </c>
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>44287</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>44114</v>
       </c>
-      <c r="R40" t="s">
-        <v>141</v>
+      <c r="R40">
+        <v>7080004330</v>
       </c>
       <c r="S40" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3742,23 +3556,23 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F1" t="s">
-        <v>168</v>
+      <c r="A1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3775,7 +3589,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3792,7 +3606,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3809,7 +3623,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3826,7 +3640,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3843,17 +3657,17 @@
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F6" t="s">
-        <v>214</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>59</v>
       </c>
-      <c r="B7" t="b">
+      <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
@@ -3863,14 +3677,14 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>59</v>
       </c>
-      <c r="B8" t="b">
+      <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
@@ -3880,14 +3694,14 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>59</v>
       </c>
-      <c r="B9" t="b">
+      <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
@@ -3897,14 +3711,14 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>59</v>
       </c>
-      <c r="B10" t="b">
+      <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
@@ -3914,14 +3728,14 @@
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>59</v>
       </c>
-      <c r="B11" t="b">
+      <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
@@ -3931,14 +3745,14 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>59</v>
       </c>
-      <c r="B12" t="b">
+      <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
@@ -3948,14 +3762,14 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>59</v>
       </c>
-      <c r="B13" t="b">
+      <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
@@ -3965,10 +3779,10 @@
         <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F13" t="s">
-        <v>215</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3985,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4002,7 +3816,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4019,7 +3833,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4036,10 +3850,10 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F17" t="s">
-        <v>216</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4056,7 +3870,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4073,7 +3887,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4090,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4107,7 +3921,7 @@
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4124,7 +3938,7 @@
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4141,7 +3955,7 @@
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4158,10 +3972,10 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F24" t="s">
-        <v>217</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4178,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4195,7 +4009,7 @@
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4212,7 +4026,7 @@
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4229,7 +4043,7 @@
         <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4246,7 +4060,7 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4263,7 +4077,7 @@
         <v>6</v>
       </c>
       <c r="E30" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4280,7 +4094,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4297,7 +4111,7 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4314,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4331,7 +4145,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4348,7 +4162,7 @@
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4365,7 +4179,7 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>177</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4382,7 +4196,7 @@
         <v>6</v>
       </c>
       <c r="E37" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4399,10 +4213,10 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="F38" t="s">
-        <v>218</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4419,7 +4233,7 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4436,7 +4250,7 @@
         <v>8</v>
       </c>
       <c r="E40" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4453,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4470,7 +4284,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4487,7 +4301,7 @@
         <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4504,7 +4318,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4521,10 +4335,10 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F45" t="s">
-        <v>219</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -4541,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4558,7 +4372,7 @@
         <v>2</v>
       </c>
       <c r="E47" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -4575,7 +4389,7 @@
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -4592,7 +4406,7 @@
         <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4609,7 +4423,7 @@
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -4626,10 +4440,10 @@
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="F51" t="s">
-        <v>220</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -4646,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4663,7 +4477,7 @@
         <v>2</v>
       </c>
       <c r="E53" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -4680,7 +4494,7 @@
         <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -4697,7 +4511,7 @@
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -4714,7 +4528,7 @@
         <v>5</v>
       </c>
       <c r="E56" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -4731,7 +4545,7 @@
         <v>6</v>
       </c>
       <c r="E57" t="s">
-        <v>184</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -4748,7 +4562,7 @@
         <v>7</v>
       </c>
       <c r="E58" t="s">
-        <v>185</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4765,10 +4579,10 @@
         <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="F59" t="s">
-        <v>221</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4785,14 +4599,14 @@
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>76</v>
       </c>
-      <c r="B61" t="b">
+      <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
@@ -4802,14 +4616,14 @@
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>76</v>
       </c>
-      <c r="B62" t="b">
+      <c r="B62">
         <v>0</v>
       </c>
       <c r="C62">
@@ -4819,14 +4633,14 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>76</v>
       </c>
-      <c r="B63" t="b">
+      <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
@@ -4836,14 +4650,14 @@
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>76</v>
       </c>
-      <c r="B64" t="b">
+      <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
@@ -4853,14 +4667,14 @@
         <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>76</v>
       </c>
-      <c r="B65" t="b">
+      <c r="B65">
         <v>0</v>
       </c>
       <c r="C65">
@@ -4870,14 +4684,14 @@
         <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>76</v>
       </c>
-      <c r="B66" t="b">
+      <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
@@ -4887,17 +4701,17 @@
         <v>6</v>
       </c>
       <c r="E66" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="F66" t="s">
-        <v>222</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>76</v>
       </c>
-      <c r="B67" t="b">
+      <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
@@ -4905,16 +4719,13 @@
       </c>
       <c r="D67">
         <v>7</v>
-      </c>
-      <c r="E67" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>76</v>
       </c>
-      <c r="B68" t="b">
+      <c r="B68">
         <v>0</v>
       </c>
       <c r="C68">
@@ -4924,14 +4735,14 @@
         <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>162</v>
+        <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>76</v>
       </c>
-      <c r="B69" t="b">
+      <c r="B69">
         <v>0</v>
       </c>
       <c r="C69">
@@ -4941,7 +4752,7 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4958,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -4975,7 +4786,7 @@
         <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4992,7 +4803,7 @@
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -5009,7 +4820,7 @@
         <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -5026,7 +4837,7 @@
         <v>7</v>
       </c>
       <c r="E74" t="s">
-        <v>188</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5043,7 +4854,7 @@
         <v>6</v>
       </c>
       <c r="E75" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -5060,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -5077,7 +4888,7 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -5094,7 +4905,7 @@
         <v>3</v>
       </c>
       <c r="E78" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -5111,7 +4922,7 @@
         <v>4</v>
       </c>
       <c r="E79" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -5128,7 +4939,7 @@
         <v>5</v>
       </c>
       <c r="E80" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -5145,7 +4956,7 @@
         <v>5</v>
       </c>
       <c r="E81" t="s">
-        <v>189</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -5162,7 +4973,7 @@
         <v>6</v>
       </c>
       <c r="E82" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -5179,7 +4990,7 @@
         <v>7</v>
       </c>
       <c r="E83" t="s">
-        <v>190</v>
+        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -5196,7 +5007,7 @@
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -5213,7 +5024,7 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -5230,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -5247,7 +5058,7 @@
         <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -5264,7 +5075,7 @@
         <v>3</v>
       </c>
       <c r="E88" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -5281,7 +5092,7 @@
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -5298,7 +5109,7 @@
         <v>8</v>
       </c>
       <c r="E90" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -5315,7 +5126,7 @@
         <v>10</v>
       </c>
       <c r="E91" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -5332,7 +5143,7 @@
         <v>7</v>
       </c>
       <c r="E92" t="s">
-        <v>191</v>
+        <v>130</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -5349,7 +5160,7 @@
         <v>7</v>
       </c>
       <c r="E93" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -5366,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -5383,7 +5194,7 @@
         <v>2</v>
       </c>
       <c r="E95" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -5400,7 +5211,7 @@
         <v>3</v>
       </c>
       <c r="E96" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -5417,7 +5228,7 @@
         <v>10</v>
       </c>
       <c r="E97" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -5434,7 +5245,7 @@
         <v>5</v>
       </c>
       <c r="E98" t="s">
-        <v>192</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -5451,7 +5262,7 @@
         <v>6</v>
       </c>
       <c r="E99" t="s">
-        <v>193</v>
+        <v>132</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -5468,7 +5279,7 @@
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>194</v>
+        <v>133</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -5485,7 +5296,7 @@
         <v>6</v>
       </c>
       <c r="E101" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -5502,7 +5313,7 @@
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5519,7 +5330,7 @@
         <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5536,7 +5347,7 @@
         <v>3</v>
       </c>
       <c r="E104" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5553,7 +5364,7 @@
         <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5570,7 +5381,7 @@
         <v>5</v>
       </c>
       <c r="E106" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5587,7 +5398,7 @@
         <v>10</v>
       </c>
       <c r="E107" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5604,7 +5415,7 @@
         <v>7</v>
       </c>
       <c r="E108" t="s">
-        <v>195</v>
+        <v>134</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5621,7 +5432,7 @@
         <v>2</v>
       </c>
       <c r="E109" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5638,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5655,7 +5466,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5672,7 +5483,7 @@
         <v>3</v>
       </c>
       <c r="E112" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -5689,7 +5500,7 @@
         <v>10</v>
       </c>
       <c r="E113" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -5706,10 +5517,10 @@
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="F114" t="s">
-        <v>223</v>
+        <v>162</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -5726,7 +5537,7 @@
         <v>7</v>
       </c>
       <c r="E115" t="s">
-        <v>197</v>
+        <v>136</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -5743,10 +5554,10 @@
         <v>8</v>
       </c>
       <c r="E116" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F116" t="s">
-        <v>224</v>
+        <v>163</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -5763,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="E117" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -5780,7 +5591,7 @@
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -5797,7 +5608,7 @@
         <v>3</v>
       </c>
       <c r="E119" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -5814,7 +5625,7 @@
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -5831,7 +5642,7 @@
         <v>10</v>
       </c>
       <c r="E121" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -5848,7 +5659,7 @@
         <v>7</v>
       </c>
       <c r="E122" t="s">
-        <v>198</v>
+        <v>137</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -5865,7 +5676,7 @@
         <v>8</v>
       </c>
       <c r="E123" t="s">
-        <v>199</v>
+        <v>138</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -5882,7 +5693,7 @@
         <v>4</v>
       </c>
       <c r="E124" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -5899,7 +5710,7 @@
         <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5916,7 +5727,7 @@
         <v>2</v>
       </c>
       <c r="E126" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -5933,7 +5744,7 @@
         <v>3</v>
       </c>
       <c r="E127" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5950,7 +5761,7 @@
         <v>10</v>
       </c>
       <c r="E128" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -5967,7 +5778,7 @@
         <v>5</v>
       </c>
       <c r="E129" t="s">
-        <v>200</v>
+        <v>139</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -5984,7 +5795,7 @@
         <v>6</v>
       </c>
       <c r="E130" t="s">
-        <v>201</v>
+        <v>140</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -6001,7 +5812,7 @@
         <v>7</v>
       </c>
       <c r="E131" t="s">
-        <v>202</v>
+        <v>141</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -6018,7 +5829,7 @@
         <v>5</v>
       </c>
       <c r="E132" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -6035,7 +5846,7 @@
         <v>4</v>
       </c>
       <c r="E133" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -6052,7 +5863,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -6069,7 +5880,7 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -6086,7 +5897,7 @@
         <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -6103,7 +5914,7 @@
         <v>4</v>
       </c>
       <c r="E137" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -6120,7 +5931,7 @@
         <v>5</v>
       </c>
       <c r="E138" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -6137,7 +5948,7 @@
         <v>6</v>
       </c>
       <c r="E139" t="s">
-        <v>203</v>
+        <v>142</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -6154,7 +5965,7 @@
         <v>7</v>
       </c>
       <c r="E140" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -6171,14 +5982,14 @@
         <v>11</v>
       </c>
       <c r="E141" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
         <v>43</v>
       </c>
-      <c r="B142" t="b">
+      <c r="B142">
         <v>0</v>
       </c>
       <c r="C142">
@@ -6188,14 +5999,14 @@
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
         <v>56</v>
       </c>
-      <c r="B143" t="b">
+      <c r="B143">
         <v>0</v>
       </c>
       <c r="C143">
@@ -6205,14 +6016,14 @@
         <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
         <v>56</v>
       </c>
-      <c r="B144" t="b">
+      <c r="B144">
         <v>0</v>
       </c>
       <c r="C144">
@@ -6222,14 +6033,14 @@
         <v>2</v>
       </c>
       <c r="E144" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
         <v>56</v>
       </c>
-      <c r="B145" t="b">
+      <c r="B145">
         <v>0</v>
       </c>
       <c r="C145">
@@ -6239,14 +6050,14 @@
         <v>3</v>
       </c>
       <c r="E145" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
         <v>56</v>
       </c>
-      <c r="B146" t="b">
+      <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
@@ -6256,14 +6067,14 @@
         <v>4</v>
       </c>
       <c r="E146" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
         <v>56</v>
       </c>
-      <c r="B147" t="b">
+      <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
@@ -6273,14 +6084,14 @@
         <v>5</v>
       </c>
       <c r="E147" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
         <v>56</v>
       </c>
-      <c r="B148" t="b">
+      <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
@@ -6290,14 +6101,14 @@
         <v>10</v>
       </c>
       <c r="E148" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
         <v>56</v>
       </c>
-      <c r="B149" t="b">
+      <c r="B149">
         <v>0</v>
       </c>
       <c r="C149">
@@ -6307,14 +6118,14 @@
         <v>6</v>
       </c>
       <c r="E149" t="s">
-        <v>205</v>
+        <v>144</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
         <v>56</v>
       </c>
-      <c r="B150" t="b">
+      <c r="B150">
         <v>0</v>
       </c>
       <c r="C150">
@@ -6324,7 +6135,7 @@
         <v>8</v>
       </c>
       <c r="E150" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -6341,7 +6152,7 @@
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -6358,7 +6169,7 @@
         <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -6375,7 +6186,7 @@
         <v>3</v>
       </c>
       <c r="E153" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -6392,7 +6203,7 @@
         <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -6409,7 +6220,7 @@
         <v>4</v>
       </c>
       <c r="E155" t="s">
-        <v>206</v>
+        <v>145</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -6426,7 +6237,7 @@
         <v>6</v>
       </c>
       <c r="E156" t="s">
-        <v>207</v>
+        <v>146</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -6443,7 +6254,7 @@
         <v>7</v>
       </c>
       <c r="E157" t="s">
-        <v>208</v>
+        <v>147</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -6460,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -6477,7 +6288,7 @@
         <v>2</v>
       </c>
       <c r="E159" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -6494,7 +6305,7 @@
         <v>3</v>
       </c>
       <c r="E160" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -6511,7 +6322,7 @@
         <v>4</v>
       </c>
       <c r="E161" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -6528,7 +6339,7 @@
         <v>5</v>
       </c>
       <c r="E162" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -6545,7 +6356,7 @@
         <v>7</v>
       </c>
       <c r="E163" t="s">
-        <v>209</v>
+        <v>148</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -6562,14 +6373,14 @@
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
         <v>49</v>
       </c>
-      <c r="B165" t="b">
+      <c r="B165">
         <v>0</v>
       </c>
       <c r="C165">
@@ -6579,14 +6390,14 @@
         <v>5</v>
       </c>
       <c r="E165" t="s">
-        <v>210</v>
+        <v>149</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
         <v>45</v>
       </c>
-      <c r="B166" t="b">
+      <c r="B166">
         <v>0</v>
       </c>
       <c r="C166">
@@ -6596,14 +6407,14 @@
         <v>1</v>
       </c>
       <c r="E166" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
         <v>45</v>
       </c>
-      <c r="B167" t="b">
+      <c r="B167">
         <v>0</v>
       </c>
       <c r="C167">
@@ -6613,14 +6424,14 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
         <v>45</v>
       </c>
-      <c r="B168" t="b">
+      <c r="B168">
         <v>0</v>
       </c>
       <c r="C168">
@@ -6630,14 +6441,14 @@
         <v>3</v>
       </c>
       <c r="E168" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
         <v>45</v>
       </c>
-      <c r="B169" t="b">
+      <c r="B169">
         <v>0</v>
       </c>
       <c r="C169">
@@ -6647,14 +6458,14 @@
         <v>4</v>
       </c>
       <c r="E169" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
         <v>45</v>
       </c>
-      <c r="B170" t="b">
+      <c r="B170">
         <v>0</v>
       </c>
       <c r="C170">
@@ -6664,14 +6475,14 @@
         <v>5</v>
       </c>
       <c r="E170" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
         <v>47</v>
       </c>
-      <c r="B171" t="b">
+      <c r="B171">
         <v>0</v>
       </c>
       <c r="C171">
@@ -6681,14 +6492,14 @@
         <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
         <v>47</v>
       </c>
-      <c r="B172" t="b">
+      <c r="B172">
         <v>0</v>
       </c>
       <c r="C172">
@@ -6698,14 +6509,14 @@
         <v>2</v>
       </c>
       <c r="E172" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
         <v>47</v>
       </c>
-      <c r="B173" t="b">
+      <c r="B173">
         <v>0</v>
       </c>
       <c r="C173">
@@ -6715,14 +6526,14 @@
         <v>3</v>
       </c>
       <c r="E173" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
         <v>47</v>
       </c>
-      <c r="B174" t="b">
+      <c r="B174">
         <v>0</v>
       </c>
       <c r="C174">
@@ -6732,14 +6543,14 @@
         <v>4</v>
       </c>
       <c r="E174" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
         <v>47</v>
       </c>
-      <c r="B175" t="b">
+      <c r="B175">
         <v>0</v>
       </c>
       <c r="C175">
@@ -6749,14 +6560,14 @@
         <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
         <v>40</v>
       </c>
-      <c r="B176" t="b">
+      <c r="B176">
         <v>0</v>
       </c>
       <c r="C176">
@@ -6766,14 +6577,14 @@
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>40</v>
       </c>
-      <c r="B177" t="b">
+      <c r="B177">
         <v>0</v>
       </c>
       <c r="C177">
@@ -6783,14 +6594,14 @@
         <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>40</v>
       </c>
-      <c r="B178" t="b">
+      <c r="B178">
         <v>0</v>
       </c>
       <c r="C178">
@@ -6800,14 +6611,14 @@
         <v>3</v>
       </c>
       <c r="E178" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>40</v>
       </c>
-      <c r="B179" t="b">
+      <c r="B179">
         <v>0</v>
       </c>
       <c r="C179">
@@ -6817,17 +6628,17 @@
         <v>8</v>
       </c>
       <c r="E179" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F179" t="s">
-        <v>225</v>
+        <v>164</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>40</v>
       </c>
-      <c r="B180" t="b">
+      <c r="B180">
         <v>0</v>
       </c>
       <c r="C180">
@@ -6837,14 +6648,14 @@
         <v>10</v>
       </c>
       <c r="E180" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>40</v>
       </c>
-      <c r="B181" t="b">
+      <c r="B181">
         <v>0</v>
       </c>
       <c r="C181">
@@ -6854,14 +6665,14 @@
         <v>4</v>
       </c>
       <c r="E181" t="s">
-        <v>211</v>
+        <v>150</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>40</v>
       </c>
-      <c r="B182" t="b">
+      <c r="B182">
         <v>0</v>
       </c>
       <c r="C182">
@@ -6871,10 +6682,10 @@
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F182" t="s">
-        <v>226</v>
+        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -6891,7 +6702,7 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -6908,7 +6719,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -6925,7 +6736,7 @@
         <v>3</v>
       </c>
       <c r="E185" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -6942,7 +6753,7 @@
         <v>4</v>
       </c>
       <c r="E186" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -6959,7 +6770,7 @@
         <v>5</v>
       </c>
       <c r="E187" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -6976,7 +6787,7 @@
         <v>7</v>
       </c>
       <c r="E188" t="s">
-        <v>212</v>
+        <v>151</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -6993,14 +6804,14 @@
         <v>3</v>
       </c>
       <c r="E189" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>54</v>
       </c>
-      <c r="B190" t="b">
+      <c r="B190">
         <v>0</v>
       </c>
       <c r="C190">
@@ -7010,14 +6821,14 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
         <v>54</v>
       </c>
-      <c r="B191" t="b">
+      <c r="B191">
         <v>0</v>
       </c>
       <c r="C191">
@@ -7027,14 +6838,14 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
         <v>54</v>
       </c>
-      <c r="B192" t="b">
+      <c r="B192">
         <v>0</v>
       </c>
       <c r="C192">
@@ -7044,14 +6855,14 @@
         <v>3</v>
       </c>
       <c r="E192" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>54</v>
       </c>
-      <c r="B193" t="b">
+      <c r="B193">
         <v>0</v>
       </c>
       <c r="C193">
@@ -7061,14 +6872,14 @@
         <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>54</v>
       </c>
-      <c r="B194" t="b">
+      <c r="B194">
         <v>0</v>
       </c>
       <c r="C194">
@@ -7078,14 +6889,14 @@
         <v>5</v>
       </c>
       <c r="E194" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>57</v>
       </c>
-      <c r="B195" t="b">
+      <c r="B195">
         <v>0</v>
       </c>
       <c r="C195">
@@ -7095,14 +6906,14 @@
         <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>57</v>
       </c>
-      <c r="B196" t="b">
+      <c r="B196">
         <v>0</v>
       </c>
       <c r="C196">
@@ -7112,14 +6923,14 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>57</v>
       </c>
-      <c r="B197" t="b">
+      <c r="B197">
         <v>0</v>
       </c>
       <c r="C197">
@@ -7129,14 +6940,14 @@
         <v>3</v>
       </c>
       <c r="E197" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>57</v>
       </c>
-      <c r="B198" t="b">
+      <c r="B198">
         <v>0</v>
       </c>
       <c r="C198">
@@ -7146,14 +6957,14 @@
         <v>4</v>
       </c>
       <c r="E198" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
         <v>57</v>
       </c>
-      <c r="B199" t="b">
+      <c r="B199">
         <v>0</v>
       </c>
       <c r="C199">
@@ -7163,14 +6974,14 @@
         <v>5</v>
       </c>
       <c r="E199" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>57</v>
       </c>
-      <c r="B200" t="b">
+      <c r="B200">
         <v>0</v>
       </c>
       <c r="C200">
@@ -7180,17 +6991,17 @@
         <v>8</v>
       </c>
       <c r="E200" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F200" t="s">
-        <v>227</v>
+        <v>166</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>57</v>
       </c>
-      <c r="B201" t="b">
+      <c r="B201">
         <v>0</v>
       </c>
       <c r="C201">
@@ -7200,14 +7011,14 @@
         <v>10</v>
       </c>
       <c r="E201" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>57</v>
       </c>
-      <c r="B202" t="b">
+      <c r="B202">
         <v>0</v>
       </c>
       <c r="C202">
@@ -7217,17 +7028,17 @@
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F202" t="s">
-        <v>227</v>
+        <v>166</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>58</v>
       </c>
-      <c r="B203" t="b">
+      <c r="B203">
         <v>0</v>
       </c>
       <c r="C203">
@@ -7237,14 +7048,14 @@
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>58</v>
       </c>
-      <c r="B204" t="b">
+      <c r="B204">
         <v>0</v>
       </c>
       <c r="C204">
@@ -7254,14 +7065,14 @@
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>58</v>
       </c>
-      <c r="B205" t="b">
+      <c r="B205">
         <v>0</v>
       </c>
       <c r="C205">
@@ -7271,14 +7082,14 @@
         <v>3</v>
       </c>
       <c r="E205" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>60</v>
       </c>
-      <c r="B206" t="b">
+      <c r="B206">
         <v>0</v>
       </c>
       <c r="C206">
@@ -7288,14 +7099,14 @@
         <v>1</v>
       </c>
       <c r="E206" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>60</v>
       </c>
-      <c r="B207" t="b">
+      <c r="B207">
         <v>0</v>
       </c>
       <c r="C207">
@@ -7305,14 +7116,14 @@
         <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>60</v>
       </c>
-      <c r="B208" t="b">
+      <c r="B208">
         <v>0</v>
       </c>
       <c r="C208">
@@ -7322,14 +7133,14 @@
         <v>3</v>
       </c>
       <c r="E208" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
         <v>60</v>
       </c>
-      <c r="B209" t="b">
+      <c r="B209">
         <v>0</v>
       </c>
       <c r="C209">
@@ -7339,14 +7150,14 @@
         <v>8</v>
       </c>
       <c r="E209" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
         <v>60</v>
       </c>
-      <c r="B210" t="b">
+      <c r="B210">
         <v>0</v>
       </c>
       <c r="C210">
@@ -7356,14 +7167,14 @@
         <v>9</v>
       </c>
       <c r="E210" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
         <v>61</v>
       </c>
-      <c r="B211" t="b">
+      <c r="B211">
         <v>0</v>
       </c>
       <c r="C211">
@@ -7373,14 +7184,14 @@
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
         <v>61</v>
       </c>
-      <c r="B212" t="b">
+      <c r="B212">
         <v>0</v>
       </c>
       <c r="C212">
@@ -7390,14 +7201,14 @@
         <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
         <v>61</v>
       </c>
-      <c r="B213" t="b">
+      <c r="B213">
         <v>0</v>
       </c>
       <c r="C213">
@@ -7407,14 +7218,14 @@
         <v>3</v>
       </c>
       <c r="E213" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
         <v>64</v>
       </c>
-      <c r="B214" t="b">
+      <c r="B214">
         <v>0</v>
       </c>
       <c r="C214">
@@ -7424,14 +7235,14 @@
         <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
         <v>64</v>
       </c>
-      <c r="B215" t="b">
+      <c r="B215">
         <v>0</v>
       </c>
       <c r="C215">
@@ -7441,14 +7252,14 @@
         <v>2</v>
       </c>
       <c r="E215" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
         <v>64</v>
       </c>
-      <c r="B216" t="b">
+      <c r="B216">
         <v>0</v>
       </c>
       <c r="C216">
@@ -7458,14 +7269,14 @@
         <v>3</v>
       </c>
       <c r="E216" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
         <v>64</v>
       </c>
-      <c r="B217" t="b">
+      <c r="B217">
         <v>0</v>
       </c>
       <c r="C217">
@@ -7475,17 +7286,17 @@
         <v>8</v>
       </c>
       <c r="E217" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F217" t="s">
-        <v>228</v>
+        <v>167</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
         <v>64</v>
       </c>
-      <c r="B218" t="b">
+      <c r="B218">
         <v>0</v>
       </c>
       <c r="C218">
@@ -7495,17 +7306,17 @@
         <v>9</v>
       </c>
       <c r="E218" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="F218" t="s">
-        <v>228</v>
+        <v>167</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
         <v>68</v>
       </c>
-      <c r="B219" t="b">
+      <c r="B219">
         <v>0</v>
       </c>
       <c r="C219">
@@ -7515,14 +7326,14 @@
         <v>1</v>
       </c>
       <c r="E219" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
         <v>68</v>
       </c>
-      <c r="B220" t="b">
+      <c r="B220">
         <v>0</v>
       </c>
       <c r="C220">
@@ -7532,14 +7343,14 @@
         <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
         <v>68</v>
       </c>
-      <c r="B221" t="b">
+      <c r="B221">
         <v>0</v>
       </c>
       <c r="C221">
@@ -7549,14 +7360,14 @@
         <v>3</v>
       </c>
       <c r="E221" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
         <v>68</v>
       </c>
-      <c r="B222" t="b">
+      <c r="B222">
         <v>0</v>
       </c>
       <c r="C222">
@@ -7566,14 +7377,14 @@
         <v>4</v>
       </c>
       <c r="E222" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
         <v>68</v>
       </c>
-      <c r="B223" t="b">
+      <c r="B223">
         <v>0</v>
       </c>
       <c r="C223">
@@ -7583,7 +7394,7 @@
         <v>5</v>
       </c>
       <c r="E223" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -7600,7 +7411,7 @@
         <v>1</v>
       </c>
       <c r="E224" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -7617,7 +7428,7 @@
         <v>2</v>
       </c>
       <c r="E225" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -7634,7 +7445,7 @@
         <v>3</v>
       </c>
       <c r="E226" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -7651,7 +7462,7 @@
         <v>4</v>
       </c>
       <c r="E227" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -7668,7 +7479,7 @@
         <v>5</v>
       </c>
       <c r="E228" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -7685,7 +7496,7 @@
         <v>10</v>
       </c>
       <c r="E229" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -7702,7 +7513,7 @@
         <v>7</v>
       </c>
       <c r="E230" t="s">
-        <v>213</v>
+        <v>152</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -7719,14 +7530,14 @@
         <v>10</v>
       </c>
       <c r="E231" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" t="s">
         <v>71</v>
       </c>
-      <c r="B232" t="b">
+      <c r="B232">
         <v>0</v>
       </c>
       <c r="C232">
@@ -7736,14 +7547,14 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" t="s">
         <v>71</v>
       </c>
-      <c r="B233" t="b">
+      <c r="B233">
         <v>0</v>
       </c>
       <c r="C233">
@@ -7753,14 +7564,14 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" t="s">
         <v>71</v>
       </c>
-      <c r="B234" t="b">
+      <c r="B234">
         <v>0</v>
       </c>
       <c r="C234">
@@ -7770,14 +7581,14 @@
         <v>3</v>
       </c>
       <c r="E234" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" t="s">
         <v>71</v>
       </c>
-      <c r="B235" t="b">
+      <c r="B235">
         <v>0</v>
       </c>
       <c r="C235">
@@ -7787,14 +7598,14 @@
         <v>4</v>
       </c>
       <c r="E235" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
         <v>71</v>
       </c>
-      <c r="B236" t="b">
+      <c r="B236">
         <v>0</v>
       </c>
       <c r="C236">
@@ -7804,14 +7615,14 @@
         <v>5</v>
       </c>
       <c r="E236" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" t="s">
         <v>52</v>
       </c>
-      <c r="B237" t="b">
+      <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
@@ -7821,14 +7632,14 @@
         <v>1</v>
       </c>
       <c r="E237" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
         <v>52</v>
       </c>
-      <c r="B238" t="b">
+      <c r="B238">
         <v>0</v>
       </c>
       <c r="C238">
@@ -7838,14 +7649,14 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" t="s">
         <v>52</v>
       </c>
-      <c r="B239" t="b">
+      <c r="B239">
         <v>0</v>
       </c>
       <c r="C239">
@@ -7855,14 +7666,14 @@
         <v>3</v>
       </c>
       <c r="E239" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
         <v>52</v>
       </c>
-      <c r="B240" t="b">
+      <c r="B240">
         <v>0</v>
       </c>
       <c r="C240">
@@ -7872,14 +7683,14 @@
         <v>10</v>
       </c>
       <c r="E240" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
         <v>75</v>
       </c>
-      <c r="B241" t="b">
+      <c r="B241">
         <v>0</v>
       </c>
       <c r="C241">
@@ -7889,14 +7700,14 @@
         <v>1</v>
       </c>
       <c r="E241" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" t="s">
         <v>75</v>
       </c>
-      <c r="B242" t="b">
+      <c r="B242">
         <v>0</v>
       </c>
       <c r="C242">
@@ -7906,14 +7717,14 @@
         <v>2</v>
       </c>
       <c r="E242" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" t="s">
         <v>75</v>
       </c>
-      <c r="B243" t="b">
+      <c r="B243">
         <v>0</v>
       </c>
       <c r="C243">
@@ -7923,14 +7734,14 @@
         <v>3</v>
       </c>
       <c r="E243" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" t="s">
         <v>75</v>
       </c>
-      <c r="B244" t="b">
+      <c r="B244">
         <v>0</v>
       </c>
       <c r="C244">
@@ -7940,14 +7751,14 @@
         <v>4</v>
       </c>
       <c r="E244" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" t="s">
         <v>75</v>
       </c>
-      <c r="B245" t="b">
+      <c r="B245">
         <v>0</v>
       </c>
       <c r="C245">
@@ -7957,7 +7768,7 @@
         <v>5</v>
       </c>
       <c r="E245" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -7971,92 +7782,92 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E1" t="s">
-        <v>232</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
-        <v>233</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
-        <v>234</v>
-      </c>
-      <c r="J1" t="s">
-        <v>235</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
-        <v>236</v>
-      </c>
-      <c r="N1" t="s">
-        <v>237</v>
-      </c>
-      <c r="O1" t="s">
-        <v>238</v>
-      </c>
-      <c r="P1" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>240</v>
-      </c>
-      <c r="R1" t="s">
-        <v>241</v>
-      </c>
-      <c r="S1" t="s">
-        <v>242</v>
-      </c>
-      <c r="T1" t="s">
-        <v>243</v>
-      </c>
-      <c r="U1" t="s">
-        <v>244</v>
-      </c>
-      <c r="V1" t="s">
-        <v>245</v>
-      </c>
-      <c r="W1" t="s">
-        <v>246</v>
-      </c>
-      <c r="X1" t="s">
-        <v>247</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>248</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>249</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>251</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>252</v>
+      <c r="M1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:29">
@@ -8064,28 +7875,28 @@
         <v>3810267428</v>
       </c>
       <c r="C2" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E2" s="1">
+        <v>194</v>
+      </c>
+      <c r="E2" s="2">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
-        <v>258</v>
-      </c>
-      <c r="G2" s="1">
+        <v>197</v>
+      </c>
+      <c r="G2" s="2">
         <v>45492</v>
       </c>
-      <c r="H2" t="s">
-        <v>36</v>
+      <c r="H2">
+        <v>3044000</v>
       </c>
       <c r="I2">
         <v>198</v>
       </c>
       <c r="J2" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K2" t="s">
         <v>58</v>
@@ -8093,38 +7904,38 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45491</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="2">
         <v>45528</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="2">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
-        <v>261</v>
-      </c>
-      <c r="V2" t="s">
-        <v>263</v>
+        <v>200</v>
+      </c>
+      <c r="V2">
+        <v>313240015920</v>
       </c>
       <c r="W2" t="s">
         <v>22</v>
       </c>
       <c r="X2" t="s">
-        <v>265</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>269</v>
+        <v>202</v>
+      </c>
+      <c r="Y2">
+        <v>3810496453</v>
       </c>
       <c r="Z2" t="s">
-        <v>282</v>
+        <v>206</v>
       </c>
       <c r="AA2" t="s">
-        <v>285</v>
+        <v>209</v>
       </c>
       <c r="AB2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -8132,28 +7943,28 @@
         <v>3810269967</v>
       </c>
       <c r="C3" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E3" s="1">
+        <v>195</v>
+      </c>
+      <c r="E3" s="2">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
-        <v>258</v>
-      </c>
-      <c r="G3" s="1">
+        <v>197</v>
+      </c>
+      <c r="G3" s="2">
         <v>45631</v>
       </c>
-      <c r="H3" t="s">
-        <v>36</v>
+      <c r="H3">
+        <v>3044000</v>
       </c>
       <c r="I3">
         <v>198</v>
       </c>
       <c r="J3" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K3" t="s">
         <v>75</v>
@@ -8161,35 +7972,35 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>45628</v>
       </c>
-      <c r="R3" s="1">
+      <c r="R3" s="2">
         <v>45632</v>
       </c>
-      <c r="S3" s="1">
+      <c r="S3" s="2">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W3" t="s">
         <v>22</v>
       </c>
       <c r="X3" t="s">
-        <v>265</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>270</v>
+        <v>202</v>
+      </c>
+      <c r="Y3">
+        <v>3810499719</v>
       </c>
       <c r="Z3" t="s">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="AA3" t="s">
-        <v>286</v>
+        <v>210</v>
       </c>
       <c r="AB3" t="s">
-        <v>291</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -8197,28 +8008,28 @@
         <v>3810271134</v>
       </c>
       <c r="C4" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D4" t="s">
-        <v>256</v>
-      </c>
-      <c r="E4" s="1">
+        <v>195</v>
+      </c>
+      <c r="E4" s="2">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
-        <v>258</v>
-      </c>
-      <c r="G4" s="1">
+        <v>197</v>
+      </c>
+      <c r="G4" s="2">
         <v>45716</v>
       </c>
-      <c r="H4" t="s">
-        <v>36</v>
+      <c r="H4">
+        <v>3044000</v>
       </c>
       <c r="I4">
         <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K4" t="s">
         <v>54</v>
@@ -8226,35 +8037,35 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45716</v>
       </c>
-      <c r="R4" s="1">
+      <c r="R4" s="2">
         <v>45722</v>
       </c>
-      <c r="S4" s="1">
+      <c r="S4" s="2">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W4" t="s">
         <v>22</v>
       </c>
       <c r="X4" t="s">
-        <v>265</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>271</v>
+        <v>202</v>
+      </c>
+      <c r="Y4">
+        <v>3810500784</v>
       </c>
       <c r="Z4" t="s">
-        <v>282</v>
+        <v>206</v>
       </c>
       <c r="AA4" t="s">
-        <v>287</v>
+        <v>211</v>
       </c>
       <c r="AB4" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -8262,28 +8073,28 @@
         <v>3810271161</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D5" t="s">
-        <v>256</v>
-      </c>
-      <c r="E5" s="1">
+        <v>195</v>
+      </c>
+      <c r="E5" s="2">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
-        <v>258</v>
-      </c>
-      <c r="G5" s="1">
+        <v>197</v>
+      </c>
+      <c r="G5" s="2">
         <v>45728</v>
       </c>
-      <c r="H5" t="s">
-        <v>36</v>
+      <c r="H5">
+        <v>3044000</v>
       </c>
       <c r="I5">
         <v>198</v>
       </c>
       <c r="J5" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K5" t="s">
         <v>44</v>
@@ -8291,35 +8102,35 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45722</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R5" s="2">
         <v>45782</v>
       </c>
-      <c r="S5" s="1">
+      <c r="S5" s="2">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W5" t="s">
         <v>22</v>
       </c>
       <c r="X5" t="s">
-        <v>265</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>272</v>
+        <v>202</v>
+      </c>
+      <c r="Y5">
+        <v>3810501279</v>
       </c>
       <c r="Z5" t="s">
-        <v>282</v>
+        <v>206</v>
       </c>
       <c r="AA5" t="s">
-        <v>285</v>
+        <v>209</v>
       </c>
       <c r="AB5" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -8330,28 +8141,28 @@
         <v>3810271161</v>
       </c>
       <c r="C6" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
-      </c>
-      <c r="E6" s="1">
+        <v>195</v>
+      </c>
+      <c r="E6" s="2">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
-        <v>258</v>
-      </c>
-      <c r="G6" s="1">
+        <v>197</v>
+      </c>
+      <c r="G6" s="2">
         <v>45755</v>
       </c>
-      <c r="H6" t="s">
-        <v>36</v>
+      <c r="H6">
+        <v>3044000</v>
       </c>
       <c r="I6">
         <v>198</v>
       </c>
       <c r="J6" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K6" t="s">
         <v>44</v>
@@ -8359,35 +8170,35 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45728</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R6" s="2">
         <v>45734</v>
       </c>
-      <c r="S6" s="1">
+      <c r="S6" s="2">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W6" t="s">
         <v>22</v>
       </c>
       <c r="X6" t="s">
-        <v>266</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>273</v>
+        <v>203</v>
+      </c>
+      <c r="Y6">
+        <v>3810502614</v>
       </c>
       <c r="Z6" t="s">
         <v>22</v>
       </c>
       <c r="AA6" t="s">
-        <v>265</v>
+        <v>202</v>
       </c>
       <c r="AB6" t="s">
-        <v>292</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -8398,25 +8209,25 @@
         <v>3810272114</v>
       </c>
       <c r="C7" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E7" s="1">
+        <v>196</v>
+      </c>
+      <c r="E7" s="2">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
-        <v>258</v>
-      </c>
-      <c r="H7" t="s">
-        <v>36</v>
+        <v>197</v>
+      </c>
+      <c r="H7">
+        <v>3044000</v>
       </c>
       <c r="I7">
         <v>198</v>
       </c>
       <c r="J7" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K7" t="s">
         <v>44</v>
@@ -8424,32 +8235,32 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45772</v>
       </c>
-      <c r="R7" s="1">
+      <c r="R7" s="2">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W7" t="s">
         <v>22</v>
       </c>
       <c r="X7" t="s">
-        <v>266</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>274</v>
+        <v>203</v>
+      </c>
+      <c r="Y7">
+        <v>3810504268</v>
       </c>
       <c r="Z7" t="s">
         <v>22</v>
       </c>
       <c r="AA7" t="s">
-        <v>288</v>
+        <v>212</v>
       </c>
       <c r="AB7" t="s">
-        <v>292</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -8460,25 +8271,25 @@
         <v>3810272114</v>
       </c>
       <c r="C8" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
-        <v>257</v>
-      </c>
-      <c r="E8" s="1">
+        <v>196</v>
+      </c>
+      <c r="E8" s="2">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H8" t="s">
-        <v>36</v>
+        <v>197</v>
+      </c>
+      <c r="H8">
+        <v>3044000</v>
       </c>
       <c r="I8">
         <v>198</v>
       </c>
       <c r="J8" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K8" t="s">
         <v>44</v>
@@ -8486,32 +8297,32 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>45762</v>
       </c>
-      <c r="R8" s="1">
+      <c r="R8" s="2">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W8" t="s">
         <v>22</v>
       </c>
       <c r="X8" t="s">
-        <v>266</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>275</v>
+        <v>203</v>
+      </c>
+      <c r="Y8">
+        <v>3810504159</v>
       </c>
       <c r="Z8" t="s">
         <v>22</v>
       </c>
       <c r="AA8" t="s">
-        <v>267</v>
+        <v>204</v>
       </c>
       <c r="AB8" t="s">
-        <v>293</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -8522,25 +8333,25 @@
         <v>3810272114</v>
       </c>
       <c r="C9" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E9" s="1">
+        <v>196</v>
+      </c>
+      <c r="E9" s="2">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
-        <v>258</v>
-      </c>
-      <c r="H9" t="s">
-        <v>36</v>
+        <v>197</v>
+      </c>
+      <c r="H9">
+        <v>3044000</v>
       </c>
       <c r="I9">
         <v>198</v>
       </c>
       <c r="J9" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K9" t="s">
         <v>44</v>
@@ -8548,32 +8359,32 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45763</v>
       </c>
-      <c r="R9" s="1">
+      <c r="R9" s="2">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W9" t="s">
         <v>22</v>
       </c>
       <c r="X9" t="s">
-        <v>266</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>276</v>
+        <v>203</v>
+      </c>
+      <c r="Y9">
+        <v>3810504182</v>
       </c>
       <c r="Z9" t="s">
         <v>22</v>
       </c>
       <c r="AA9" t="s">
-        <v>267</v>
+        <v>204</v>
       </c>
       <c r="AB9" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -8584,28 +8395,28 @@
         <v>3810271161</v>
       </c>
       <c r="C10" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="D10" t="s">
-        <v>256</v>
-      </c>
-      <c r="E10" s="1">
+        <v>195</v>
+      </c>
+      <c r="E10" s="2">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
-        <v>258</v>
-      </c>
-      <c r="G10" s="1">
+        <v>197</v>
+      </c>
+      <c r="G10" s="2">
         <v>45755</v>
       </c>
-      <c r="H10" t="s">
-        <v>36</v>
+      <c r="H10">
+        <v>3044000</v>
       </c>
       <c r="I10">
         <v>198</v>
       </c>
       <c r="J10" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K10" t="s">
         <v>44</v>
@@ -8613,35 +8424,35 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45754</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R10" s="2">
         <v>45849</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S10" s="2">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W10" t="s">
         <v>22</v>
       </c>
       <c r="X10" t="s">
-        <v>267</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>277</v>
+        <v>204</v>
+      </c>
+      <c r="Y10">
+        <v>3810503807</v>
       </c>
       <c r="Z10" t="s">
         <v>22</v>
       </c>
       <c r="AA10" t="s">
-        <v>288</v>
+        <v>212</v>
       </c>
       <c r="AB10" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -8649,64 +8460,64 @@
         <v>3810255268</v>
       </c>
       <c r="C11" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="D11" t="s">
-        <v>256</v>
-      </c>
-      <c r="E11" s="1">
+        <v>195</v>
+      </c>
+      <c r="E11" s="2">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
-        <v>258</v>
-      </c>
-      <c r="G11" s="1">
+        <v>197</v>
+      </c>
+      <c r="G11" s="2">
         <v>44973</v>
       </c>
-      <c r="H11" t="s">
-        <v>36</v>
+      <c r="H11">
+        <v>3044000</v>
       </c>
       <c r="I11">
         <v>198</v>
       </c>
       <c r="J11" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K11" t="s">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44973</v>
       </c>
-      <c r="R11" s="1">
+      <c r="R11" s="2">
         <v>45687</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S11" s="2">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W11" t="s">
         <v>22</v>
       </c>
       <c r="X11" t="s">
-        <v>268</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>278</v>
+        <v>205</v>
+      </c>
+      <c r="Y11">
+        <v>3810481813</v>
       </c>
       <c r="Z11" t="s">
         <v>22</v>
       </c>
       <c r="AA11" t="s">
-        <v>265</v>
+        <v>202</v>
       </c>
       <c r="AB11" t="s">
-        <v>296</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -8714,28 +8525,28 @@
         <v>3810264674</v>
       </c>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
-        <v>256</v>
-      </c>
-      <c r="E12" s="1">
+        <v>195</v>
+      </c>
+      <c r="E12" s="2">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
-        <v>258</v>
-      </c>
-      <c r="G12" s="1">
+        <v>197</v>
+      </c>
+      <c r="G12" s="2">
         <v>45358</v>
       </c>
-      <c r="H12" t="s">
-        <v>36</v>
+      <c r="H12">
+        <v>3044000</v>
       </c>
       <c r="I12">
         <v>198</v>
       </c>
       <c r="J12" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K12" t="s">
         <v>68</v>
@@ -8743,35 +8554,35 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45358</v>
       </c>
-      <c r="R12" s="1">
+      <c r="R12" s="2">
         <v>45517</v>
       </c>
-      <c r="S12" s="1">
+      <c r="S12" s="2">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W12" t="s">
         <v>22</v>
       </c>
       <c r="X12" t="s">
-        <v>268</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>279</v>
+        <v>205</v>
+      </c>
+      <c r="Y12">
+        <v>3810492521</v>
       </c>
       <c r="Z12" t="s">
-        <v>284</v>
+        <v>208</v>
       </c>
       <c r="AA12" t="s">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="AB12" t="s">
-        <v>297</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -8779,28 +8590,28 @@
         <v>3810268863</v>
       </c>
       <c r="C13" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="D13" t="s">
-        <v>256</v>
-      </c>
-      <c r="E13" s="1">
+        <v>195</v>
+      </c>
+      <c r="E13" s="2">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
-        <v>258</v>
-      </c>
-      <c r="G13" s="1">
+        <v>197</v>
+      </c>
+      <c r="G13" s="2">
         <v>45573</v>
       </c>
-      <c r="H13" t="s">
-        <v>36</v>
+      <c r="H13">
+        <v>3044000</v>
       </c>
       <c r="I13">
         <v>198</v>
       </c>
       <c r="J13" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K13" t="s">
         <v>55</v>
@@ -8808,38 +8619,38 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45572</v>
       </c>
-      <c r="R13" s="1">
+      <c r="R13" s="2">
         <v>45572</v>
       </c>
-      <c r="S13" s="1">
+      <c r="S13" s="2">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
-        <v>261</v>
-      </c>
-      <c r="V13" t="s">
-        <v>264</v>
+        <v>200</v>
+      </c>
+      <c r="V13">
+        <v>313240016031</v>
       </c>
       <c r="W13" t="s">
         <v>22</v>
       </c>
       <c r="X13" t="s">
-        <v>268</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>280</v>
+        <v>205</v>
+      </c>
+      <c r="Y13">
+        <v>3810499557</v>
       </c>
       <c r="Z13" t="s">
         <v>22</v>
       </c>
       <c r="AA13" t="s">
-        <v>265</v>
+        <v>202</v>
       </c>
       <c r="AB13" t="s">
-        <v>298</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -8847,28 +8658,28 @@
         <v>3810271550</v>
       </c>
       <c r="C14" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="D14" t="s">
-        <v>256</v>
-      </c>
-      <c r="E14" s="1">
+        <v>195</v>
+      </c>
+      <c r="E14" s="2">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
-        <v>258</v>
-      </c>
-      <c r="G14" s="1">
+        <v>197</v>
+      </c>
+      <c r="G14" s="2">
         <v>45747</v>
       </c>
-      <c r="H14" t="s">
-        <v>36</v>
+      <c r="H14">
+        <v>3044000</v>
       </c>
       <c r="I14">
         <v>198</v>
       </c>
       <c r="J14" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="K14" t="s">
         <v>53</v>
@@ -8876,35 +8687,35 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>45736</v>
       </c>
-      <c r="R14" s="1">
+      <c r="R14" s="2">
         <v>46101</v>
       </c>
-      <c r="S14" s="1">
+      <c r="S14" s="2">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="W14" t="s">
         <v>22</v>
       </c>
       <c r="X14" t="s">
-        <v>268</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>281</v>
+        <v>205</v>
+      </c>
+      <c r="Y14">
+        <v>3810499086</v>
       </c>
       <c r="Z14" t="s">
         <v>22</v>
       </c>
       <c r="AA14" t="s">
-        <v>265</v>
+        <v>202</v>
       </c>
       <c r="AB14" t="s">
-        <v>299</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -8918,91 +8729,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E2" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I2" t="s">
-        <v>314</v>
+        <v>238</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K2">
         <v>797.33</v>
@@ -9016,40 +8827,40 @@
       <c r="N2">
         <v>4000</v>
       </c>
-      <c r="O2" t="s">
-        <v>102</v>
-      </c>
-      <c r="P2" s="1">
+      <c r="O2">
+        <v>2709</v>
+      </c>
+      <c r="P2" s="2">
         <v>45490</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45015</v>
       </c>
-      <c r="R2" t="s">
-        <v>361</v>
+      <c r="R2">
+        <v>3130006005</v>
       </c>
       <c r="S2" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>301</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E3" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I3" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K3">
         <v>1001.83</v>
@@ -9063,40 +8874,40 @@
       <c r="N3">
         <v>4000</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3">
+        <v>2703</v>
+      </c>
+      <c r="P3" s="2">
+        <v>45618</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>45614</v>
+      </c>
+      <c r="R3">
+        <v>6890000562</v>
+      </c>
+      <c r="S3" t="s">
         <v>81</v>
-      </c>
-      <c r="P3" s="1">
-        <v>45618</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>45614</v>
-      </c>
-      <c r="R3" t="s">
-        <v>362</v>
-      </c>
-      <c r="S3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E4" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I4" t="s">
-        <v>316</v>
+        <v>240</v>
       </c>
       <c r="J4" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K4">
         <v>2813.92</v>
@@ -9110,40 +8921,40 @@
       <c r="N4">
         <v>4000</v>
       </c>
-      <c r="O4" t="s">
-        <v>97</v>
-      </c>
-      <c r="P4" s="1">
+      <c r="O4">
+        <v>2739</v>
+      </c>
+      <c r="P4" s="2">
         <v>45539</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45539</v>
       </c>
-      <c r="R4" t="s">
-        <v>363</v>
+      <c r="R4">
+        <v>3040075245</v>
       </c>
       <c r="S4" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E5" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I5" t="s">
-        <v>317</v>
+        <v>241</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K5">
         <v>1258.5</v>
@@ -9157,40 +8968,40 @@
       <c r="N5">
         <v>4000</v>
       </c>
-      <c r="O5" t="s">
-        <v>98</v>
-      </c>
-      <c r="P5" s="1">
+      <c r="O5">
+        <v>2722</v>
+      </c>
+      <c r="P5" s="2">
         <v>45567</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45490</v>
       </c>
-      <c r="R5" t="s">
-        <v>364</v>
+      <c r="R5">
+        <v>3290007931</v>
       </c>
       <c r="S5" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E6" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I6" t="s">
-        <v>318</v>
+        <v>242</v>
       </c>
       <c r="J6" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K6">
         <v>708.33</v>
@@ -9204,40 +9015,40 @@
       <c r="N6">
         <v>4000</v>
       </c>
-      <c r="O6" t="s">
-        <v>95</v>
-      </c>
-      <c r="P6" s="1">
+      <c r="O6">
+        <v>2741</v>
+      </c>
+      <c r="P6" s="2">
         <v>45568</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45526</v>
       </c>
-      <c r="R6" t="s">
-        <v>365</v>
+      <c r="R6">
+        <v>7090002248</v>
       </c>
       <c r="S6" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E7" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I7" t="s">
-        <v>319</v>
+        <v>243</v>
       </c>
       <c r="J7" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K7">
         <v>133.42</v>
@@ -9251,40 +9062,40 @@
       <c r="N7">
         <v>4000</v>
       </c>
-      <c r="O7" t="s">
-        <v>83</v>
-      </c>
-      <c r="P7" s="1">
+      <c r="O7">
+        <v>2728</v>
+      </c>
+      <c r="P7" s="2">
         <v>45831</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45352</v>
       </c>
-      <c r="R7" t="s">
-        <v>366</v>
+      <c r="R7">
+        <v>3130006789</v>
       </c>
       <c r="S7" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E8" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I8" t="s">
-        <v>320</v>
+        <v>244</v>
       </c>
       <c r="J8" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K8">
         <v>224.08</v>
@@ -9298,40 +9109,40 @@
       <c r="N8">
         <v>4000</v>
       </c>
-      <c r="O8" t="s">
-        <v>103</v>
-      </c>
-      <c r="P8" s="1">
+      <c r="O8">
+        <v>2720</v>
+      </c>
+      <c r="P8" s="2">
         <v>45601</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>44704</v>
       </c>
-      <c r="R8" t="s">
-        <v>367</v>
+      <c r="R8">
+        <v>7090002894</v>
       </c>
       <c r="S8" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E9" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I9" t="s">
-        <v>321</v>
+        <v>245</v>
       </c>
       <c r="J9" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K9">
         <v>783.42</v>
@@ -9345,40 +9156,40 @@
       <c r="N9">
         <v>4000</v>
       </c>
-      <c r="O9" t="s">
-        <v>92</v>
-      </c>
-      <c r="P9" s="1">
+      <c r="O9">
+        <v>2736</v>
+      </c>
+      <c r="P9" s="2">
         <v>45631</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45628</v>
       </c>
-      <c r="R9" t="s">
-        <v>368</v>
+      <c r="R9">
+        <v>3130005796</v>
       </c>
       <c r="S9" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>306</v>
+        <v>230</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E10" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I10" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
       <c r="J10" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K10">
         <v>2718.58</v>
@@ -9392,40 +9203,40 @@
       <c r="N10">
         <v>4000</v>
       </c>
-      <c r="O10" t="s">
-        <v>89</v>
-      </c>
-      <c r="P10" s="1">
+      <c r="O10">
+        <v>2727</v>
+      </c>
+      <c r="P10" s="2">
         <v>43902</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>43549</v>
       </c>
-      <c r="R10" t="s">
-        <v>369</v>
+      <c r="R10">
+        <v>7100002436</v>
       </c>
       <c r="S10" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>208</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E11" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I11" t="s">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c r="J11" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K11">
         <v>3603.17</v>
@@ -9439,40 +9250,40 @@
       <c r="N11">
         <v>4000</v>
       </c>
-      <c r="O11" t="s">
-        <v>99</v>
-      </c>
-      <c r="P11" s="1">
+      <c r="O11">
+        <v>2724</v>
+      </c>
+      <c r="P11" s="2">
         <v>44736</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44735</v>
       </c>
-      <c r="R11" t="s">
-        <v>370</v>
+      <c r="R11">
+        <v>3040057779</v>
       </c>
       <c r="S11" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E12" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I12" t="s">
-        <v>324</v>
+        <v>248</v>
       </c>
       <c r="J12" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K12">
         <v>2298.67</v>
@@ -9486,40 +9297,40 @@
       <c r="N12">
         <v>4000</v>
       </c>
-      <c r="O12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P12" s="1">
+      <c r="O12">
+        <v>2719</v>
+      </c>
+      <c r="P12" s="2">
         <v>45776</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45776</v>
       </c>
-      <c r="R12" t="s">
-        <v>371</v>
+      <c r="R12">
+        <v>3040073019</v>
       </c>
       <c r="S12" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>307</v>
+        <v>231</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E13" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I13" t="s">
-        <v>325</v>
+        <v>249</v>
       </c>
       <c r="J13" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K13">
         <v>2132.08</v>
@@ -9533,20 +9344,20 @@
       <c r="N13">
         <v>4000</v>
       </c>
-      <c r="O13" t="s">
-        <v>80</v>
-      </c>
-      <c r="P13" s="1">
+      <c r="O13">
+        <v>2702</v>
+      </c>
+      <c r="P13" s="2">
         <v>45772</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45600</v>
       </c>
-      <c r="R13" t="s">
-        <v>372</v>
+      <c r="R13">
+        <v>3040090256</v>
       </c>
       <c r="S13" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -9557,16 +9368,16 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E14" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I14" t="s">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="J14" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K14">
         <v>1013.92</v>
@@ -9580,40 +9391,40 @@
       <c r="N14">
         <v>4000</v>
       </c>
-      <c r="O14" t="s">
-        <v>100</v>
-      </c>
-      <c r="P14" s="1">
+      <c r="O14">
+        <v>2723</v>
+      </c>
+      <c r="P14" s="2">
         <v>45000</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>44630</v>
       </c>
-      <c r="R14" t="s">
-        <v>373</v>
+      <c r="R14">
+        <v>7090002718</v>
       </c>
       <c r="S14" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E15" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I15" t="s">
-        <v>327</v>
+        <v>251</v>
       </c>
       <c r="J15" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K15">
         <v>209.92</v>
@@ -9627,34 +9438,34 @@
       <c r="N15">
         <v>4000</v>
       </c>
-      <c r="O15" t="s">
-        <v>94</v>
-      </c>
-      <c r="P15" s="1">
+      <c r="O15">
+        <v>2721</v>
+      </c>
+      <c r="P15" s="2">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E16" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I16" t="s">
-        <v>328</v>
+        <v>252</v>
       </c>
       <c r="J16" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K16">
         <v>49.33</v>
@@ -9668,34 +9479,34 @@
       <c r="N16">
         <v>4000</v>
       </c>
-      <c r="O16" t="s">
-        <v>90</v>
-      </c>
-      <c r="P16" s="1">
+      <c r="O16">
+        <v>2738</v>
+      </c>
+      <c r="P16" s="2">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E17" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I17" t="s">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="J17" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K17">
         <v>923.83</v>
@@ -9709,40 +9520,40 @@
       <c r="N17">
         <v>4000</v>
       </c>
-      <c r="O17" t="s">
-        <v>93</v>
-      </c>
-      <c r="P17" s="1">
+      <c r="O17">
+        <v>2731</v>
+      </c>
+      <c r="P17" s="2">
         <v>45371</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45026</v>
       </c>
-      <c r="R17" t="s">
-        <v>374</v>
+      <c r="R17">
+        <v>3040077697</v>
       </c>
       <c r="S17" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E18" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I18" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="J18" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K18">
         <v>112.33</v>
@@ -9756,40 +9567,40 @@
       <c r="N18">
         <v>4000</v>
       </c>
-      <c r="O18" t="s">
-        <v>91</v>
-      </c>
-      <c r="P18" s="1">
+      <c r="O18">
+        <v>2737</v>
+      </c>
+      <c r="P18" s="2">
         <v>46001</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>45371</v>
       </c>
-      <c r="R18" t="s">
-        <v>375</v>
+      <c r="R18">
+        <v>3960004903</v>
       </c>
       <c r="S18" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E19" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I19" t="s">
-        <v>331</v>
+        <v>255</v>
       </c>
       <c r="J19" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K19">
         <v>598</v>
@@ -9803,20 +9614,20 @@
       <c r="N19">
         <v>4000</v>
       </c>
-      <c r="O19" t="s">
-        <v>104</v>
-      </c>
-      <c r="P19" s="1">
+      <c r="O19">
+        <v>2729</v>
+      </c>
+      <c r="P19" s="2">
         <v>45436</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>45294</v>
       </c>
-      <c r="R19" t="s">
-        <v>376</v>
+      <c r="R19">
+        <v>3130006599</v>
       </c>
       <c r="S19" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -9827,16 +9638,16 @@
         <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E20" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I20" t="s">
-        <v>332</v>
+        <v>256</v>
       </c>
       <c r="J20" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K20">
         <v>779.67</v>
@@ -9850,40 +9661,40 @@
       <c r="N20">
         <v>4000</v>
       </c>
-      <c r="O20" t="s">
-        <v>96</v>
-      </c>
-      <c r="P20" s="1">
+      <c r="O20">
+        <v>2704</v>
+      </c>
+      <c r="P20" s="2">
         <v>44372</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>44369</v>
       </c>
-      <c r="R20" t="s">
-        <v>377</v>
+      <c r="R20">
+        <v>7090000956</v>
       </c>
       <c r="S20" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E21" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I21" t="s">
-        <v>333</v>
+        <v>257</v>
       </c>
       <c r="J21" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K21">
         <v>1685.25</v>
@@ -9897,40 +9708,40 @@
       <c r="N21">
         <v>4000</v>
       </c>
-      <c r="O21" t="s">
-        <v>105</v>
-      </c>
-      <c r="P21" s="1">
+      <c r="O21">
+        <v>2708</v>
+      </c>
+      <c r="P21" s="2">
         <v>44362</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>43894</v>
       </c>
-      <c r="R21" t="s">
-        <v>378</v>
+      <c r="R21">
+        <v>7080003306</v>
       </c>
       <c r="S21" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E22" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I22" t="s">
-        <v>334</v>
+        <v>258</v>
       </c>
       <c r="J22" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K22">
         <v>1926.58</v>
@@ -9944,20 +9755,20 @@
       <c r="N22">
         <v>4000</v>
       </c>
-      <c r="O22" t="s">
-        <v>86</v>
-      </c>
-      <c r="P22" s="1">
+      <c r="O22">
+        <v>2740</v>
+      </c>
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45509</v>
       </c>
-      <c r="R22" t="s">
-        <v>379</v>
+      <c r="R22">
+        <v>7080005315</v>
       </c>
       <c r="S22" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -9968,16 +9779,16 @@
         <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E23" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I23" t="s">
-        <v>335</v>
+        <v>259</v>
       </c>
       <c r="J23" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="L23">
         <v>2562.83</v>
@@ -9985,25 +9796,25 @@
       <c r="N23">
         <v>4000</v>
       </c>
-      <c r="O23" t="s">
-        <v>359</v>
-      </c>
-      <c r="P23" s="1">
+      <c r="O23">
+        <v>2725</v>
+      </c>
+      <c r="P23" s="2">
         <v>40044</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>40126</v>
       </c>
-      <c r="R23" t="s">
-        <v>380</v>
+      <c r="R23">
+        <v>3130007478</v>
       </c>
       <c r="S23" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T23" t="s">
-        <v>399</v>
-      </c>
-      <c r="U23" s="1">
+        <v>283</v>
+      </c>
+      <c r="U23" s="2">
         <v>45775</v>
       </c>
     </row>
@@ -10015,16 +9826,16 @@
         <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E24" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I24" t="s">
-        <v>336</v>
+        <v>260</v>
       </c>
       <c r="J24" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K24">
         <v>1903.17</v>
@@ -10038,25 +9849,25 @@
       <c r="N24">
         <v>4000</v>
       </c>
-      <c r="O24" t="s">
+      <c r="O24">
+        <v>2702</v>
+      </c>
+      <c r="P24" s="2">
+        <v>43549</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>45772</v>
+      </c>
+      <c r="R24">
+        <v>3040091287</v>
+      </c>
+      <c r="S24" t="s">
         <v>80</v>
       </c>
-      <c r="P24" s="1">
-        <v>43549</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>45772</v>
-      </c>
-      <c r="R24" t="s">
-        <v>381</v>
-      </c>
-      <c r="S24" t="s">
-        <v>142</v>
-      </c>
       <c r="T24" t="s">
-        <v>400</v>
-      </c>
-      <c r="U24" s="1">
+        <v>284</v>
+      </c>
+      <c r="U24" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -10068,16 +9879,16 @@
         <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E25" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I25" t="s">
-        <v>337</v>
+        <v>261</v>
       </c>
       <c r="J25" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K25">
         <v>835.42</v>
@@ -10091,25 +9902,25 @@
       <c r="N25">
         <v>4000</v>
       </c>
-      <c r="O25" t="s">
-        <v>86</v>
-      </c>
-      <c r="P25" s="1">
+      <c r="O25">
+        <v>2740</v>
+      </c>
+      <c r="P25" s="2">
         <v>45447</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45510</v>
       </c>
-      <c r="R25" t="s">
-        <v>382</v>
+      <c r="R25">
+        <v>3130007827</v>
       </c>
       <c r="S25" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T25" t="s">
-        <v>401</v>
-      </c>
-      <c r="U25" s="1">
+        <v>285</v>
+      </c>
+      <c r="U25" s="2">
         <v>45937</v>
       </c>
     </row>
@@ -10121,16 +9932,16 @@
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E26" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I26" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="J26" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K26">
         <v>1657.42</v>
@@ -10144,25 +9955,25 @@
       <c r="N26">
         <v>4000</v>
       </c>
-      <c r="O26" t="s">
-        <v>100</v>
-      </c>
-      <c r="P26" s="1">
+      <c r="O26">
+        <v>2723</v>
+      </c>
+      <c r="P26" s="2">
         <v>44485</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>44959</v>
       </c>
-      <c r="R26" t="s">
-        <v>383</v>
+      <c r="R26">
+        <v>4190000750</v>
       </c>
       <c r="S26" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T26" t="s">
-        <v>402</v>
-      </c>
-      <c r="U26" s="1">
+        <v>286</v>
+      </c>
+      <c r="U26" s="2">
         <v>45580</v>
       </c>
     </row>
@@ -10174,16 +9985,16 @@
         <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E27" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I27" t="s">
-        <v>339</v>
+        <v>263</v>
       </c>
       <c r="J27" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K27">
         <v>39.92</v>
@@ -10197,25 +10008,25 @@
       <c r="N27">
         <v>4000</v>
       </c>
-      <c r="O27" t="s">
-        <v>86</v>
-      </c>
-      <c r="P27" s="1">
+      <c r="O27">
+        <v>2740</v>
+      </c>
+      <c r="P27" s="2">
         <v>45420</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45446</v>
       </c>
-      <c r="R27" t="s">
-        <v>384</v>
+      <c r="R27">
+        <v>3130007058</v>
       </c>
       <c r="S27" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T27" t="s">
-        <v>403</v>
-      </c>
-      <c r="U27" s="1">
+        <v>287</v>
+      </c>
+      <c r="U27" s="2">
         <v>45588</v>
       </c>
     </row>
@@ -10227,16 +10038,16 @@
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E28" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I28" t="s">
-        <v>340</v>
+        <v>264</v>
       </c>
       <c r="J28" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K28">
         <v>4204.25</v>
@@ -10250,25 +10061,25 @@
       <c r="N28">
         <v>4000</v>
       </c>
-      <c r="O28" t="s">
-        <v>101</v>
-      </c>
-      <c r="P28" s="1">
+      <c r="O28">
+        <v>2743</v>
+      </c>
+      <c r="P28" s="2">
         <v>44369</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>45824</v>
       </c>
-      <c r="R28" t="s">
-        <v>385</v>
+      <c r="R28">
+        <v>3040091753</v>
       </c>
       <c r="S28" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T28" t="s">
-        <v>404</v>
-      </c>
-      <c r="U28" s="1">
+        <v>288</v>
+      </c>
+      <c r="U28" s="2">
         <v>45831</v>
       </c>
     </row>
@@ -10280,16 +10091,16 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E29" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I29" t="s">
-        <v>341</v>
+        <v>265</v>
       </c>
       <c r="J29" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K29">
         <v>1891.33</v>
@@ -10303,25 +10114,25 @@
       <c r="N29">
         <v>4000</v>
       </c>
-      <c r="O29" t="s">
-        <v>98</v>
-      </c>
-      <c r="P29" s="1">
+      <c r="O29">
+        <v>2722</v>
+      </c>
+      <c r="P29" s="2">
         <v>44652</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>45567</v>
       </c>
-      <c r="R29" t="s">
-        <v>386</v>
+      <c r="R29">
+        <v>6850004453</v>
       </c>
       <c r="S29" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T29" t="s">
-        <v>405</v>
-      </c>
-      <c r="U29" s="1">
+        <v>289</v>
+      </c>
+      <c r="U29" s="2">
         <v>45734</v>
       </c>
     </row>
@@ -10333,27 +10144,27 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E30" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I30" t="s">
-        <v>342</v>
+        <v>266</v>
       </c>
       <c r="J30" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="N30">
         <v>4000</v>
       </c>
       <c r="S30" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T30" t="s">
-        <v>406</v>
-      </c>
-      <c r="U30" s="1">
+        <v>290</v>
+      </c>
+      <c r="U30" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10365,27 +10176,27 @@
         <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E31" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I31" t="s">
-        <v>343</v>
+        <v>267</v>
       </c>
       <c r="J31" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="N31">
         <v>4000</v>
       </c>
       <c r="S31" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T31" t="s">
-        <v>407</v>
-      </c>
-      <c r="U31" s="1">
+        <v>291</v>
+      </c>
+      <c r="U31" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10397,48 +10208,48 @@
         <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E32" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I32" t="s">
-        <v>344</v>
+        <v>268</v>
       </c>
       <c r="J32" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="N32">
         <v>4000</v>
       </c>
       <c r="S32" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="T32" t="s">
-        <v>408</v>
-      </c>
-      <c r="U32" s="1">
+        <v>292</v>
+      </c>
+      <c r="U32" s="2">
         <v>46001</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>282</v>
+        <v>206</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E33" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I33" t="s">
-        <v>345</v>
+        <v>269</v>
       </c>
       <c r="J33" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K33">
         <v>3238.83</v>
@@ -10452,25 +10263,25 @@
       <c r="N33">
         <v>4000</v>
       </c>
-      <c r="O33" t="s">
-        <v>90</v>
-      </c>
-      <c r="P33" s="1">
+      <c r="O33">
+        <v>2738</v>
+      </c>
+      <c r="P33" s="2">
         <v>43762</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>46031</v>
       </c>
-      <c r="R33" t="s">
-        <v>387</v>
+      <c r="R33">
+        <v>3130008485</v>
       </c>
       <c r="S33" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="T33" t="s">
-        <v>387</v>
-      </c>
-      <c r="U33" s="1">
+        <v>293</v>
+      </c>
+      <c r="U33" s="2">
         <v>46037</v>
       </c>
     </row>
@@ -10482,16 +10293,16 @@
         <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E34" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I34" t="s">
-        <v>346</v>
+        <v>270</v>
       </c>
       <c r="J34" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K34">
         <v>833.58</v>
@@ -10505,40 +10316,40 @@
       <c r="N34">
         <v>4000</v>
       </c>
-      <c r="O34" t="s">
-        <v>360</v>
-      </c>
-      <c r="P34" s="1">
+      <c r="O34">
+        <v>2735</v>
+      </c>
+      <c r="P34" s="2">
         <v>40071</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
-        <v>146</v>
-      </c>
-      <c r="U34" s="1">
+        <v>84</v>
+      </c>
+      <c r="U34" s="2">
         <v>41023</v>
       </c>
     </row>
     <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E35" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I35" t="s">
-        <v>347</v>
+        <v>271</v>
       </c>
       <c r="J35" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="L35">
         <v>6168.75</v>
@@ -10546,43 +10357,43 @@
       <c r="N35">
         <v>4000</v>
       </c>
-      <c r="O35" t="s">
-        <v>87</v>
-      </c>
-      <c r="P35" s="1">
+      <c r="O35">
+        <v>2732</v>
+      </c>
+      <c r="P35" s="2">
         <v>44784</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>45259</v>
       </c>
-      <c r="R35" t="s">
-        <v>388</v>
+      <c r="R35">
+        <v>3130006532</v>
       </c>
       <c r="S35" t="s">
-        <v>146</v>
-      </c>
-      <c r="U35" s="1">
+        <v>84</v>
+      </c>
+      <c r="U35" s="2">
         <v>45259</v>
       </c>
     </row>
     <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E36" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I36" t="s">
-        <v>348</v>
+        <v>272</v>
       </c>
       <c r="J36" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K36">
         <v>2184.17</v>
@@ -10596,69 +10407,69 @@
       <c r="N36">
         <v>4000</v>
       </c>
-      <c r="O36" t="s">
-        <v>91</v>
-      </c>
-      <c r="P36" s="1">
+      <c r="O36">
+        <v>2737</v>
+      </c>
+      <c r="P36" s="2">
         <v>45103</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>46000</v>
       </c>
-      <c r="R36" t="s">
-        <v>389</v>
+      <c r="R36">
+        <v>6890000560</v>
       </c>
       <c r="S36" t="s">
-        <v>146</v>
-      </c>
-      <c r="U36" s="1">
+        <v>84</v>
+      </c>
+      <c r="U36" s="2">
         <v>46000</v>
       </c>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="E37" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I37" t="s">
-        <v>331</v>
+        <v>255</v>
       </c>
       <c r="J37" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="N37">
         <v>4000</v>
       </c>
       <c r="S37" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="B38" t="s">
         <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E38" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I38" t="s">
-        <v>349</v>
+        <v>273</v>
       </c>
       <c r="J38" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K38">
         <v>553.17</v>
@@ -10672,22 +10483,22 @@
       <c r="N38">
         <v>4000</v>
       </c>
-      <c r="O38" t="s">
-        <v>96</v>
-      </c>
-      <c r="P38" s="1">
+      <c r="O38">
+        <v>2704</v>
+      </c>
+      <c r="P38" s="2">
         <v>38511</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>39068</v>
       </c>
-      <c r="R38" t="s">
-        <v>390</v>
+      <c r="R38">
+        <v>3070018395</v>
       </c>
       <c r="S38" t="s">
-        <v>146</v>
-      </c>
-      <c r="U38" s="1">
+        <v>84</v>
+      </c>
+      <c r="U38" s="2">
         <v>39068</v>
       </c>
     </row>
@@ -10699,16 +10510,16 @@
         <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E39" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I39" t="s">
-        <v>350</v>
+        <v>274</v>
       </c>
       <c r="J39" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K39">
         <v>85.58</v>
@@ -10722,25 +10533,25 @@
       <c r="N39">
         <v>4000</v>
       </c>
-      <c r="O39" t="s">
-        <v>103</v>
-      </c>
-      <c r="P39" s="1">
+      <c r="O39">
+        <v>2720</v>
+      </c>
+      <c r="P39" s="2">
         <v>39006</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>40568</v>
       </c>
-      <c r="R39" t="s">
-        <v>391</v>
+      <c r="R39">
+        <v>3130002407</v>
       </c>
       <c r="S39" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="T39" t="s">
-        <v>409</v>
-      </c>
-      <c r="U39" s="1">
+        <v>294</v>
+      </c>
+      <c r="U39" s="2">
         <v>40568</v>
       </c>
     </row>
@@ -10752,16 +10563,16 @@
         <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>311</v>
+        <v>235</v>
       </c>
       <c r="E40" t="s">
-        <v>313</v>
+        <v>237</v>
       </c>
       <c r="I40" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
       <c r="J40" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K40">
         <v>796.67</v>
@@ -10769,25 +10580,25 @@
       <c r="L40">
         <v>3739.5</v>
       </c>
-      <c r="O40" t="s">
-        <v>100</v>
-      </c>
-      <c r="P40" s="1">
+      <c r="O40">
+        <v>2723</v>
+      </c>
+      <c r="P40" s="2">
         <v>40836</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>42270</v>
       </c>
-      <c r="R40" t="s">
-        <v>392</v>
+      <c r="R40">
+        <v>3040050893</v>
       </c>
       <c r="S40" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="T40" t="s">
-        <v>410</v>
-      </c>
-      <c r="U40" s="1">
+        <v>295</v>
+      </c>
+      <c r="U40" s="2">
         <v>42270</v>
       </c>
     </row>
@@ -10799,16 +10610,16 @@
         <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E41" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I41" t="s">
-        <v>352</v>
+        <v>276</v>
       </c>
       <c r="J41" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K41">
         <v>981.58</v>
@@ -10822,25 +10633,25 @@
       <c r="N41">
         <v>4000</v>
       </c>
-      <c r="O41" t="s">
-        <v>95</v>
-      </c>
-      <c r="P41" s="1">
+      <c r="O41">
+        <v>2741</v>
+      </c>
+      <c r="P41" s="2">
         <v>42940</v>
       </c>
-      <c r="Q41" s="1">
+      <c r="Q41" s="2">
         <v>43494</v>
       </c>
-      <c r="R41" t="s">
-        <v>393</v>
+      <c r="R41">
+        <v>3040080066</v>
       </c>
       <c r="S41" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="T41" t="s">
-        <v>411</v>
-      </c>
-      <c r="U41" s="1">
+        <v>296</v>
+      </c>
+      <c r="U41" s="2">
         <v>44148</v>
       </c>
     </row>
@@ -10852,16 +10663,16 @@
         <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E42" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I42" t="s">
-        <v>353</v>
+        <v>277</v>
       </c>
       <c r="J42" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K42">
         <v>3152</v>
@@ -10875,25 +10686,25 @@
       <c r="N42">
         <v>4000</v>
       </c>
-      <c r="O42" t="s">
+      <c r="O42">
+        <v>2719</v>
+      </c>
+      <c r="P42" s="2">
+        <v>43696</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>45776</v>
+      </c>
+      <c r="R42">
+        <v>6850005706</v>
+      </c>
+      <c r="S42" t="s">
         <v>82</v>
       </c>
-      <c r="P42" s="1">
-        <v>43696</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>45776</v>
-      </c>
-      <c r="R42" t="s">
-        <v>394</v>
-      </c>
-      <c r="S42" t="s">
-        <v>144</v>
-      </c>
       <c r="T42" t="s">
-        <v>412</v>
-      </c>
-      <c r="U42" s="1">
+        <v>297</v>
+      </c>
+      <c r="U42" s="2">
         <v>43185</v>
       </c>
     </row>
@@ -10905,16 +10716,16 @@
         <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E43" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I43" t="s">
-        <v>354</v>
+        <v>278</v>
       </c>
       <c r="J43" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K43">
         <v>2787.25</v>
@@ -10928,25 +10739,25 @@
       <c r="N43">
         <v>4000</v>
       </c>
-      <c r="O43" t="s">
-        <v>84</v>
-      </c>
-      <c r="P43" s="1">
+      <c r="O43">
+        <v>2742</v>
+      </c>
+      <c r="P43" s="2">
         <v>43544</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="Q43" s="2">
         <v>45916</v>
       </c>
-      <c r="R43" t="s">
-        <v>395</v>
+      <c r="R43">
+        <v>3860010942</v>
       </c>
       <c r="S43" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="T43" t="s">
-        <v>413</v>
-      </c>
-      <c r="U43" s="1">
+        <v>298</v>
+      </c>
+      <c r="U43" s="2">
         <v>42850</v>
       </c>
     </row>
@@ -10958,16 +10769,16 @@
         <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E44" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I44" t="s">
-        <v>355</v>
+        <v>279</v>
       </c>
       <c r="J44" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K44">
         <v>2413.42</v>
@@ -10981,25 +10792,25 @@
       <c r="N44">
         <v>4000</v>
       </c>
-      <c r="O44" t="s">
-        <v>97</v>
-      </c>
-      <c r="P44" s="1">
+      <c r="O44">
+        <v>2739</v>
+      </c>
+      <c r="P44" s="2">
         <v>45076</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="Q44" s="2">
         <v>45539</v>
       </c>
-      <c r="R44" t="s">
-        <v>396</v>
+      <c r="R44">
+        <v>3960005216</v>
       </c>
       <c r="S44" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="T44" t="s">
-        <v>414</v>
-      </c>
-      <c r="U44" s="1">
+        <v>299</v>
+      </c>
+      <c r="U44" s="2">
         <v>44404</v>
       </c>
     </row>
@@ -11011,16 +10822,16 @@
         <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E45" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I45" t="s">
-        <v>356</v>
+        <v>280</v>
       </c>
       <c r="J45" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K45">
         <v>2266.5</v>
@@ -11034,25 +10845,25 @@
       <c r="N45">
         <v>4000</v>
       </c>
-      <c r="O45" t="s">
-        <v>81</v>
-      </c>
-      <c r="P45" s="1">
+      <c r="O45">
+        <v>2703</v>
+      </c>
+      <c r="P45" s="2">
         <v>42963</v>
       </c>
-      <c r="Q45" s="1">
+      <c r="Q45" s="2">
         <v>45239</v>
       </c>
-      <c r="R45" t="s">
-        <v>397</v>
+      <c r="R45">
+        <v>3040088304</v>
       </c>
       <c r="S45" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="T45" t="s">
-        <v>415</v>
-      </c>
-      <c r="U45" s="1">
+        <v>300</v>
+      </c>
+      <c r="U45" s="2">
         <v>42698</v>
       </c>
     </row>
@@ -11064,16 +10875,16 @@
         <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="E46" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="I46" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="J46" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="K46">
         <v>545.75</v>
@@ -11087,25 +10898,25 @@
       <c r="N46">
         <v>4000</v>
       </c>
-      <c r="O46" t="s">
-        <v>88</v>
-      </c>
-      <c r="P46" s="1">
+      <c r="O46">
+        <v>2733</v>
+      </c>
+      <c r="P46" s="2">
         <v>45054</v>
       </c>
-      <c r="Q46" s="1">
+      <c r="Q46" s="2">
         <v>45586</v>
       </c>
-      <c r="R46" t="s">
-        <v>398</v>
+      <c r="R46">
+        <v>3130007348</v>
       </c>
       <c r="S46" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="T46" t="s">
-        <v>416</v>
-      </c>
-      <c r="U46" s="1">
+        <v>301</v>
+      </c>
+      <c r="U46" s="2">
         <v>43941</v>
       </c>
     </row>
@@ -11120,26 +10931,26 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" t="s">
-        <v>417</v>
-      </c>
-      <c r="D1" t="s">
-        <v>418</v>
-      </c>
-      <c r="E1" t="s">
-        <v>419</v>
-      </c>
-      <c r="F1" t="s">
-        <v>420</v>
-      </c>
-      <c r="G1" t="s">
-        <v>421</v>
+      <c r="A1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -11810,7 +11621,537 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>171</v>
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F2">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F3">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E4" t="s">
+        <v>350</v>
+      </c>
+      <c r="F4">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D5" t="s">
+        <v>328</v>
+      </c>
+      <c r="E5" t="s">
+        <v>350</v>
+      </c>
+      <c r="F5">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F6">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E7" t="s">
+        <v>350</v>
+      </c>
+      <c r="F7">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B8" t="s">
+        <v>317</v>
+      </c>
+      <c r="C8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D8" t="s">
+        <v>331</v>
+      </c>
+      <c r="E8" t="s">
+        <v>350</v>
+      </c>
+      <c r="F8">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" t="s">
+        <v>321</v>
+      </c>
+      <c r="D9" t="s">
+        <v>332</v>
+      </c>
+      <c r="E9" t="s">
+        <v>350</v>
+      </c>
+      <c r="F9">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C10" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" t="s">
+        <v>333</v>
+      </c>
+      <c r="E10" t="s">
+        <v>350</v>
+      </c>
+      <c r="F10">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" t="s">
+        <v>334</v>
+      </c>
+      <c r="E11" t="s">
+        <v>350</v>
+      </c>
+      <c r="F11">
+        <v>563000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>313</v>
+      </c>
+      <c r="B12" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" t="s">
+        <v>318</v>
+      </c>
+      <c r="D12" t="s">
+        <v>335</v>
+      </c>
+      <c r="E12" t="s">
+        <v>350</v>
+      </c>
+      <c r="F12">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>313</v>
+      </c>
+      <c r="B13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C13" t="s">
+        <v>322</v>
+      </c>
+      <c r="D13" t="s">
+        <v>336</v>
+      </c>
+      <c r="E13" t="s">
+        <v>350</v>
+      </c>
+      <c r="F13">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>315</v>
+      </c>
+      <c r="B14" t="s">
+        <v>317</v>
+      </c>
+      <c r="C14" t="s">
+        <v>322</v>
+      </c>
+      <c r="D14" t="s">
+        <v>337</v>
+      </c>
+      <c r="E14" t="s">
+        <v>350</v>
+      </c>
+      <c r="F14">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>313</v>
+      </c>
+      <c r="B15" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" t="s">
+        <v>322</v>
+      </c>
+      <c r="D15" t="s">
+        <v>338</v>
+      </c>
+      <c r="E15" t="s">
+        <v>350</v>
+      </c>
+      <c r="F15">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>315</v>
+      </c>
+      <c r="B16" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" t="s">
+        <v>322</v>
+      </c>
+      <c r="D16" t="s">
+        <v>339</v>
+      </c>
+      <c r="E16" t="s">
+        <v>350</v>
+      </c>
+      <c r="F16">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>316</v>
+      </c>
+      <c r="B17" t="s">
+        <v>317</v>
+      </c>
+      <c r="C17" t="s">
+        <v>323</v>
+      </c>
+      <c r="D17" t="s">
+        <v>340</v>
+      </c>
+      <c r="E17" t="s">
+        <v>350</v>
+      </c>
+      <c r="F17">
+        <v>3800000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>316</v>
+      </c>
+      <c r="B18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C18" t="s">
+        <v>323</v>
+      </c>
+      <c r="D18" t="s">
+        <v>341</v>
+      </c>
+      <c r="E18" t="s">
+        <v>350</v>
+      </c>
+      <c r="F18">
+        <v>3800000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>313</v>
+      </c>
+      <c r="B19" t="s">
+        <v>317</v>
+      </c>
+      <c r="C19" t="s">
+        <v>323</v>
+      </c>
+      <c r="D19" t="s">
+        <v>342</v>
+      </c>
+      <c r="E19" t="s">
+        <v>350</v>
+      </c>
+      <c r="F19">
+        <v>3800000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" t="s">
+        <v>317</v>
+      </c>
+      <c r="C20" t="s">
+        <v>324</v>
+      </c>
+      <c r="D20" t="s">
+        <v>343</v>
+      </c>
+      <c r="E20" t="s">
+        <v>350</v>
+      </c>
+      <c r="F20">
+        <v>3800000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" t="s">
+        <v>317</v>
+      </c>
+      <c r="C21" t="s">
+        <v>324</v>
+      </c>
+      <c r="D21" t="s">
+        <v>344</v>
+      </c>
+      <c r="E21" t="s">
+        <v>350</v>
+      </c>
+      <c r="F21">
+        <v>3800000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>314</v>
+      </c>
+      <c r="B22" t="s">
+        <v>317</v>
+      </c>
+      <c r="C22" t="s">
+        <v>324</v>
+      </c>
+      <c r="D22" t="s">
+        <v>345</v>
+      </c>
+      <c r="E22" t="s">
+        <v>350</v>
+      </c>
+      <c r="F22">
+        <v>3800000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>313</v>
+      </c>
+      <c r="B23" t="s">
+        <v>317</v>
+      </c>
+      <c r="C23" t="s">
+        <v>322</v>
+      </c>
+      <c r="D23" t="s">
+        <v>346</v>
+      </c>
+      <c r="E23" t="s">
+        <v>350</v>
+      </c>
+      <c r="F23">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>313</v>
+      </c>
+      <c r="B24" t="s">
+        <v>317</v>
+      </c>
+      <c r="C24" t="s">
+        <v>322</v>
+      </c>
+      <c r="D24" t="s">
+        <v>347</v>
+      </c>
+      <c r="E24" t="s">
+        <v>350</v>
+      </c>
+      <c r="F24">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B25" t="s">
+        <v>317</v>
+      </c>
+      <c r="C25" t="s">
+        <v>322</v>
+      </c>
+      <c r="D25" t="s">
+        <v>348</v>
+      </c>
+      <c r="E25" t="s">
+        <v>350</v>
+      </c>
+      <c r="F25">
+        <v>425000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>313</v>
+      </c>
+      <c r="B26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C26" t="s">
+        <v>322</v>
+      </c>
+      <c r="D26" t="s">
+        <v>349</v>
+      </c>
+      <c r="E26" t="s">
+        <v>350</v>
+      </c>
+      <c r="F26">
+        <v>60000</v>
       </c>
     </row>
   </sheetData>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="466">
   <si>
     <t>om</t>
   </si>
@@ -261,6 +261,192 @@
     <t>H - Horas de Vôo</t>
   </si>
   <si>
+    <t>2702</t>
+  </si>
+  <si>
+    <t>2703</t>
+  </si>
+  <si>
+    <t>2719</t>
+  </si>
+  <si>
+    <t>2728</t>
+  </si>
+  <si>
+    <t>2742</t>
+  </si>
+  <si>
+    <t>2734</t>
+  </si>
+  <si>
+    <t>2740</t>
+  </si>
+  <si>
+    <t>2732</t>
+  </si>
+  <si>
+    <t>2733</t>
+  </si>
+  <si>
+    <t>2727</t>
+  </si>
+  <si>
+    <t>2738</t>
+  </si>
+  <si>
+    <t>2737</t>
+  </si>
+  <si>
+    <t>2736</t>
+  </si>
+  <si>
+    <t>2731</t>
+  </si>
+  <si>
+    <t>2721</t>
+  </si>
+  <si>
+    <t>2741</t>
+  </si>
+  <si>
+    <t>2704</t>
+  </si>
+  <si>
+    <t>2739</t>
+  </si>
+  <si>
+    <t>2722</t>
+  </si>
+  <si>
+    <t>2724</t>
+  </si>
+  <si>
+    <t>2723</t>
+  </si>
+  <si>
+    <t>2743</t>
+  </si>
+  <si>
+    <t>2709</t>
+  </si>
+  <si>
+    <t>2720</t>
+  </si>
+  <si>
+    <t>2729</t>
+  </si>
+  <si>
+    <t>2708</t>
+  </si>
+  <si>
+    <t>3040093565</t>
+  </si>
+  <si>
+    <t>3040083839</t>
+  </si>
+  <si>
+    <t>2260002888</t>
+  </si>
+  <si>
+    <t>3040093881</t>
+  </si>
+  <si>
+    <t>3130007347</t>
+  </si>
+  <si>
+    <t>3810139776</t>
+  </si>
+  <si>
+    <t>3810113895</t>
+  </si>
+  <si>
+    <t>3810140243</t>
+  </si>
+  <si>
+    <t>7080005835</t>
+  </si>
+  <si>
+    <t>3040093764</t>
+  </si>
+  <si>
+    <t>3810134655</t>
+  </si>
+  <si>
+    <t>6850006787</t>
+  </si>
+  <si>
+    <t>3810135032</t>
+  </si>
+  <si>
+    <t>3810140063</t>
+  </si>
+  <si>
+    <t>3810135107</t>
+  </si>
+  <si>
+    <t>3290008824</t>
+  </si>
+  <si>
+    <t>6900004625</t>
+  </si>
+  <si>
+    <t>3810140068</t>
+  </si>
+  <si>
+    <t>3130008877</t>
+  </si>
+  <si>
+    <t>3810138909</t>
+  </si>
+  <si>
+    <t>3810138523</t>
+  </si>
+  <si>
+    <t>6890000683</t>
+  </si>
+  <si>
+    <t>3810112732</t>
+  </si>
+  <si>
+    <t>3810139780</t>
+  </si>
+  <si>
+    <t>3810126785</t>
+  </si>
+  <si>
+    <t>3860011562</t>
+  </si>
+  <si>
+    <t>3950001218</t>
+  </si>
+  <si>
+    <t>6890001058</t>
+  </si>
+  <si>
+    <t>3810118951</t>
+  </si>
+  <si>
+    <t>7080002856</t>
+  </si>
+  <si>
+    <t>3810129323</t>
+  </si>
+  <si>
+    <t>3130005802</t>
+  </si>
+  <si>
+    <t>3740026391</t>
+  </si>
+  <si>
+    <t>3290008244</t>
+  </si>
+  <si>
+    <t>3810139583</t>
+  </si>
+  <si>
+    <t>7080004330</t>
+  </si>
+  <si>
     <t>OS</t>
   </si>
   <si>
@@ -303,15 +489,9 @@
     <t>3810280317</t>
   </si>
   <si>
-    <t>6900004625</t>
-  </si>
-  <si>
     <t>3810279579</t>
   </si>
   <si>
-    <t>3130008877</t>
-  </si>
-  <si>
     <t>3810276969</t>
   </si>
   <si>
@@ -400,6 +580,9 @@
   </si>
   <si>
     <t>19.2</t>
+  </si>
+  <si>
+    <t>#N/A</t>
   </si>
   <si>
     <t>5.1586629</t>
@@ -646,6 +829,12 @@
     <t>M</t>
   </si>
   <si>
+    <t>313240015920</t>
+  </si>
+  <si>
+    <t>313240016031</t>
+  </si>
+  <si>
     <t>S4J</t>
   </si>
   <si>
@@ -658,6 +847,45 @@
     <t>SEP</t>
   </si>
   <si>
+    <t>3810496453</t>
+  </si>
+  <si>
+    <t>3810499719</t>
+  </si>
+  <si>
+    <t>3810500784</t>
+  </si>
+  <si>
+    <t>3810501279</t>
+  </si>
+  <si>
+    <t>3810502614</t>
+  </si>
+  <si>
+    <t>3810504268</t>
+  </si>
+  <si>
+    <t>3810504159</t>
+  </si>
+  <si>
+    <t>3810504182</t>
+  </si>
+  <si>
+    <t>3810503807</t>
+  </si>
+  <si>
+    <t>3810481813</t>
+  </si>
+  <si>
+    <t>3810492521</t>
+  </si>
+  <si>
+    <t>3810499557</t>
+  </si>
+  <si>
+    <t>3810499086</t>
+  </si>
+  <si>
     <t>BAMN</t>
   </si>
   <si>
@@ -889,6 +1117,126 @@
     <t>H-HorasdeVôo</t>
   </si>
   <si>
+    <t>2725</t>
+  </si>
+  <si>
+    <t>2735</t>
+  </si>
+  <si>
+    <t>3130006005</t>
+  </si>
+  <si>
+    <t>6890000562</t>
+  </si>
+  <si>
+    <t>3040075245</t>
+  </si>
+  <si>
+    <t>3290007931</t>
+  </si>
+  <si>
+    <t>7090002248</t>
+  </si>
+  <si>
+    <t>3130006789</t>
+  </si>
+  <si>
+    <t>7090002894</t>
+  </si>
+  <si>
+    <t>3130005796</t>
+  </si>
+  <si>
+    <t>7100002436</t>
+  </si>
+  <si>
+    <t>3040057779</t>
+  </si>
+  <si>
+    <t>3040073019</t>
+  </si>
+  <si>
+    <t>3040090256</t>
+  </si>
+  <si>
+    <t>7090002718</t>
+  </si>
+  <si>
+    <t>3040077697</t>
+  </si>
+  <si>
+    <t>3960004903</t>
+  </si>
+  <si>
+    <t>3130006599</t>
+  </si>
+  <si>
+    <t>7090000956</t>
+  </si>
+  <si>
+    <t>7080003306</t>
+  </si>
+  <si>
+    <t>7080005315</t>
+  </si>
+  <si>
+    <t>3130007478</t>
+  </si>
+  <si>
+    <t>3040091287</t>
+  </si>
+  <si>
+    <t>3130007827</t>
+  </si>
+  <si>
+    <t>4190000750</t>
+  </si>
+  <si>
+    <t>3130007058</t>
+  </si>
+  <si>
+    <t>3040091753</t>
+  </si>
+  <si>
+    <t>6850004453</t>
+  </si>
+  <si>
+    <t>3130008485</t>
+  </si>
+  <si>
+    <t>3130006532</t>
+  </si>
+  <si>
+    <t>6890000560</t>
+  </si>
+  <si>
+    <t>3070018395</t>
+  </si>
+  <si>
+    <t>3130002407</t>
+  </si>
+  <si>
+    <t>3040050893</t>
+  </si>
+  <si>
+    <t>3040080066</t>
+  </si>
+  <si>
+    <t>6850005706</t>
+  </si>
+  <si>
+    <t>3860010942</t>
+  </si>
+  <si>
+    <t>3960005216</t>
+  </si>
+  <si>
+    <t>3040088304</t>
+  </si>
+  <si>
+    <t>3130007348</t>
+  </si>
+  <si>
     <t>3040252386</t>
   </si>
   <si>
@@ -917,9 +1265,6 @@
   </si>
   <si>
     <t>3040260407</t>
-  </si>
-  <si>
-    <t>3130008485</t>
   </si>
   <si>
     <t>3040040322</t>
@@ -1554,8 +1899,8 @@
       <c r="M2">
         <v>128.48</v>
       </c>
-      <c r="N2">
-        <v>2702</v>
+      <c r="N2" t="s">
+        <v>80</v>
       </c>
       <c r="O2">
         <v>4000</v>
@@ -1566,14 +1911,14 @@
       <c r="Q2" s="2">
         <v>46134</v>
       </c>
-      <c r="R2">
-        <v>3040093565</v>
+      <c r="R2" t="s">
+        <v>106</v>
       </c>
       <c r="S2" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T2" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="U2" s="2">
         <v>46170</v>
@@ -1610,8 +1955,8 @@
       <c r="M3">
         <v>102.93</v>
       </c>
-      <c r="N3">
-        <v>2703</v>
+      <c r="N3" t="s">
+        <v>81</v>
       </c>
       <c r="O3">
         <v>4000</v>
@@ -1622,11 +1967,11 @@
       <c r="Q3" s="2">
         <v>44652</v>
       </c>
-      <c r="R3">
-        <v>3040083839</v>
+      <c r="R3" t="s">
+        <v>107</v>
       </c>
       <c r="S3" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1660,8 +2005,8 @@
       <c r="M4">
         <v>106.56</v>
       </c>
-      <c r="N4">
-        <v>2719</v>
+      <c r="N4" t="s">
+        <v>82</v>
       </c>
       <c r="O4">
         <v>4000</v>
@@ -1672,11 +2017,11 @@
       <c r="Q4" s="2">
         <v>44348</v>
       </c>
-      <c r="R4">
-        <v>2260002888</v>
+      <c r="R4" t="s">
+        <v>108</v>
       </c>
       <c r="S4" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1710,8 +2055,8 @@
       <c r="M5">
         <v>1.48</v>
       </c>
-      <c r="N5">
-        <v>2728</v>
+      <c r="N5" t="s">
+        <v>83</v>
       </c>
       <c r="O5">
         <v>4000</v>
@@ -1722,14 +2067,14 @@
       <c r="Q5" s="2">
         <v>46203</v>
       </c>
-      <c r="R5">
-        <v>3040093881</v>
+      <c r="R5" t="s">
+        <v>109</v>
       </c>
       <c r="S5" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T5" t="s">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="U5" s="2">
         <v>46210</v>
@@ -1763,8 +2108,8 @@
       <c r="M6">
         <v>18.72</v>
       </c>
-      <c r="N6">
-        <v>2742</v>
+      <c r="N6" t="s">
+        <v>84</v>
       </c>
       <c r="O6">
         <v>4000</v>
@@ -1775,11 +2120,11 @@
       <c r="Q6" s="2">
         <v>45510</v>
       </c>
-      <c r="R6">
-        <v>3130007347</v>
+      <c r="R6" t="s">
+        <v>110</v>
       </c>
       <c r="S6" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1813,8 +2158,8 @@
       <c r="M7">
         <v>124.93</v>
       </c>
-      <c r="N7">
-        <v>2734</v>
+      <c r="N7" t="s">
+        <v>85</v>
       </c>
       <c r="O7">
         <v>4000</v>
@@ -1825,14 +2170,14 @@
       <c r="Q7" s="2">
         <v>45301</v>
       </c>
-      <c r="R7">
-        <v>3810139776</v>
+      <c r="R7" t="s">
+        <v>111</v>
       </c>
       <c r="S7" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="T7" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="U7" s="2">
         <v>43507</v>
@@ -1869,8 +2214,8 @@
       <c r="M8">
         <v>80.92</v>
       </c>
-      <c r="N8">
-        <v>2740</v>
+      <c r="N8" t="s">
+        <v>86</v>
       </c>
       <c r="O8">
         <v>4000</v>
@@ -1881,11 +2226,11 @@
       <c r="Q8" s="2">
         <v>43725</v>
       </c>
-      <c r="R8">
-        <v>3810113895</v>
+      <c r="R8" t="s">
+        <v>112</v>
       </c>
       <c r="S8" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -1919,8 +2264,8 @@
       <c r="M9">
         <v>72.23999999999999</v>
       </c>
-      <c r="N9">
-        <v>2732</v>
+      <c r="N9" t="s">
+        <v>87</v>
       </c>
       <c r="O9">
         <v>4000</v>
@@ -1931,14 +2276,14 @@
       <c r="Q9" s="2">
         <v>45716</v>
       </c>
-      <c r="R9">
-        <v>3810140243</v>
+      <c r="R9" t="s">
+        <v>113</v>
       </c>
       <c r="S9" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="T9" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="U9" s="2">
         <v>44665</v>
@@ -1975,8 +2320,8 @@
       <c r="M10">
         <v>103.29</v>
       </c>
-      <c r="N10">
-        <v>2733</v>
+      <c r="N10" t="s">
+        <v>88</v>
       </c>
       <c r="O10">
         <v>4000</v>
@@ -1987,11 +2332,11 @@
       <c r="Q10" s="2">
         <v>45048</v>
       </c>
-      <c r="R10">
-        <v>7080005835</v>
+      <c r="R10" t="s">
+        <v>114</v>
       </c>
       <c r="S10" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -2019,8 +2364,8 @@
       <c r="L11">
         <v>16595</v>
       </c>
-      <c r="N11">
-        <v>2702</v>
+      <c r="N11" t="s">
+        <v>80</v>
       </c>
       <c r="O11">
         <v>4000</v>
@@ -2031,14 +2376,14 @@
       <c r="Q11" s="2">
         <v>46169</v>
       </c>
-      <c r="R11">
-        <v>3040093764</v>
+      <c r="R11" t="s">
+        <v>115</v>
       </c>
       <c r="S11" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T11" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="U11" s="2">
         <v>46203</v>
@@ -2072,8 +2417,8 @@
       <c r="M12">
         <v>0.3</v>
       </c>
-      <c r="N12">
-        <v>2727</v>
+      <c r="N12" t="s">
+        <v>89</v>
       </c>
       <c r="O12">
         <v>4000</v>
@@ -2082,7 +2427,7 @@
         <v>46125</v>
       </c>
       <c r="S12" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2113,8 +2458,8 @@
       <c r="M13">
         <v>0.57</v>
       </c>
-      <c r="N13">
-        <v>2738</v>
+      <c r="N13" t="s">
+        <v>90</v>
       </c>
       <c r="O13">
         <v>4000</v>
@@ -2125,11 +2470,11 @@
       <c r="Q13" s="2">
         <v>41861</v>
       </c>
-      <c r="R13">
-        <v>3810134655</v>
+      <c r="R13" t="s">
+        <v>116</v>
       </c>
       <c r="S13" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -2160,8 +2505,8 @@
       <c r="M14">
         <v>3.57</v>
       </c>
-      <c r="N14">
-        <v>2728</v>
+      <c r="N14" t="s">
+        <v>83</v>
       </c>
       <c r="O14">
         <v>4000</v>
@@ -2172,14 +2517,14 @@
       <c r="Q14" s="2">
         <v>46059</v>
       </c>
-      <c r="R14">
-        <v>6850006787</v>
+      <c r="R14" t="s">
+        <v>117</v>
       </c>
       <c r="S14" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T14" t="s">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="U14" s="2">
         <v>46072</v>
@@ -2216,8 +2561,8 @@
       <c r="M15">
         <v>7.31</v>
       </c>
-      <c r="N15">
-        <v>2737</v>
+      <c r="N15" t="s">
+        <v>91</v>
       </c>
       <c r="O15">
         <v>4000</v>
@@ -2228,11 +2573,11 @@
       <c r="Q15" s="2">
         <v>43592</v>
       </c>
-      <c r="R15">
-        <v>3810135032</v>
+      <c r="R15" t="s">
+        <v>118</v>
       </c>
       <c r="S15" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2266,8 +2611,8 @@
       <c r="M16">
         <v>111.99</v>
       </c>
-      <c r="N16">
-        <v>2736</v>
+      <c r="N16" t="s">
+        <v>92</v>
       </c>
       <c r="O16">
         <v>4000</v>
@@ -2278,14 +2623,14 @@
       <c r="Q16" s="2">
         <v>45524</v>
       </c>
-      <c r="R16">
-        <v>3810140063</v>
+      <c r="R16" t="s">
+        <v>119</v>
       </c>
       <c r="S16" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T16" t="s">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="U16" s="2">
         <v>46157</v>
@@ -2322,8 +2667,8 @@
       <c r="M17">
         <v>8.880000000000001</v>
       </c>
-      <c r="N17">
-        <v>2731</v>
+      <c r="N17" t="s">
+        <v>93</v>
       </c>
       <c r="O17">
         <v>4000</v>
@@ -2334,11 +2679,11 @@
       <c r="Q17" s="2">
         <v>45061</v>
       </c>
-      <c r="R17">
-        <v>3810135107</v>
+      <c r="R17" t="s">
+        <v>120</v>
       </c>
       <c r="S17" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2372,8 +2717,8 @@
       <c r="M18">
         <v>6.68</v>
       </c>
-      <c r="N18">
-        <v>2721</v>
+      <c r="N18" t="s">
+        <v>94</v>
       </c>
       <c r="O18">
         <v>4000</v>
@@ -2384,14 +2729,14 @@
       <c r="Q18" s="2">
         <v>46184</v>
       </c>
-      <c r="R18">
-        <v>3290008824</v>
+      <c r="R18" t="s">
+        <v>121</v>
       </c>
       <c r="S18" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T18" t="s">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="U18" s="2">
         <v>46198</v>
@@ -2428,8 +2773,8 @@
       <c r="M19">
         <v>130</v>
       </c>
-      <c r="N19">
-        <v>2727</v>
+      <c r="N19" t="s">
+        <v>89</v>
       </c>
       <c r="O19">
         <v>4000</v>
@@ -2440,14 +2785,14 @@
       <c r="Q19" s="2">
         <v>46014</v>
       </c>
-      <c r="R19">
-        <v>6900004625</v>
+      <c r="R19" t="s">
+        <v>122</v>
       </c>
       <c r="S19" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="T19" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="U19" s="2">
         <v>46153</v>
@@ -2487,8 +2832,8 @@
       <c r="M20">
         <v>120.81</v>
       </c>
-      <c r="N20">
-        <v>2740</v>
+      <c r="N20" t="s">
+        <v>86</v>
       </c>
       <c r="O20">
         <v>4000</v>
@@ -2499,14 +2844,14 @@
       <c r="Q20" s="2">
         <v>45446</v>
       </c>
-      <c r="R20">
-        <v>3810140068</v>
+      <c r="R20" t="s">
+        <v>123</v>
       </c>
       <c r="S20" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T20" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="U20" s="2">
         <v>46157</v>
@@ -2543,8 +2888,8 @@
       <c r="M21">
         <v>111.25</v>
       </c>
-      <c r="N21">
-        <v>2738</v>
+      <c r="N21" t="s">
+        <v>90</v>
       </c>
       <c r="O21">
         <v>4000</v>
@@ -2555,14 +2900,14 @@
       <c r="Q21" s="2">
         <v>46199</v>
       </c>
-      <c r="R21">
-        <v>3130008877</v>
+      <c r="R21" t="s">
+        <v>124</v>
       </c>
       <c r="S21" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="T21" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="U21" s="2">
         <v>46209</v>
@@ -2599,8 +2944,8 @@
       <c r="M22">
         <v>115.75</v>
       </c>
-      <c r="N22">
-        <v>2731</v>
+      <c r="N22" t="s">
+        <v>93</v>
       </c>
       <c r="O22">
         <v>4000</v>
@@ -2611,14 +2956,14 @@
       <c r="Q22" s="2">
         <v>45922</v>
       </c>
-      <c r="R22">
-        <v>3810138909</v>
+      <c r="R22" t="s">
+        <v>125</v>
       </c>
       <c r="S22" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T22" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="U22" s="2">
         <v>45995</v>
@@ -2652,8 +2997,8 @@
       <c r="L23">
         <v>5094.67</v>
       </c>
-      <c r="N23">
-        <v>2737</v>
+      <c r="N23" t="s">
+        <v>91</v>
       </c>
       <c r="O23">
         <v>4000</v>
@@ -2664,11 +3009,11 @@
       <c r="Q23" s="2">
         <v>45810</v>
       </c>
-      <c r="R23">
-        <v>3810138523</v>
+      <c r="R23" t="s">
+        <v>126</v>
       </c>
       <c r="S23" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="U23" s="2">
         <v>45810</v>
@@ -2705,8 +3050,8 @@
       <c r="M24">
         <v>77.38</v>
       </c>
-      <c r="N24">
-        <v>2741</v>
+      <c r="N24" t="s">
+        <v>95</v>
       </c>
       <c r="O24">
         <v>4000</v>
@@ -2717,11 +3062,11 @@
       <c r="Q24" s="2">
         <v>45925</v>
       </c>
-      <c r="R24">
-        <v>6890000683</v>
+      <c r="R24" t="s">
+        <v>127</v>
       </c>
       <c r="S24" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2755,8 +3100,8 @@
       <c r="M25">
         <v>121.42</v>
       </c>
-      <c r="N25">
-        <v>2704</v>
+      <c r="N25" t="s">
+        <v>96</v>
       </c>
       <c r="O25">
         <v>4000</v>
@@ -2767,11 +3112,11 @@
       <c r="Q25" s="2">
         <v>45062</v>
       </c>
-      <c r="R25">
-        <v>3810112732</v>
+      <c r="R25" t="s">
+        <v>128</v>
       </c>
       <c r="S25" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2805,8 +3150,8 @@
       <c r="M26">
         <v>133.71</v>
       </c>
-      <c r="N26">
-        <v>2742</v>
+      <c r="N26" t="s">
+        <v>84</v>
       </c>
       <c r="O26">
         <v>4000</v>
@@ -2817,14 +3162,14 @@
       <c r="Q26" s="2">
         <v>45916</v>
       </c>
-      <c r="R26">
-        <v>3810139780</v>
+      <c r="R26" t="s">
+        <v>129</v>
       </c>
       <c r="S26" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T26" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="U26" s="2">
         <v>46150</v>
@@ -2861,8 +3206,8 @@
       <c r="M27">
         <v>29.88</v>
       </c>
-      <c r="N27">
-        <v>2739</v>
+      <c r="N27" t="s">
+        <v>97</v>
       </c>
       <c r="O27">
         <v>4000</v>
@@ -2873,11 +3218,11 @@
       <c r="Q27" s="2">
         <v>45579</v>
       </c>
-      <c r="R27">
-        <v>3810126785</v>
+      <c r="R27" t="s">
+        <v>130</v>
       </c>
       <c r="S27" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2911,8 +3256,8 @@
       <c r="M28">
         <v>11.92</v>
       </c>
-      <c r="N28">
-        <v>2702</v>
+      <c r="N28" t="s">
+        <v>80</v>
       </c>
       <c r="O28">
         <v>4000</v>
@@ -2923,11 +3268,11 @@
       <c r="Q28" s="2">
         <v>46149</v>
       </c>
-      <c r="R28">
-        <v>3860011562</v>
+      <c r="R28" t="s">
+        <v>131</v>
       </c>
       <c r="S28" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2961,8 +3306,8 @@
       <c r="M29">
         <v>101.98</v>
       </c>
-      <c r="N29">
-        <v>2722</v>
+      <c r="N29" t="s">
+        <v>98</v>
       </c>
       <c r="O29">
         <v>4000</v>
@@ -2973,11 +3318,11 @@
       <c r="Q29" s="2">
         <v>44320</v>
       </c>
-      <c r="R29">
-        <v>3950001218</v>
+      <c r="R29" t="s">
+        <v>132</v>
       </c>
       <c r="S29" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -3011,8 +3356,8 @@
       <c r="M30">
         <v>83.67</v>
       </c>
-      <c r="N30">
-        <v>2724</v>
+      <c r="N30" t="s">
+        <v>99</v>
       </c>
       <c r="O30">
         <v>4000</v>
@@ -3023,14 +3368,14 @@
       <c r="Q30" s="2">
         <v>45252</v>
       </c>
-      <c r="R30">
-        <v>6890001058</v>
+      <c r="R30" t="s">
+        <v>133</v>
       </c>
       <c r="S30" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T30" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="U30" s="2">
         <v>45358</v>
@@ -3067,8 +3412,8 @@
       <c r="M31">
         <v>96.72</v>
       </c>
-      <c r="N31">
-        <v>2732</v>
+      <c r="N31" t="s">
+        <v>87</v>
       </c>
       <c r="O31">
         <v>4000</v>
@@ -3079,11 +3424,11 @@
       <c r="Q31" s="2">
         <v>46064</v>
       </c>
-      <c r="R31">
-        <v>3810118951</v>
+      <c r="R31" t="s">
+        <v>134</v>
       </c>
       <c r="S31" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3117,8 +3462,8 @@
       <c r="M32">
         <v>70.77</v>
       </c>
-      <c r="N32">
-        <v>2723</v>
+      <c r="N32" t="s">
+        <v>100</v>
       </c>
       <c r="O32">
         <v>4000</v>
@@ -3129,11 +3474,11 @@
       <c r="Q32" s="2">
         <v>43725</v>
       </c>
-      <c r="R32">
-        <v>7080002856</v>
+      <c r="R32" t="s">
+        <v>135</v>
       </c>
       <c r="S32" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3167,8 +3512,8 @@
       <c r="M33">
         <v>9.640000000000001</v>
       </c>
-      <c r="N33">
-        <v>2731</v>
+      <c r="N33" t="s">
+        <v>93</v>
       </c>
       <c r="O33">
         <v>4000</v>
@@ -3179,14 +3524,14 @@
       <c r="Q33" s="2">
         <v>43159</v>
       </c>
-      <c r="R33">
-        <v>3810129323</v>
+      <c r="R33" t="s">
+        <v>136</v>
       </c>
       <c r="S33" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="T33" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="U33" s="2">
         <v>43802</v>
@@ -3223,8 +3568,8 @@
       <c r="M34">
         <v>108.65</v>
       </c>
-      <c r="N34">
-        <v>2743</v>
+      <c r="N34" t="s">
+        <v>101</v>
       </c>
       <c r="O34">
         <v>4000</v>
@@ -3235,11 +3580,11 @@
       <c r="Q34" s="2">
         <v>44910</v>
       </c>
-      <c r="R34">
-        <v>3130005802</v>
+      <c r="R34" t="s">
+        <v>137</v>
       </c>
       <c r="S34" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3273,8 +3618,8 @@
       <c r="M35">
         <v>68.05</v>
       </c>
-      <c r="N35">
-        <v>2709</v>
+      <c r="N35" t="s">
+        <v>102</v>
       </c>
       <c r="O35">
         <v>4000</v>
@@ -3285,11 +3630,11 @@
       <c r="Q35" s="2">
         <v>41149</v>
       </c>
-      <c r="R35">
-        <v>3740026391</v>
+      <c r="R35" t="s">
+        <v>138</v>
       </c>
       <c r="S35" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -3323,8 +3668,8 @@
       <c r="M36">
         <v>79.41</v>
       </c>
-      <c r="N36">
-        <v>2720</v>
+      <c r="N36" t="s">
+        <v>103</v>
       </c>
       <c r="O36">
         <v>4000</v>
@@ -3335,11 +3680,11 @@
       <c r="Q36" s="2">
         <v>45754</v>
       </c>
-      <c r="R36">
-        <v>3290008244</v>
+      <c r="R36" t="s">
+        <v>139</v>
       </c>
       <c r="S36" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -3373,8 +3718,8 @@
       <c r="M37">
         <v>45.47</v>
       </c>
-      <c r="N37">
-        <v>2731</v>
+      <c r="N37" t="s">
+        <v>93</v>
       </c>
       <c r="O37">
         <v>4000</v>
@@ -3385,14 +3730,14 @@
       <c r="Q37" s="2">
         <v>45509</v>
       </c>
-      <c r="R37">
-        <v>3810139583</v>
+      <c r="R37" t="s">
+        <v>140</v>
       </c>
       <c r="S37" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T37" t="s">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="U37" s="2">
         <v>46184</v>
@@ -3429,8 +3774,8 @@
       <c r="M38">
         <v>70.81999999999999</v>
       </c>
-      <c r="N38">
-        <v>2729</v>
+      <c r="N38" t="s">
+        <v>104</v>
       </c>
       <c r="O38">
         <v>4000</v>
@@ -3442,10 +3787,10 @@
         <v>45579</v>
       </c>
       <c r="S38" t="s">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="V38" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -3479,8 +3824,8 @@
       <c r="M39">
         <v>97.23999999999999</v>
       </c>
-      <c r="N39">
-        <v>2736</v>
+      <c r="N39" t="s">
+        <v>92</v>
       </c>
       <c r="O39">
         <v>4000</v>
@@ -3492,7 +3837,7 @@
         <v>45740</v>
       </c>
       <c r="S39" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -3526,8 +3871,8 @@
       <c r="M40">
         <v>56.08</v>
       </c>
-      <c r="N40">
-        <v>2708</v>
+      <c r="N40" t="s">
+        <v>105</v>
       </c>
       <c r="O40">
         <v>4000</v>
@@ -3538,11 +3883,11 @@
       <c r="Q40" s="2">
         <v>44114</v>
       </c>
-      <c r="R40">
-        <v>7080004330</v>
+      <c r="R40" t="s">
+        <v>141</v>
       </c>
       <c r="S40" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3557,22 +3902,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3589,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3606,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3623,7 +3968,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3640,7 +3985,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3657,17 +4002,17 @@
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F6" t="s">
-        <v>153</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>59</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="b">
         <v>0</v>
       </c>
       <c r="C7">
@@ -3677,14 +4022,14 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>59</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="b">
         <v>0</v>
       </c>
       <c r="C8">
@@ -3694,14 +4039,14 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>59</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="b">
         <v>0</v>
       </c>
       <c r="C9">
@@ -3711,14 +4056,14 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>59</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="b">
         <v>0</v>
       </c>
       <c r="C10">
@@ -3728,14 +4073,14 @@
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>59</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="b">
         <v>0</v>
       </c>
       <c r="C11">
@@ -3745,14 +4090,14 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>59</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="b">
         <v>0</v>
       </c>
       <c r="C12">
@@ -3762,14 +4107,14 @@
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>59</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="b">
         <v>0</v>
       </c>
       <c r="C13">
@@ -3779,10 +4124,10 @@
         <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F13" t="s">
-        <v>154</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3799,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3816,7 +4161,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3833,7 +4178,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3850,10 +4195,10 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F17" t="s">
-        <v>155</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3870,7 +4215,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3887,7 +4232,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3904,7 +4249,7 @@
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3921,7 +4266,7 @@
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3938,7 +4283,7 @@
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3955,7 +4300,7 @@
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3972,10 +4317,10 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F24" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3992,7 +4337,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4009,7 +4354,7 @@
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4026,7 +4371,7 @@
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4043,7 +4388,7 @@
         <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4060,7 +4405,7 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4077,7 +4422,7 @@
         <v>6</v>
       </c>
       <c r="E30" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4094,7 +4439,7 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4111,7 +4456,7 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4128,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4145,7 +4490,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4162,7 +4507,7 @@
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4179,7 +4524,7 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4196,7 +4541,7 @@
         <v>6</v>
       </c>
       <c r="E37" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4213,10 +4558,10 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="F38" t="s">
-        <v>157</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4233,7 +4578,7 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4250,7 +4595,7 @@
         <v>8</v>
       </c>
       <c r="E40" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4267,7 +4612,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4284,7 +4629,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4301,7 +4646,7 @@
         <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4318,7 +4663,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4335,10 +4680,10 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F45" t="s">
-        <v>158</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -4355,7 +4700,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4372,7 +4717,7 @@
         <v>2</v>
       </c>
       <c r="E47" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -4389,7 +4734,7 @@
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -4406,7 +4751,7 @@
         <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4423,7 +4768,7 @@
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -4440,10 +4785,10 @@
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="F51" t="s">
-        <v>159</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -4460,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4477,7 +4822,7 @@
         <v>2</v>
       </c>
       <c r="E53" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -4494,7 +4839,7 @@
         <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -4511,7 +4856,7 @@
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -4528,7 +4873,7 @@
         <v>5</v>
       </c>
       <c r="E56" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -4545,7 +4890,7 @@
         <v>6</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -4562,7 +4907,7 @@
         <v>7</v>
       </c>
       <c r="E58" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4579,10 +4924,10 @@
         <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="F59" t="s">
-        <v>160</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4599,14 +4944,14 @@
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>76</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="b">
         <v>0</v>
       </c>
       <c r="C61">
@@ -4616,14 +4961,14 @@
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>76</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="b">
         <v>0</v>
       </c>
       <c r="C62">
@@ -4633,14 +4978,14 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>76</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="b">
         <v>0</v>
       </c>
       <c r="C63">
@@ -4650,14 +4995,14 @@
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>76</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="b">
         <v>0</v>
       </c>
       <c r="C64">
@@ -4667,14 +5012,14 @@
         <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>76</v>
       </c>
-      <c r="B65">
+      <c r="B65" t="b">
         <v>0</v>
       </c>
       <c r="C65">
@@ -4684,14 +5029,14 @@
         <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>76</v>
       </c>
-      <c r="B66">
+      <c r="B66" t="b">
         <v>0</v>
       </c>
       <c r="C66">
@@ -4701,17 +5046,17 @@
         <v>6</v>
       </c>
       <c r="E66" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="F66" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>76</v>
       </c>
-      <c r="B67">
+      <c r="B67" t="b">
         <v>0</v>
       </c>
       <c r="C67">
@@ -4719,13 +5064,16 @@
       </c>
       <c r="D67">
         <v>7</v>
+      </c>
+      <c r="E67" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>76</v>
       </c>
-      <c r="B68">
+      <c r="B68" t="b">
         <v>0</v>
       </c>
       <c r="C68">
@@ -4735,14 +5083,14 @@
         <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>76</v>
       </c>
-      <c r="B69">
+      <c r="B69" t="b">
         <v>0</v>
       </c>
       <c r="C69">
@@ -4752,7 +5100,7 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4769,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -4786,7 +5134,7 @@
         <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4803,7 +5151,7 @@
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -4820,7 +5168,7 @@
         <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4837,7 +5185,7 @@
         <v>7</v>
       </c>
       <c r="E74" t="s">
-        <v>127</v>
+        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4854,7 +5202,7 @@
         <v>6</v>
       </c>
       <c r="E75" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -4871,7 +5219,7 @@
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -4888,7 +5236,7 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -4905,7 +5253,7 @@
         <v>3</v>
       </c>
       <c r="E78" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -4922,7 +5270,7 @@
         <v>4</v>
       </c>
       <c r="E79" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -4939,7 +5287,7 @@
         <v>5</v>
       </c>
       <c r="E80" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4956,7 +5304,7 @@
         <v>5</v>
       </c>
       <c r="E81" t="s">
-        <v>128</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4973,7 +5321,7 @@
         <v>6</v>
       </c>
       <c r="E82" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4990,7 +5338,7 @@
         <v>7</v>
       </c>
       <c r="E83" t="s">
-        <v>129</v>
+        <v>190</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -5007,7 +5355,7 @@
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -5024,7 +5372,7 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -5041,7 +5389,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -5058,7 +5406,7 @@
         <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -5075,7 +5423,7 @@
         <v>3</v>
       </c>
       <c r="E88" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -5092,7 +5440,7 @@
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -5109,7 +5457,7 @@
         <v>8</v>
       </c>
       <c r="E90" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -5126,7 +5474,7 @@
         <v>10</v>
       </c>
       <c r="E91" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -5143,7 +5491,7 @@
         <v>7</v>
       </c>
       <c r="E92" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -5160,7 +5508,7 @@
         <v>7</v>
       </c>
       <c r="E93" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -5177,7 +5525,7 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -5194,7 +5542,7 @@
         <v>2</v>
       </c>
       <c r="E95" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -5211,7 +5559,7 @@
         <v>3</v>
       </c>
       <c r="E96" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -5228,7 +5576,7 @@
         <v>10</v>
       </c>
       <c r="E97" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -5245,7 +5593,7 @@
         <v>5</v>
       </c>
       <c r="E98" t="s">
-        <v>131</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -5262,7 +5610,7 @@
         <v>6</v>
       </c>
       <c r="E99" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -5279,7 +5627,7 @@
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -5296,7 +5644,7 @@
         <v>6</v>
       </c>
       <c r="E101" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -5313,7 +5661,7 @@
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5330,7 +5678,7 @@
         <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5347,7 +5695,7 @@
         <v>3</v>
       </c>
       <c r="E104" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5364,7 +5712,7 @@
         <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5381,7 +5729,7 @@
         <v>5</v>
       </c>
       <c r="E106" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5398,7 +5746,7 @@
         <v>10</v>
       </c>
       <c r="E107" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5415,7 +5763,7 @@
         <v>7</v>
       </c>
       <c r="E108" t="s">
-        <v>134</v>
+        <v>195</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5432,7 +5780,7 @@
         <v>2</v>
       </c>
       <c r="E109" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5449,7 +5797,7 @@
         <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5466,7 +5814,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5483,7 +5831,7 @@
         <v>3</v>
       </c>
       <c r="E112" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -5500,7 +5848,7 @@
         <v>10</v>
       </c>
       <c r="E113" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -5517,10 +5865,10 @@
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="F114" t="s">
-        <v>162</v>
+        <v>223</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -5537,7 +5885,7 @@
         <v>7</v>
       </c>
       <c r="E115" t="s">
-        <v>136</v>
+        <v>197</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -5554,10 +5902,10 @@
         <v>8</v>
       </c>
       <c r="E116" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F116" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -5574,7 +5922,7 @@
         <v>1</v>
       </c>
       <c r="E117" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -5591,7 +5939,7 @@
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -5608,7 +5956,7 @@
         <v>3</v>
       </c>
       <c r="E119" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -5625,7 +5973,7 @@
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -5642,7 +5990,7 @@
         <v>10</v>
       </c>
       <c r="E121" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -5659,7 +6007,7 @@
         <v>7</v>
       </c>
       <c r="E122" t="s">
-        <v>137</v>
+        <v>198</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -5676,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="E123" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -5693,7 +6041,7 @@
         <v>4</v>
       </c>
       <c r="E124" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -5710,7 +6058,7 @@
         <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5727,7 +6075,7 @@
         <v>2</v>
       </c>
       <c r="E126" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -5744,7 +6092,7 @@
         <v>3</v>
       </c>
       <c r="E127" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5761,7 +6109,7 @@
         <v>10</v>
       </c>
       <c r="E128" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -5778,7 +6126,7 @@
         <v>5</v>
       </c>
       <c r="E129" t="s">
-        <v>139</v>
+        <v>200</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -5795,7 +6143,7 @@
         <v>6</v>
       </c>
       <c r="E130" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -5812,7 +6160,7 @@
         <v>7</v>
       </c>
       <c r="E131" t="s">
-        <v>141</v>
+        <v>202</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -5829,7 +6177,7 @@
         <v>5</v>
       </c>
       <c r="E132" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -5846,7 +6194,7 @@
         <v>4</v>
       </c>
       <c r="E133" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -5863,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -5880,7 +6228,7 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -5897,7 +6245,7 @@
         <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -5914,7 +6262,7 @@
         <v>4</v>
       </c>
       <c r="E137" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -5931,7 +6279,7 @@
         <v>5</v>
       </c>
       <c r="E138" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -5948,7 +6296,7 @@
         <v>6</v>
       </c>
       <c r="E139" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -5965,7 +6313,7 @@
         <v>7</v>
       </c>
       <c r="E140" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -5982,14 +6330,14 @@
         <v>11</v>
       </c>
       <c r="E141" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
         <v>43</v>
       </c>
-      <c r="B142">
+      <c r="B142" t="b">
         <v>0</v>
       </c>
       <c r="C142">
@@ -5999,14 +6347,14 @@
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
         <v>56</v>
       </c>
-      <c r="B143">
+      <c r="B143" t="b">
         <v>0</v>
       </c>
       <c r="C143">
@@ -6016,14 +6364,14 @@
         <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
         <v>56</v>
       </c>
-      <c r="B144">
+      <c r="B144" t="b">
         <v>0</v>
       </c>
       <c r="C144">
@@ -6033,14 +6381,14 @@
         <v>2</v>
       </c>
       <c r="E144" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
         <v>56</v>
       </c>
-      <c r="B145">
+      <c r="B145" t="b">
         <v>0</v>
       </c>
       <c r="C145">
@@ -6050,14 +6398,14 @@
         <v>3</v>
       </c>
       <c r="E145" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
         <v>56</v>
       </c>
-      <c r="B146">
+      <c r="B146" t="b">
         <v>0</v>
       </c>
       <c r="C146">
@@ -6067,14 +6415,14 @@
         <v>4</v>
       </c>
       <c r="E146" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
         <v>56</v>
       </c>
-      <c r="B147">
+      <c r="B147" t="b">
         <v>0</v>
       </c>
       <c r="C147">
@@ -6084,14 +6432,14 @@
         <v>5</v>
       </c>
       <c r="E147" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
         <v>56</v>
       </c>
-      <c r="B148">
+      <c r="B148" t="b">
         <v>0</v>
       </c>
       <c r="C148">
@@ -6101,14 +6449,14 @@
         <v>10</v>
       </c>
       <c r="E148" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
         <v>56</v>
       </c>
-      <c r="B149">
+      <c r="B149" t="b">
         <v>0</v>
       </c>
       <c r="C149">
@@ -6118,14 +6466,14 @@
         <v>6</v>
       </c>
       <c r="E149" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
         <v>56</v>
       </c>
-      <c r="B150">
+      <c r="B150" t="b">
         <v>0</v>
       </c>
       <c r="C150">
@@ -6135,7 +6483,7 @@
         <v>8</v>
       </c>
       <c r="E150" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -6152,7 +6500,7 @@
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -6169,7 +6517,7 @@
         <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -6186,7 +6534,7 @@
         <v>3</v>
       </c>
       <c r="E153" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -6203,7 +6551,7 @@
         <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -6220,7 +6568,7 @@
         <v>4</v>
       </c>
       <c r="E155" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -6237,7 +6585,7 @@
         <v>6</v>
       </c>
       <c r="E156" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -6254,7 +6602,7 @@
         <v>7</v>
       </c>
       <c r="E157" t="s">
-        <v>147</v>
+        <v>208</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -6271,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -6288,7 +6636,7 @@
         <v>2</v>
       </c>
       <c r="E159" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -6305,7 +6653,7 @@
         <v>3</v>
       </c>
       <c r="E160" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -6322,7 +6670,7 @@
         <v>4</v>
       </c>
       <c r="E161" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -6339,7 +6687,7 @@
         <v>5</v>
       </c>
       <c r="E162" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -6356,7 +6704,7 @@
         <v>7</v>
       </c>
       <c r="E163" t="s">
-        <v>148</v>
+        <v>209</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -6373,14 +6721,14 @@
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
         <v>49</v>
       </c>
-      <c r="B165">
+      <c r="B165" t="b">
         <v>0</v>
       </c>
       <c r="C165">
@@ -6390,14 +6738,14 @@
         <v>5</v>
       </c>
       <c r="E165" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
         <v>45</v>
       </c>
-      <c r="B166">
+      <c r="B166" t="b">
         <v>0</v>
       </c>
       <c r="C166">
@@ -6407,14 +6755,14 @@
         <v>1</v>
       </c>
       <c r="E166" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
         <v>45</v>
       </c>
-      <c r="B167">
+      <c r="B167" t="b">
         <v>0</v>
       </c>
       <c r="C167">
@@ -6424,14 +6772,14 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
         <v>45</v>
       </c>
-      <c r="B168">
+      <c r="B168" t="b">
         <v>0</v>
       </c>
       <c r="C168">
@@ -6441,14 +6789,14 @@
         <v>3</v>
       </c>
       <c r="E168" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" t="s">
         <v>45</v>
       </c>
-      <c r="B169">
+      <c r="B169" t="b">
         <v>0</v>
       </c>
       <c r="C169">
@@ -6458,14 +6806,14 @@
         <v>4</v>
       </c>
       <c r="E169" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" t="s">
         <v>45</v>
       </c>
-      <c r="B170">
+      <c r="B170" t="b">
         <v>0</v>
       </c>
       <c r="C170">
@@ -6475,14 +6823,14 @@
         <v>5</v>
       </c>
       <c r="E170" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
         <v>47</v>
       </c>
-      <c r="B171">
+      <c r="B171" t="b">
         <v>0</v>
       </c>
       <c r="C171">
@@ -6492,14 +6840,14 @@
         <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
         <v>47</v>
       </c>
-      <c r="B172">
+      <c r="B172" t="b">
         <v>0</v>
       </c>
       <c r="C172">
@@ -6509,14 +6857,14 @@
         <v>2</v>
       </c>
       <c r="E172" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
         <v>47</v>
       </c>
-      <c r="B173">
+      <c r="B173" t="b">
         <v>0</v>
       </c>
       <c r="C173">
@@ -6526,14 +6874,14 @@
         <v>3</v>
       </c>
       <c r="E173" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" t="s">
         <v>47</v>
       </c>
-      <c r="B174">
+      <c r="B174" t="b">
         <v>0</v>
       </c>
       <c r="C174">
@@ -6543,14 +6891,14 @@
         <v>4</v>
       </c>
       <c r="E174" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" t="s">
         <v>47</v>
       </c>
-      <c r="B175">
+      <c r="B175" t="b">
         <v>0</v>
       </c>
       <c r="C175">
@@ -6560,14 +6908,14 @@
         <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
         <v>40</v>
       </c>
-      <c r="B176">
+      <c r="B176" t="b">
         <v>0</v>
       </c>
       <c r="C176">
@@ -6577,14 +6925,14 @@
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>40</v>
       </c>
-      <c r="B177">
+      <c r="B177" t="b">
         <v>0</v>
       </c>
       <c r="C177">
@@ -6594,14 +6942,14 @@
         <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>40</v>
       </c>
-      <c r="B178">
+      <c r="B178" t="b">
         <v>0</v>
       </c>
       <c r="C178">
@@ -6611,14 +6959,14 @@
         <v>3</v>
       </c>
       <c r="E178" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>40</v>
       </c>
-      <c r="B179">
+      <c r="B179" t="b">
         <v>0</v>
       </c>
       <c r="C179">
@@ -6628,17 +6976,17 @@
         <v>8</v>
       </c>
       <c r="E179" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F179" t="s">
-        <v>164</v>
+        <v>225</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>40</v>
       </c>
-      <c r="B180">
+      <c r="B180" t="b">
         <v>0</v>
       </c>
       <c r="C180">
@@ -6648,14 +6996,14 @@
         <v>10</v>
       </c>
       <c r="E180" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>40</v>
       </c>
-      <c r="B181">
+      <c r="B181" t="b">
         <v>0</v>
       </c>
       <c r="C181">
@@ -6665,14 +7013,14 @@
         <v>4</v>
       </c>
       <c r="E181" t="s">
-        <v>150</v>
+        <v>211</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>40</v>
       </c>
-      <c r="B182">
+      <c r="B182" t="b">
         <v>0</v>
       </c>
       <c r="C182">
@@ -6682,10 +7030,10 @@
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F182" t="s">
-        <v>165</v>
+        <v>226</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -6702,7 +7050,7 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -6719,7 +7067,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -6736,7 +7084,7 @@
         <v>3</v>
       </c>
       <c r="E185" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -6753,7 +7101,7 @@
         <v>4</v>
       </c>
       <c r="E186" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -6770,7 +7118,7 @@
         <v>5</v>
       </c>
       <c r="E187" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -6787,7 +7135,7 @@
         <v>7</v>
       </c>
       <c r="E188" t="s">
-        <v>151</v>
+        <v>212</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -6804,14 +7152,14 @@
         <v>3</v>
       </c>
       <c r="E189" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>54</v>
       </c>
-      <c r="B190">
+      <c r="B190" t="b">
         <v>0</v>
       </c>
       <c r="C190">
@@ -6821,14 +7169,14 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
         <v>54</v>
       </c>
-      <c r="B191">
+      <c r="B191" t="b">
         <v>0</v>
       </c>
       <c r="C191">
@@ -6838,14 +7186,14 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
         <v>54</v>
       </c>
-      <c r="B192">
+      <c r="B192" t="b">
         <v>0</v>
       </c>
       <c r="C192">
@@ -6855,14 +7203,14 @@
         <v>3</v>
       </c>
       <c r="E192" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>54</v>
       </c>
-      <c r="B193">
+      <c r="B193" t="b">
         <v>0</v>
       </c>
       <c r="C193">
@@ -6872,14 +7220,14 @@
         <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>54</v>
       </c>
-      <c r="B194">
+      <c r="B194" t="b">
         <v>0</v>
       </c>
       <c r="C194">
@@ -6889,14 +7237,14 @@
         <v>5</v>
       </c>
       <c r="E194" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>57</v>
       </c>
-      <c r="B195">
+      <c r="B195" t="b">
         <v>0</v>
       </c>
       <c r="C195">
@@ -6906,14 +7254,14 @@
         <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>57</v>
       </c>
-      <c r="B196">
+      <c r="B196" t="b">
         <v>0</v>
       </c>
       <c r="C196">
@@ -6923,14 +7271,14 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>57</v>
       </c>
-      <c r="B197">
+      <c r="B197" t="b">
         <v>0</v>
       </c>
       <c r="C197">
@@ -6940,14 +7288,14 @@
         <v>3</v>
       </c>
       <c r="E197" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>57</v>
       </c>
-      <c r="B198">
+      <c r="B198" t="b">
         <v>0</v>
       </c>
       <c r="C198">
@@ -6957,14 +7305,14 @@
         <v>4</v>
       </c>
       <c r="E198" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
         <v>57</v>
       </c>
-      <c r="B199">
+      <c r="B199" t="b">
         <v>0</v>
       </c>
       <c r="C199">
@@ -6974,14 +7322,14 @@
         <v>5</v>
       </c>
       <c r="E199" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>57</v>
       </c>
-      <c r="B200">
+      <c r="B200" t="b">
         <v>0</v>
       </c>
       <c r="C200">
@@ -6991,17 +7339,17 @@
         <v>8</v>
       </c>
       <c r="E200" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F200" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>57</v>
       </c>
-      <c r="B201">
+      <c r="B201" t="b">
         <v>0</v>
       </c>
       <c r="C201">
@@ -7011,14 +7359,14 @@
         <v>10</v>
       </c>
       <c r="E201" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>57</v>
       </c>
-      <c r="B202">
+      <c r="B202" t="b">
         <v>0</v>
       </c>
       <c r="C202">
@@ -7028,17 +7376,17 @@
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F202" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>58</v>
       </c>
-      <c r="B203">
+      <c r="B203" t="b">
         <v>0</v>
       </c>
       <c r="C203">
@@ -7048,14 +7396,14 @@
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>58</v>
       </c>
-      <c r="B204">
+      <c r="B204" t="b">
         <v>0</v>
       </c>
       <c r="C204">
@@ -7065,14 +7413,14 @@
         <v>2</v>
       </c>
       <c r="E204" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>58</v>
       </c>
-      <c r="B205">
+      <c r="B205" t="b">
         <v>0</v>
       </c>
       <c r="C205">
@@ -7082,14 +7430,14 @@
         <v>3</v>
       </c>
       <c r="E205" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>60</v>
       </c>
-      <c r="B206">
+      <c r="B206" t="b">
         <v>0</v>
       </c>
       <c r="C206">
@@ -7099,14 +7447,14 @@
         <v>1</v>
       </c>
       <c r="E206" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>60</v>
       </c>
-      <c r="B207">
+      <c r="B207" t="b">
         <v>0</v>
       </c>
       <c r="C207">
@@ -7116,14 +7464,14 @@
         <v>2</v>
       </c>
       <c r="E207" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>60</v>
       </c>
-      <c r="B208">
+      <c r="B208" t="b">
         <v>0</v>
       </c>
       <c r="C208">
@@ -7133,14 +7481,14 @@
         <v>3</v>
       </c>
       <c r="E208" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
         <v>60</v>
       </c>
-      <c r="B209">
+      <c r="B209" t="b">
         <v>0</v>
       </c>
       <c r="C209">
@@ -7150,14 +7498,14 @@
         <v>8</v>
       </c>
       <c r="E209" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
         <v>60</v>
       </c>
-      <c r="B210">
+      <c r="B210" t="b">
         <v>0</v>
       </c>
       <c r="C210">
@@ -7167,14 +7515,14 @@
         <v>9</v>
       </c>
       <c r="E210" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
         <v>61</v>
       </c>
-      <c r="B211">
+      <c r="B211" t="b">
         <v>0</v>
       </c>
       <c r="C211">
@@ -7184,14 +7532,14 @@
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
         <v>61</v>
       </c>
-      <c r="B212">
+      <c r="B212" t="b">
         <v>0</v>
       </c>
       <c r="C212">
@@ -7201,14 +7549,14 @@
         <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
         <v>61</v>
       </c>
-      <c r="B213">
+      <c r="B213" t="b">
         <v>0</v>
       </c>
       <c r="C213">
@@ -7218,14 +7566,14 @@
         <v>3</v>
       </c>
       <c r="E213" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
         <v>64</v>
       </c>
-      <c r="B214">
+      <c r="B214" t="b">
         <v>0</v>
       </c>
       <c r="C214">
@@ -7235,14 +7583,14 @@
         <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
         <v>64</v>
       </c>
-      <c r="B215">
+      <c r="B215" t="b">
         <v>0</v>
       </c>
       <c r="C215">
@@ -7252,14 +7600,14 @@
         <v>2</v>
       </c>
       <c r="E215" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
         <v>64</v>
       </c>
-      <c r="B216">
+      <c r="B216" t="b">
         <v>0</v>
       </c>
       <c r="C216">
@@ -7269,14 +7617,14 @@
         <v>3</v>
       </c>
       <c r="E216" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
         <v>64</v>
       </c>
-      <c r="B217">
+      <c r="B217" t="b">
         <v>0</v>
       </c>
       <c r="C217">
@@ -7286,17 +7634,17 @@
         <v>8</v>
       </c>
       <c r="E217" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F217" t="s">
-        <v>167</v>
+        <v>228</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
         <v>64</v>
       </c>
-      <c r="B218">
+      <c r="B218" t="b">
         <v>0</v>
       </c>
       <c r="C218">
@@ -7306,17 +7654,17 @@
         <v>9</v>
       </c>
       <c r="E218" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F218" t="s">
-        <v>167</v>
+        <v>228</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
         <v>68</v>
       </c>
-      <c r="B219">
+      <c r="B219" t="b">
         <v>0</v>
       </c>
       <c r="C219">
@@ -7326,14 +7674,14 @@
         <v>1</v>
       </c>
       <c r="E219" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
         <v>68</v>
       </c>
-      <c r="B220">
+      <c r="B220" t="b">
         <v>0</v>
       </c>
       <c r="C220">
@@ -7343,14 +7691,14 @@
         <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
         <v>68</v>
       </c>
-      <c r="B221">
+      <c r="B221" t="b">
         <v>0</v>
       </c>
       <c r="C221">
@@ -7360,14 +7708,14 @@
         <v>3</v>
       </c>
       <c r="E221" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
         <v>68</v>
       </c>
-      <c r="B222">
+      <c r="B222" t="b">
         <v>0</v>
       </c>
       <c r="C222">
@@ -7377,14 +7725,14 @@
         <v>4</v>
       </c>
       <c r="E222" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
         <v>68</v>
       </c>
-      <c r="B223">
+      <c r="B223" t="b">
         <v>0</v>
       </c>
       <c r="C223">
@@ -7394,7 +7742,7 @@
         <v>5</v>
       </c>
       <c r="E223" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -7411,7 +7759,7 @@
         <v>1</v>
       </c>
       <c r="E224" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -7428,7 +7776,7 @@
         <v>2</v>
       </c>
       <c r="E225" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -7445,7 +7793,7 @@
         <v>3</v>
       </c>
       <c r="E226" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -7462,7 +7810,7 @@
         <v>4</v>
       </c>
       <c r="E227" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -7479,7 +7827,7 @@
         <v>5</v>
       </c>
       <c r="E228" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -7496,7 +7844,7 @@
         <v>10</v>
       </c>
       <c r="E229" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -7513,7 +7861,7 @@
         <v>7</v>
       </c>
       <c r="E230" t="s">
-        <v>152</v>
+        <v>213</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -7530,14 +7878,14 @@
         <v>10</v>
       </c>
       <c r="E231" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" t="s">
         <v>71</v>
       </c>
-      <c r="B232">
+      <c r="B232" t="b">
         <v>0</v>
       </c>
       <c r="C232">
@@ -7547,14 +7895,14 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" t="s">
         <v>71</v>
       </c>
-      <c r="B233">
+      <c r="B233" t="b">
         <v>0</v>
       </c>
       <c r="C233">
@@ -7564,14 +7912,14 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" t="s">
         <v>71</v>
       </c>
-      <c r="B234">
+      <c r="B234" t="b">
         <v>0</v>
       </c>
       <c r="C234">
@@ -7581,14 +7929,14 @@
         <v>3</v>
       </c>
       <c r="E234" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" t="s">
         <v>71</v>
       </c>
-      <c r="B235">
+      <c r="B235" t="b">
         <v>0</v>
       </c>
       <c r="C235">
@@ -7598,14 +7946,14 @@
         <v>4</v>
       </c>
       <c r="E235" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
         <v>71</v>
       </c>
-      <c r="B236">
+      <c r="B236" t="b">
         <v>0</v>
       </c>
       <c r="C236">
@@ -7615,14 +7963,14 @@
         <v>5</v>
       </c>
       <c r="E236" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" t="s">
         <v>52</v>
       </c>
-      <c r="B237">
+      <c r="B237" t="b">
         <v>0</v>
       </c>
       <c r="C237">
@@ -7632,14 +7980,14 @@
         <v>1</v>
       </c>
       <c r="E237" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
         <v>52</v>
       </c>
-      <c r="B238">
+      <c r="B238" t="b">
         <v>0</v>
       </c>
       <c r="C238">
@@ -7649,14 +7997,14 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" t="s">
         <v>52</v>
       </c>
-      <c r="B239">
+      <c r="B239" t="b">
         <v>0</v>
       </c>
       <c r="C239">
@@ -7666,14 +8014,14 @@
         <v>3</v>
       </c>
       <c r="E239" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
         <v>52</v>
       </c>
-      <c r="B240">
+      <c r="B240" t="b">
         <v>0</v>
       </c>
       <c r="C240">
@@ -7683,14 +8031,14 @@
         <v>10</v>
       </c>
       <c r="E240" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
         <v>75</v>
       </c>
-      <c r="B241">
+      <c r="B241" t="b">
         <v>0</v>
       </c>
       <c r="C241">
@@ -7700,14 +8048,14 @@
         <v>1</v>
       </c>
       <c r="E241" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" t="s">
         <v>75</v>
       </c>
-      <c r="B242">
+      <c r="B242" t="b">
         <v>0</v>
       </c>
       <c r="C242">
@@ -7717,14 +8065,14 @@
         <v>2</v>
       </c>
       <c r="E242" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" t="s">
         <v>75</v>
       </c>
-      <c r="B243">
+      <c r="B243" t="b">
         <v>0</v>
       </c>
       <c r="C243">
@@ -7734,14 +8082,14 @@
         <v>3</v>
       </c>
       <c r="E243" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" t="s">
         <v>75</v>
       </c>
-      <c r="B244">
+      <c r="B244" t="b">
         <v>0</v>
       </c>
       <c r="C244">
@@ -7751,14 +8099,14 @@
         <v>4</v>
       </c>
       <c r="E244" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" t="s">
         <v>75</v>
       </c>
-      <c r="B245">
+      <c r="B245" t="b">
         <v>0</v>
       </c>
       <c r="C245">
@@ -7768,7 +8116,7 @@
         <v>5</v>
       </c>
       <c r="E245" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -7783,34 +8131,34 @@
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>229</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>173</v>
+        <v>234</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
@@ -7819,55 +8167,55 @@
         <v>13</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>176</v>
+        <v>237</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>177</v>
+        <v>238</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>185</v>
+        <v>246</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>186</v>
+        <v>247</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>187</v>
+        <v>248</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>188</v>
+        <v>249</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>189</v>
+        <v>250</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>190</v>
+        <v>251</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>191</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:29">
@@ -7875,28 +8223,28 @@
         <v>3810267428</v>
       </c>
       <c r="C2" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="D2" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="E2" s="2">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="G2" s="2">
         <v>45492</v>
       </c>
-      <c r="H2">
-        <v>3044000</v>
+      <c r="H2" t="s">
+        <v>36</v>
       </c>
       <c r="I2">
         <v>198</v>
       </c>
       <c r="J2" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K2" t="s">
         <v>58</v>
@@ -7914,28 +8262,28 @@
         <v>45492</v>
       </c>
       <c r="U2" t="s">
-        <v>200</v>
-      </c>
-      <c r="V2">
-        <v>313240015920</v>
+        <v>261</v>
+      </c>
+      <c r="V2" t="s">
+        <v>263</v>
       </c>
       <c r="W2" t="s">
         <v>22</v>
       </c>
       <c r="X2" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y2">
-        <v>3810496453</v>
+        <v>265</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>269</v>
       </c>
       <c r="Z2" t="s">
-        <v>206</v>
+        <v>282</v>
       </c>
       <c r="AA2" t="s">
-        <v>209</v>
+        <v>285</v>
       </c>
       <c r="AB2" t="s">
-        <v>214</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -7943,28 +8291,28 @@
         <v>3810269967</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="D3" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E3" s="2">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="G3" s="2">
         <v>45631</v>
       </c>
-      <c r="H3">
-        <v>3044000</v>
+      <c r="H3" t="s">
+        <v>36</v>
       </c>
       <c r="I3">
         <v>198</v>
       </c>
       <c r="J3" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K3" t="s">
         <v>75</v>
@@ -7982,25 +8330,25 @@
         <v>45631</v>
       </c>
       <c r="U3" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W3" t="s">
         <v>22</v>
       </c>
       <c r="X3" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y3">
-        <v>3810499719</v>
+        <v>265</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>270</v>
       </c>
       <c r="Z3" t="s">
-        <v>207</v>
+        <v>283</v>
       </c>
       <c r="AA3" t="s">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="AB3" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -8008,28 +8356,28 @@
         <v>3810271134</v>
       </c>
       <c r="C4" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="D4" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E4" s="2">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="G4" s="2">
         <v>45716</v>
       </c>
-      <c r="H4">
-        <v>3044000</v>
+      <c r="H4" t="s">
+        <v>36</v>
       </c>
       <c r="I4">
         <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K4" t="s">
         <v>54</v>
@@ -8047,25 +8395,25 @@
         <v>45716</v>
       </c>
       <c r="U4" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W4" t="s">
         <v>22</v>
       </c>
       <c r="X4" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y4">
-        <v>3810500784</v>
+        <v>265</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>271</v>
       </c>
       <c r="Z4" t="s">
-        <v>206</v>
+        <v>282</v>
       </c>
       <c r="AA4" t="s">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="AB4" t="s">
-        <v>214</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -8073,28 +8421,28 @@
         <v>3810271161</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="D5" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E5" s="2">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="G5" s="2">
         <v>45728</v>
       </c>
-      <c r="H5">
-        <v>3044000</v>
+      <c r="H5" t="s">
+        <v>36</v>
       </c>
       <c r="I5">
         <v>198</v>
       </c>
       <c r="J5" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K5" t="s">
         <v>44</v>
@@ -8112,25 +8460,25 @@
         <v>45728</v>
       </c>
       <c r="U5" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W5" t="s">
         <v>22</v>
       </c>
       <c r="X5" t="s">
-        <v>202</v>
-      </c>
-      <c r="Y5">
-        <v>3810501279</v>
+        <v>265</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>272</v>
       </c>
       <c r="Z5" t="s">
-        <v>206</v>
+        <v>282</v>
       </c>
       <c r="AA5" t="s">
-        <v>209</v>
+        <v>285</v>
       </c>
       <c r="AB5" t="s">
-        <v>214</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -8141,28 +8489,28 @@
         <v>3810271161</v>
       </c>
       <c r="C6" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="D6" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E6" s="2">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="G6" s="2">
         <v>45755</v>
       </c>
-      <c r="H6">
-        <v>3044000</v>
+      <c r="H6" t="s">
+        <v>36</v>
       </c>
       <c r="I6">
         <v>198</v>
       </c>
       <c r="J6" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K6" t="s">
         <v>44</v>
@@ -8180,25 +8528,25 @@
         <v>45755</v>
       </c>
       <c r="U6" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W6" t="s">
         <v>22</v>
       </c>
       <c r="X6" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y6">
-        <v>3810502614</v>
+        <v>266</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>273</v>
       </c>
       <c r="Z6" t="s">
         <v>22</v>
       </c>
       <c r="AA6" t="s">
-        <v>202</v>
+        <v>265</v>
       </c>
       <c r="AB6" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -8209,25 +8557,25 @@
         <v>3810272114</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="E7" s="2">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H7">
-        <v>3044000</v>
+        <v>258</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
       </c>
       <c r="I7">
         <v>198</v>
       </c>
       <c r="J7" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K7" t="s">
         <v>44</v>
@@ -8242,25 +8590,25 @@
         <v>45775</v>
       </c>
       <c r="U7" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W7" t="s">
         <v>22</v>
       </c>
       <c r="X7" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y7">
-        <v>3810504268</v>
+        <v>266</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>274</v>
       </c>
       <c r="Z7" t="s">
         <v>22</v>
       </c>
       <c r="AA7" t="s">
-        <v>212</v>
+        <v>288</v>
       </c>
       <c r="AB7" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -8271,25 +8619,25 @@
         <v>3810272114</v>
       </c>
       <c r="C8" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="D8" t="s">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="E8" s="2">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
-        <v>197</v>
-      </c>
-      <c r="H8">
-        <v>3044000</v>
+        <v>258</v>
+      </c>
+      <c r="H8" t="s">
+        <v>36</v>
       </c>
       <c r="I8">
         <v>198</v>
       </c>
       <c r="J8" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K8" t="s">
         <v>44</v>
@@ -8304,25 +8652,25 @@
         <v>45770</v>
       </c>
       <c r="U8" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W8" t="s">
         <v>22</v>
       </c>
       <c r="X8" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y8">
-        <v>3810504159</v>
+        <v>266</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>275</v>
       </c>
       <c r="Z8" t="s">
         <v>22</v>
       </c>
       <c r="AA8" t="s">
-        <v>204</v>
+        <v>267</v>
       </c>
       <c r="AB8" t="s">
-        <v>217</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -8333,25 +8681,25 @@
         <v>3810272114</v>
       </c>
       <c r="C9" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="D9" t="s">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="E9" s="2">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
-        <v>197</v>
-      </c>
-      <c r="H9">
-        <v>3044000</v>
+        <v>258</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
       </c>
       <c r="I9">
         <v>198</v>
       </c>
       <c r="J9" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K9" t="s">
         <v>44</v>
@@ -8366,25 +8714,25 @@
         <v>45777</v>
       </c>
       <c r="U9" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W9" t="s">
         <v>22</v>
       </c>
       <c r="X9" t="s">
-        <v>203</v>
-      </c>
-      <c r="Y9">
-        <v>3810504182</v>
+        <v>266</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>276</v>
       </c>
       <c r="Z9" t="s">
         <v>22</v>
       </c>
       <c r="AA9" t="s">
-        <v>204</v>
+        <v>267</v>
       </c>
       <c r="AB9" t="s">
-        <v>218</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -8395,28 +8743,28 @@
         <v>3810271161</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="D10" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E10" s="2">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="G10" s="2">
         <v>45755</v>
       </c>
-      <c r="H10">
-        <v>3044000</v>
+      <c r="H10" t="s">
+        <v>36</v>
       </c>
       <c r="I10">
         <v>198</v>
       </c>
       <c r="J10" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K10" t="s">
         <v>44</v>
@@ -8434,25 +8782,25 @@
         <v>45754</v>
       </c>
       <c r="U10" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W10" t="s">
         <v>22</v>
       </c>
       <c r="X10" t="s">
-        <v>204</v>
-      </c>
-      <c r="Y10">
-        <v>3810503807</v>
+        <v>267</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>277</v>
       </c>
       <c r="Z10" t="s">
         <v>22</v>
       </c>
       <c r="AA10" t="s">
-        <v>212</v>
+        <v>288</v>
       </c>
       <c r="AB10" t="s">
-        <v>219</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -8460,31 +8808,31 @@
         <v>3810255268</v>
       </c>
       <c r="C11" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="D11" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E11" s="2">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="G11" s="2">
         <v>44973</v>
       </c>
-      <c r="H11">
-        <v>3044000</v>
+      <c r="H11" t="s">
+        <v>36</v>
       </c>
       <c r="I11">
         <v>198</v>
       </c>
       <c r="J11" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K11" t="s">
-        <v>199</v>
+        <v>260</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -8499,25 +8847,25 @@
         <v>44973</v>
       </c>
       <c r="U11" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W11" t="s">
         <v>22</v>
       </c>
       <c r="X11" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y11">
-        <v>3810481813</v>
+        <v>268</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>278</v>
       </c>
       <c r="Z11" t="s">
         <v>22</v>
       </c>
       <c r="AA11" t="s">
-        <v>202</v>
+        <v>265</v>
       </c>
       <c r="AB11" t="s">
-        <v>220</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -8525,28 +8873,28 @@
         <v>3810264674</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="D12" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E12" s="2">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="G12" s="2">
         <v>45358</v>
       </c>
-      <c r="H12">
-        <v>3044000</v>
+      <c r="H12" t="s">
+        <v>36</v>
       </c>
       <c r="I12">
         <v>198</v>
       </c>
       <c r="J12" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K12" t="s">
         <v>68</v>
@@ -8564,25 +8912,25 @@
         <v>45358</v>
       </c>
       <c r="U12" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W12" t="s">
         <v>22</v>
       </c>
       <c r="X12" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y12">
-        <v>3810492521</v>
+        <v>268</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>279</v>
       </c>
       <c r="Z12" t="s">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="AA12" t="s">
-        <v>213</v>
+        <v>289</v>
       </c>
       <c r="AB12" t="s">
-        <v>221</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -8590,28 +8938,28 @@
         <v>3810268863</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="D13" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E13" s="2">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="G13" s="2">
         <v>45573</v>
       </c>
-      <c r="H13">
-        <v>3044000</v>
+      <c r="H13" t="s">
+        <v>36</v>
       </c>
       <c r="I13">
         <v>198</v>
       </c>
       <c r="J13" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K13" t="s">
         <v>55</v>
@@ -8629,28 +8977,28 @@
         <v>45573</v>
       </c>
       <c r="U13" t="s">
-        <v>200</v>
-      </c>
-      <c r="V13">
-        <v>313240016031</v>
+        <v>261</v>
+      </c>
+      <c r="V13" t="s">
+        <v>264</v>
       </c>
       <c r="W13" t="s">
         <v>22</v>
       </c>
       <c r="X13" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y13">
-        <v>3810499557</v>
+        <v>268</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>280</v>
       </c>
       <c r="Z13" t="s">
         <v>22</v>
       </c>
       <c r="AA13" t="s">
-        <v>202</v>
+        <v>265</v>
       </c>
       <c r="AB13" t="s">
-        <v>222</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -8658,28 +9006,28 @@
         <v>3810271550</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="D14" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E14" s="2">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="G14" s="2">
         <v>45747</v>
       </c>
-      <c r="H14">
-        <v>3044000</v>
+      <c r="H14" t="s">
+        <v>36</v>
       </c>
       <c r="I14">
         <v>198</v>
       </c>
       <c r="J14" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="K14" t="s">
         <v>53</v>
@@ -8697,25 +9045,25 @@
         <v>45747</v>
       </c>
       <c r="U14" t="s">
-        <v>201</v>
+        <v>262</v>
       </c>
       <c r="W14" t="s">
         <v>22</v>
       </c>
       <c r="X14" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y14">
-        <v>3810499086</v>
+        <v>268</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>281</v>
       </c>
       <c r="Z14" t="s">
         <v>22</v>
       </c>
       <c r="AA14" t="s">
-        <v>202</v>
+        <v>265</v>
       </c>
       <c r="AB14" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -8798,22 +9146,22 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E2" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I2" t="s">
-        <v>238</v>
+        <v>314</v>
       </c>
       <c r="J2" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K2">
         <v>797.33</v>
@@ -8827,8 +9175,8 @@
       <c r="N2">
         <v>4000</v>
       </c>
-      <c r="O2">
-        <v>2709</v>
+      <c r="O2" t="s">
+        <v>102</v>
       </c>
       <c r="P2" s="2">
         <v>45490</v>
@@ -8836,31 +9184,31 @@
       <c r="Q2" s="2">
         <v>45015</v>
       </c>
-      <c r="R2">
-        <v>3130006005</v>
+      <c r="R2" t="s">
+        <v>361</v>
       </c>
       <c r="S2" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>301</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E3" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I3" t="s">
-        <v>239</v>
+        <v>315</v>
       </c>
       <c r="J3" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K3">
         <v>1001.83</v>
@@ -8874,8 +9222,8 @@
       <c r="N3">
         <v>4000</v>
       </c>
-      <c r="O3">
-        <v>2703</v>
+      <c r="O3" t="s">
+        <v>81</v>
       </c>
       <c r="P3" s="2">
         <v>45618</v>
@@ -8883,31 +9231,31 @@
       <c r="Q3" s="2">
         <v>45614</v>
       </c>
-      <c r="R3">
-        <v>6890000562</v>
+      <c r="R3" t="s">
+        <v>362</v>
       </c>
       <c r="S3" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>302</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E4" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I4" t="s">
-        <v>240</v>
+        <v>316</v>
       </c>
       <c r="J4" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K4">
         <v>2813.92</v>
@@ -8921,8 +9269,8 @@
       <c r="N4">
         <v>4000</v>
       </c>
-      <c r="O4">
-        <v>2739</v>
+      <c r="O4" t="s">
+        <v>97</v>
       </c>
       <c r="P4" s="2">
         <v>45539</v>
@@ -8930,31 +9278,31 @@
       <c r="Q4" s="2">
         <v>45539</v>
       </c>
-      <c r="R4">
-        <v>3040075245</v>
+      <c r="R4" t="s">
+        <v>363</v>
       </c>
       <c r="S4" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>227</v>
+        <v>303</v>
       </c>
       <c r="B5" t="s">
         <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E5" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I5" t="s">
-        <v>241</v>
+        <v>317</v>
       </c>
       <c r="J5" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K5">
         <v>1258.5</v>
@@ -8968,8 +9316,8 @@
       <c r="N5">
         <v>4000</v>
       </c>
-      <c r="O5">
-        <v>2722</v>
+      <c r="O5" t="s">
+        <v>98</v>
       </c>
       <c r="P5" s="2">
         <v>45567</v>
@@ -8977,31 +9325,31 @@
       <c r="Q5" s="2">
         <v>45490</v>
       </c>
-      <c r="R5">
-        <v>3290007931</v>
+      <c r="R5" t="s">
+        <v>364</v>
       </c>
       <c r="S5" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E6" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I6" t="s">
-        <v>242</v>
+        <v>318</v>
       </c>
       <c r="J6" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K6">
         <v>708.33</v>
@@ -9015,8 +9363,8 @@
       <c r="N6">
         <v>4000</v>
       </c>
-      <c r="O6">
-        <v>2741</v>
+      <c r="O6" t="s">
+        <v>95</v>
       </c>
       <c r="P6" s="2">
         <v>45568</v>
@@ -9024,31 +9372,31 @@
       <c r="Q6" s="2">
         <v>45526</v>
       </c>
-      <c r="R6">
-        <v>7090002248</v>
+      <c r="R6" t="s">
+        <v>365</v>
       </c>
       <c r="S6" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E7" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I7" t="s">
-        <v>243</v>
+        <v>319</v>
       </c>
       <c r="J7" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K7">
         <v>133.42</v>
@@ -9062,8 +9410,8 @@
       <c r="N7">
         <v>4000</v>
       </c>
-      <c r="O7">
-        <v>2728</v>
+      <c r="O7" t="s">
+        <v>83</v>
       </c>
       <c r="P7" s="2">
         <v>45831</v>
@@ -9071,31 +9419,31 @@
       <c r="Q7" s="2">
         <v>45352</v>
       </c>
-      <c r="R7">
-        <v>3130006789</v>
+      <c r="R7" t="s">
+        <v>366</v>
       </c>
       <c r="S7" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E8" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I8" t="s">
-        <v>244</v>
+        <v>320</v>
       </c>
       <c r="J8" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K8">
         <v>224.08</v>
@@ -9109,8 +9457,8 @@
       <c r="N8">
         <v>4000</v>
       </c>
-      <c r="O8">
-        <v>2720</v>
+      <c r="O8" t="s">
+        <v>103</v>
       </c>
       <c r="P8" s="2">
         <v>45601</v>
@@ -9118,31 +9466,31 @@
       <c r="Q8" s="2">
         <v>44704</v>
       </c>
-      <c r="R8">
-        <v>7090002894</v>
+      <c r="R8" t="s">
+        <v>367</v>
       </c>
       <c r="S8" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E9" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I9" t="s">
-        <v>245</v>
+        <v>321</v>
       </c>
       <c r="J9" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K9">
         <v>783.42</v>
@@ -9156,8 +9504,8 @@
       <c r="N9">
         <v>4000</v>
       </c>
-      <c r="O9">
-        <v>2736</v>
+      <c r="O9" t="s">
+        <v>92</v>
       </c>
       <c r="P9" s="2">
         <v>45631</v>
@@ -9165,31 +9513,31 @@
       <c r="Q9" s="2">
         <v>45628</v>
       </c>
-      <c r="R9">
-        <v>3130005796</v>
+      <c r="R9" t="s">
+        <v>368</v>
       </c>
       <c r="S9" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="B10" t="s">
         <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E10" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I10" t="s">
-        <v>246</v>
+        <v>322</v>
       </c>
       <c r="J10" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K10">
         <v>2718.58</v>
@@ -9203,8 +9551,8 @@
       <c r="N10">
         <v>4000</v>
       </c>
-      <c r="O10">
-        <v>2727</v>
+      <c r="O10" t="s">
+        <v>89</v>
       </c>
       <c r="P10" s="2">
         <v>43902</v>
@@ -9212,31 +9560,31 @@
       <c r="Q10" s="2">
         <v>43549</v>
       </c>
-      <c r="R10">
-        <v>7100002436</v>
+      <c r="R10" t="s">
+        <v>369</v>
       </c>
       <c r="S10" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E11" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I11" t="s">
-        <v>247</v>
+        <v>323</v>
       </c>
       <c r="J11" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K11">
         <v>3603.17</v>
@@ -9250,8 +9598,8 @@
       <c r="N11">
         <v>4000</v>
       </c>
-      <c r="O11">
-        <v>2724</v>
+      <c r="O11" t="s">
+        <v>99</v>
       </c>
       <c r="P11" s="2">
         <v>44736</v>
@@ -9259,31 +9607,31 @@
       <c r="Q11" s="2">
         <v>44735</v>
       </c>
-      <c r="R11">
-        <v>3040057779</v>
+      <c r="R11" t="s">
+        <v>370</v>
       </c>
       <c r="S11" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>227</v>
+        <v>303</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E12" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I12" t="s">
-        <v>248</v>
+        <v>324</v>
       </c>
       <c r="J12" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K12">
         <v>2298.67</v>
@@ -9297,8 +9645,8 @@
       <c r="N12">
         <v>4000</v>
       </c>
-      <c r="O12">
-        <v>2719</v>
+      <c r="O12" t="s">
+        <v>82</v>
       </c>
       <c r="P12" s="2">
         <v>45776</v>
@@ -9306,31 +9654,31 @@
       <c r="Q12" s="2">
         <v>45776</v>
       </c>
-      <c r="R12">
-        <v>3040073019</v>
+      <c r="R12" t="s">
+        <v>371</v>
       </c>
       <c r="S12" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>231</v>
+        <v>307</v>
       </c>
       <c r="B13" t="s">
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E13" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I13" t="s">
-        <v>249</v>
+        <v>325</v>
       </c>
       <c r="J13" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K13">
         <v>2132.08</v>
@@ -9344,8 +9692,8 @@
       <c r="N13">
         <v>4000</v>
       </c>
-      <c r="O13">
-        <v>2702</v>
+      <c r="O13" t="s">
+        <v>80</v>
       </c>
       <c r="P13" s="2">
         <v>45772</v>
@@ -9353,11 +9701,11 @@
       <c r="Q13" s="2">
         <v>45600</v>
       </c>
-      <c r="R13">
-        <v>3040090256</v>
+      <c r="R13" t="s">
+        <v>372</v>
       </c>
       <c r="S13" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -9368,16 +9716,16 @@
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E14" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I14" t="s">
-        <v>250</v>
+        <v>326</v>
       </c>
       <c r="J14" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K14">
         <v>1013.92</v>
@@ -9391,8 +9739,8 @@
       <c r="N14">
         <v>4000</v>
       </c>
-      <c r="O14">
-        <v>2723</v>
+      <c r="O14" t="s">
+        <v>100</v>
       </c>
       <c r="P14" s="2">
         <v>45000</v>
@@ -9400,31 +9748,31 @@
       <c r="Q14" s="2">
         <v>44630</v>
       </c>
-      <c r="R14">
-        <v>7090002718</v>
+      <c r="R14" t="s">
+        <v>373</v>
       </c>
       <c r="S14" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E15" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I15" t="s">
-        <v>251</v>
+        <v>327</v>
       </c>
       <c r="J15" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K15">
         <v>209.92</v>
@@ -9438,34 +9786,34 @@
       <c r="N15">
         <v>4000</v>
       </c>
-      <c r="O15">
-        <v>2721</v>
+      <c r="O15" t="s">
+        <v>94</v>
       </c>
       <c r="P15" s="2">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E16" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I16" t="s">
-        <v>252</v>
+        <v>328</v>
       </c>
       <c r="J16" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K16">
         <v>49.33</v>
@@ -9479,34 +9827,34 @@
       <c r="N16">
         <v>4000</v>
       </c>
-      <c r="O16">
-        <v>2738</v>
+      <c r="O16" t="s">
+        <v>90</v>
       </c>
       <c r="P16" s="2">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>302</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E17" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I17" t="s">
-        <v>253</v>
+        <v>329</v>
       </c>
       <c r="J17" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K17">
         <v>923.83</v>
@@ -9520,8 +9868,8 @@
       <c r="N17">
         <v>4000</v>
       </c>
-      <c r="O17">
-        <v>2731</v>
+      <c r="O17" t="s">
+        <v>93</v>
       </c>
       <c r="P17" s="2">
         <v>45371</v>
@@ -9529,31 +9877,31 @@
       <c r="Q17" s="2">
         <v>45026</v>
       </c>
-      <c r="R17">
-        <v>3040077697</v>
+      <c r="R17" t="s">
+        <v>374</v>
       </c>
       <c r="S17" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E18" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I18" t="s">
-        <v>254</v>
+        <v>330</v>
       </c>
       <c r="J18" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K18">
         <v>112.33</v>
@@ -9567,8 +9915,8 @@
       <c r="N18">
         <v>4000</v>
       </c>
-      <c r="O18">
-        <v>2737</v>
+      <c r="O18" t="s">
+        <v>91</v>
       </c>
       <c r="P18" s="2">
         <v>46001</v>
@@ -9576,31 +9924,31 @@
       <c r="Q18" s="2">
         <v>45371</v>
       </c>
-      <c r="R18">
-        <v>3960004903</v>
+      <c r="R18" t="s">
+        <v>375</v>
       </c>
       <c r="S18" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E19" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I19" t="s">
-        <v>255</v>
+        <v>331</v>
       </c>
       <c r="J19" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K19">
         <v>598</v>
@@ -9614,8 +9962,8 @@
       <c r="N19">
         <v>4000</v>
       </c>
-      <c r="O19">
-        <v>2729</v>
+      <c r="O19" t="s">
+        <v>104</v>
       </c>
       <c r="P19" s="2">
         <v>45436</v>
@@ -9623,11 +9971,11 @@
       <c r="Q19" s="2">
         <v>45294</v>
       </c>
-      <c r="R19">
-        <v>3130006599</v>
+      <c r="R19" t="s">
+        <v>376</v>
       </c>
       <c r="S19" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -9638,16 +9986,16 @@
         <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E20" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I20" t="s">
-        <v>256</v>
+        <v>332</v>
       </c>
       <c r="J20" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K20">
         <v>779.67</v>
@@ -9661,8 +10009,8 @@
       <c r="N20">
         <v>4000</v>
       </c>
-      <c r="O20">
-        <v>2704</v>
+      <c r="O20" t="s">
+        <v>96</v>
       </c>
       <c r="P20" s="2">
         <v>44372</v>
@@ -9670,31 +10018,31 @@
       <c r="Q20" s="2">
         <v>44369</v>
       </c>
-      <c r="R20">
-        <v>7090000956</v>
+      <c r="R20" t="s">
+        <v>377</v>
       </c>
       <c r="S20" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>229</v>
+        <v>305</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E21" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I21" t="s">
-        <v>257</v>
+        <v>333</v>
       </c>
       <c r="J21" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K21">
         <v>1685.25</v>
@@ -9708,8 +10056,8 @@
       <c r="N21">
         <v>4000</v>
       </c>
-      <c r="O21">
-        <v>2708</v>
+      <c r="O21" t="s">
+        <v>105</v>
       </c>
       <c r="P21" s="2">
         <v>44362</v>
@@ -9717,31 +10065,31 @@
       <c r="Q21" s="2">
         <v>43894</v>
       </c>
-      <c r="R21">
-        <v>7080003306</v>
+      <c r="R21" t="s">
+        <v>378</v>
       </c>
       <c r="S21" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E22" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I22" t="s">
-        <v>258</v>
+        <v>334</v>
       </c>
       <c r="J22" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K22">
         <v>1926.58</v>
@@ -9755,8 +10103,8 @@
       <c r="N22">
         <v>4000</v>
       </c>
-      <c r="O22">
-        <v>2740</v>
+      <c r="O22" t="s">
+        <v>86</v>
       </c>
       <c r="P22" s="2">
         <v>45511</v>
@@ -9764,11 +10112,11 @@
       <c r="Q22" s="2">
         <v>45509</v>
       </c>
-      <c r="R22">
-        <v>7080005315</v>
+      <c r="R22" t="s">
+        <v>379</v>
       </c>
       <c r="S22" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -9779,16 +10127,16 @@
         <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E23" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I23" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="J23" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="L23">
         <v>2562.83</v>
@@ -9796,8 +10144,8 @@
       <c r="N23">
         <v>4000</v>
       </c>
-      <c r="O23">
-        <v>2725</v>
+      <c r="O23" t="s">
+        <v>359</v>
       </c>
       <c r="P23" s="2">
         <v>40044</v>
@@ -9805,14 +10153,14 @@
       <c r="Q23" s="2">
         <v>40126</v>
       </c>
-      <c r="R23">
-        <v>3130007478</v>
+      <c r="R23" t="s">
+        <v>380</v>
       </c>
       <c r="S23" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T23" t="s">
-        <v>283</v>
+        <v>399</v>
       </c>
       <c r="U23" s="2">
         <v>45775</v>
@@ -9826,16 +10174,16 @@
         <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E24" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I24" t="s">
-        <v>260</v>
+        <v>336</v>
       </c>
       <c r="J24" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K24">
         <v>1903.17</v>
@@ -9849,8 +10197,8 @@
       <c r="N24">
         <v>4000</v>
       </c>
-      <c r="O24">
-        <v>2702</v>
+      <c r="O24" t="s">
+        <v>80</v>
       </c>
       <c r="P24" s="2">
         <v>43549</v>
@@ -9858,14 +10206,14 @@
       <c r="Q24" s="2">
         <v>45772</v>
       </c>
-      <c r="R24">
-        <v>3040091287</v>
+      <c r="R24" t="s">
+        <v>381</v>
       </c>
       <c r="S24" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T24" t="s">
-        <v>284</v>
+        <v>400</v>
       </c>
       <c r="U24" s="2">
         <v>45810</v>
@@ -9879,16 +10227,16 @@
         <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E25" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I25" t="s">
-        <v>261</v>
+        <v>337</v>
       </c>
       <c r="J25" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K25">
         <v>835.42</v>
@@ -9902,8 +10250,8 @@
       <c r="N25">
         <v>4000</v>
       </c>
-      <c r="O25">
-        <v>2740</v>
+      <c r="O25" t="s">
+        <v>86</v>
       </c>
       <c r="P25" s="2">
         <v>45447</v>
@@ -9911,14 +10259,14 @@
       <c r="Q25" s="2">
         <v>45510</v>
       </c>
-      <c r="R25">
-        <v>3130007827</v>
+      <c r="R25" t="s">
+        <v>382</v>
       </c>
       <c r="S25" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T25" t="s">
-        <v>285</v>
+        <v>401</v>
       </c>
       <c r="U25" s="2">
         <v>45937</v>
@@ -9932,16 +10280,16 @@
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E26" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I26" t="s">
-        <v>262</v>
+        <v>338</v>
       </c>
       <c r="J26" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K26">
         <v>1657.42</v>
@@ -9955,8 +10303,8 @@
       <c r="N26">
         <v>4000</v>
       </c>
-      <c r="O26">
-        <v>2723</v>
+      <c r="O26" t="s">
+        <v>100</v>
       </c>
       <c r="P26" s="2">
         <v>44485</v>
@@ -9964,14 +10312,14 @@
       <c r="Q26" s="2">
         <v>44959</v>
       </c>
-      <c r="R26">
-        <v>4190000750</v>
+      <c r="R26" t="s">
+        <v>383</v>
       </c>
       <c r="S26" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T26" t="s">
-        <v>286</v>
+        <v>402</v>
       </c>
       <c r="U26" s="2">
         <v>45580</v>
@@ -9985,16 +10333,16 @@
         <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E27" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I27" t="s">
-        <v>263</v>
+        <v>339</v>
       </c>
       <c r="J27" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K27">
         <v>39.92</v>
@@ -10008,8 +10356,8 @@
       <c r="N27">
         <v>4000</v>
       </c>
-      <c r="O27">
-        <v>2740</v>
+      <c r="O27" t="s">
+        <v>86</v>
       </c>
       <c r="P27" s="2">
         <v>45420</v>
@@ -10017,14 +10365,14 @@
       <c r="Q27" s="2">
         <v>45446</v>
       </c>
-      <c r="R27">
-        <v>3130007058</v>
+      <c r="R27" t="s">
+        <v>384</v>
       </c>
       <c r="S27" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T27" t="s">
-        <v>287</v>
+        <v>403</v>
       </c>
       <c r="U27" s="2">
         <v>45588</v>
@@ -10038,16 +10386,16 @@
         <v>34</v>
       </c>
       <c r="C28" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E28" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I28" t="s">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="J28" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K28">
         <v>4204.25</v>
@@ -10061,8 +10409,8 @@
       <c r="N28">
         <v>4000</v>
       </c>
-      <c r="O28">
-        <v>2743</v>
+      <c r="O28" t="s">
+        <v>101</v>
       </c>
       <c r="P28" s="2">
         <v>44369</v>
@@ -10070,14 +10418,14 @@
       <c r="Q28" s="2">
         <v>45824</v>
       </c>
-      <c r="R28">
-        <v>3040091753</v>
+      <c r="R28" t="s">
+        <v>385</v>
       </c>
       <c r="S28" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T28" t="s">
-        <v>288</v>
+        <v>404</v>
       </c>
       <c r="U28" s="2">
         <v>45831</v>
@@ -10091,16 +10439,16 @@
         <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E29" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I29" t="s">
-        <v>265</v>
+        <v>341</v>
       </c>
       <c r="J29" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K29">
         <v>1891.33</v>
@@ -10114,8 +10462,8 @@
       <c r="N29">
         <v>4000</v>
       </c>
-      <c r="O29">
-        <v>2722</v>
+      <c r="O29" t="s">
+        <v>98</v>
       </c>
       <c r="P29" s="2">
         <v>44652</v>
@@ -10123,14 +10471,14 @@
       <c r="Q29" s="2">
         <v>45567</v>
       </c>
-      <c r="R29">
-        <v>6850004453</v>
+      <c r="R29" t="s">
+        <v>386</v>
       </c>
       <c r="S29" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T29" t="s">
-        <v>289</v>
+        <v>405</v>
       </c>
       <c r="U29" s="2">
         <v>45734</v>
@@ -10144,25 +10492,25 @@
         <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E30" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I30" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="J30" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="N30">
         <v>4000</v>
       </c>
       <c r="S30" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T30" t="s">
-        <v>290</v>
+        <v>406</v>
       </c>
       <c r="U30" s="2">
         <v>46001</v>
@@ -10176,25 +10524,25 @@
         <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E31" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I31" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="J31" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="N31">
         <v>4000</v>
       </c>
       <c r="S31" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T31" t="s">
-        <v>291</v>
+        <v>407</v>
       </c>
       <c r="U31" s="2">
         <v>46001</v>
@@ -10208,25 +10556,25 @@
         <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E32" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I32" t="s">
-        <v>268</v>
+        <v>344</v>
       </c>
       <c r="J32" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="N32">
         <v>4000</v>
       </c>
       <c r="S32" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="T32" t="s">
-        <v>292</v>
+        <v>408</v>
       </c>
       <c r="U32" s="2">
         <v>46001</v>
@@ -10234,22 +10582,22 @@
     </row>
     <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>206</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E33" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I33" t="s">
-        <v>269</v>
+        <v>345</v>
       </c>
       <c r="J33" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K33">
         <v>3238.83</v>
@@ -10263,8 +10611,8 @@
       <c r="N33">
         <v>4000</v>
       </c>
-      <c r="O33">
-        <v>2738</v>
+      <c r="O33" t="s">
+        <v>90</v>
       </c>
       <c r="P33" s="2">
         <v>43762</v>
@@ -10272,14 +10620,14 @@
       <c r="Q33" s="2">
         <v>46031</v>
       </c>
-      <c r="R33">
-        <v>3130008485</v>
+      <c r="R33" t="s">
+        <v>387</v>
       </c>
       <c r="S33" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="T33" t="s">
-        <v>293</v>
+        <v>387</v>
       </c>
       <c r="U33" s="2">
         <v>46037</v>
@@ -10293,16 +10641,16 @@
         <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E34" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I34" t="s">
-        <v>270</v>
+        <v>346</v>
       </c>
       <c r="J34" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K34">
         <v>833.58</v>
@@ -10316,8 +10664,8 @@
       <c r="N34">
         <v>4000</v>
       </c>
-      <c r="O34">
-        <v>2735</v>
+      <c r="O34" t="s">
+        <v>360</v>
       </c>
       <c r="P34" s="2">
         <v>40071</v>
@@ -10326,7 +10674,7 @@
         <v>41023</v>
       </c>
       <c r="S34" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="U34" s="2">
         <v>41023</v>
@@ -10334,22 +10682,22 @@
     </row>
     <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s">
         <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E35" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I35" t="s">
-        <v>271</v>
+        <v>347</v>
       </c>
       <c r="J35" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="L35">
         <v>6168.75</v>
@@ -10357,8 +10705,8 @@
       <c r="N35">
         <v>4000</v>
       </c>
-      <c r="O35">
-        <v>2732</v>
+      <c r="O35" t="s">
+        <v>87</v>
       </c>
       <c r="P35" s="2">
         <v>44784</v>
@@ -10366,11 +10714,11 @@
       <c r="Q35" s="2">
         <v>45259</v>
       </c>
-      <c r="R35">
-        <v>3130006532</v>
+      <c r="R35" t="s">
+        <v>388</v>
       </c>
       <c r="S35" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="U35" s="2">
         <v>45259</v>
@@ -10378,22 +10726,22 @@
     </row>
     <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s">
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E36" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I36" t="s">
-        <v>272</v>
+        <v>348</v>
       </c>
       <c r="J36" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K36">
         <v>2184.17</v>
@@ -10407,8 +10755,8 @@
       <c r="N36">
         <v>4000</v>
       </c>
-      <c r="O36">
-        <v>2737</v>
+      <c r="O36" t="s">
+        <v>91</v>
       </c>
       <c r="P36" s="2">
         <v>45103</v>
@@ -10416,11 +10764,11 @@
       <c r="Q36" s="2">
         <v>46000</v>
       </c>
-      <c r="R36">
-        <v>6890000560</v>
+      <c r="R36" t="s">
+        <v>389</v>
       </c>
       <c r="S36" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="U36" s="2">
         <v>46000</v>
@@ -10428,48 +10776,48 @@
     </row>
     <row r="37" spans="1:21">
       <c r="A37" t="s">
-        <v>228</v>
+        <v>304</v>
       </c>
       <c r="B37" t="s">
         <v>34</v>
       </c>
       <c r="C37" t="s">
-        <v>234</v>
+        <v>310</v>
       </c>
       <c r="E37" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I37" t="s">
-        <v>255</v>
+        <v>331</v>
       </c>
       <c r="J37" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="N37">
         <v>4000</v>
       </c>
       <c r="S37" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>226</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s">
         <v>34</v>
       </c>
       <c r="C38" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E38" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I38" t="s">
-        <v>273</v>
+        <v>349</v>
       </c>
       <c r="J38" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K38">
         <v>553.17</v>
@@ -10483,8 +10831,8 @@
       <c r="N38">
         <v>4000</v>
       </c>
-      <c r="O38">
-        <v>2704</v>
+      <c r="O38" t="s">
+        <v>96</v>
       </c>
       <c r="P38" s="2">
         <v>38511</v>
@@ -10492,11 +10840,11 @@
       <c r="Q38" s="2">
         <v>39068</v>
       </c>
-      <c r="R38">
-        <v>3070018395</v>
+      <c r="R38" t="s">
+        <v>390</v>
       </c>
       <c r="S38" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="U38" s="2">
         <v>39068</v>
@@ -10510,16 +10858,16 @@
         <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E39" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I39" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
       <c r="J39" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K39">
         <v>85.58</v>
@@ -10533,8 +10881,8 @@
       <c r="N39">
         <v>4000</v>
       </c>
-      <c r="O39">
-        <v>2720</v>
+      <c r="O39" t="s">
+        <v>103</v>
       </c>
       <c r="P39" s="2">
         <v>39006</v>
@@ -10542,14 +10890,14 @@
       <c r="Q39" s="2">
         <v>40568</v>
       </c>
-      <c r="R39">
-        <v>3130002407</v>
+      <c r="R39" t="s">
+        <v>391</v>
       </c>
       <c r="S39" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="T39" t="s">
-        <v>294</v>
+        <v>409</v>
       </c>
       <c r="U39" s="2">
         <v>40568</v>
@@ -10563,16 +10911,16 @@
         <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>235</v>
+        <v>311</v>
       </c>
       <c r="E40" t="s">
-        <v>237</v>
+        <v>313</v>
       </c>
       <c r="I40" t="s">
-        <v>275</v>
+        <v>351</v>
       </c>
       <c r="J40" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K40">
         <v>796.67</v>
@@ -10580,8 +10928,8 @@
       <c r="L40">
         <v>3739.5</v>
       </c>
-      <c r="O40">
-        <v>2723</v>
+      <c r="O40" t="s">
+        <v>100</v>
       </c>
       <c r="P40" s="2">
         <v>40836</v>
@@ -10589,14 +10937,14 @@
       <c r="Q40" s="2">
         <v>42270</v>
       </c>
-      <c r="R40">
-        <v>3040050893</v>
+      <c r="R40" t="s">
+        <v>392</v>
       </c>
       <c r="S40" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="T40" t="s">
-        <v>295</v>
+        <v>410</v>
       </c>
       <c r="U40" s="2">
         <v>42270</v>
@@ -10610,16 +10958,16 @@
         <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E41" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I41" t="s">
-        <v>276</v>
+        <v>352</v>
       </c>
       <c r="J41" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K41">
         <v>981.58</v>
@@ -10633,8 +10981,8 @@
       <c r="N41">
         <v>4000</v>
       </c>
-      <c r="O41">
-        <v>2741</v>
+      <c r="O41" t="s">
+        <v>95</v>
       </c>
       <c r="P41" s="2">
         <v>42940</v>
@@ -10642,14 +10990,14 @@
       <c r="Q41" s="2">
         <v>43494</v>
       </c>
-      <c r="R41">
-        <v>3040080066</v>
+      <c r="R41" t="s">
+        <v>393</v>
       </c>
       <c r="S41" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="T41" t="s">
-        <v>296</v>
+        <v>411</v>
       </c>
       <c r="U41" s="2">
         <v>44148</v>
@@ -10663,16 +11011,16 @@
         <v>34</v>
       </c>
       <c r="C42" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E42" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I42" t="s">
-        <v>277</v>
+        <v>353</v>
       </c>
       <c r="J42" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K42">
         <v>3152</v>
@@ -10686,8 +11034,8 @@
       <c r="N42">
         <v>4000</v>
       </c>
-      <c r="O42">
-        <v>2719</v>
+      <c r="O42" t="s">
+        <v>82</v>
       </c>
       <c r="P42" s="2">
         <v>43696</v>
@@ -10695,14 +11043,14 @@
       <c r="Q42" s="2">
         <v>45776</v>
       </c>
-      <c r="R42">
-        <v>6850005706</v>
+      <c r="R42" t="s">
+        <v>394</v>
       </c>
       <c r="S42" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="T42" t="s">
-        <v>297</v>
+        <v>412</v>
       </c>
       <c r="U42" s="2">
         <v>43185</v>
@@ -10716,16 +11064,16 @@
         <v>34</v>
       </c>
       <c r="C43" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E43" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I43" t="s">
-        <v>278</v>
+        <v>354</v>
       </c>
       <c r="J43" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K43">
         <v>2787.25</v>
@@ -10739,8 +11087,8 @@
       <c r="N43">
         <v>4000</v>
       </c>
-      <c r="O43">
-        <v>2742</v>
+      <c r="O43" t="s">
+        <v>84</v>
       </c>
       <c r="P43" s="2">
         <v>43544</v>
@@ -10748,14 +11096,14 @@
       <c r="Q43" s="2">
         <v>45916</v>
       </c>
-      <c r="R43">
-        <v>3860010942</v>
+      <c r="R43" t="s">
+        <v>395</v>
       </c>
       <c r="S43" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="T43" t="s">
-        <v>298</v>
+        <v>413</v>
       </c>
       <c r="U43" s="2">
         <v>42850</v>
@@ -10769,16 +11117,16 @@
         <v>34</v>
       </c>
       <c r="C44" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E44" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I44" t="s">
-        <v>279</v>
+        <v>355</v>
       </c>
       <c r="J44" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K44">
         <v>2413.42</v>
@@ -10792,8 +11140,8 @@
       <c r="N44">
         <v>4000</v>
       </c>
-      <c r="O44">
-        <v>2739</v>
+      <c r="O44" t="s">
+        <v>97</v>
       </c>
       <c r="P44" s="2">
         <v>45076</v>
@@ -10801,14 +11149,14 @@
       <c r="Q44" s="2">
         <v>45539</v>
       </c>
-      <c r="R44">
-        <v>3960005216</v>
+      <c r="R44" t="s">
+        <v>396</v>
       </c>
       <c r="S44" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="T44" t="s">
-        <v>299</v>
+        <v>414</v>
       </c>
       <c r="U44" s="2">
         <v>44404</v>
@@ -10822,16 +11170,16 @@
         <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="E45" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I45" t="s">
-        <v>280</v>
+        <v>356</v>
       </c>
       <c r="J45" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K45">
         <v>2266.5</v>
@@ -10845,8 +11193,8 @@
       <c r="N45">
         <v>4000</v>
       </c>
-      <c r="O45">
-        <v>2703</v>
+      <c r="O45" t="s">
+        <v>81</v>
       </c>
       <c r="P45" s="2">
         <v>42963</v>
@@ -10854,14 +11202,14 @@
       <c r="Q45" s="2">
         <v>45239</v>
       </c>
-      <c r="R45">
-        <v>3040088304</v>
+      <c r="R45" t="s">
+        <v>397</v>
       </c>
       <c r="S45" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="T45" t="s">
-        <v>300</v>
+        <v>415</v>
       </c>
       <c r="U45" s="2">
         <v>42698</v>
@@ -10875,16 +11223,16 @@
         <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>232</v>
+        <v>308</v>
       </c>
       <c r="E46" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="I46" t="s">
-        <v>281</v>
+        <v>357</v>
       </c>
       <c r="J46" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="K46">
         <v>545.75</v>
@@ -10898,8 +11246,8 @@
       <c r="N46">
         <v>4000</v>
       </c>
-      <c r="O46">
-        <v>2733</v>
+      <c r="O46" t="s">
+        <v>88</v>
       </c>
       <c r="P46" s="2">
         <v>45054</v>
@@ -10907,14 +11255,14 @@
       <c r="Q46" s="2">
         <v>45586</v>
       </c>
-      <c r="R46">
-        <v>3130007348</v>
+      <c r="R46" t="s">
+        <v>398</v>
       </c>
       <c r="S46" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="T46" t="s">
-        <v>301</v>
+        <v>416</v>
       </c>
       <c r="U46" s="2">
         <v>43941</v>
@@ -10932,25 +11280,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>302</v>
+        <v>417</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>303</v>
+        <v>418</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>304</v>
+        <v>419</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>305</v>
+        <v>420</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>306</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -11621,7 +11969,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -11636,39 +11984,39 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>422</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>308</v>
+        <v>423</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>309</v>
+        <v>424</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>310</v>
+        <v>425</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>311</v>
+        <v>426</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>312</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B2" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C2" t="s">
-        <v>318</v>
+        <v>433</v>
       </c>
       <c r="D2" t="s">
-        <v>325</v>
+        <v>440</v>
       </c>
       <c r="E2" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F2">
         <v>200000</v>
@@ -11676,19 +12024,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C3" t="s">
-        <v>319</v>
+        <v>434</v>
       </c>
       <c r="D3" t="s">
-        <v>326</v>
+        <v>441</v>
       </c>
       <c r="E3" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F3">
         <v>700000</v>
@@ -11696,19 +12044,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>314</v>
+        <v>429</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C4" t="s">
-        <v>319</v>
+        <v>434</v>
       </c>
       <c r="D4" t="s">
-        <v>327</v>
+        <v>442</v>
       </c>
       <c r="E4" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F4">
         <v>800000</v>
@@ -11716,19 +12064,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B5" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C5" t="s">
-        <v>320</v>
+        <v>435</v>
       </c>
       <c r="D5" t="s">
-        <v>328</v>
+        <v>443</v>
       </c>
       <c r="E5" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F5">
         <v>400000</v>
@@ -11736,19 +12084,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C6" t="s">
-        <v>320</v>
+        <v>435</v>
       </c>
       <c r="D6" t="s">
-        <v>329</v>
+        <v>444</v>
       </c>
       <c r="E6" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F6">
         <v>400000</v>
@@ -11756,19 +12104,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C7" t="s">
-        <v>320</v>
+        <v>435</v>
       </c>
       <c r="D7" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="E7" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F7">
         <v>400000</v>
@@ -11776,19 +12124,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B8" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C8" t="s">
-        <v>321</v>
+        <v>436</v>
       </c>
       <c r="D8" t="s">
-        <v>331</v>
+        <v>446</v>
       </c>
       <c r="E8" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F8">
         <v>1000000</v>
@@ -11796,19 +12144,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>314</v>
+        <v>429</v>
       </c>
       <c r="B9" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C9" t="s">
-        <v>321</v>
+        <v>436</v>
       </c>
       <c r="D9" t="s">
-        <v>332</v>
+        <v>447</v>
       </c>
       <c r="E9" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F9">
         <v>1000000</v>
@@ -11816,19 +12164,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>314</v>
+        <v>429</v>
       </c>
       <c r="B10" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C10" t="s">
-        <v>321</v>
+        <v>436</v>
       </c>
       <c r="D10" t="s">
-        <v>333</v>
+        <v>448</v>
       </c>
       <c r="E10" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F10">
         <v>1000000</v>
@@ -11836,19 +12184,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B11" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C11" t="s">
-        <v>318</v>
+        <v>433</v>
       </c>
       <c r="D11" t="s">
-        <v>334</v>
+        <v>449</v>
       </c>
       <c r="E11" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F11">
         <v>563000</v>
@@ -11856,19 +12204,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B12" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C12" t="s">
-        <v>318</v>
+        <v>433</v>
       </c>
       <c r="D12" t="s">
-        <v>335</v>
+        <v>450</v>
       </c>
       <c r="E12" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F12">
         <v>320000</v>
@@ -11876,19 +12224,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B13" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C13" t="s">
-        <v>322</v>
+        <v>437</v>
       </c>
       <c r="D13" t="s">
-        <v>336</v>
+        <v>451</v>
       </c>
       <c r="E13" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F13">
         <v>120000</v>
@@ -11896,19 +12244,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>315</v>
+        <v>430</v>
       </c>
       <c r="B14" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C14" t="s">
-        <v>322</v>
+        <v>437</v>
       </c>
       <c r="D14" t="s">
-        <v>337</v>
+        <v>452</v>
       </c>
       <c r="E14" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F14">
         <v>120000</v>
@@ -11916,19 +12264,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B15" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C15" t="s">
-        <v>322</v>
+        <v>437</v>
       </c>
       <c r="D15" t="s">
-        <v>338</v>
+        <v>453</v>
       </c>
       <c r="E15" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F15">
         <v>80000</v>
@@ -11936,19 +12284,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>315</v>
+        <v>430</v>
       </c>
       <c r="B16" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C16" t="s">
-        <v>322</v>
+        <v>437</v>
       </c>
       <c r="D16" t="s">
-        <v>339</v>
+        <v>454</v>
       </c>
       <c r="E16" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F16">
         <v>80000</v>
@@ -11956,19 +12304,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>316</v>
+        <v>431</v>
       </c>
       <c r="B17" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C17" t="s">
-        <v>323</v>
+        <v>438</v>
       </c>
       <c r="D17" t="s">
-        <v>340</v>
+        <v>455</v>
       </c>
       <c r="E17" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F17">
         <v>3800000</v>
@@ -11976,19 +12324,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>316</v>
+        <v>431</v>
       </c>
       <c r="B18" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C18" t="s">
-        <v>323</v>
+        <v>438</v>
       </c>
       <c r="D18" t="s">
-        <v>341</v>
+        <v>456</v>
       </c>
       <c r="E18" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F18">
         <v>3800000</v>
@@ -11996,19 +12344,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B19" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C19" t="s">
-        <v>323</v>
+        <v>438</v>
       </c>
       <c r="D19" t="s">
-        <v>342</v>
+        <v>457</v>
       </c>
       <c r="E19" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F19">
         <v>3800000</v>
@@ -12016,19 +12364,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B20" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C20" t="s">
-        <v>324</v>
+        <v>439</v>
       </c>
       <c r="D20" t="s">
-        <v>343</v>
+        <v>458</v>
       </c>
       <c r="E20" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F20">
         <v>3800000</v>
@@ -12036,19 +12384,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>314</v>
+        <v>429</v>
       </c>
       <c r="B21" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C21" t="s">
-        <v>324</v>
+        <v>439</v>
       </c>
       <c r="D21" t="s">
-        <v>344</v>
+        <v>459</v>
       </c>
       <c r="E21" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F21">
         <v>3800000</v>
@@ -12056,19 +12404,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>314</v>
+        <v>429</v>
       </c>
       <c r="B22" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C22" t="s">
-        <v>324</v>
+        <v>439</v>
       </c>
       <c r="D22" t="s">
-        <v>345</v>
+        <v>460</v>
       </c>
       <c r="E22" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F22">
         <v>3800000</v>
@@ -12076,19 +12424,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B23" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C23" t="s">
-        <v>322</v>
+        <v>437</v>
       </c>
       <c r="D23" t="s">
-        <v>346</v>
+        <v>461</v>
       </c>
       <c r="E23" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F23">
         <v>430000</v>
@@ -12096,19 +12444,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B24" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C24" t="s">
-        <v>322</v>
+        <v>437</v>
       </c>
       <c r="D24" t="s">
-        <v>347</v>
+        <v>462</v>
       </c>
       <c r="E24" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F24">
         <v>430000</v>
@@ -12116,19 +12464,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B25" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C25" t="s">
-        <v>322</v>
+        <v>437</v>
       </c>
       <c r="D25" t="s">
-        <v>348</v>
+        <v>463</v>
       </c>
       <c r="E25" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F25">
         <v>425000</v>
@@ -12136,19 +12484,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="B26" t="s">
-        <v>317</v>
+        <v>432</v>
       </c>
       <c r="C26" t="s">
-        <v>322</v>
+        <v>437</v>
       </c>
       <c r="D26" t="s">
-        <v>349</v>
+        <v>464</v>
       </c>
       <c r="E26" t="s">
-        <v>350</v>
+        <v>465</v>
       </c>
       <c r="F26">
         <v>60000</v>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1445,16 +1445,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1470,7 +1462,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1478,30 +1470,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1801,70 +1775,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1905,10 +1879,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>41754</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1920,7 +1894,7 @@
       <c r="T2" t="s">
         <v>148</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="1">
         <v>46170</v>
       </c>
     </row>
@@ -1961,10 +1935,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>44709</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -2011,10 +1985,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>44348</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -2061,10 +2035,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>46059</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -2076,7 +2050,7 @@
       <c r="T5" t="s">
         <v>149</v>
       </c>
-      <c r="U5" s="2">
+      <c r="U5" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -2114,10 +2088,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>46149</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -2164,10 +2138,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>43731</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -2179,7 +2153,7 @@
       <c r="T7" t="s">
         <v>150</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U7" s="1">
         <v>43507</v>
       </c>
     </row>
@@ -2220,10 +2194,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45511</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2270,10 +2244,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45716</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2285,7 +2259,7 @@
       <c r="T9" t="s">
         <v>151</v>
       </c>
-      <c r="U9" s="2">
+      <c r="U9" s="1">
         <v>44665</v>
       </c>
     </row>
@@ -2326,10 +2300,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>45064</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2370,10 +2344,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>46135</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2385,7 +2359,7 @@
       <c r="T11" t="s">
         <v>152</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="1">
         <v>46203</v>
       </c>
     </row>
@@ -2423,7 +2397,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2464,10 +2438,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>46199</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2511,10 +2485,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45667</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2526,7 +2500,7 @@
       <c r="T14" t="s">
         <v>153</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" s="1">
         <v>46072</v>
       </c>
     </row>
@@ -2567,10 +2541,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>46064</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="1">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2617,10 +2591,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>44285</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="1">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2632,7 +2606,7 @@
       <c r="T16" t="s">
         <v>154</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2673,10 +2647,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45922</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2723,10 +2697,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>45930</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2738,7 +2712,7 @@
       <c r="T18" t="s">
         <v>155</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" s="1">
         <v>46198</v>
       </c>
     </row>
@@ -2779,10 +2753,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45524</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2794,7 +2768,7 @@
       <c r="T19" t="s">
         <v>122</v>
       </c>
-      <c r="U19" s="2">
+      <c r="U19" s="1">
         <v>46153</v>
       </c>
       <c r="V19">
@@ -2838,10 +2812,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>45026</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2853,7 +2827,7 @@
       <c r="T20" t="s">
         <v>156</v>
       </c>
-      <c r="U20" s="2">
+      <c r="U20" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2894,10 +2868,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>45159</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2909,7 +2883,7 @@
       <c r="T21" t="s">
         <v>124</v>
       </c>
-      <c r="U21" s="2">
+      <c r="U21" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2950,10 +2924,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2965,7 +2939,7 @@
       <c r="T22" t="s">
         <v>157</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" s="1">
         <v>45995</v>
       </c>
     </row>
@@ -3003,10 +2977,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>45713</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -3015,7 +2989,7 @@
       <c r="S23" t="s">
         <v>146</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -3056,10 +3030,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>46062</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>45925</v>
       </c>
       <c r="R24" t="s">
@@ -3106,10 +3080,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45079</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -3156,10 +3130,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>41346</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -3171,7 +3145,7 @@
       <c r="T26" t="s">
         <v>158</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>46150</v>
       </c>
     </row>
@@ -3212,10 +3186,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45579</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3262,10 +3236,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>46171</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3312,10 +3286,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44320</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3362,10 +3336,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="1">
         <v>42661</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="1">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3377,7 +3351,7 @@
       <c r="T30" t="s">
         <v>159</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>45358</v>
       </c>
     </row>
@@ -3418,10 +3392,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="1">
         <v>46064</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="1">
         <v>46064</v>
       </c>
       <c r="R31" t="s">
@@ -3468,10 +3442,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="1">
         <v>43797</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="1">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3518,10 +3492,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>42810</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3533,7 +3507,7 @@
       <c r="T33" t="s">
         <v>160</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>43802</v>
       </c>
     </row>
@@ -3574,10 +3548,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>45070</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>44910</v>
       </c>
       <c r="R34" t="s">
@@ -3624,10 +3598,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>43250</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3674,10 +3648,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45841</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3724,10 +3698,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="2">
+      <c r="P37" s="1">
         <v>45105</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="1">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3739,7 +3713,7 @@
       <c r="T37" t="s">
         <v>161</v>
       </c>
-      <c r="U37" s="2">
+      <c r="U37" s="1">
         <v>46184</v>
       </c>
     </row>
@@ -3780,10 +3754,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>45636</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>45579</v>
       </c>
       <c r="S38" t="s">
@@ -3830,10 +3804,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>45831</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3877,10 +3851,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>44287</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3901,22 +3875,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>164</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>165</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>166</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>167</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -8130,91 +8104,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>230</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>231</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>232</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>233</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>234</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>235</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>236</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>237</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>238</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>239</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>240</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>241</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>242</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>243</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>244</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>245</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>246</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>247</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>248</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>249</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>250</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>251</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>252</v>
       </c>
     </row>
@@ -8228,13 +8202,13 @@
       <c r="D2" t="s">
         <v>255</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
         <v>258</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>45492</v>
       </c>
       <c r="H2" t="s">
@@ -8252,13 +8226,13 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45491</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="1">
         <v>45528</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="1">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
@@ -8296,13 +8270,13 @@
       <c r="D3" t="s">
         <v>256</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
         <v>258</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>45631</v>
       </c>
       <c r="H3" t="s">
@@ -8320,13 +8294,13 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45628</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>45632</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
@@ -8361,13 +8335,13 @@
       <c r="D4" t="s">
         <v>256</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
         <v>258</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>45716</v>
       </c>
       <c r="H4" t="s">
@@ -8385,13 +8359,13 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45716</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <v>45722</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="1">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
@@ -8426,13 +8400,13 @@
       <c r="D5" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
         <v>258</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>45728</v>
       </c>
       <c r="H5" t="s">
@@ -8450,13 +8424,13 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45722</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <v>45782</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="1">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
@@ -8494,13 +8468,13 @@
       <c r="D6" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
         <v>258</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>45755</v>
       </c>
       <c r="H6" t="s">
@@ -8518,13 +8492,13 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45728</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="1">
         <v>45734</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="1">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
@@ -8562,7 +8536,7 @@
       <c r="D7" t="s">
         <v>257</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
@@ -8583,10 +8557,10 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45772</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="1">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
@@ -8624,7 +8598,7 @@
       <c r="D8" t="s">
         <v>257</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
@@ -8645,10 +8619,10 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>45762</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="1">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
@@ -8686,7 +8660,7 @@
       <c r="D9" t="s">
         <v>257</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
@@ -8707,10 +8681,10 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45763</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="1">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
@@ -8748,13 +8722,13 @@
       <c r="D10" t="s">
         <v>256</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
         <v>258</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>45755</v>
       </c>
       <c r="H10" t="s">
@@ -8772,13 +8746,13 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45754</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="1">
         <v>45849</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="1">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
@@ -8813,13 +8787,13 @@
       <c r="D11" t="s">
         <v>256</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
         <v>258</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>44973</v>
       </c>
       <c r="H11" t="s">
@@ -8837,13 +8811,13 @@
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44973</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="1">
         <v>45687</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" s="1">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
@@ -8878,13 +8852,13 @@
       <c r="D12" t="s">
         <v>256</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
         <v>258</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>45358</v>
       </c>
       <c r="H12" t="s">
@@ -8902,13 +8876,13 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45358</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="1">
         <v>45517</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12" s="1">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
@@ -8943,13 +8917,13 @@
       <c r="D13" t="s">
         <v>256</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
         <v>258</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>45573</v>
       </c>
       <c r="H13" t="s">
@@ -8967,13 +8941,13 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45572</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="1">
         <v>45572</v>
       </c>
-      <c r="S13" s="2">
+      <c r="S13" s="1">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
@@ -9011,13 +8985,13 @@
       <c r="D14" t="s">
         <v>256</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
         <v>258</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>45747</v>
       </c>
       <c r="H14" t="s">
@@ -9035,13 +9009,13 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>45736</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" s="1">
         <v>46101</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14" s="1">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
@@ -9077,70 +9051,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9178,10 +9152,10 @@
       <c r="O2" t="s">
         <v>102</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>45490</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -9225,10 +9199,10 @@
       <c r="O3" t="s">
         <v>81</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>45618</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -9272,10 +9246,10 @@
       <c r="O4" t="s">
         <v>97</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>45539</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -9319,10 +9293,10 @@
       <c r="O5" t="s">
         <v>98</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>45567</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -9366,10 +9340,10 @@
       <c r="O6" t="s">
         <v>95</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>45568</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -9413,10 +9387,10 @@
       <c r="O7" t="s">
         <v>83</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>45831</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -9460,10 +9434,10 @@
       <c r="O8" t="s">
         <v>103</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45601</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -9507,10 +9481,10 @@
       <c r="O9" t="s">
         <v>92</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45631</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -9554,10 +9528,10 @@
       <c r="O10" t="s">
         <v>89</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>43902</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -9601,10 +9575,10 @@
       <c r="O11" t="s">
         <v>99</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>44736</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -9648,10 +9622,10 @@
       <c r="O12" t="s">
         <v>82</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>45776</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -9695,10 +9669,10 @@
       <c r="O13" t="s">
         <v>80</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>45772</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -9742,10 +9716,10 @@
       <c r="O14" t="s">
         <v>100</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45000</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -9789,7 +9763,7 @@
       <c r="O15" t="s">
         <v>94</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -9830,7 +9804,7 @@
       <c r="O16" t="s">
         <v>90</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -9871,10 +9845,10 @@
       <c r="O17" t="s">
         <v>93</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45371</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -9918,10 +9892,10 @@
       <c r="O18" t="s">
         <v>91</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>46001</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -9965,10 +9939,10 @@
       <c r="O19" t="s">
         <v>104</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45436</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -10012,10 +9986,10 @@
       <c r="O20" t="s">
         <v>96</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>44372</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -10059,10 +10033,10 @@
       <c r="O21" t="s">
         <v>105</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>44362</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -10106,10 +10080,10 @@
       <c r="O22" t="s">
         <v>86</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -10147,10 +10121,10 @@
       <c r="O23" t="s">
         <v>359</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>40044</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -10162,7 +10136,7 @@
       <c r="T23" t="s">
         <v>399</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45775</v>
       </c>
     </row>
@@ -10200,10 +10174,10 @@
       <c r="O24" t="s">
         <v>80</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>43549</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -10215,7 +10189,7 @@
       <c r="T24" t="s">
         <v>400</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -10253,10 +10227,10 @@
       <c r="O25" t="s">
         <v>86</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45447</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -10268,7 +10242,7 @@
       <c r="T25" t="s">
         <v>401</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U25" s="1">
         <v>45937</v>
       </c>
     </row>
@@ -10306,10 +10280,10 @@
       <c r="O26" t="s">
         <v>100</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>44485</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -10321,7 +10295,7 @@
       <c r="T26" t="s">
         <v>402</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>45580</v>
       </c>
     </row>
@@ -10359,10 +10333,10 @@
       <c r="O27" t="s">
         <v>86</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45420</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -10374,7 +10348,7 @@
       <c r="T27" t="s">
         <v>403</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U27" s="1">
         <v>45588</v>
       </c>
     </row>
@@ -10412,10 +10386,10 @@
       <c r="O28" t="s">
         <v>101</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>44369</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -10427,7 +10401,7 @@
       <c r="T28" t="s">
         <v>404</v>
       </c>
-      <c r="U28" s="2">
+      <c r="U28" s="1">
         <v>45831</v>
       </c>
     </row>
@@ -10465,10 +10439,10 @@
       <c r="O29" t="s">
         <v>98</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44652</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -10480,7 +10454,7 @@
       <c r="T29" t="s">
         <v>405</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U29" s="1">
         <v>45734</v>
       </c>
     </row>
@@ -10512,7 +10486,7 @@
       <c r="T30" t="s">
         <v>406</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10544,7 +10518,7 @@
       <c r="T31" t="s">
         <v>407</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10576,7 +10550,7 @@
       <c r="T32" t="s">
         <v>408</v>
       </c>
-      <c r="U32" s="2">
+      <c r="U32" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10614,10 +10588,10 @@
       <c r="O33" t="s">
         <v>90</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>43762</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -10629,7 +10603,7 @@
       <c r="T33" t="s">
         <v>387</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>46037</v>
       </c>
     </row>
@@ -10667,16 +10641,16 @@
       <c r="O34" t="s">
         <v>360</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>40071</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>146</v>
       </c>
-      <c r="U34" s="2">
+      <c r="U34" s="1">
         <v>41023</v>
       </c>
     </row>
@@ -10708,10 +10682,10 @@
       <c r="O35" t="s">
         <v>87</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>44784</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -10720,7 +10694,7 @@
       <c r="S35" t="s">
         <v>146</v>
       </c>
-      <c r="U35" s="2">
+      <c r="U35" s="1">
         <v>45259</v>
       </c>
     </row>
@@ -10758,10 +10732,10 @@
       <c r="O36" t="s">
         <v>91</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45103</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -10770,7 +10744,7 @@
       <c r="S36" t="s">
         <v>146</v>
       </c>
-      <c r="U36" s="2">
+      <c r="U36" s="1">
         <v>46000</v>
       </c>
     </row>
@@ -10834,10 +10808,10 @@
       <c r="O38" t="s">
         <v>96</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>38511</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -10846,7 +10820,7 @@
       <c r="S38" t="s">
         <v>146</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>39068</v>
       </c>
     </row>
@@ -10884,10 +10858,10 @@
       <c r="O39" t="s">
         <v>103</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>39006</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -10899,7 +10873,7 @@
       <c r="T39" t="s">
         <v>409</v>
       </c>
-      <c r="U39" s="2">
+      <c r="U39" s="1">
         <v>40568</v>
       </c>
     </row>
@@ -10931,10 +10905,10 @@
       <c r="O40" t="s">
         <v>100</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>40836</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -10946,7 +10920,7 @@
       <c r="T40" t="s">
         <v>410</v>
       </c>
-      <c r="U40" s="2">
+      <c r="U40" s="1">
         <v>42270</v>
       </c>
     </row>
@@ -10984,10 +10958,10 @@
       <c r="O41" t="s">
         <v>95</v>
       </c>
-      <c r="P41" s="2">
+      <c r="P41" s="1">
         <v>42940</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="1">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -10999,7 +10973,7 @@
       <c r="T41" t="s">
         <v>411</v>
       </c>
-      <c r="U41" s="2">
+      <c r="U41" s="1">
         <v>44148</v>
       </c>
     </row>
@@ -11037,10 +11011,10 @@
       <c r="O42" t="s">
         <v>82</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="1">
         <v>43696</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="1">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -11052,7 +11026,7 @@
       <c r="T42" t="s">
         <v>412</v>
       </c>
-      <c r="U42" s="2">
+      <c r="U42" s="1">
         <v>43185</v>
       </c>
     </row>
@@ -11090,10 +11064,10 @@
       <c r="O43" t="s">
         <v>84</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="1">
         <v>43544</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="1">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -11105,7 +11079,7 @@
       <c r="T43" t="s">
         <v>413</v>
       </c>
-      <c r="U43" s="2">
+      <c r="U43" s="1">
         <v>42850</v>
       </c>
     </row>
@@ -11143,10 +11117,10 @@
       <c r="O44" t="s">
         <v>97</v>
       </c>
-      <c r="P44" s="2">
+      <c r="P44" s="1">
         <v>45076</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="1">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -11158,7 +11132,7 @@
       <c r="T44" t="s">
         <v>414</v>
       </c>
-      <c r="U44" s="2">
+      <c r="U44" s="1">
         <v>44404</v>
       </c>
     </row>
@@ -11196,10 +11170,10 @@
       <c r="O45" t="s">
         <v>81</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="1">
         <v>42963</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="1">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -11211,7 +11185,7 @@
       <c r="T45" t="s">
         <v>415</v>
       </c>
-      <c r="U45" s="2">
+      <c r="U45" s="1">
         <v>42698</v>
       </c>
     </row>
@@ -11249,10 +11223,10 @@
       <c r="O46" t="s">
         <v>88</v>
       </c>
-      <c r="P46" s="2">
+      <c r="P46" s="1">
         <v>45054</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="1">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -11264,7 +11238,7 @@
       <c r="T46" t="s">
         <v>416</v>
       </c>
-      <c r="U46" s="2">
+      <c r="U46" s="1">
         <v>43941</v>
       </c>
     </row>
@@ -11279,25 +11253,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>163</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>164</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>417</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>418</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>419</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>420</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>421</v>
       </c>
     </row>
@@ -11983,22 +11957,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>422</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>423</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>424</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>425</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>426</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>427</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -531,61 +531,97 @@
     <t>1.0</t>
   </si>
   <si>
+    <t>HSI</t>
+  </si>
+  <si>
+    <t>TBO</t>
+  </si>
+  <si>
     <t>NÃO HÁ AT</t>
   </si>
   <si>
-    <t>TBO</t>
+    <t>6.081703911</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
+    <t>HÁ AT</t>
+  </si>
+  <si>
+    <t>2.662374151</t>
+  </si>
+  <si>
+    <t>TBO*</t>
+  </si>
+  <si>
+    <t>HSI, FEITO EM 13/05</t>
+  </si>
+  <si>
+    <t>7.432022084</t>
+  </si>
+  <si>
+    <t>5.1586629</t>
+  </si>
+  <si>
+    <t>17.3</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>19.5</t>
+  </si>
+  <si>
+    <t>13.60098136</t>
+  </si>
+  <si>
+    <t>15.25999355</t>
+  </si>
+  <si>
+    <t>Rachadura na CT DISK, vai recolher</t>
+  </si>
+  <si>
+    <t>19.2</t>
+  </si>
+  <si>
+    <t>#N/A</t>
+  </si>
+  <si>
+    <t>17.5</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>3.109763441</t>
+  </si>
+  <si>
     <t>34.2</t>
   </si>
   <si>
     <t>22.0</t>
   </si>
   <si>
-    <t>HSI</t>
-  </si>
-  <si>
     <t>27.0</t>
   </si>
   <si>
-    <t>17.3</t>
-  </si>
-  <si>
-    <t>16.0</t>
-  </si>
-  <si>
-    <t>19.5</t>
-  </si>
-  <si>
-    <t>HÁ AT</t>
-  </si>
-  <si>
-    <t>2.662374151</t>
-  </si>
-  <si>
-    <t>TBO*</t>
-  </si>
-  <si>
-    <t>17.5</t>
-  </si>
-  <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>3.109763441</t>
-  </si>
-  <si>
-    <t>19.2</t>
-  </si>
-  <si>
-    <t>#N/A</t>
-  </si>
-  <si>
-    <t>5.1586629</t>
+    <t>22.5</t>
+  </si>
+  <si>
+    <t>25.0</t>
+  </si>
+  <si>
+    <t>16.8975204</t>
+  </si>
+  <si>
+    <t>57.1</t>
+  </si>
+  <si>
+    <t>47.0</t>
+  </si>
+  <si>
+    <t>5.546485261</t>
   </si>
   <si>
     <t>28.1</t>
@@ -594,40 +630,19 @@
     <t>9.627027027</t>
   </si>
   <si>
-    <t>6.081703911</t>
-  </si>
-  <si>
-    <t>57.1</t>
-  </si>
-  <si>
-    <t>47.0</t>
-  </si>
-  <si>
-    <t>5.546485261</t>
-  </si>
-  <si>
-    <t>13.60098136</t>
-  </si>
-  <si>
-    <t>HSI, FEITO EM 13/05</t>
-  </si>
-  <si>
-    <t>7.432022084</t>
-  </si>
-  <si>
-    <t>15.25999355</t>
-  </si>
-  <si>
-    <t>Rachadura na CT DISK, vai recolher</t>
-  </si>
-  <si>
-    <t>22.5</t>
-  </si>
-  <si>
-    <t>25.0</t>
-  </si>
-  <si>
-    <t>16.8975204</t>
+    <t>T5 elevada, vai recolher</t>
+  </si>
+  <si>
+    <t>38.0</t>
+  </si>
+  <si>
+    <t>25.26224105</t>
+  </si>
+  <si>
+    <t>Recolhido por pane 12/06. Aguardando DPE do PAMASP</t>
+  </si>
+  <si>
+    <t>30.40106477</t>
   </si>
   <si>
     <t>30.0</t>
@@ -636,40 +651,42 @@
     <t>22.58188266</t>
   </si>
   <si>
-    <t>Recolhido por pane 12/06. Aguardando DPE do PAMASP</t>
-  </si>
-  <si>
-    <t>T5 elevada, vai recolher</t>
-  </si>
-  <si>
-    <t>38.0</t>
-  </si>
-  <si>
-    <t>25.26224105</t>
+    <t>Motor novo, não atingiu performance (CAIXA DE ACESSÓRIOS PESADA) 27/05</t>
+  </si>
+  <si>
+    <t>recolhido 23/04. adiantou o tbo</t>
   </si>
   <si>
     <t>29.10388459</t>
   </si>
   <si>
-    <t>Motor novo, não atingiu performance (CAIXA DE ACESSÓRIOS PESADA) 27/05</t>
-  </si>
-  <si>
-    <t>recolhido 23/04. adiantou o tbo</t>
-  </si>
-  <si>
     <t>54.82962963</t>
-  </si>
-  <si>
-    <t>30.40106477</t>
-  </si>
-  <si>
-    <t>AT 386000001002  500H
-Disponível no CAN-SP no dia 02/07, emergência já atrelada.</t>
   </si>
   <si>
     <t>AT 313000000695
 4450H
 Motor substituto já em MN</t>
+  </si>
+  <si>
+    <t>AT 386000001002  500H
+Disponível no CAN-SP no dia 02/07, emergência já atrelada.</t>
+  </si>
+  <si>
+    <t>PREVISÃO PARA O PRÓXIMO HSI COM 4665:30 TSO
+AT 685000001688
+4.700:00 FH, PARA REVISÃO GERAL.
+*Está previsto p/JAN. Puxamos p/ DEZ pensando no pior cenário.</t>
+  </si>
+  <si>
+    <t>AT 396000000363  / 4.500:00 HORAS PARA REVISÃO GERAL
+AT 396000000321   /  MOTOR DISPONÍVEL 232:05 PARA HSI; TSN 6.327:40; TSO: 3.825:30H;  /   HSI COM 4057H</t>
+  </si>
+  <si>
+    <t>AT 396000000363  / 4.500:00 HORAS PARA REVISÃO GERAL
+AT 396000000321   /  MOTOR DISPONÍVEL 232:05 PARA HSI; TSN 6.327:40; TSO: 3.825:30H;  /   HSI COM 4057H</t>
+  </si>
+  <si>
+    <t>AT 685000002046, CONCEDEU MAIS 400H</t>
   </si>
   <si>
     <t>AT  13000000580  /  Possui em vigor uma extensão de 150h para o cumprimento da HSI (AT 313000000528), das quais já voou 136:25h (portanto, restam 13:35h até a parada para execução da HSI). 3300H FEZ HSI.
@@ -685,30 +702,13 @@
 motor POSSUI TSO DE 2.941:00H, RESTANDO 500:15H . vai casar exatamente com o HSI 3.441,25</t>
   </si>
   <si>
-    <t>AT 685000002046, CONCEDEU MAIS 400H</t>
-  </si>
-  <si>
-    <t>PREVISÃO PARA O PRÓXIMO HSI COM 4665:30 TSO
-AT 685000001688
-4.700:00 FH, PARA REVISÃO GERAL.
-*Está previsto p/JAN. Puxamos p/ DEZ pensando no pior cenário.</t>
+    <t>AT 685000001498   /  2.439:15 HORAS DE MOTOR COM 707:05 HORAS DISPONÍVEIS PARA HSI.OU SEJA 3146:20
+O PAMASP ADIANTOU POR AT, POIS PARÂMETROS DEGRADARAM.</t>
   </si>
   <si>
     <t>1326 h disponíveis em fev/26 segundo operador. tbo 4000h
 PROXIMO HSI COM 
 3.239</t>
-  </si>
-  <si>
-    <t>AT 685000001498   /  2.439:15 HORAS DE MOTOR COM 707:05 HORAS DISPONÍVEIS PARA HSI.OU SEJA 3146:20
-O PAMASP ADIANTOU POR AT, POIS PARÂMETROS DEGRADARAM.</t>
-  </si>
-  <si>
-    <t>AT 396000000363  / 4.500:00 HORAS PARA REVISÃO GERAL
-AT 396000000321   /  MOTOR DISPONÍVEL 232:05 PARA HSI; TSN 6.327:40; TSO: 3.825:30H;  /   HSI COM 4057H</t>
-  </si>
-  <si>
-    <t>AT 396000000363  / 4.500:00 HORAS PARA REVISÃO GERAL
-AT 396000000321   /  MOTOR DISPONÍVEL 232:05 PARA HSI; TSN 6.327:40; TSO: 3.825:30H;  /   HSI COM 4057H</t>
   </si>
   <si>
     <t>contabilizado AT
@@ -3896,10 +3896,10 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B2">
-        <v>2743</v>
+        <v>2704</v>
       </c>
       <c r="C2">
         <v>2025</v>
@@ -3913,10 +3913,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B3">
-        <v>2743</v>
+        <v>2704</v>
       </c>
       <c r="C3">
         <v>2025</v>
@@ -3930,10 +3930,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B4">
-        <v>2743</v>
+        <v>2704</v>
       </c>
       <c r="C4">
         <v>2025</v>
@@ -3947,16 +3947,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B5">
-        <v>2743</v>
+        <v>2704</v>
       </c>
       <c r="C5">
         <v>2025</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
         <v>170</v>
@@ -3964,13 +3964,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B6">
-        <v>2743</v>
+        <v>2704</v>
       </c>
       <c r="C6">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D6">
         <v>8</v>
@@ -3978,22 +3978,19 @@
       <c r="E6" t="s">
         <v>171</v>
       </c>
-      <c r="F6" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" t="b">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="B7">
+        <v>2704</v>
       </c>
       <c r="C7">
         <v>2025</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>172</v>
@@ -4001,36 +3998,36 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" t="b">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="B8">
+        <v>2704</v>
       </c>
       <c r="C8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" t="b">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="B9">
+        <v>2704</v>
       </c>
       <c r="C9">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4044,10 +4041,10 @@
         <v>2025</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4061,10 +4058,10 @@
         <v>2025</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4078,10 +4075,10 @@
         <v>2025</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4092,135 +4089,132 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>171</v>
-      </c>
-      <c r="F13" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14">
-        <v>2736</v>
+        <v>59</v>
+      </c>
+      <c r="B14" t="b">
+        <v>0</v>
       </c>
       <c r="C14">
         <v>2025</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15">
-        <v>2736</v>
+        <v>59</v>
+      </c>
+      <c r="B15" t="b">
+        <v>0</v>
       </c>
       <c r="C15">
         <v>2025</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16">
-        <v>2736</v>
+        <v>59</v>
+      </c>
+      <c r="B16" t="b">
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>169</v>
+        <v>171</v>
+      </c>
+      <c r="F16" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B17">
-        <v>2736</v>
+        <v>2743</v>
       </c>
       <c r="C17">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>171</v>
-      </c>
-      <c r="F17" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B18">
-        <v>2732</v>
+        <v>2743</v>
       </c>
       <c r="C18">
         <v>2025</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B19">
-        <v>2732</v>
+        <v>2743</v>
       </c>
       <c r="C19">
         <v>2025</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B20">
-        <v>2732</v>
+        <v>2743</v>
       </c>
       <c r="C20">
         <v>2025</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="s">
         <v>172</v>
@@ -4228,189 +4222,192 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B21">
-        <v>2732</v>
+        <v>2743</v>
       </c>
       <c r="C21">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>172</v>
+        <v>171</v>
+      </c>
+      <c r="F21" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B22">
-        <v>2732</v>
+        <v>2719</v>
       </c>
       <c r="C22">
         <v>2025</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B23">
-        <v>2732</v>
+        <v>2719</v>
       </c>
       <c r="C23">
         <v>2025</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B24">
-        <v>2732</v>
+        <v>2719</v>
       </c>
       <c r="C24">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>171</v>
-      </c>
-      <c r="F24" t="s">
-        <v>217</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="B25">
-        <v>2709</v>
+        <v>2719</v>
       </c>
       <c r="C25">
         <v>2025</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="B26">
-        <v>2709</v>
+        <v>2719</v>
       </c>
       <c r="C26">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>2709</v>
+        <v>2719</v>
       </c>
       <c r="C27">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>169</v>
+        <v>177</v>
+      </c>
+      <c r="F27" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B28">
-        <v>2709</v>
+        <v>2733</v>
       </c>
       <c r="C28">
         <v>2025</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B29">
-        <v>2709</v>
+        <v>2733</v>
       </c>
       <c r="C29">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B30">
-        <v>2709</v>
+        <v>2733</v>
       </c>
       <c r="C30">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B31">
-        <v>2709</v>
+        <v>2733</v>
       </c>
       <c r="C31">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E31" t="s">
         <v>175</v>
@@ -4418,67 +4415,73 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B32">
-        <v>2709</v>
+        <v>2733</v>
       </c>
       <c r="C32">
         <v>2026</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>176</v>
+        <v>178</v>
+      </c>
+      <c r="F32" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>2740</v>
+        <v>2733</v>
       </c>
       <c r="C33">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B34">
-        <v>2740</v>
+        <v>2733</v>
       </c>
       <c r="C34">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E34" t="s">
-        <v>169</v>
+        <v>171</v>
+      </c>
+      <c r="F34" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B35">
-        <v>2740</v>
+        <v>2703</v>
       </c>
       <c r="C35">
         <v>2025</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="s">
         <v>169</v>
@@ -4486,87 +4489,84 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B36">
-        <v>2740</v>
+        <v>2703</v>
       </c>
       <c r="C36">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B37">
-        <v>2740</v>
+        <v>2703</v>
       </c>
       <c r="C37">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B38">
-        <v>2740</v>
+        <v>2703</v>
       </c>
       <c r="C38">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
         <v>175</v>
       </c>
-      <c r="F38" t="s">
-        <v>218</v>
-      </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B39">
-        <v>2740</v>
+        <v>2703</v>
       </c>
       <c r="C39">
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B40">
-        <v>2740</v>
+        <v>2703</v>
       </c>
       <c r="C40">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E40" t="s">
         <v>171</v>
@@ -4637,7 +4637,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4662,10 +4662,10 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B46">
-        <v>2719</v>
+        <v>2736</v>
       </c>
       <c r="C46">
         <v>2025</v>
@@ -4679,10 +4679,10 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B47">
-        <v>2719</v>
+        <v>2736</v>
       </c>
       <c r="C47">
         <v>2025</v>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B48">
-        <v>2719</v>
+        <v>2736</v>
       </c>
       <c r="C48">
         <v>2025</v>
@@ -4713,115 +4713,115 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B49">
-        <v>2719</v>
+        <v>2736</v>
       </c>
       <c r="C49">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>180</v>
+        <v>171</v>
+      </c>
+      <c r="F49" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B50">
-        <v>2719</v>
+        <v>2732</v>
       </c>
       <c r="C50">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D50">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B51">
-        <v>2719</v>
+        <v>2732</v>
       </c>
       <c r="C51">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>182</v>
-      </c>
-      <c r="F51" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B52">
-        <v>2723</v>
+        <v>2732</v>
       </c>
       <c r="C52">
         <v>2025</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B53">
-        <v>2723</v>
+        <v>2732</v>
       </c>
       <c r="C53">
         <v>2025</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B54">
-        <v>2723</v>
+        <v>2732</v>
       </c>
       <c r="C54">
         <v>2025</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E54" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B55">
-        <v>2723</v>
+        <v>2732</v>
       </c>
       <c r="C55">
         <v>2025</v>
@@ -4830,1149 +4830,1149 @@
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B56">
-        <v>2723</v>
+        <v>2732</v>
       </c>
       <c r="C56">
         <v>2026</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>183</v>
+        <v>171</v>
+      </c>
+      <c r="F56" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B57">
-        <v>2723</v>
+        <v>2740</v>
       </c>
       <c r="C57">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D57">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B58">
-        <v>2723</v>
+        <v>2740</v>
       </c>
       <c r="C58">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D58">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B59">
-        <v>2723</v>
+        <v>2740</v>
       </c>
       <c r="C59">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="D59">
         <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>175</v>
-      </c>
-      <c r="F59" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B60">
-        <v>2723</v>
+        <v>2740</v>
       </c>
       <c r="C60">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>76</v>
-      </c>
-      <c r="B61" t="b">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="B61">
+        <v>2740</v>
       </c>
       <c r="C61">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E61" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>76</v>
-      </c>
-      <c r="B62" t="b">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="B62">
+        <v>2740</v>
       </c>
       <c r="C62">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="F62" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>76</v>
-      </c>
-      <c r="B63" t="b">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="B63">
+        <v>2740</v>
       </c>
       <c r="C63">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64" t="b">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="B64">
+        <v>2740</v>
       </c>
       <c r="C64">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D64">
+        <v>8</v>
+      </c>
+      <c r="E64" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65">
+        <v>2720</v>
+      </c>
+      <c r="C65">
+        <v>2025</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66">
+        <v>2720</v>
+      </c>
+      <c r="C66">
+        <v>2025</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67">
+        <v>2720</v>
+      </c>
+      <c r="C67">
+        <v>2025</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68">
+        <v>2720</v>
+      </c>
+      <c r="C68">
+        <v>2025</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69">
+        <v>2720</v>
+      </c>
+      <c r="C69">
+        <v>2025</v>
+      </c>
+      <c r="D69">
+        <v>5</v>
+      </c>
+      <c r="E69" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70">
+        <v>2720</v>
+      </c>
+      <c r="C70">
+        <v>2025</v>
+      </c>
+      <c r="D70">
         <v>10</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E70" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71">
+        <v>2720</v>
+      </c>
+      <c r="C71">
+        <v>2026</v>
+      </c>
+      <c r="D71">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72">
+        <v>2720</v>
+      </c>
+      <c r="C72">
+        <v>2028</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73">
+        <v>2741</v>
+      </c>
+      <c r="C73">
+        <v>2025</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74">
+        <v>2741</v>
+      </c>
+      <c r="C74">
+        <v>2025</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+      <c r="E74" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75">
+        <v>2741</v>
+      </c>
+      <c r="C75">
+        <v>2025</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="E75" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76">
+        <v>2741</v>
+      </c>
+      <c r="C76">
+        <v>2025</v>
+      </c>
+      <c r="D76">
+        <v>9</v>
+      </c>
+      <c r="E76" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
-        <v>76</v>
-      </c>
-      <c r="B65" t="b">
-        <v>0</v>
-      </c>
-      <c r="C65">
-        <v>2026</v>
-      </c>
-      <c r="D65">
-        <v>5</v>
-      </c>
-      <c r="E65" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
-        <v>76</v>
-      </c>
-      <c r="B66" t="b">
-        <v>0</v>
-      </c>
-      <c r="C66">
-        <v>2026</v>
-      </c>
-      <c r="D66">
-        <v>6</v>
-      </c>
-      <c r="E66" t="s">
-        <v>175</v>
-      </c>
-      <c r="F66" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
-        <v>76</v>
-      </c>
-      <c r="B67" t="b">
-        <v>0</v>
-      </c>
-      <c r="C67">
-        <v>2026</v>
-      </c>
-      <c r="D67">
-        <v>7</v>
-      </c>
-      <c r="E67" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
-        <v>76</v>
-      </c>
-      <c r="B68" t="b">
-        <v>0</v>
-      </c>
-      <c r="C68">
-        <v>2026</v>
-      </c>
-      <c r="D68">
-        <v>8</v>
-      </c>
-      <c r="E68" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" t="s">
-        <v>76</v>
-      </c>
-      <c r="B69" t="b">
-        <v>0</v>
-      </c>
-      <c r="C69">
-        <v>2028</v>
-      </c>
-      <c r="D69">
-        <v>12</v>
-      </c>
-      <c r="E69" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70">
-        <v>2703</v>
-      </c>
-      <c r="C70">
-        <v>2025</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-      <c r="E70" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71">
-        <v>2703</v>
-      </c>
-      <c r="C71">
-        <v>2025</v>
-      </c>
-      <c r="D71">
-        <v>2</v>
-      </c>
-      <c r="E71" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72">
-        <v>2703</v>
-      </c>
-      <c r="C72">
-        <v>2025</v>
-      </c>
-      <c r="D72">
-        <v>3</v>
-      </c>
-      <c r="E72" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
-        <v>41</v>
-      </c>
-      <c r="B73">
-        <v>2703</v>
-      </c>
-      <c r="C73">
-        <v>2025</v>
-      </c>
-      <c r="D73">
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77">
+        <v>2741</v>
+      </c>
+      <c r="C77">
+        <v>2025</v>
+      </c>
+      <c r="D77">
         <v>10</v>
-      </c>
-      <c r="E73" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74">
-        <v>2703</v>
-      </c>
-      <c r="C74">
-        <v>2026</v>
-      </c>
-      <c r="D74">
-        <v>7</v>
-      </c>
-      <c r="E74" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75">
-        <v>2703</v>
-      </c>
-      <c r="C75">
-        <v>2027</v>
-      </c>
-      <c r="D75">
-        <v>6</v>
-      </c>
-      <c r="E75" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" t="s">
-        <v>44</v>
-      </c>
-      <c r="B76">
-        <v>2742</v>
-      </c>
-      <c r="C76">
-        <v>2025</v>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77">
-        <v>2742</v>
-      </c>
-      <c r="C77">
-        <v>2025</v>
-      </c>
-      <c r="D77">
-        <v>2</v>
       </c>
       <c r="E77" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B78">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="C78">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D78">
+        <v>7</v>
+      </c>
+      <c r="E78" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79">
+        <v>2741</v>
+      </c>
+      <c r="C79">
+        <v>2026</v>
+      </c>
+      <c r="D79">
+        <v>8</v>
+      </c>
+      <c r="E79" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80">
+        <v>2741</v>
+      </c>
+      <c r="C80">
+        <v>2028</v>
+      </c>
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
+        <v>76</v>
+      </c>
+      <c r="B81" t="b">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>2025</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>76</v>
+      </c>
+      <c r="B82" t="b">
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <v>2025</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>76</v>
+      </c>
+      <c r="B83" t="b">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>2025</v>
+      </c>
+      <c r="D83">
         <v>3</v>
       </c>
-      <c r="E78" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79">
-        <v>2742</v>
-      </c>
-      <c r="C79">
-        <v>2025</v>
-      </c>
-      <c r="D79">
-        <v>4</v>
-      </c>
-      <c r="E79" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80">
-        <v>2742</v>
-      </c>
-      <c r="C80">
-        <v>2025</v>
-      </c>
-      <c r="D80">
-        <v>5</v>
-      </c>
-      <c r="E80" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81">
-        <v>2742</v>
-      </c>
-      <c r="C81">
-        <v>2026</v>
-      </c>
-      <c r="D81">
-        <v>5</v>
-      </c>
-      <c r="E81" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82">
-        <v>2742</v>
-      </c>
-      <c r="C82">
-        <v>2026</v>
-      </c>
-      <c r="D82">
-        <v>6</v>
-      </c>
-      <c r="E82" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" t="s">
-        <v>44</v>
-      </c>
-      <c r="B83">
-        <v>2742</v>
-      </c>
-      <c r="C83">
-        <v>2026</v>
-      </c>
-      <c r="D83">
-        <v>7</v>
-      </c>
       <c r="E83" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>44</v>
-      </c>
-      <c r="B84">
-        <v>2742</v>
+        <v>76</v>
+      </c>
+      <c r="B84" t="b">
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="D84">
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>44</v>
-      </c>
-      <c r="B85">
-        <v>2742</v>
+        <v>76</v>
+      </c>
+      <c r="B85" t="b">
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D85">
+        <v>5</v>
+      </c>
+      <c r="E85" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
+        <v>76</v>
+      </c>
+      <c r="B86" t="b">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>2026</v>
+      </c>
+      <c r="D86">
+        <v>6</v>
+      </c>
+      <c r="E86" t="s">
+        <v>170</v>
+      </c>
+      <c r="F86" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
+        <v>76</v>
+      </c>
+      <c r="B87" t="b">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>2026</v>
+      </c>
+      <c r="D87">
+        <v>7</v>
+      </c>
+      <c r="E87" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>76</v>
+      </c>
+      <c r="B88" t="b">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>2026</v>
+      </c>
+      <c r="D88">
+        <v>8</v>
+      </c>
+      <c r="E88" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>76</v>
+      </c>
+      <c r="B89" t="b">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>2028</v>
+      </c>
+      <c r="D89">
         <v>12</v>
       </c>
-      <c r="E85" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" t="s">
-        <v>63</v>
-      </c>
-      <c r="B86">
-        <v>2704</v>
-      </c>
-      <c r="C86">
-        <v>2025</v>
-      </c>
-      <c r="D86">
+      <c r="E89" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
+        <v>70</v>
+      </c>
+      <c r="B90">
+        <v>2723</v>
+      </c>
+      <c r="C90">
+        <v>2025</v>
+      </c>
+      <c r="D90">
         <v>1</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E90" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
-      <c r="A87" t="s">
-        <v>63</v>
-      </c>
-      <c r="B87">
-        <v>2704</v>
-      </c>
-      <c r="C87">
-        <v>2025</v>
-      </c>
-      <c r="D87">
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91">
+        <v>2723</v>
+      </c>
+      <c r="C91">
+        <v>2025</v>
+      </c>
+      <c r="D91">
         <v>2</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E91" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
-      <c r="A88" t="s">
-        <v>63</v>
-      </c>
-      <c r="B88">
-        <v>2704</v>
-      </c>
-      <c r="C88">
-        <v>2025</v>
-      </c>
-      <c r="D88">
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>70</v>
+      </c>
+      <c r="B92">
+        <v>2723</v>
+      </c>
+      <c r="C92">
+        <v>2025</v>
+      </c>
+      <c r="D92">
         <v>3</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E92" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
-      <c r="A89" t="s">
-        <v>63</v>
-      </c>
-      <c r="B89">
-        <v>2704</v>
-      </c>
-      <c r="C89">
-        <v>2025</v>
-      </c>
-      <c r="D89">
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>70</v>
+      </c>
+      <c r="B93">
+        <v>2723</v>
+      </c>
+      <c r="C93">
+        <v>2025</v>
+      </c>
+      <c r="D93">
+        <v>10</v>
+      </c>
+      <c r="E93" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>70</v>
+      </c>
+      <c r="B94">
+        <v>2723</v>
+      </c>
+      <c r="C94">
+        <v>2026</v>
+      </c>
+      <c r="D94">
         <v>5</v>
       </c>
-      <c r="E89" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" t="s">
-        <v>63</v>
-      </c>
-      <c r="B90">
-        <v>2704</v>
-      </c>
-      <c r="C90">
-        <v>2025</v>
-      </c>
-      <c r="D90">
-        <v>8</v>
-      </c>
-      <c r="E90" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" t="s">
-        <v>63</v>
-      </c>
-      <c r="B91">
-        <v>2704</v>
-      </c>
-      <c r="C91">
-        <v>2025</v>
-      </c>
-      <c r="D91">
-        <v>10</v>
-      </c>
-      <c r="E91" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" t="s">
-        <v>63</v>
-      </c>
-      <c r="B92">
-        <v>2704</v>
-      </c>
-      <c r="C92">
+      <c r="E94" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>70</v>
+      </c>
+      <c r="B95">
+        <v>2723</v>
+      </c>
+      <c r="C95">
         <v>2026</v>
       </c>
-      <c r="D92">
+      <c r="D95">
+        <v>6</v>
+      </c>
+      <c r="E95" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>70</v>
+      </c>
+      <c r="B96">
+        <v>2723</v>
+      </c>
+      <c r="C96">
+        <v>2026</v>
+      </c>
+      <c r="D96">
         <v>7</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E96" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
-      <c r="A93" t="s">
-        <v>63</v>
-      </c>
-      <c r="B93">
-        <v>2704</v>
-      </c>
-      <c r="C93">
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97">
+        <v>2723</v>
+      </c>
+      <c r="C97">
         <v>2027</v>
       </c>
-      <c r="D93">
-        <v>7</v>
-      </c>
-      <c r="E93" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" t="s">
-        <v>65</v>
-      </c>
-      <c r="B94">
-        <v>2739</v>
-      </c>
-      <c r="C94">
-        <v>2025</v>
-      </c>
-      <c r="D94">
-        <v>1</v>
-      </c>
-      <c r="E94" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" t="s">
-        <v>65</v>
-      </c>
-      <c r="B95">
-        <v>2739</v>
-      </c>
-      <c r="C95">
-        <v>2025</v>
-      </c>
-      <c r="D95">
-        <v>2</v>
-      </c>
-      <c r="E95" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" t="s">
-        <v>65</v>
-      </c>
-      <c r="B96">
-        <v>2739</v>
-      </c>
-      <c r="C96">
-        <v>2025</v>
-      </c>
-      <c r="D96">
+      <c r="D97">
         <v>3</v>
-      </c>
-      <c r="E96" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" t="s">
-        <v>65</v>
-      </c>
-      <c r="B97">
-        <v>2739</v>
-      </c>
-      <c r="C97">
-        <v>2025</v>
-      </c>
-      <c r="D97">
-        <v>10</v>
       </c>
       <c r="E97" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="F97" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B98">
-        <v>2739</v>
+        <v>2723</v>
       </c>
       <c r="C98">
+        <v>2028</v>
+      </c>
+      <c r="D98">
+        <v>7</v>
+      </c>
+      <c r="E98" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>73</v>
+      </c>
+      <c r="B99">
+        <v>2709</v>
+      </c>
+      <c r="C99">
+        <v>2025</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>73</v>
+      </c>
+      <c r="B100">
+        <v>2709</v>
+      </c>
+      <c r="C100">
+        <v>2025</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+      <c r="E100" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>73</v>
+      </c>
+      <c r="B101">
+        <v>2709</v>
+      </c>
+      <c r="C101">
+        <v>2025</v>
+      </c>
+      <c r="D101">
+        <v>3</v>
+      </c>
+      <c r="E101" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>73</v>
+      </c>
+      <c r="B102">
+        <v>2709</v>
+      </c>
+      <c r="C102">
+        <v>2025</v>
+      </c>
+      <c r="D102">
+        <v>10</v>
+      </c>
+      <c r="E102" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>73</v>
+      </c>
+      <c r="B103">
+        <v>2709</v>
+      </c>
+      <c r="C103">
         <v>2026</v>
       </c>
-      <c r="D98">
+      <c r="D103">
         <v>5</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E103" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
-      <c r="A99" t="s">
-        <v>65</v>
-      </c>
-      <c r="B99">
-        <v>2739</v>
-      </c>
-      <c r="C99">
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>73</v>
+      </c>
+      <c r="B104">
+        <v>2709</v>
+      </c>
+      <c r="C104">
         <v>2026</v>
       </c>
-      <c r="D99">
+      <c r="D104">
         <v>6</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E104" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
-      <c r="A100" t="s">
-        <v>65</v>
-      </c>
-      <c r="B100">
-        <v>2739</v>
-      </c>
-      <c r="C100">
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>73</v>
+      </c>
+      <c r="B105">
+        <v>2709</v>
+      </c>
+      <c r="C105">
         <v>2026</v>
       </c>
-      <c r="D100">
+      <c r="D105">
+        <v>11</v>
+      </c>
+      <c r="E105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>73</v>
+      </c>
+      <c r="B106">
+        <v>2709</v>
+      </c>
+      <c r="C106">
+        <v>2026</v>
+      </c>
+      <c r="D106">
+        <v>12</v>
+      </c>
+      <c r="E106" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>78</v>
+      </c>
+      <c r="B107">
+        <v>2708</v>
+      </c>
+      <c r="C107">
+        <v>2025</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>78</v>
+      </c>
+      <c r="B108">
+        <v>2708</v>
+      </c>
+      <c r="C108">
+        <v>2025</v>
+      </c>
+      <c r="D108">
+        <v>2</v>
+      </c>
+      <c r="E108" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>78</v>
+      </c>
+      <c r="B109">
+        <v>2708</v>
+      </c>
+      <c r="C109">
+        <v>2025</v>
+      </c>
+      <c r="D109">
+        <v>3</v>
+      </c>
+      <c r="E109" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>78</v>
+      </c>
+      <c r="B110">
+        <v>2708</v>
+      </c>
+      <c r="C110">
+        <v>2025</v>
+      </c>
+      <c r="D110">
+        <v>10</v>
+      </c>
+      <c r="E110" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>78</v>
+      </c>
+      <c r="B111">
+        <v>2708</v>
+      </c>
+      <c r="C111">
+        <v>2026</v>
+      </c>
+      <c r="D111">
+        <v>5</v>
+      </c>
+      <c r="E111" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>78</v>
+      </c>
+      <c r="B112">
+        <v>2708</v>
+      </c>
+      <c r="C112">
+        <v>2026</v>
+      </c>
+      <c r="D112">
+        <v>6</v>
+      </c>
+      <c r="E112" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>78</v>
+      </c>
+      <c r="B113">
+        <v>2708</v>
+      </c>
+      <c r="C113">
+        <v>2026</v>
+      </c>
+      <c r="D113">
         <v>7</v>
       </c>
-      <c r="E100" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" t="s">
-        <v>65</v>
-      </c>
-      <c r="B101">
-        <v>2739</v>
-      </c>
-      <c r="C101">
-        <v>2027</v>
-      </c>
-      <c r="D101">
-        <v>6</v>
-      </c>
-      <c r="E101" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" t="s">
-        <v>74</v>
-      </c>
-      <c r="B102">
-        <v>2720</v>
-      </c>
-      <c r="C102">
-        <v>2025</v>
-      </c>
-      <c r="D102">
-        <v>1</v>
-      </c>
-      <c r="E102" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" t="s">
-        <v>74</v>
-      </c>
-      <c r="B103">
-        <v>2720</v>
-      </c>
-      <c r="C103">
-        <v>2025</v>
-      </c>
-      <c r="D103">
-        <v>2</v>
-      </c>
-      <c r="E103" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" t="s">
-        <v>74</v>
-      </c>
-      <c r="B104">
-        <v>2720</v>
-      </c>
-      <c r="C104">
-        <v>2025</v>
-      </c>
-      <c r="D104">
-        <v>3</v>
-      </c>
-      <c r="E104" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" t="s">
-        <v>74</v>
-      </c>
-      <c r="B105">
-        <v>2720</v>
-      </c>
-      <c r="C105">
-        <v>2025</v>
-      </c>
-      <c r="D105">
-        <v>4</v>
-      </c>
-      <c r="E105" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" t="s">
-        <v>74</v>
-      </c>
-      <c r="B106">
-        <v>2720</v>
-      </c>
-      <c r="C106">
-        <v>2025</v>
-      </c>
-      <c r="D106">
-        <v>5</v>
-      </c>
-      <c r="E106" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" t="s">
-        <v>74</v>
-      </c>
-      <c r="B107">
-        <v>2720</v>
-      </c>
-      <c r="C107">
-        <v>2025</v>
-      </c>
-      <c r="D107">
-        <v>10</v>
-      </c>
-      <c r="E107" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" t="s">
-        <v>74</v>
-      </c>
-      <c r="B108">
-        <v>2720</v>
-      </c>
-      <c r="C108">
-        <v>2026</v>
-      </c>
-      <c r="D108">
-        <v>7</v>
-      </c>
-      <c r="E108" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" t="s">
-        <v>74</v>
-      </c>
-      <c r="B109">
-        <v>2720</v>
-      </c>
-      <c r="C109">
+      <c r="E113" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>78</v>
+      </c>
+      <c r="B114">
+        <v>2708</v>
+      </c>
+      <c r="C114">
         <v>2028</v>
-      </c>
-      <c r="D109">
-        <v>2</v>
-      </c>
-      <c r="E109" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" t="s">
-        <v>48</v>
-      </c>
-      <c r="B110">
-        <v>2733</v>
-      </c>
-      <c r="C110">
-        <v>2025</v>
-      </c>
-      <c r="D110">
-        <v>1</v>
-      </c>
-      <c r="E110" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" t="s">
-        <v>48</v>
-      </c>
-      <c r="B111">
-        <v>2733</v>
-      </c>
-      <c r="C111">
-        <v>2025</v>
-      </c>
-      <c r="D111">
-        <v>2</v>
-      </c>
-      <c r="E111" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" t="s">
-        <v>48</v>
-      </c>
-      <c r="B112">
-        <v>2733</v>
-      </c>
-      <c r="C112">
-        <v>2025</v>
-      </c>
-      <c r="D112">
-        <v>3</v>
-      </c>
-      <c r="E112" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113" t="s">
-        <v>48</v>
-      </c>
-      <c r="B113">
-        <v>2733</v>
-      </c>
-      <c r="C113">
-        <v>2025</v>
-      </c>
-      <c r="D113">
-        <v>10</v>
-      </c>
-      <c r="E113" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114" t="s">
-        <v>48</v>
-      </c>
-      <c r="B114">
-        <v>2733</v>
-      </c>
-      <c r="C114">
-        <v>2026</v>
       </c>
       <c r="D114">
         <v>5</v>
       </c>
       <c r="E114" t="s">
-        <v>196</v>
-      </c>
-      <c r="F114" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="B115">
-        <v>2733</v>
+        <v>2708</v>
       </c>
       <c r="C115">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="D115">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E115" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B116">
-        <v>2733</v>
+        <v>2739</v>
       </c>
       <c r="C116">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="D116">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E116" t="s">
-        <v>171</v>
-      </c>
-      <c r="F116" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B117">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="C117">
         <v>2025</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B118">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="C118">
         <v>2025</v>
       </c>
       <c r="D118">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E118" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B119">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="C119">
         <v>2025</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E119" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B120">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="C120">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D120">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E120" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B121">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="C121">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D121">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E121" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B122">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="C122">
         <v>2026</v>
@@ -5981,117 +5981,117 @@
         <v>7</v>
       </c>
       <c r="E122" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B123">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="C123">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="D123">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E123" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B124">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="C124">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="D124">
+        <v>1</v>
+      </c>
+      <c r="E124" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>44</v>
+      </c>
+      <c r="B125">
+        <v>2742</v>
+      </c>
+      <c r="C125">
+        <v>2025</v>
+      </c>
+      <c r="D125">
+        <v>2</v>
+      </c>
+      <c r="E125" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>44</v>
+      </c>
+      <c r="B126">
+        <v>2742</v>
+      </c>
+      <c r="C126">
+        <v>2025</v>
+      </c>
+      <c r="D126">
+        <v>3</v>
+      </c>
+      <c r="E126" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
+        <v>44</v>
+      </c>
+      <c r="B127">
+        <v>2742</v>
+      </c>
+      <c r="C127">
+        <v>2025</v>
+      </c>
+      <c r="D127">
         <v>4</v>
       </c>
-      <c r="E124" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" t="s">
-        <v>78</v>
-      </c>
-      <c r="B125">
-        <v>2708</v>
-      </c>
-      <c r="C125">
-        <v>2025</v>
-      </c>
-      <c r="D125">
-        <v>1</v>
-      </c>
-      <c r="E125" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126" t="s">
-        <v>78</v>
-      </c>
-      <c r="B126">
-        <v>2708</v>
-      </c>
-      <c r="C126">
-        <v>2025</v>
-      </c>
-      <c r="D126">
-        <v>2</v>
-      </c>
-      <c r="E126" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127" t="s">
-        <v>78</v>
-      </c>
-      <c r="B127">
-        <v>2708</v>
-      </c>
-      <c r="C127">
-        <v>2025</v>
-      </c>
-      <c r="D127">
-        <v>3</v>
-      </c>
       <c r="E127" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B128">
-        <v>2708</v>
+        <v>2742</v>
       </c>
       <c r="C128">
         <v>2025</v>
       </c>
       <c r="D128">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E128" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B129">
-        <v>2708</v>
+        <v>2742</v>
       </c>
       <c r="C129">
         <v>2026</v>
@@ -6100,15 +6100,15 @@
         <v>5</v>
       </c>
       <c r="E129" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B130">
-        <v>2708</v>
+        <v>2742</v>
       </c>
       <c r="C130">
         <v>2026</v>
@@ -6117,15 +6117,15 @@
         <v>6</v>
       </c>
       <c r="E130" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B131">
-        <v>2708</v>
+        <v>2742</v>
       </c>
       <c r="C131">
         <v>2026</v>
@@ -6139,44 +6139,44 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B132">
-        <v>2708</v>
+        <v>2742</v>
       </c>
       <c r="C132">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="D132">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E132" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B133">
-        <v>2708</v>
+        <v>2742</v>
       </c>
       <c r="C133">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="D133">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E133" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B134">
-        <v>2737</v>
+        <v>2702</v>
       </c>
       <c r="C134">
         <v>2025</v>
@@ -6185,15 +6185,15 @@
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B135">
-        <v>2737</v>
+        <v>2702</v>
       </c>
       <c r="C135">
         <v>2025</v>
@@ -6202,15 +6202,15 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B136">
-        <v>2737</v>
+        <v>2702</v>
       </c>
       <c r="C136">
         <v>2025</v>
@@ -6219,21 +6219,21 @@
         <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B137">
-        <v>2737</v>
+        <v>2702</v>
       </c>
       <c r="C137">
         <v>2025</v>
       </c>
       <c r="D137">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E137" t="s">
         <v>172</v>
@@ -6241,27 +6241,27 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B138">
-        <v>2737</v>
+        <v>2702</v>
       </c>
       <c r="C138">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D138">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E138" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B139">
-        <v>2737</v>
+        <v>2702</v>
       </c>
       <c r="C139">
         <v>2026</v>
@@ -6270,15 +6270,15 @@
         <v>6</v>
       </c>
       <c r="E139" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B140">
-        <v>2737</v>
+        <v>2702</v>
       </c>
       <c r="C140">
         <v>2026</v>
@@ -6287,41 +6287,41 @@
         <v>7</v>
       </c>
       <c r="E140" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>53</v>
-      </c>
-      <c r="B141">
-        <v>2737</v>
+        <v>43</v>
+      </c>
+      <c r="B141" t="b">
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="D141">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E141" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B142" t="b">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="D142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -6335,10 +6335,10 @@
         <v>2025</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -6352,10 +6352,10 @@
         <v>2025</v>
       </c>
       <c r="D144">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E144" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -6369,10 +6369,10 @@
         <v>2025</v>
       </c>
       <c r="D145">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E145" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -6386,10 +6386,10 @@
         <v>2025</v>
       </c>
       <c r="D146">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E146" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -6403,7 +6403,7 @@
         <v>2025</v>
       </c>
       <c r="D147">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E147" t="s">
         <v>172</v>
@@ -6417,13 +6417,13 @@
         <v>0</v>
       </c>
       <c r="C148">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D148">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E148" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -6434,129 +6434,129 @@
         <v>0</v>
       </c>
       <c r="C149">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="D149">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E149" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>56</v>
-      </c>
-      <c r="B150" t="b">
-        <v>0</v>
+        <v>55</v>
+      </c>
+      <c r="B150">
+        <v>2731</v>
       </c>
       <c r="C150">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="D150">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B151">
-        <v>2702</v>
+        <v>2731</v>
       </c>
       <c r="C151">
         <v>2025</v>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B152">
-        <v>2702</v>
+        <v>2731</v>
       </c>
       <c r="C152">
         <v>2025</v>
       </c>
       <c r="D152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E152" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B153">
-        <v>2702</v>
+        <v>2731</v>
       </c>
       <c r="C153">
         <v>2025</v>
       </c>
       <c r="D153">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E153" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B154">
-        <v>2702</v>
+        <v>2731</v>
       </c>
       <c r="C154">
         <v>2025</v>
       </c>
       <c r="D154">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E154" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B155">
-        <v>2702</v>
+        <v>2731</v>
       </c>
       <c r="C155">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D155">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E155" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B156">
-        <v>2702</v>
+        <v>2731</v>
       </c>
       <c r="C156">
         <v>2026</v>
       </c>
       <c r="D156">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E156" t="s">
         <v>207</v>
@@ -6564,27 +6564,27 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B157">
-        <v>2702</v>
+        <v>2731</v>
       </c>
       <c r="C157">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="D157">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E157" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B158">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="C158">
         <v>2025</v>
@@ -6593,15 +6593,15 @@
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B159">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="C159">
         <v>2025</v>
@@ -6610,15 +6610,15 @@
         <v>2</v>
       </c>
       <c r="E159" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B160">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="C160">
         <v>2025</v>
@@ -6627,15 +6627,15 @@
         <v>3</v>
       </c>
       <c r="E160" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B161">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="C161">
         <v>2025</v>
@@ -6644,15 +6644,15 @@
         <v>4</v>
       </c>
       <c r="E161" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B162">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="C162">
         <v>2025</v>
@@ -6661,75 +6661,75 @@
         <v>5</v>
       </c>
       <c r="E162" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B163">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="C163">
         <v>2026</v>
       </c>
       <c r="D163">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E163" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B164">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="C164">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E164" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>49</v>
-      </c>
-      <c r="B165" t="b">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="B165">
+        <v>2737</v>
       </c>
       <c r="C165">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="D165">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E165" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B166" t="b">
         <v>0</v>
       </c>
       <c r="C166">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D166">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E166" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -6743,10 +6743,10 @@
         <v>2025</v>
       </c>
       <c r="D167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -6760,10 +6760,10 @@
         <v>2025</v>
       </c>
       <c r="D168">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -6777,10 +6777,10 @@
         <v>2025</v>
       </c>
       <c r="D169">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E169" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -6794,15 +6794,15 @@
         <v>2025</v>
       </c>
       <c r="D170">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E170" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B171" t="b">
         <v>0</v>
@@ -6811,10 +6811,10 @@
         <v>2025</v>
       </c>
       <c r="D171">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E171" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -6828,10 +6828,10 @@
         <v>2025</v>
       </c>
       <c r="D172">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -6845,10 +6845,10 @@
         <v>2025</v>
       </c>
       <c r="D173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E173" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -6862,10 +6862,10 @@
         <v>2025</v>
       </c>
       <c r="D174">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E174" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -6879,15 +6879,15 @@
         <v>2025</v>
       </c>
       <c r="D175">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E175" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B176" t="b">
         <v>0</v>
@@ -6896,10 +6896,10 @@
         <v>2025</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E176" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -6913,7 +6913,7 @@
         <v>2025</v>
       </c>
       <c r="D177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="s">
         <v>169</v>
@@ -6930,7 +6930,7 @@
         <v>2025</v>
       </c>
       <c r="D178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E178" t="s">
         <v>169</v>
@@ -6947,13 +6947,10 @@
         <v>2025</v>
       </c>
       <c r="D179">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E179" t="s">
-        <v>171</v>
-      </c>
-      <c r="F179" t="s">
-        <v>225</v>
+        <v>169</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -6967,10 +6964,13 @@
         <v>2025</v>
       </c>
       <c r="D180">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E180" t="s">
-        <v>180</v>
+        <v>171</v>
+      </c>
+      <c r="F180" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -6981,13 +6981,13 @@
         <v>0</v>
       </c>
       <c r="C181">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D181">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E181" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -7001,149 +7001,149 @@
         <v>2026</v>
       </c>
       <c r="D182">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E182" t="s">
-        <v>171</v>
-      </c>
-      <c r="F182" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>50</v>
-      </c>
-      <c r="B183">
-        <v>2727</v>
+        <v>40</v>
+      </c>
+      <c r="B183" t="b">
+        <v>0</v>
       </c>
       <c r="C183">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D183">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E183" t="s">
-        <v>172</v>
+        <v>171</v>
+      </c>
+      <c r="F183" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B184">
-        <v>2727</v>
+        <v>2738</v>
       </c>
       <c r="C184">
         <v>2025</v>
       </c>
       <c r="D184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B185">
-        <v>2727</v>
+        <v>2738</v>
       </c>
       <c r="C185">
         <v>2025</v>
       </c>
       <c r="D185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E185" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B186">
-        <v>2727</v>
+        <v>2738</v>
       </c>
       <c r="C186">
         <v>2025</v>
       </c>
       <c r="D186">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E186" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B187">
-        <v>2727</v>
+        <v>2738</v>
       </c>
       <c r="C187">
         <v>2025</v>
       </c>
       <c r="D187">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E187" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B188">
-        <v>2727</v>
+        <v>2738</v>
       </c>
       <c r="C188">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D188">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E188" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B189">
-        <v>2727</v>
+        <v>2738</v>
       </c>
       <c r="C189">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D189">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E189" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>54</v>
-      </c>
-      <c r="B190" t="b">
-        <v>0</v>
+        <v>51</v>
+      </c>
+      <c r="B190">
+        <v>2738</v>
       </c>
       <c r="C190">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D190">
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -7157,10 +7157,10 @@
         <v>2025</v>
       </c>
       <c r="D191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -7174,10 +7174,10 @@
         <v>2025</v>
       </c>
       <c r="D192">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E192" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -7191,10 +7191,10 @@
         <v>2025</v>
       </c>
       <c r="D193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E193" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -7208,15 +7208,15 @@
         <v>2025</v>
       </c>
       <c r="D194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E194" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B195" t="b">
         <v>0</v>
@@ -7225,10 +7225,10 @@
         <v>2025</v>
       </c>
       <c r="D195">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E195" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -7242,10 +7242,10 @@
         <v>2025</v>
       </c>
       <c r="D196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -7259,10 +7259,10 @@
         <v>2025</v>
       </c>
       <c r="D197">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E197" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -7276,10 +7276,10 @@
         <v>2025</v>
       </c>
       <c r="D198">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E198" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -7293,10 +7293,10 @@
         <v>2025</v>
       </c>
       <c r="D199">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E199" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -7310,13 +7310,10 @@
         <v>2025</v>
       </c>
       <c r="D200">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E200" t="s">
-        <v>171</v>
-      </c>
-      <c r="F200" t="s">
-        <v>227</v>
+        <v>174</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -7330,10 +7327,13 @@
         <v>2025</v>
       </c>
       <c r="D201">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E201" t="s">
-        <v>180</v>
+        <v>171</v>
+      </c>
+      <c r="F201" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -7344,33 +7344,33 @@
         <v>0</v>
       </c>
       <c r="C202">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E202" t="s">
-        <v>171</v>
-      </c>
-      <c r="F202" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B203" t="b">
         <v>0</v>
       </c>
       <c r="C203">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D203">
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>169</v>
+        <v>171</v>
+      </c>
+      <c r="F203" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -7384,7 +7384,7 @@
         <v>2025</v>
       </c>
       <c r="D204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E204" t="s">
         <v>169</v>
@@ -7401,7 +7401,7 @@
         <v>2025</v>
       </c>
       <c r="D205">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E205" t="s">
         <v>169</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B206" t="b">
         <v>0</v>
@@ -7418,7 +7418,7 @@
         <v>2025</v>
       </c>
       <c r="D206">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E206" t="s">
         <v>169</v>
@@ -7435,7 +7435,7 @@
         <v>2025</v>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E207" t="s">
         <v>169</v>
@@ -7452,7 +7452,7 @@
         <v>2025</v>
       </c>
       <c r="D208">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E208" t="s">
         <v>169</v>
@@ -7469,10 +7469,10 @@
         <v>2025</v>
       </c>
       <c r="D209">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E209" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -7486,7 +7486,7 @@
         <v>2025</v>
       </c>
       <c r="D210">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E210" t="s">
         <v>171</v>
@@ -7494,7 +7494,7 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B211" t="b">
         <v>0</v>
@@ -7503,10 +7503,10 @@
         <v>2025</v>
       </c>
       <c r="D211">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E211" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -7520,7 +7520,7 @@
         <v>2025</v>
       </c>
       <c r="D212">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E212" t="s">
         <v>169</v>
@@ -7537,7 +7537,7 @@
         <v>2025</v>
       </c>
       <c r="D213">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E213" t="s">
         <v>169</v>
@@ -7545,7 +7545,7 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B214" t="b">
         <v>0</v>
@@ -7554,7 +7554,7 @@
         <v>2025</v>
       </c>
       <c r="D214">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E214" t="s">
         <v>169</v>
@@ -7571,10 +7571,10 @@
         <v>2025</v>
       </c>
       <c r="D215">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E215" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -7588,10 +7588,10 @@
         <v>2025</v>
       </c>
       <c r="D216">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -7605,13 +7605,10 @@
         <v>2025</v>
       </c>
       <c r="D217">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E217" t="s">
-        <v>171</v>
-      </c>
-      <c r="F217" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -7625,7 +7622,7 @@
         <v>2025</v>
       </c>
       <c r="D218">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E218" t="s">
         <v>171</v>
@@ -7636,7 +7633,7 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B219" t="b">
         <v>0</v>
@@ -7645,10 +7642,13 @@
         <v>2025</v>
       </c>
       <c r="D219">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E219" t="s">
-        <v>172</v>
+        <v>171</v>
+      </c>
+      <c r="F219" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -7662,10 +7662,10 @@
         <v>2025</v>
       </c>
       <c r="D220">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E220" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -7679,10 +7679,10 @@
         <v>2025</v>
       </c>
       <c r="D221">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E221" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -7696,10 +7696,10 @@
         <v>2025</v>
       </c>
       <c r="D222">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E222" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -7713,120 +7713,120 @@
         <v>2025</v>
       </c>
       <c r="D223">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E223" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>55</v>
-      </c>
-      <c r="B224">
-        <v>2731</v>
+        <v>68</v>
+      </c>
+      <c r="B224" t="b">
+        <v>0</v>
       </c>
       <c r="C224">
         <v>2025</v>
       </c>
       <c r="D224">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E224" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B225">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="C225">
         <v>2025</v>
       </c>
       <c r="D225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B226">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="C226">
         <v>2025</v>
       </c>
       <c r="D226">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B227">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="C227">
         <v>2025</v>
       </c>
       <c r="D227">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E227" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B228">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="C228">
         <v>2025</v>
       </c>
       <c r="D228">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E228" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B229">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="C229">
         <v>2025</v>
       </c>
       <c r="D229">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E229" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B230">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="C230">
         <v>2026</v>
@@ -7840,19 +7840,19 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B231">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="C231">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="D231">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E231" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -7869,7 +7869,7 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -7886,7 +7886,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -7903,7 +7903,7 @@
         <v>3</v>
       </c>
       <c r="E234" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -7920,7 +7920,7 @@
         <v>4</v>
       </c>
       <c r="E235" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -7937,7 +7937,7 @@
         <v>5</v>
       </c>
       <c r="E236" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -8005,7 +8005,7 @@
         <v>10</v>
       </c>
       <c r="E240" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -8022,7 +8022,7 @@
         <v>1</v>
       </c>
       <c r="E241" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -8039,7 +8039,7 @@
         <v>2</v>
       </c>
       <c r="E242" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -8056,7 +8056,7 @@
         <v>3</v>
       </c>
       <c r="E243" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -8073,7 +8073,7 @@
         <v>4</v>
       </c>
       <c r="E244" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -8090,7 +8090,7 @@
         <v>5</v>
       </c>
       <c r="E245" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -11277,25 +11277,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B2">
-        <v>2743</v>
+        <v>2704</v>
       </c>
       <c r="C2">
-        <v>4345.83</v>
+        <v>4856.75</v>
       </c>
       <c r="D2">
-        <v>154.1666667</v>
+        <v>143.25</v>
       </c>
       <c r="E2">
-        <v>93.5</v>
+        <v>10.21090909</v>
       </c>
       <c r="F2">
-        <v>514.25</v>
+        <v>56.16</v>
       </c>
       <c r="G2">
-        <v>1.648841355</v>
+        <v>14.02911325</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -11311,94 +11311,94 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B4">
-        <v>2736</v>
+        <v>2743</v>
       </c>
       <c r="C4">
-        <v>3889.5</v>
+        <v>4345.83</v>
       </c>
       <c r="D4">
-        <v>110.5</v>
+        <v>154.1666667</v>
       </c>
       <c r="E4">
-        <v>49.72969697</v>
+        <v>93.5</v>
       </c>
       <c r="F4">
-        <v>273.5133333</v>
+        <v>514.25</v>
       </c>
       <c r="G4">
-        <v>2.222012333</v>
+        <v>1.648841355</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B5">
-        <v>2732</v>
+        <v>2719</v>
       </c>
       <c r="C5">
-        <v>3868.67</v>
+        <v>4262.5</v>
       </c>
       <c r="D5">
-        <v>131.3333333</v>
+        <v>437.5</v>
       </c>
       <c r="E5">
-        <v>49.72969697</v>
+        <v>58.87090909</v>
       </c>
       <c r="F5">
-        <v>273.5133333</v>
+        <v>323.79</v>
       </c>
       <c r="G5">
-        <v>2.640943769</v>
+        <v>7.431514253</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B6">
-        <v>2709</v>
+        <v>2733</v>
       </c>
       <c r="C6">
-        <v>2722.08</v>
+        <v>4131.58</v>
       </c>
       <c r="D6">
-        <v>180.9166667</v>
+        <v>368.4166667</v>
       </c>
       <c r="E6">
-        <v>49.75727273</v>
+        <v>21.29818182</v>
       </c>
       <c r="F6">
-        <v>273.665</v>
+        <v>117.14</v>
       </c>
       <c r="G6">
-        <v>3.635984385</v>
+        <v>17.29803369</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B7">
-        <v>2740</v>
+        <v>2703</v>
       </c>
       <c r="C7">
-        <v>3236.83</v>
+        <v>4117.25</v>
       </c>
       <c r="D7">
-        <v>204.1666667</v>
+        <v>382.75</v>
       </c>
       <c r="E7">
-        <v>49.72969697</v>
+        <v>39.70818182</v>
       </c>
       <c r="F7">
-        <v>273.5133333</v>
+        <v>218.395</v>
       </c>
       <c r="G7">
-        <v>4.105528067</v>
+        <v>9.639071406999999</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -11426,162 +11426,165 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B9">
-        <v>2719</v>
+        <v>2736</v>
       </c>
       <c r="C9">
-        <v>4262.5</v>
+        <v>3889.5</v>
       </c>
       <c r="D9">
-        <v>437.5</v>
+        <v>110.5</v>
       </c>
       <c r="E9">
-        <v>58.87090909</v>
+        <v>49.72969697</v>
       </c>
       <c r="F9">
-        <v>323.79</v>
+        <v>273.5133333</v>
       </c>
       <c r="G9">
-        <v>7.431514253</v>
+        <v>2.222012333</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10">
-        <v>2723</v>
+        <v>2732</v>
       </c>
       <c r="C10">
-        <v>2830.67</v>
+        <v>3868.67</v>
       </c>
       <c r="D10">
-        <v>408.3333333</v>
+        <v>131.3333333</v>
       </c>
       <c r="E10">
-        <v>52.33272727</v>
+        <v>49.72969697</v>
       </c>
       <c r="F10">
-        <v>287.83</v>
+        <v>273.5133333</v>
       </c>
       <c r="G10">
-        <v>7.802638131</v>
+        <v>2.640943769</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>46</v>
+      </c>
+      <c r="B11">
+        <v>2740</v>
       </c>
       <c r="C11">
-        <v>2832.83</v>
+        <v>3236.83</v>
       </c>
       <c r="D11">
-        <v>1167.166667</v>
+        <v>204.1666667</v>
+      </c>
+      <c r="E11">
+        <v>49.72969697</v>
+      </c>
+      <c r="F11">
+        <v>273.5133333</v>
+      </c>
+      <c r="G11">
+        <v>4.105528067</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="B12">
-        <v>2703</v>
+        <v>2720</v>
       </c>
       <c r="C12">
-        <v>4117.25</v>
+        <v>3176.58</v>
       </c>
       <c r="D12">
-        <v>382.75</v>
+        <v>823.4166667</v>
       </c>
       <c r="E12">
-        <v>39.70818182</v>
+        <v>49.75727273</v>
       </c>
       <c r="F12">
-        <v>218.395</v>
+        <v>273.665</v>
       </c>
       <c r="G12">
-        <v>9.639071406999999</v>
+        <v>16.5486696</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B13">
-        <v>2742</v>
+        <v>2741</v>
+      </c>
+      <c r="C13">
+        <v>3095.33</v>
       </c>
       <c r="D13">
-        <v>751.25</v>
+        <v>904.6666667</v>
       </c>
       <c r="E13">
-        <v>55.63636364</v>
+        <v>49.72969697</v>
       </c>
       <c r="F13">
-        <v>306</v>
+        <v>273.5133333</v>
       </c>
       <c r="G13">
-        <v>13.50285948</v>
+        <v>18.19167865</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14">
-        <v>2704</v>
+        <v>76</v>
       </c>
       <c r="C14">
-        <v>4856.75</v>
+        <v>2832.83</v>
       </c>
       <c r="D14">
-        <v>143.25</v>
-      </c>
-      <c r="E14">
-        <v>10.21090909</v>
-      </c>
-      <c r="F14">
-        <v>56.16</v>
-      </c>
-      <c r="G14">
-        <v>14.02911325</v>
+        <v>1167.166667</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B15">
-        <v>2739</v>
+        <v>2723</v>
       </c>
       <c r="C15">
-        <v>1195.33</v>
+        <v>2830.67</v>
       </c>
       <c r="D15">
-        <v>304.6666667</v>
+        <v>408.3333333</v>
       </c>
       <c r="E15">
-        <v>21.29818182</v>
+        <v>52.33272727</v>
       </c>
       <c r="F15">
-        <v>117.14</v>
+        <v>287.83</v>
       </c>
       <c r="G15">
-        <v>14.30482044</v>
+        <v>7.802638131</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B16">
-        <v>2720</v>
+        <v>2709</v>
       </c>
       <c r="C16">
-        <v>3176.58</v>
+        <v>2722.08</v>
       </c>
       <c r="D16">
-        <v>823.4166667</v>
+        <v>180.9166667</v>
       </c>
       <c r="E16">
         <v>49.75727273</v>
@@ -11590,99 +11593,96 @@
         <v>273.665</v>
       </c>
       <c r="G16">
-        <v>16.5486696</v>
+        <v>3.635984385</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="B17">
-        <v>2733</v>
+        <v>2708</v>
       </c>
       <c r="C17">
-        <v>4131.58</v>
+        <v>2243.25</v>
       </c>
       <c r="D17">
-        <v>368.4166667</v>
+        <v>756.75</v>
       </c>
       <c r="E17">
-        <v>21.29818182</v>
+        <v>39.70818182</v>
       </c>
       <c r="F17">
-        <v>117.14</v>
+        <v>218.395</v>
       </c>
       <c r="G17">
-        <v>17.29803369</v>
+        <v>19.05778521</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B18">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="C18">
-        <v>3095.33</v>
+        <v>1195.33</v>
       </c>
       <c r="D18">
-        <v>904.6666667</v>
+        <v>304.6666667</v>
       </c>
       <c r="E18">
-        <v>49.72969697</v>
+        <v>21.29818182</v>
       </c>
       <c r="F18">
-        <v>273.5133333</v>
+        <v>117.14</v>
       </c>
       <c r="G18">
-        <v>18.19167865</v>
+        <v>14.30482044</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B19">
-        <v>2708</v>
-      </c>
-      <c r="C19">
-        <v>2243.25</v>
+        <v>2742</v>
       </c>
       <c r="D19">
-        <v>756.75</v>
+        <v>751.25</v>
       </c>
       <c r="E19">
-        <v>39.70818182</v>
+        <v>55.63636364</v>
       </c>
       <c r="F19">
-        <v>218.395</v>
+        <v>306</v>
       </c>
       <c r="G19">
-        <v>19.05778521</v>
+        <v>13.50285948</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B20">
-        <v>2737</v>
+        <v>2702</v>
       </c>
       <c r="C20">
-        <v>292.5</v>
+        <v>476.75</v>
       </c>
       <c r="D20">
-        <v>1207.5</v>
+        <v>1023.25</v>
       </c>
       <c r="E20">
-        <v>49.72969697</v>
+        <v>39.70818182</v>
       </c>
       <c r="F20">
-        <v>273.5133333</v>
+        <v>218.395</v>
       </c>
       <c r="G20">
-        <v>24.281266</v>
+        <v>25.76924838</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -11709,36 +11709,39 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B23">
-        <v>2702</v>
+        <v>2731</v>
       </c>
       <c r="C23">
-        <v>476.75</v>
+        <v>355</v>
       </c>
       <c r="D23">
-        <v>1023.25</v>
+        <v>1145</v>
       </c>
       <c r="E23">
-        <v>39.70818182</v>
+        <v>21.29818182</v>
       </c>
       <c r="F23">
-        <v>218.395</v>
+        <v>117.14</v>
       </c>
       <c r="G23">
-        <v>25.76924838</v>
+        <v>53.76045757</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B24">
-        <v>2738</v>
+        <v>2737</v>
+      </c>
+      <c r="C24">
+        <v>292.5</v>
       </c>
       <c r="D24">
-        <v>1477.25</v>
+        <v>1207.5</v>
       </c>
       <c r="E24">
         <v>49.72969697</v>
@@ -11747,7 +11750,7 @@
         <v>273.5133333</v>
       </c>
       <c r="G24">
-        <v>29.70559022</v>
+        <v>24.281266</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -11796,22 +11799,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29">
-        <v>2727</v>
+        <v>2738</v>
       </c>
       <c r="D29">
-        <v>1488.166667</v>
+        <v>1477.25</v>
       </c>
       <c r="E29">
-        <v>46.27272727</v>
+        <v>49.72969697</v>
       </c>
       <c r="F29">
-        <v>254.5</v>
+        <v>273.5133333</v>
       </c>
       <c r="G29">
-        <v>32.16077276</v>
+        <v>29.70559022</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -11890,25 +11893,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B37">
-        <v>2731</v>
-      </c>
-      <c r="C37">
-        <v>355</v>
+        <v>2727</v>
       </c>
       <c r="D37">
-        <v>1145</v>
+        <v>1488.166667</v>
       </c>
       <c r="E37">
-        <v>21.29818182</v>
+        <v>46.27272727</v>
       </c>
       <c r="F37">
-        <v>117.14</v>
+        <v>254.5</v>
       </c>
       <c r="G37">
-        <v>53.76045757</v>
+        <v>32.16077276</v>
       </c>
     </row>
     <row r="38" spans="1:7">

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="461">
   <si>
     <t>om</t>
   </si>
@@ -544,6 +544,9 @@
   </si>
   <si>
     <t>NÃO HÁ AT</t>
+  </si>
+  <si>
+    <t>vazamento de oleo pelo flange</t>
   </si>
   <si>
     <t>17.3</t>
@@ -680,10 +683,12 @@
 Motor substituto já em MN</t>
   </si>
   <si>
-    <t>AT 386000001002  500H</t>
-  </si>
-  <si>
-    <t>sem at</t>
+    <t>AT 386000001002  500H
+Motor já está no GLOG-CO</t>
+  </si>
+  <si>
+    <t>sem at
+Possui AT de 200H, porém foi encontrada  uma trinca e o housing será recolhido.</t>
   </si>
   <si>
     <t>Fez o 1° HSI COM 1941H, O PROX SERÁ COM 3441.
@@ -3852,7 +3857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F244"/>
+  <dimension ref="A1:F245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -3943,7 +3948,7 @@
         <v>172</v>
       </c>
       <c r="F5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4065,7 +4070,7 @@
         <v>172</v>
       </c>
       <c r="F12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4153,7 +4158,7 @@
         <v>172</v>
       </c>
       <c r="F17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4269,30 +4274,30 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>172</v>
-      </c>
-      <c r="F24" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="B25">
-        <v>2740</v>
+        <v>2741</v>
       </c>
       <c r="C25">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="F25" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4306,7 +4311,7 @@
         <v>2025</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
         <v>171</v>
@@ -4323,7 +4328,7 @@
         <v>2025</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="s">
         <v>171</v>
@@ -4337,13 +4342,13 @@
         <v>2740</v>
       </c>
       <c r="C28">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4357,7 +4362,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
         <v>176</v>
@@ -4374,13 +4379,10 @@
         <v>2026</v>
       </c>
       <c r="D30">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E30" t="s">
         <v>177</v>
-      </c>
-      <c r="F30" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4394,10 +4396,13 @@
         <v>2026</v>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31" t="s">
         <v>178</v>
+      </c>
+      <c r="F31" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4408,30 +4413,30 @@
         <v>2740</v>
       </c>
       <c r="C32">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>2709</v>
+        <v>2740</v>
       </c>
       <c r="C33">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4445,7 +4450,7 @@
         <v>2025</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
         <v>171</v>
@@ -4462,7 +4467,7 @@
         <v>2025</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="s">
         <v>171</v>
@@ -4479,10 +4484,10 @@
         <v>2025</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4493,13 +4498,13 @@
         <v>2709</v>
       </c>
       <c r="C37">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4513,7 +4518,7 @@
         <v>2026</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
         <v>180</v>
@@ -4530,10 +4535,10 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4547,27 +4552,27 @@
         <v>2026</v>
       </c>
       <c r="D40">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B41">
-        <v>2722</v>
+        <v>2709</v>
       </c>
       <c r="C41">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4581,7 +4586,7 @@
         <v>2025</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
         <v>171</v>
@@ -4598,7 +4603,7 @@
         <v>2025</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" t="s">
         <v>171</v>
@@ -4615,10 +4620,10 @@
         <v>2025</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4629,33 +4634,33 @@
         <v>2722</v>
       </c>
       <c r="C45">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D45">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>172</v>
-      </c>
-      <c r="F45" t="s">
-        <v>222</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="B46">
-        <v>2719</v>
+        <v>2722</v>
       </c>
       <c r="C46">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="F46" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4669,7 +4674,7 @@
         <v>2025</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" t="s">
         <v>171</v>
@@ -4686,7 +4691,7 @@
         <v>2025</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" t="s">
         <v>171</v>
@@ -4703,10 +4708,10 @@
         <v>2025</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4717,10 +4722,10 @@
         <v>2719</v>
       </c>
       <c r="C50">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D50">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
         <v>183</v>
@@ -4734,33 +4739,33 @@
         <v>2719</v>
       </c>
       <c r="C51">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E51" t="s">
         <v>184</v>
       </c>
-      <c r="F51" t="s">
-        <v>223</v>
-      </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="B52">
-        <v>2723</v>
+        <v>2719</v>
       </c>
       <c r="C52">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="s">
-        <v>171</v>
+        <v>185</v>
+      </c>
+      <c r="F52" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4774,7 +4779,7 @@
         <v>2025</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="s">
         <v>171</v>
@@ -4791,7 +4796,7 @@
         <v>2025</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="s">
         <v>171</v>
@@ -4808,10 +4813,10 @@
         <v>2025</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -4822,13 +4827,13 @@
         <v>2723</v>
       </c>
       <c r="C56">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -4842,7 +4847,7 @@
         <v>2026</v>
       </c>
       <c r="D57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E57" t="s">
         <v>186</v>
@@ -4859,7 +4864,7 @@
         <v>2026</v>
       </c>
       <c r="D58">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E58" t="s">
         <v>187</v>
@@ -4873,16 +4878,13 @@
         <v>2723</v>
       </c>
       <c r="C59">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>177</v>
-      </c>
-      <c r="F59" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4893,30 +4895,33 @@
         <v>2723</v>
       </c>
       <c r="C60">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="D60">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>172</v>
+        <v>178</v>
+      </c>
+      <c r="F60" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="B61">
-        <v>2703</v>
+        <v>2723</v>
       </c>
       <c r="C61">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -4930,7 +4935,7 @@
         <v>2025</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="s">
         <v>171</v>
@@ -4947,7 +4952,7 @@
         <v>2025</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" t="s">
         <v>171</v>
@@ -4964,10 +4969,10 @@
         <v>2025</v>
       </c>
       <c r="D64">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -4978,13 +4983,13 @@
         <v>2703</v>
       </c>
       <c r="C65">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D65">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -4995,30 +5000,30 @@
         <v>2703</v>
       </c>
       <c r="C66">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E66" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B67">
-        <v>2742</v>
+        <v>2703</v>
       </c>
       <c r="C67">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -5032,7 +5037,7 @@
         <v>2025</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="s">
         <v>173</v>
@@ -5049,7 +5054,7 @@
         <v>2025</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" t="s">
         <v>173</v>
@@ -5066,7 +5071,7 @@
         <v>2025</v>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E70" t="s">
         <v>173</v>
@@ -5083,7 +5088,7 @@
         <v>2025</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E71" t="s">
         <v>173</v>
@@ -5097,13 +5102,13 @@
         <v>2742</v>
       </c>
       <c r="C72">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D72">
         <v>5</v>
       </c>
       <c r="E72" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -5117,7 +5122,7 @@
         <v>2026</v>
       </c>
       <c r="D73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
         <v>190</v>
@@ -5134,7 +5139,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E74" t="s">
         <v>191</v>
@@ -5148,13 +5153,13 @@
         <v>2742</v>
       </c>
       <c r="C75">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E75" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -5165,30 +5170,30 @@
         <v>2742</v>
       </c>
       <c r="C76">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="D76">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>64</v>
-      </c>
-      <c r="B77" t="b">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="B77">
+        <v>2742</v>
       </c>
       <c r="C77">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -5202,7 +5207,7 @@
         <v>2025</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="s">
         <v>171</v>
@@ -5219,7 +5224,7 @@
         <v>2025</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E79" t="s">
         <v>171</v>
@@ -5236,10 +5241,10 @@
         <v>2025</v>
       </c>
       <c r="D80">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E80" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -5253,10 +5258,10 @@
         <v>2025</v>
       </c>
       <c r="D81">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -5267,13 +5272,13 @@
         <v>0</v>
       </c>
       <c r="C82">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D82">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E82" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -5287,7 +5292,7 @@
         <v>2026</v>
       </c>
       <c r="D83">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E83" t="s">
         <v>193</v>
@@ -5295,19 +5300,19 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B84" t="b">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E84" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5321,7 +5326,7 @@
         <v>2025</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="s">
         <v>171</v>
@@ -5338,7 +5343,7 @@
         <v>2025</v>
       </c>
       <c r="D86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="s">
         <v>171</v>
@@ -5355,10 +5360,10 @@
         <v>2025</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E87" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -5369,13 +5374,13 @@
         <v>0</v>
       </c>
       <c r="C88">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -5389,13 +5394,10 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>177</v>
-      </c>
-      <c r="F89" t="s">
-        <v>225</v>
+        <v>195</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -5409,10 +5411,13 @@
         <v>2026</v>
       </c>
       <c r="D90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E90" t="s">
-        <v>192</v>
+        <v>178</v>
+      </c>
+      <c r="F90" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -5426,27 +5431,27 @@
         <v>2026</v>
       </c>
       <c r="D91">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E91" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>67</v>
-      </c>
-      <c r="B92">
-        <v>2739</v>
+        <v>78</v>
+      </c>
+      <c r="B92" t="b">
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -5460,7 +5465,7 @@
         <v>2025</v>
       </c>
       <c r="D93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="s">
         <v>171</v>
@@ -5477,7 +5482,7 @@
         <v>2025</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" t="s">
         <v>171</v>
@@ -5494,10 +5499,10 @@
         <v>2025</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E95" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -5508,13 +5513,13 @@
         <v>2739</v>
       </c>
       <c r="C96">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -5528,7 +5533,7 @@
         <v>2026</v>
       </c>
       <c r="D97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E97" t="s">
         <v>197</v>
@@ -5545,7 +5550,7 @@
         <v>2026</v>
       </c>
       <c r="D98">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E98" t="s">
         <v>198</v>
@@ -5559,30 +5564,30 @@
         <v>2739</v>
       </c>
       <c r="C99">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D99">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E99" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B100">
-        <v>2704</v>
+        <v>2739</v>
       </c>
       <c r="C100">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E100" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -5596,7 +5601,7 @@
         <v>2025</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" t="s">
         <v>171</v>
@@ -5613,7 +5618,7 @@
         <v>2025</v>
       </c>
       <c r="D102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" t="s">
         <v>171</v>
@@ -5630,10 +5635,10 @@
         <v>2025</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E103" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5647,10 +5652,10 @@
         <v>2025</v>
       </c>
       <c r="D104">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E104" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5664,10 +5669,10 @@
         <v>2025</v>
       </c>
       <c r="D105">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E105" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5678,13 +5683,13 @@
         <v>2704</v>
       </c>
       <c r="C106">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D106">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E106" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5695,30 +5700,30 @@
         <v>2704</v>
       </c>
       <c r="C107">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D107">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E107" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B108">
-        <v>2720</v>
+        <v>2704</v>
       </c>
       <c r="C108">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E108" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5732,7 +5737,7 @@
         <v>2025</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" t="s">
         <v>171</v>
@@ -5749,7 +5754,7 @@
         <v>2025</v>
       </c>
       <c r="D110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E110" t="s">
         <v>171</v>
@@ -5766,10 +5771,10 @@
         <v>2025</v>
       </c>
       <c r="D111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E111" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5783,7 +5788,7 @@
         <v>2025</v>
       </c>
       <c r="D112">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E112" t="s">
         <v>173</v>
@@ -5800,10 +5805,10 @@
         <v>2025</v>
       </c>
       <c r="D113">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5814,13 +5819,13 @@
         <v>2720</v>
       </c>
       <c r="C114">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D114">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E114" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5831,30 +5836,30 @@
         <v>2720</v>
       </c>
       <c r="C115">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E115" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B116">
-        <v>2708</v>
+        <v>2720</v>
       </c>
       <c r="C116">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5868,7 +5873,7 @@
         <v>2025</v>
       </c>
       <c r="D117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" t="s">
         <v>171</v>
@@ -5885,7 +5890,7 @@
         <v>2025</v>
       </c>
       <c r="D118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E118" t="s">
         <v>171</v>
@@ -5902,10 +5907,10 @@
         <v>2025</v>
       </c>
       <c r="D119">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E119" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -5916,13 +5921,13 @@
         <v>2708</v>
       </c>
       <c r="C120">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D120">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E120" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5936,7 +5941,7 @@
         <v>2026</v>
       </c>
       <c r="D121">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E121" t="s">
         <v>202</v>
@@ -5953,7 +5958,7 @@
         <v>2026</v>
       </c>
       <c r="D122">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E122" t="s">
         <v>203</v>
@@ -5967,13 +5972,13 @@
         <v>2708</v>
       </c>
       <c r="C123">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E123" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -5984,30 +5989,30 @@
         <v>2708</v>
       </c>
       <c r="C124">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="D124">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E124" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B125">
-        <v>2737</v>
+        <v>2708</v>
       </c>
       <c r="C125">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E125" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -6021,7 +6026,7 @@
         <v>2025</v>
       </c>
       <c r="D126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E126" t="s">
         <v>173</v>
@@ -6038,7 +6043,7 @@
         <v>2025</v>
       </c>
       <c r="D127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" t="s">
         <v>173</v>
@@ -6055,7 +6060,7 @@
         <v>2025</v>
       </c>
       <c r="D128">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E128" t="s">
         <v>173</v>
@@ -6072,7 +6077,7 @@
         <v>2025</v>
       </c>
       <c r="D129">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E129" t="s">
         <v>173</v>
@@ -6086,13 +6091,13 @@
         <v>2737</v>
       </c>
       <c r="C130">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D130">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E130" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -6106,7 +6111,7 @@
         <v>2026</v>
       </c>
       <c r="D131">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E131" t="s">
         <v>205</v>
@@ -6120,30 +6125,30 @@
         <v>2737</v>
       </c>
       <c r="C132">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D132">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E132" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B133">
-        <v>2733</v>
+        <v>2737</v>
       </c>
       <c r="C133">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E133" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -6157,7 +6162,7 @@
         <v>2025</v>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" t="s">
         <v>171</v>
@@ -6174,7 +6179,7 @@
         <v>2025</v>
       </c>
       <c r="D135">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" t="s">
         <v>171</v>
@@ -6191,10 +6196,10 @@
         <v>2025</v>
       </c>
       <c r="D136">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -6205,16 +6210,13 @@
         <v>2733</v>
       </c>
       <c r="C137">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D137">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E137" t="s">
-        <v>206</v>
-      </c>
-      <c r="F137" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -6228,10 +6230,13 @@
         <v>2026</v>
       </c>
       <c r="D138">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E138" t="s">
         <v>207</v>
+      </c>
+      <c r="F138" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -6242,50 +6247,50 @@
         <v>2733</v>
       </c>
       <c r="C139">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D139">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E139" t="s">
-        <v>172</v>
-      </c>
-      <c r="F139" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>45</v>
-      </c>
-      <c r="B140" t="b">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="B140">
+        <v>2733</v>
       </c>
       <c r="C140">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="D140">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>177</v>
+        <v>172</v>
+      </c>
+      <c r="F140" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B141" t="b">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6299,7 +6304,7 @@
         <v>2025</v>
       </c>
       <c r="D142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" t="s">
         <v>173</v>
@@ -6316,7 +6321,7 @@
         <v>2025</v>
       </c>
       <c r="D143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" t="s">
         <v>173</v>
@@ -6333,7 +6338,7 @@
         <v>2025</v>
       </c>
       <c r="D144">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E144" t="s">
         <v>173</v>
@@ -6350,7 +6355,7 @@
         <v>2025</v>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E145" t="s">
         <v>173</v>
@@ -6367,10 +6372,10 @@
         <v>2025</v>
       </c>
       <c r="D146">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E146" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -6381,13 +6386,13 @@
         <v>0</v>
       </c>
       <c r="C147">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D147">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E147" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -6398,30 +6403,30 @@
         <v>0</v>
       </c>
       <c r="C148">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D148">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E148" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>68</v>
-      </c>
-      <c r="B149">
-        <v>2702</v>
+        <v>58</v>
+      </c>
+      <c r="B149" t="b">
+        <v>0</v>
       </c>
       <c r="C149">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D149">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E149" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -6435,7 +6440,7 @@
         <v>2025</v>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150" t="s">
         <v>171</v>
@@ -6452,7 +6457,7 @@
         <v>2025</v>
       </c>
       <c r="D151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E151" t="s">
         <v>171</v>
@@ -6469,10 +6474,10 @@
         <v>2025</v>
       </c>
       <c r="D152">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E152" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -6483,13 +6488,13 @@
         <v>2702</v>
       </c>
       <c r="C153">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D153">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E153" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -6503,7 +6508,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E154" t="s">
         <v>210</v>
@@ -6520,7 +6525,7 @@
         <v>2026</v>
       </c>
       <c r="D155">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E155" t="s">
         <v>211</v>
@@ -6534,30 +6539,30 @@
         <v>2702</v>
       </c>
       <c r="C156">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D156">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E156" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B157">
-        <v>2738</v>
+        <v>2702</v>
       </c>
       <c r="C157">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D157">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E157" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -6571,7 +6576,7 @@
         <v>2025</v>
       </c>
       <c r="D158">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" t="s">
         <v>173</v>
@@ -6588,7 +6593,7 @@
         <v>2025</v>
       </c>
       <c r="D159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159" t="s">
         <v>173</v>
@@ -6605,7 +6610,7 @@
         <v>2025</v>
       </c>
       <c r="D160">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E160" t="s">
         <v>173</v>
@@ -6622,7 +6627,7 @@
         <v>2025</v>
       </c>
       <c r="D161">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E161" t="s">
         <v>173</v>
@@ -6636,13 +6641,13 @@
         <v>2738</v>
       </c>
       <c r="C162">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D162">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E162" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -6653,13 +6658,13 @@
         <v>2738</v>
       </c>
       <c r="C163">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D163">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E163" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -6670,47 +6675,47 @@
         <v>2738</v>
       </c>
       <c r="C164">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E164" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>51</v>
-      </c>
-      <c r="B165" t="b">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="B165">
+        <v>2738</v>
       </c>
       <c r="C165">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="D165">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B166" t="b">
         <v>0</v>
       </c>
       <c r="C166">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D166">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E166" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -6724,7 +6729,7 @@
         <v>2025</v>
       </c>
       <c r="D167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167" t="s">
         <v>173</v>
@@ -6741,7 +6746,7 @@
         <v>2025</v>
       </c>
       <c r="D168">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" t="s">
         <v>173</v>
@@ -6758,7 +6763,7 @@
         <v>2025</v>
       </c>
       <c r="D169">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E169" t="s">
         <v>173</v>
@@ -6775,7 +6780,7 @@
         <v>2025</v>
       </c>
       <c r="D170">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E170" t="s">
         <v>173</v>
@@ -6783,7 +6788,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B171" t="b">
         <v>0</v>
@@ -6792,7 +6797,7 @@
         <v>2025</v>
       </c>
       <c r="D171">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E171" t="s">
         <v>173</v>
@@ -6809,7 +6814,7 @@
         <v>2025</v>
       </c>
       <c r="D172">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E172" t="s">
         <v>173</v>
@@ -6826,7 +6831,7 @@
         <v>2025</v>
       </c>
       <c r="D173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E173" t="s">
         <v>173</v>
@@ -6843,7 +6848,7 @@
         <v>2025</v>
       </c>
       <c r="D174">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E174" t="s">
         <v>173</v>
@@ -6860,7 +6865,7 @@
         <v>2025</v>
       </c>
       <c r="D175">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E175" t="s">
         <v>173</v>
@@ -6868,7 +6873,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B176" t="b">
         <v>0</v>
@@ -6877,10 +6882,10 @@
         <v>2025</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E176" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -6894,7 +6899,7 @@
         <v>2025</v>
       </c>
       <c r="D177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="s">
         <v>171</v>
@@ -6911,7 +6916,7 @@
         <v>2025</v>
       </c>
       <c r="D178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E178" t="s">
         <v>171</v>
@@ -6928,13 +6933,10 @@
         <v>2025</v>
       </c>
       <c r="D179">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E179" t="s">
-        <v>172</v>
-      </c>
-      <c r="F179" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -6948,10 +6950,13 @@
         <v>2025</v>
       </c>
       <c r="D180">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E180" t="s">
-        <v>182</v>
+        <v>172</v>
+      </c>
+      <c r="F180" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -6962,30 +6967,30 @@
         <v>0</v>
       </c>
       <c r="C181">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D181">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E181" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>52</v>
-      </c>
-      <c r="B182">
-        <v>2727</v>
+        <v>42</v>
+      </c>
+      <c r="B182" t="b">
+        <v>0</v>
       </c>
       <c r="C182">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E182" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -6999,7 +7004,7 @@
         <v>2025</v>
       </c>
       <c r="D183">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" t="s">
         <v>173</v>
@@ -7016,7 +7021,7 @@
         <v>2025</v>
       </c>
       <c r="D184">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E184" t="s">
         <v>173</v>
@@ -7033,7 +7038,7 @@
         <v>2025</v>
       </c>
       <c r="D185">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E185" t="s">
         <v>173</v>
@@ -7050,7 +7055,7 @@
         <v>2025</v>
       </c>
       <c r="D186">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E186" t="s">
         <v>173</v>
@@ -7064,13 +7069,13 @@
         <v>2727</v>
       </c>
       <c r="C187">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D187">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E187" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -7081,30 +7086,30 @@
         <v>2727</v>
       </c>
       <c r="C188">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D188">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E188" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>56</v>
-      </c>
-      <c r="B189" t="b">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="B189">
+        <v>2727</v>
       </c>
       <c r="C189">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D189">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E189" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -7118,7 +7123,7 @@
         <v>2025</v>
       </c>
       <c r="D190">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E190" t="s">
         <v>173</v>
@@ -7135,7 +7140,7 @@
         <v>2025</v>
       </c>
       <c r="D191">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E191" t="s">
         <v>173</v>
@@ -7152,7 +7157,7 @@
         <v>2025</v>
       </c>
       <c r="D192">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E192" t="s">
         <v>173</v>
@@ -7169,7 +7174,7 @@
         <v>2025</v>
       </c>
       <c r="D193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E193" t="s">
         <v>173</v>
@@ -7177,7 +7182,7 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B194" t="b">
         <v>0</v>
@@ -7186,7 +7191,7 @@
         <v>2025</v>
       </c>
       <c r="D194">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E194" t="s">
         <v>173</v>
@@ -7203,7 +7208,7 @@
         <v>2025</v>
       </c>
       <c r="D195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E195" t="s">
         <v>173</v>
@@ -7220,7 +7225,7 @@
         <v>2025</v>
       </c>
       <c r="D196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E196" t="s">
         <v>173</v>
@@ -7237,7 +7242,7 @@
         <v>2025</v>
       </c>
       <c r="D197">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E197" t="s">
         <v>173</v>
@@ -7254,7 +7259,7 @@
         <v>2025</v>
       </c>
       <c r="D198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E198" t="s">
         <v>173</v>
@@ -7271,13 +7276,10 @@
         <v>2025</v>
       </c>
       <c r="D199">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E199" t="s">
-        <v>172</v>
-      </c>
-      <c r="F199" t="s">
-        <v>229</v>
+        <v>173</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -7291,10 +7293,13 @@
         <v>2025</v>
       </c>
       <c r="D200">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E200" t="s">
-        <v>182</v>
+        <v>172</v>
+      </c>
+      <c r="F200" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -7305,33 +7310,33 @@
         <v>0</v>
       </c>
       <c r="C201">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D201">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E201" t="s">
-        <v>172</v>
-      </c>
-      <c r="F201" t="s">
-        <v>229</v>
+        <v>183</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B202" t="b">
         <v>0</v>
       </c>
       <c r="C202">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D202">
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="F202" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -7345,7 +7350,7 @@
         <v>2025</v>
       </c>
       <c r="D203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E203" t="s">
         <v>171</v>
@@ -7362,7 +7367,7 @@
         <v>2025</v>
       </c>
       <c r="D204">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E204" t="s">
         <v>171</v>
@@ -7370,7 +7375,7 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B205" t="b">
         <v>0</v>
@@ -7379,7 +7384,7 @@
         <v>2025</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E205" t="s">
         <v>171</v>
@@ -7396,7 +7401,7 @@
         <v>2025</v>
       </c>
       <c r="D206">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E206" t="s">
         <v>171</v>
@@ -7413,7 +7418,7 @@
         <v>2025</v>
       </c>
       <c r="D207">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E207" t="s">
         <v>171</v>
@@ -7430,10 +7435,10 @@
         <v>2025</v>
       </c>
       <c r="D208">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E208" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -7447,7 +7452,7 @@
         <v>2025</v>
       </c>
       <c r="D209">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E209" t="s">
         <v>172</v>
@@ -7455,7 +7460,7 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B210" t="b">
         <v>0</v>
@@ -7464,10 +7469,10 @@
         <v>2025</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E210" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -7481,7 +7486,7 @@
         <v>2025</v>
       </c>
       <c r="D211">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E211" t="s">
         <v>171</v>
@@ -7498,7 +7503,7 @@
         <v>2025</v>
       </c>
       <c r="D212">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E212" t="s">
         <v>171</v>
@@ -7506,7 +7511,7 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B213" t="b">
         <v>0</v>
@@ -7515,7 +7520,7 @@
         <v>2025</v>
       </c>
       <c r="D213">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E213" t="s">
         <v>171</v>
@@ -7532,10 +7537,10 @@
         <v>2025</v>
       </c>
       <c r="D214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -7549,10 +7554,10 @@
         <v>2025</v>
       </c>
       <c r="D215">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E215" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -7566,13 +7571,10 @@
         <v>2025</v>
       </c>
       <c r="D216">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E216" t="s">
-        <v>172</v>
-      </c>
-      <c r="F216" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -7586,18 +7588,18 @@
         <v>2025</v>
       </c>
       <c r="D217">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E217" t="s">
         <v>172</v>
       </c>
       <c r="F217" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B218" t="b">
         <v>0</v>
@@ -7606,10 +7608,13 @@
         <v>2025</v>
       </c>
       <c r="D218">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
-        <v>173</v>
+        <v>172</v>
+      </c>
+      <c r="F218" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -7623,7 +7628,7 @@
         <v>2025</v>
       </c>
       <c r="D219">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E219" t="s">
         <v>173</v>
@@ -7640,7 +7645,7 @@
         <v>2025</v>
       </c>
       <c r="D220">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E220" t="s">
         <v>173</v>
@@ -7657,7 +7662,7 @@
         <v>2025</v>
       </c>
       <c r="D221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E221" t="s">
         <v>173</v>
@@ -7674,7 +7679,7 @@
         <v>2025</v>
       </c>
       <c r="D222">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E222" t="s">
         <v>173</v>
@@ -7682,16 +7687,16 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>57</v>
-      </c>
-      <c r="B223">
-        <v>2731</v>
+        <v>70</v>
+      </c>
+      <c r="B223" t="b">
+        <v>0</v>
       </c>
       <c r="C223">
         <v>2025</v>
       </c>
       <c r="D223">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E223" t="s">
         <v>173</v>
@@ -7708,7 +7713,7 @@
         <v>2025</v>
       </c>
       <c r="D224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E224" t="s">
         <v>173</v>
@@ -7725,7 +7730,7 @@
         <v>2025</v>
       </c>
       <c r="D225">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E225" t="s">
         <v>173</v>
@@ -7742,7 +7747,7 @@
         <v>2025</v>
       </c>
       <c r="D226">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E226" t="s">
         <v>173</v>
@@ -7759,7 +7764,7 @@
         <v>2025</v>
       </c>
       <c r="D227">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E227" t="s">
         <v>173</v>
@@ -7776,10 +7781,10 @@
         <v>2025</v>
       </c>
       <c r="D228">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E228" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -7790,13 +7795,13 @@
         <v>2731</v>
       </c>
       <c r="C229">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D229">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E229" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -7807,30 +7812,30 @@
         <v>2731</v>
       </c>
       <c r="C230">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="D230">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E230" t="s">
-        <v>177</v>
+        <v>217</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>73</v>
-      </c>
-      <c r="B231" t="b">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="B231">
+        <v>2731</v>
       </c>
       <c r="C231">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E231" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -7844,7 +7849,7 @@
         <v>2025</v>
       </c>
       <c r="D232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E232" t="s">
         <v>173</v>
@@ -7861,7 +7866,7 @@
         <v>2025</v>
       </c>
       <c r="D233">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E233" t="s">
         <v>173</v>
@@ -7878,7 +7883,7 @@
         <v>2025</v>
       </c>
       <c r="D234">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E234" t="s">
         <v>173</v>
@@ -7895,7 +7900,7 @@
         <v>2025</v>
       </c>
       <c r="D235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E235" t="s">
         <v>173</v>
@@ -7903,7 +7908,7 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B236" t="b">
         <v>0</v>
@@ -7912,10 +7917,10 @@
         <v>2025</v>
       </c>
       <c r="D236">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E236" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -7929,7 +7934,7 @@
         <v>2025</v>
       </c>
       <c r="D237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E237" t="s">
         <v>171</v>
@@ -7946,7 +7951,7 @@
         <v>2025</v>
       </c>
       <c r="D238">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E238" t="s">
         <v>171</v>
@@ -7963,15 +7968,15 @@
         <v>2025</v>
       </c>
       <c r="D239">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E239" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B240" t="b">
         <v>0</v>
@@ -7980,10 +7985,10 @@
         <v>2025</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E240" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -7997,7 +8002,7 @@
         <v>2025</v>
       </c>
       <c r="D241">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E241" t="s">
         <v>173</v>
@@ -8014,7 +8019,7 @@
         <v>2025</v>
       </c>
       <c r="D242">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E242" t="s">
         <v>173</v>
@@ -8031,7 +8036,7 @@
         <v>2025</v>
       </c>
       <c r="D243">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E243" t="s">
         <v>173</v>
@@ -8048,9 +8053,26 @@
         <v>2025</v>
       </c>
       <c r="D244">
+        <v>4</v>
+      </c>
+      <c r="E244" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" t="s">
+        <v>77</v>
+      </c>
+      <c r="B245" t="b">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>2025</v>
+      </c>
+      <c r="D245">
         <v>5</v>
       </c>
-      <c r="E244" t="s">
+      <c r="E245" t="s">
         <v>173</v>
       </c>
     </row>
@@ -8066,34 +8088,34 @@
   <sheetData>
     <row r="1" spans="1:29">
       <c r="A1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H1" t="s">
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
@@ -8102,55 +8124,55 @@
         <v>13</v>
       </c>
       <c r="M1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="S1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="T1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="U1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="V1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="W1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="X1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Y1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Z1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AB1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AC1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:29">
@@ -8158,16 +8180,16 @@
         <v>3810267428</v>
       </c>
       <c r="C2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E2" s="1">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G2" s="1">
         <v>45492</v>
@@ -8179,7 +8201,7 @@
         <v>198</v>
       </c>
       <c r="J2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K2" t="s">
         <v>60</v>
@@ -8197,28 +8219,28 @@
         <v>45492</v>
       </c>
       <c r="U2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="V2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="W2" t="s">
         <v>22</v>
       </c>
       <c r="X2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Y2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Z2" t="s">
         <v>30</v>
       </c>
       <c r="AA2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AB2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -8226,16 +8248,16 @@
         <v>3810269967</v>
       </c>
       <c r="C3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E3" s="1">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G3" s="1">
         <v>45631</v>
@@ -8247,7 +8269,7 @@
         <v>198</v>
       </c>
       <c r="J3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K3" t="s">
         <v>77</v>
@@ -8265,25 +8287,25 @@
         <v>45631</v>
       </c>
       <c r="U3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W3" t="s">
         <v>22</v>
       </c>
       <c r="X3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Y3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AA3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AB3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -8291,16 +8313,16 @@
         <v>3810271134</v>
       </c>
       <c r="C4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E4" s="1">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G4" s="1">
         <v>45716</v>
@@ -8312,7 +8334,7 @@
         <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K4" t="s">
         <v>56</v>
@@ -8330,25 +8352,25 @@
         <v>45716</v>
       </c>
       <c r="U4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W4" t="s">
         <v>22</v>
       </c>
       <c r="X4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Y4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z4" t="s">
         <v>30</v>
       </c>
       <c r="AA4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AB4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -8356,16 +8378,16 @@
         <v>3810271161</v>
       </c>
       <c r="C5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E5" s="1">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G5" s="1">
         <v>45728</v>
@@ -8377,7 +8399,7 @@
         <v>198</v>
       </c>
       <c r="J5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K5" t="s">
         <v>46</v>
@@ -8395,25 +8417,25 @@
         <v>45728</v>
       </c>
       <c r="U5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W5" t="s">
         <v>22</v>
       </c>
       <c r="X5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Y5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Z5" t="s">
         <v>30</v>
       </c>
       <c r="AA5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AB5" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -8424,16 +8446,16 @@
         <v>3810271161</v>
       </c>
       <c r="C6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E6" s="1">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G6" s="1">
         <v>45755</v>
@@ -8445,7 +8467,7 @@
         <v>198</v>
       </c>
       <c r="J6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K6" t="s">
         <v>46</v>
@@ -8463,25 +8485,25 @@
         <v>45755</v>
       </c>
       <c r="U6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W6" t="s">
         <v>22</v>
       </c>
       <c r="X6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Y6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Z6" t="s">
         <v>22</v>
       </c>
       <c r="AA6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AB6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -8492,16 +8514,16 @@
         <v>3810272114</v>
       </c>
       <c r="C7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E7" s="1">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H7" t="s">
         <v>38</v>
@@ -8510,7 +8532,7 @@
         <v>198</v>
       </c>
       <c r="J7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K7" t="s">
         <v>46</v>
@@ -8525,25 +8547,25 @@
         <v>45775</v>
       </c>
       <c r="U7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W7" t="s">
         <v>22</v>
       </c>
       <c r="X7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Y7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z7" t="s">
         <v>22</v>
       </c>
       <c r="AA7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AB7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -8554,16 +8576,16 @@
         <v>3810272114</v>
       </c>
       <c r="C8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E8" s="1">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H8" t="s">
         <v>38</v>
@@ -8572,7 +8594,7 @@
         <v>198</v>
       </c>
       <c r="J8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K8" t="s">
         <v>46</v>
@@ -8587,25 +8609,25 @@
         <v>45770</v>
       </c>
       <c r="U8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W8" t="s">
         <v>22</v>
       </c>
       <c r="X8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Y8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z8" t="s">
         <v>22</v>
       </c>
       <c r="AA8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AB8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -8616,16 +8638,16 @@
         <v>3810272114</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E9" s="1">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H9" t="s">
         <v>38</v>
@@ -8634,7 +8656,7 @@
         <v>198</v>
       </c>
       <c r="J9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K9" t="s">
         <v>46</v>
@@ -8649,25 +8671,25 @@
         <v>45777</v>
       </c>
       <c r="U9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W9" t="s">
         <v>22</v>
       </c>
       <c r="X9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Y9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Z9" t="s">
         <v>22</v>
       </c>
       <c r="AA9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AB9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -8678,16 +8700,16 @@
         <v>3810271161</v>
       </c>
       <c r="C10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E10" s="1">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G10" s="1">
         <v>45755</v>
@@ -8699,7 +8721,7 @@
         <v>198</v>
       </c>
       <c r="J10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K10" t="s">
         <v>46</v>
@@ -8717,25 +8739,25 @@
         <v>45754</v>
       </c>
       <c r="U10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W10" t="s">
         <v>22</v>
       </c>
       <c r="X10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z10" t="s">
         <v>22</v>
       </c>
       <c r="AA10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AB10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -8743,16 +8765,16 @@
         <v>3810255268</v>
       </c>
       <c r="C11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E11" s="1">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G11" s="1">
         <v>44973</v>
@@ -8764,10 +8786,10 @@
         <v>198</v>
       </c>
       <c r="J11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P11">
         <v>1</v>
@@ -8782,25 +8804,25 @@
         <v>44973</v>
       </c>
       <c r="U11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W11" t="s">
         <v>22</v>
       </c>
       <c r="X11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z11" t="s">
         <v>22</v>
       </c>
       <c r="AA11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AB11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -8808,16 +8830,16 @@
         <v>3810264674</v>
       </c>
       <c r="C12" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E12" s="1">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G12" s="1">
         <v>45358</v>
@@ -8829,7 +8851,7 @@
         <v>198</v>
       </c>
       <c r="J12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K12" t="s">
         <v>70</v>
@@ -8847,25 +8869,25 @@
         <v>45358</v>
       </c>
       <c r="U12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W12" t="s">
         <v>22</v>
       </c>
       <c r="X12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Y12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AB12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -8873,16 +8895,16 @@
         <v>3810268863</v>
       </c>
       <c r="C13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E13" s="1">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G13" s="1">
         <v>45573</v>
@@ -8894,7 +8916,7 @@
         <v>198</v>
       </c>
       <c r="J13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K13" t="s">
         <v>57</v>
@@ -8912,28 +8934,28 @@
         <v>45573</v>
       </c>
       <c r="U13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="V13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="W13" t="s">
         <v>22</v>
       </c>
       <c r="X13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Y13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z13" t="s">
         <v>22</v>
       </c>
       <c r="AA13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AB13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -8941,16 +8963,16 @@
         <v>3810271550</v>
       </c>
       <c r="C14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E14" s="1">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G14" s="1">
         <v>45747</v>
@@ -8962,7 +8984,7 @@
         <v>198</v>
       </c>
       <c r="J14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K14" t="s">
         <v>55</v>
@@ -8980,25 +9002,25 @@
         <v>45747</v>
       </c>
       <c r="U14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="W14" t="s">
         <v>22</v>
       </c>
       <c r="X14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Y14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z14" t="s">
         <v>22</v>
       </c>
       <c r="AA14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AB14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -9087,13 +9109,13 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J2" t="s">
         <v>81</v>
@@ -9120,7 +9142,7 @@
         <v>45015</v>
       </c>
       <c r="R2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="S2" t="s">
         <v>145</v>
@@ -9128,19 +9150,19 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B3" t="s">
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J3" t="s">
         <v>81</v>
@@ -9167,7 +9189,7 @@
         <v>45614</v>
       </c>
       <c r="R3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="S3" t="s">
         <v>145</v>
@@ -9181,13 +9203,13 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J4" t="s">
         <v>81</v>
@@ -9214,7 +9236,7 @@
         <v>45539</v>
       </c>
       <c r="R4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S4" t="s">
         <v>145</v>
@@ -9228,13 +9250,13 @@
         <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J5" t="s">
         <v>81</v>
@@ -9261,7 +9283,7 @@
         <v>45490</v>
       </c>
       <c r="R5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="S5" t="s">
         <v>145</v>
@@ -9275,13 +9297,13 @@
         <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J6" t="s">
         <v>81</v>
@@ -9308,7 +9330,7 @@
         <v>45526</v>
       </c>
       <c r="R6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S6" t="s">
         <v>145</v>
@@ -9322,13 +9344,13 @@
         <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J7" t="s">
         <v>81</v>
@@ -9355,7 +9377,7 @@
         <v>45352</v>
       </c>
       <c r="R7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="S7" t="s">
         <v>145</v>
@@ -9369,13 +9391,13 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J8" t="s">
         <v>81</v>
@@ -9402,7 +9424,7 @@
         <v>44704</v>
       </c>
       <c r="R8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S8" t="s">
         <v>145</v>
@@ -9416,13 +9438,13 @@
         <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J9" t="s">
         <v>81</v>
@@ -9449,7 +9471,7 @@
         <v>45628</v>
       </c>
       <c r="R9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="S9" t="s">
         <v>145</v>
@@ -9463,13 +9485,13 @@
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J10" t="s">
         <v>81</v>
@@ -9496,7 +9518,7 @@
         <v>43549</v>
       </c>
       <c r="R10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="S10" t="s">
         <v>145</v>
@@ -9504,19 +9526,19 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B11" t="s">
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J11" t="s">
         <v>81</v>
@@ -9543,7 +9565,7 @@
         <v>44735</v>
       </c>
       <c r="R11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="S11" t="s">
         <v>145</v>
@@ -9557,13 +9579,13 @@
         <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J12" t="s">
         <v>81</v>
@@ -9590,7 +9612,7 @@
         <v>45776</v>
       </c>
       <c r="R12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="S12" t="s">
         <v>145</v>
@@ -9598,19 +9620,19 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B13" t="s">
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J13" t="s">
         <v>81</v>
@@ -9637,7 +9659,7 @@
         <v>45600</v>
       </c>
       <c r="R13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S13" t="s">
         <v>145</v>
@@ -9651,13 +9673,13 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J14" t="s">
         <v>81</v>
@@ -9684,7 +9706,7 @@
         <v>44630</v>
       </c>
       <c r="R14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S14" t="s">
         <v>145</v>
@@ -9698,13 +9720,13 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J15" t="s">
         <v>81</v>
@@ -9739,13 +9761,13 @@
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J16" t="s">
         <v>81</v>
@@ -9780,13 +9802,13 @@
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E17" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I17" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J17" t="s">
         <v>81</v>
@@ -9813,7 +9835,7 @@
         <v>45026</v>
       </c>
       <c r="R17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="S17" t="s">
         <v>145</v>
@@ -9827,13 +9849,13 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E18" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I18" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J18" t="s">
         <v>81</v>
@@ -9860,7 +9882,7 @@
         <v>45371</v>
       </c>
       <c r="R18" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="S18" t="s">
         <v>145</v>
@@ -9874,13 +9896,13 @@
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J19" t="s">
         <v>81</v>
@@ -9907,7 +9929,7 @@
         <v>45294</v>
       </c>
       <c r="R19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="S19" t="s">
         <v>145</v>
@@ -9921,13 +9943,13 @@
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J20" t="s">
         <v>81</v>
@@ -9954,7 +9976,7 @@
         <v>44369</v>
       </c>
       <c r="R20" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="S20" t="s">
         <v>145</v>
@@ -9968,13 +9990,13 @@
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J21" t="s">
         <v>81</v>
@@ -10001,7 +10023,7 @@
         <v>43894</v>
       </c>
       <c r="R21" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S21" t="s">
         <v>145</v>
@@ -10015,13 +10037,13 @@
         <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E22" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I22" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J22" t="s">
         <v>81</v>
@@ -10048,7 +10070,7 @@
         <v>45509</v>
       </c>
       <c r="R22" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="S22" t="s">
         <v>145</v>
@@ -10062,13 +10084,13 @@
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E23" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I23" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J23" t="s">
         <v>81</v>
@@ -10080,7 +10102,7 @@
         <v>4000</v>
       </c>
       <c r="O23" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P23" s="1">
         <v>40044</v>
@@ -10089,13 +10111,13 @@
         <v>40126</v>
       </c>
       <c r="R23" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="S23" t="s">
         <v>144</v>
       </c>
       <c r="T23" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="U23" s="1">
         <v>45775</v>
@@ -10109,13 +10131,13 @@
         <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E24" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I24" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J24" t="s">
         <v>81</v>
@@ -10142,13 +10164,13 @@
         <v>45772</v>
       </c>
       <c r="R24" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="S24" t="s">
         <v>144</v>
       </c>
       <c r="T24" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U24" s="1">
         <v>45810</v>
@@ -10162,13 +10184,13 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E25" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I25" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J25" t="s">
         <v>81</v>
@@ -10195,13 +10217,13 @@
         <v>45510</v>
       </c>
       <c r="R25" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="S25" t="s">
         <v>144</v>
       </c>
       <c r="T25" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="U25" s="1">
         <v>45937</v>
@@ -10215,13 +10237,13 @@
         <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E26" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I26" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J26" t="s">
         <v>81</v>
@@ -10248,13 +10270,13 @@
         <v>44959</v>
       </c>
       <c r="R26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="S26" t="s">
         <v>144</v>
       </c>
       <c r="T26" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="U26" s="1">
         <v>45580</v>
@@ -10268,13 +10290,13 @@
         <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E27" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I27" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J27" t="s">
         <v>81</v>
@@ -10301,13 +10323,13 @@
         <v>45446</v>
       </c>
       <c r="R27" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="S27" t="s">
         <v>144</v>
       </c>
       <c r="T27" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U27" s="1">
         <v>45588</v>
@@ -10321,13 +10343,13 @@
         <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E28" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I28" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J28" t="s">
         <v>81</v>
@@ -10354,13 +10376,13 @@
         <v>45824</v>
       </c>
       <c r="R28" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="S28" t="s">
         <v>144</v>
       </c>
       <c r="T28" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="U28" s="1">
         <v>45831</v>
@@ -10374,13 +10396,13 @@
         <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E29" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I29" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J29" t="s">
         <v>81</v>
@@ -10407,13 +10429,13 @@
         <v>45567</v>
       </c>
       <c r="R29" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="S29" t="s">
         <v>144</v>
       </c>
       <c r="T29" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="U29" s="1">
         <v>45734</v>
@@ -10427,13 +10449,13 @@
         <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E30" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I30" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J30" t="s">
         <v>81</v>
@@ -10445,7 +10467,7 @@
         <v>144</v>
       </c>
       <c r="T30" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="U30" s="1">
         <v>46001</v>
@@ -10459,13 +10481,13 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E31" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I31" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J31" t="s">
         <v>81</v>
@@ -10477,7 +10499,7 @@
         <v>144</v>
       </c>
       <c r="T31" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="U31" s="1">
         <v>46001</v>
@@ -10491,13 +10513,13 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E32" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I32" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J32" t="s">
         <v>81</v>
@@ -10509,7 +10531,7 @@
         <v>144</v>
       </c>
       <c r="T32" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="U32" s="1">
         <v>46001</v>
@@ -10523,13 +10545,13 @@
         <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E33" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I33" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J33" t="s">
         <v>81</v>
@@ -10556,13 +10578,13 @@
         <v>46031</v>
       </c>
       <c r="R33" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S33" t="s">
         <v>148</v>
       </c>
       <c r="T33" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="U33" s="1">
         <v>46037</v>
@@ -10576,13 +10598,13 @@
         <v>36</v>
       </c>
       <c r="C34" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E34" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I34" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J34" t="s">
         <v>81</v>
@@ -10600,7 +10622,7 @@
         <v>4000</v>
       </c>
       <c r="O34" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P34" s="1">
         <v>40071</v>
@@ -10617,19 +10639,19 @@
     </row>
     <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s">
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E35" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I35" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J35" t="s">
         <v>81</v>
@@ -10650,7 +10672,7 @@
         <v>45259</v>
       </c>
       <c r="R35" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="S35" t="s">
         <v>149</v>
@@ -10667,13 +10689,13 @@
         <v>36</v>
       </c>
       <c r="C36" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E36" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I36" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J36" t="s">
         <v>81</v>
@@ -10700,7 +10722,7 @@
         <v>46000</v>
       </c>
       <c r="R36" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="S36" t="s">
         <v>149</v>
@@ -10717,13 +10739,13 @@
         <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E37" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I37" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J37" t="s">
         <v>81</v>
@@ -10743,13 +10765,13 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E38" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I38" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J38" t="s">
         <v>81</v>
@@ -10776,7 +10798,7 @@
         <v>39068</v>
       </c>
       <c r="R38" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="S38" t="s">
         <v>149</v>
@@ -10793,13 +10815,13 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I39" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J39" t="s">
         <v>81</v>
@@ -10826,13 +10848,13 @@
         <v>40568</v>
       </c>
       <c r="R39" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="S39" t="s">
         <v>149</v>
       </c>
       <c r="T39" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="U39" s="1">
         <v>40568</v>
@@ -10846,13 +10868,13 @@
         <v>36</v>
       </c>
       <c r="C40" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E40" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I40" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J40" t="s">
         <v>81</v>
@@ -10873,13 +10895,13 @@
         <v>42270</v>
       </c>
       <c r="R40" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="S40" t="s">
         <v>149</v>
       </c>
       <c r="T40" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="U40" s="1">
         <v>42270</v>
@@ -10893,13 +10915,13 @@
         <v>36</v>
       </c>
       <c r="C41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E41" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I41" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J41" t="s">
         <v>81</v>
@@ -10926,13 +10948,13 @@
         <v>43494</v>
       </c>
       <c r="R41" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="S41" t="s">
         <v>146</v>
       </c>
       <c r="T41" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="U41" s="1">
         <v>44148</v>
@@ -10946,13 +10968,13 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E42" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I42" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J42" t="s">
         <v>81</v>
@@ -10979,13 +11001,13 @@
         <v>45776</v>
       </c>
       <c r="R42" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="S42" t="s">
         <v>146</v>
       </c>
       <c r="T42" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="U42" s="1">
         <v>43185</v>
@@ -10999,13 +11021,13 @@
         <v>36</v>
       </c>
       <c r="C43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E43" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I43" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J43" t="s">
         <v>81</v>
@@ -11032,13 +11054,13 @@
         <v>45916</v>
       </c>
       <c r="R43" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="S43" t="s">
         <v>146</v>
       </c>
       <c r="T43" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="U43" s="1">
         <v>42850</v>
@@ -11052,13 +11074,13 @@
         <v>36</v>
       </c>
       <c r="C44" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I44" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J44" t="s">
         <v>81</v>
@@ -11085,13 +11107,13 @@
         <v>45539</v>
       </c>
       <c r="R44" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="S44" t="s">
         <v>146</v>
       </c>
       <c r="T44" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="U44" s="1">
         <v>44404</v>
@@ -11105,13 +11127,13 @@
         <v>36</v>
       </c>
       <c r="C45" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I45" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J45" t="s">
         <v>81</v>
@@ -11138,13 +11160,13 @@
         <v>45239</v>
       </c>
       <c r="R45" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="S45" t="s">
         <v>146</v>
       </c>
       <c r="T45" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="U45" s="1">
         <v>42698</v>
@@ -11158,13 +11180,13 @@
         <v>36</v>
       </c>
       <c r="C46" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I46" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J46" t="s">
         <v>81</v>
@@ -11191,13 +11213,13 @@
         <v>45586</v>
       </c>
       <c r="R46" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="S46" t="s">
         <v>146</v>
       </c>
       <c r="T46" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="U46" s="1">
         <v>43941</v>
@@ -11221,19 +11243,19 @@
         <v>166</v>
       </c>
       <c r="C1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -11907,39 +11929,39 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F2">
         <v>200000</v>
@@ -11947,19 +11969,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F3">
         <v>700000</v>
@@ -11967,19 +11989,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F4">
         <v>800000</v>
@@ -11987,19 +12009,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F5">
         <v>400000</v>
@@ -12007,19 +12029,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F6">
         <v>400000</v>
@@ -12027,19 +12049,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F7">
         <v>400000</v>
@@ -12047,19 +12069,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C8" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D8" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E8" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F8">
         <v>1000000</v>
@@ -12067,19 +12089,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F9">
         <v>1000000</v>
@@ -12087,19 +12109,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F10">
         <v>1000000</v>
@@ -12107,19 +12129,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F11">
         <v>563000</v>
@@ -12127,19 +12149,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E12" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F12">
         <v>320000</v>
@@ -12147,19 +12169,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C13" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D13" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F13">
         <v>120000</v>
@@ -12167,19 +12189,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F14">
         <v>120000</v>
@@ -12187,19 +12209,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B15" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C15" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F15">
         <v>80000</v>
@@ -12207,19 +12229,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C16" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D16" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E16" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F16">
         <v>80000</v>
@@ -12227,19 +12249,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C17" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D17" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F17">
         <v>3800000</v>
@@ -12247,19 +12269,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B18" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C18" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D18" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E18" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F18">
         <v>3800000</v>
@@ -12267,19 +12289,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B19" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C19" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D19" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E19" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F19">
         <v>3800000</v>
@@ -12287,19 +12309,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C20" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D20" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E20" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F20">
         <v>3800000</v>
@@ -12307,19 +12329,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B21" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E21" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F21">
         <v>3800000</v>
@@ -12327,19 +12349,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B22" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C22" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D22" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E22" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F22">
         <v>3800000</v>
@@ -12347,19 +12369,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B23" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C23" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F23">
         <v>430000</v>
@@ -12367,19 +12389,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B24" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C24" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D24" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F24">
         <v>430000</v>
@@ -12387,19 +12409,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B25" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C25" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D25" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E25" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F25">
         <v>425000</v>
@@ -12407,19 +12429,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B26" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C26" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D26" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E26" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F26">
         <v>60000</v>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -687,8 +687,7 @@
 Motor já está no GLOG-CO</t>
   </si>
   <si>
-    <t>sem at
-Possui AT de 200H, porém foi encontrada  uma trinca e o housing será recolhido.</t>
+    <t>Possui AT 313000000812 de 200H, porém foi encontrada  uma trinca e o housing será recolhido.</t>
   </si>
   <si>
     <t>Fez o 1° HSI COM 1941H, O PROX SERÁ COM 3441.
@@ -4288,10 +4287,10 @@
         <v>2741</v>
       </c>
       <c r="C25">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="D25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E25" t="s">
         <v>172</v>
@@ -11326,7 +11325,7 @@
         <v>3886.67</v>
       </c>
       <c r="D5">
-        <v>113.3333333</v>
+        <v>313.3333333</v>
       </c>
       <c r="E5">
         <v>55.52851064</v>
@@ -11335,7 +11334,7 @@
         <v>260.984</v>
       </c>
       <c r="G5">
-        <v>2.040993573</v>
+        <v>5.642746937</v>
       </c>
     </row>
     <row r="6" spans="1:7">

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1427,8 +1427,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1444,7 +1452,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1452,12 +1460,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1757,70 +1783,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1861,10 +1887,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>41754</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1876,7 +1902,7 @@
       <c r="T2" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="1">
+      <c r="U2" s="2">
         <v>46170</v>
       </c>
     </row>
@@ -1917,10 +1943,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>44709</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1967,10 +1993,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>44348</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -2014,10 +2040,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>46059</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -2029,7 +2055,7 @@
       <c r="T5" t="s">
         <v>151</v>
       </c>
-      <c r="U5" s="1">
+      <c r="U5" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -2070,10 +2096,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>46149</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -2120,10 +2146,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>43731</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -2135,7 +2161,7 @@
       <c r="T7" t="s">
         <v>152</v>
       </c>
-      <c r="U7" s="1">
+      <c r="U7" s="2">
         <v>43507</v>
       </c>
     </row>
@@ -2176,10 +2202,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45511</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2226,10 +2252,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45716</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2241,7 +2267,7 @@
       <c r="T9" t="s">
         <v>153</v>
       </c>
-      <c r="U9" s="1">
+      <c r="U9" s="2">
         <v>44665</v>
       </c>
     </row>
@@ -2282,10 +2308,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>45064</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2323,10 +2349,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>46135</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2338,7 +2364,7 @@
       <c r="T11" t="s">
         <v>154</v>
       </c>
-      <c r="U11" s="1">
+      <c r="U11" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -2376,7 +2402,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2417,10 +2443,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>46199</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2467,10 +2493,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45667</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2482,7 +2508,7 @@
       <c r="T14" t="s">
         <v>155</v>
       </c>
-      <c r="U14" s="1">
+      <c r="U14" s="2">
         <v>46072</v>
       </c>
     </row>
@@ -2523,10 +2549,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>46064</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="Q15" s="2">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2573,10 +2599,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>44285</v>
       </c>
-      <c r="Q16" s="1">
+      <c r="Q16" s="2">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2588,7 +2614,7 @@
       <c r="T16" t="s">
         <v>156</v>
       </c>
-      <c r="U16" s="1">
+      <c r="U16" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2629,10 +2655,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45922</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2679,10 +2705,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>45930</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2694,7 +2720,7 @@
       <c r="T18" t="s">
         <v>157</v>
       </c>
-      <c r="U18" s="1">
+      <c r="U18" s="2">
         <v>46198</v>
       </c>
     </row>
@@ -2735,10 +2761,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45524</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2750,7 +2776,7 @@
       <c r="T19" t="s">
         <v>124</v>
       </c>
-      <c r="U19" s="1">
+      <c r="U19" s="2">
         <v>46153</v>
       </c>
     </row>
@@ -2791,10 +2817,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>45026</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2806,7 +2832,7 @@
       <c r="T20" t="s">
         <v>158</v>
       </c>
-      <c r="U20" s="1">
+      <c r="U20" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2847,10 +2873,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>45159</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2862,7 +2888,7 @@
       <c r="T21" t="s">
         <v>126</v>
       </c>
-      <c r="U21" s="1">
+      <c r="U21" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -2903,10 +2929,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2918,7 +2944,7 @@
       <c r="T22" t="s">
         <v>159</v>
       </c>
-      <c r="U22" s="1">
+      <c r="U22" s="2">
         <v>45995</v>
       </c>
     </row>
@@ -2956,10 +2982,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>45713</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -2968,7 +2994,7 @@
       <c r="S23" t="s">
         <v>149</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -3009,10 +3035,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>46062</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>46220</v>
       </c>
       <c r="R24" t="s">
@@ -3021,7 +3047,7 @@
       <c r="S24" t="s">
         <v>149</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -3062,10 +3088,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45079</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -3112,10 +3138,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>41346</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -3127,7 +3153,7 @@
       <c r="T26" t="s">
         <v>160</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>46150</v>
       </c>
     </row>
@@ -3168,10 +3194,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45579</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3218,10 +3244,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>46171</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3268,10 +3294,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44320</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3318,10 +3344,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="2">
         <v>42661</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="Q30" s="2">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3333,7 +3359,7 @@
       <c r="T30" t="s">
         <v>161</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="2">
         <v>45358</v>
       </c>
     </row>
@@ -3374,10 +3400,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="2">
         <v>46220</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="Q31" s="2">
         <v>46220</v>
       </c>
       <c r="R31" t="s">
@@ -3424,10 +3450,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="2">
         <v>43797</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="Q32" s="2">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3474,10 +3500,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>42810</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3489,7 +3515,7 @@
       <c r="T33" t="s">
         <v>162</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="2">
         <v>43802</v>
       </c>
     </row>
@@ -3530,10 +3556,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>45070</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>44910</v>
       </c>
       <c r="R34" t="s">
@@ -3580,10 +3606,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>43250</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3630,10 +3656,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45841</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3680,10 +3706,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="2">
         <v>45105</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="Q37" s="2">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3695,7 +3721,7 @@
       <c r="T37" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="1">
+      <c r="U37" s="2">
         <v>46184</v>
       </c>
     </row>
@@ -3736,10 +3762,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>45636</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>46219</v>
       </c>
       <c r="S38" t="s">
@@ -3748,7 +3774,7 @@
       <c r="T38" t="s">
         <v>164</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="2">
         <v>45351</v>
       </c>
     </row>
@@ -3789,10 +3815,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>45831</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3836,10 +3862,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>44287</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3860,22 +3886,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>170</v>
       </c>
     </row>
@@ -8086,91 +8112,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>255</v>
       </c>
     </row>
@@ -8184,13 +8210,13 @@
       <c r="D2" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
         <v>261</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>45492</v>
       </c>
       <c r="H2" t="s">
@@ -8208,13 +8234,13 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45491</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="2">
         <v>45528</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="2">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
@@ -8252,13 +8278,13 @@
       <c r="D3" t="s">
         <v>259</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
         <v>261</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="2">
         <v>45631</v>
       </c>
       <c r="H3" t="s">
@@ -8276,13 +8302,13 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>45628</v>
       </c>
-      <c r="R3" s="1">
+      <c r="R3" s="2">
         <v>45632</v>
       </c>
-      <c r="S3" s="1">
+      <c r="S3" s="2">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
@@ -8317,13 +8343,13 @@
       <c r="D4" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
         <v>261</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="2">
         <v>45716</v>
       </c>
       <c r="H4" t="s">
@@ -8341,13 +8367,13 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45716</v>
       </c>
-      <c r="R4" s="1">
+      <c r="R4" s="2">
         <v>45722</v>
       </c>
-      <c r="S4" s="1">
+      <c r="S4" s="2">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
@@ -8382,13 +8408,13 @@
       <c r="D5" t="s">
         <v>259</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
         <v>261</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <v>45728</v>
       </c>
       <c r="H5" t="s">
@@ -8406,13 +8432,13 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45722</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R5" s="2">
         <v>45782</v>
       </c>
-      <c r="S5" s="1">
+      <c r="S5" s="2">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
@@ -8450,13 +8476,13 @@
       <c r="D6" t="s">
         <v>259</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
         <v>261</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <v>45755</v>
       </c>
       <c r="H6" t="s">
@@ -8474,13 +8500,13 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45728</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R6" s="2">
         <v>45734</v>
       </c>
-      <c r="S6" s="1">
+      <c r="S6" s="2">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
@@ -8518,7 +8544,7 @@
       <c r="D7" t="s">
         <v>260</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
@@ -8539,10 +8565,10 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45772</v>
       </c>
-      <c r="R7" s="1">
+      <c r="R7" s="2">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
@@ -8580,7 +8606,7 @@
       <c r="D8" t="s">
         <v>260</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
@@ -8601,10 +8627,10 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>45762</v>
       </c>
-      <c r="R8" s="1">
+      <c r="R8" s="2">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
@@ -8642,7 +8668,7 @@
       <c r="D9" t="s">
         <v>260</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
@@ -8663,10 +8689,10 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45763</v>
       </c>
-      <c r="R9" s="1">
+      <c r="R9" s="2">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
@@ -8704,13 +8730,13 @@
       <c r="D10" t="s">
         <v>259</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
         <v>261</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="2">
         <v>45755</v>
       </c>
       <c r="H10" t="s">
@@ -8728,13 +8754,13 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45754</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R10" s="2">
         <v>45849</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S10" s="2">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
@@ -8769,13 +8795,13 @@
       <c r="D11" t="s">
         <v>259</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
         <v>261</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="2">
         <v>44973</v>
       </c>
       <c r="H11" t="s">
@@ -8793,13 +8819,13 @@
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44973</v>
       </c>
-      <c r="R11" s="1">
+      <c r="R11" s="2">
         <v>45687</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S11" s="2">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
@@ -8834,13 +8860,13 @@
       <c r="D12" t="s">
         <v>259</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
         <v>261</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="2">
         <v>45358</v>
       </c>
       <c r="H12" t="s">
@@ -8858,13 +8884,13 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45358</v>
       </c>
-      <c r="R12" s="1">
+      <c r="R12" s="2">
         <v>45517</v>
       </c>
-      <c r="S12" s="1">
+      <c r="S12" s="2">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
@@ -8899,13 +8925,13 @@
       <c r="D13" t="s">
         <v>259</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
         <v>261</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="2">
         <v>45573</v>
       </c>
       <c r="H13" t="s">
@@ -8923,13 +8949,13 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45572</v>
       </c>
-      <c r="R13" s="1">
+      <c r="R13" s="2">
         <v>45572</v>
       </c>
-      <c r="S13" s="1">
+      <c r="S13" s="2">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
@@ -8967,13 +8993,13 @@
       <c r="D14" t="s">
         <v>259</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
         <v>261</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="2">
         <v>45747</v>
       </c>
       <c r="H14" t="s">
@@ -8991,13 +9017,13 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>45736</v>
       </c>
-      <c r="R14" s="1">
+      <c r="R14" s="2">
         <v>46101</v>
       </c>
-      <c r="S14" s="1">
+      <c r="S14" s="2">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
@@ -9033,70 +9059,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9134,10 +9160,10 @@
       <c r="O2" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>45490</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -9181,10 +9207,10 @@
       <c r="O3" t="s">
         <v>83</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>45618</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -9228,10 +9254,10 @@
       <c r="O4" t="s">
         <v>99</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>45539</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -9275,10 +9301,10 @@
       <c r="O5" t="s">
         <v>100</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>45567</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -9322,10 +9348,10 @@
       <c r="O6" t="s">
         <v>97</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>45568</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -9369,10 +9395,10 @@
       <c r="O7" t="s">
         <v>85</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>45831</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -9416,10 +9442,10 @@
       <c r="O8" t="s">
         <v>105</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45601</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -9463,10 +9489,10 @@
       <c r="O9" t="s">
         <v>94</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45631</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -9510,10 +9536,10 @@
       <c r="O10" t="s">
         <v>91</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>43902</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -9557,10 +9583,10 @@
       <c r="O11" t="s">
         <v>101</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>44736</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -9604,10 +9630,10 @@
       <c r="O12" t="s">
         <v>84</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>45776</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -9651,10 +9677,10 @@
       <c r="O13" t="s">
         <v>82</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>45772</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -9698,10 +9724,10 @@
       <c r="O14" t="s">
         <v>102</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45000</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -9745,7 +9771,7 @@
       <c r="O15" t="s">
         <v>96</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -9786,7 +9812,7 @@
       <c r="O16" t="s">
         <v>92</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -9827,10 +9853,10 @@
       <c r="O17" t="s">
         <v>95</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45371</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -9874,10 +9900,10 @@
       <c r="O18" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>46001</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -9921,10 +9947,10 @@
       <c r="O19" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45436</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -9968,10 +9994,10 @@
       <c r="O20" t="s">
         <v>98</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>44372</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -10015,10 +10041,10 @@
       <c r="O21" t="s">
         <v>107</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>44362</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -10062,10 +10088,10 @@
       <c r="O22" t="s">
         <v>88</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -10103,10 +10129,10 @@
       <c r="O23" t="s">
         <v>354</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>40044</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -10118,7 +10144,7 @@
       <c r="T23" t="s">
         <v>394</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>45775</v>
       </c>
     </row>
@@ -10156,10 +10182,10 @@
       <c r="O24" t="s">
         <v>82</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>43549</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -10171,7 +10197,7 @@
       <c r="T24" t="s">
         <v>395</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -10209,10 +10235,10 @@
       <c r="O25" t="s">
         <v>88</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45447</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -10224,7 +10250,7 @@
       <c r="T25" t="s">
         <v>396</v>
       </c>
-      <c r="U25" s="1">
+      <c r="U25" s="2">
         <v>45937</v>
       </c>
     </row>
@@ -10262,10 +10288,10 @@
       <c r="O26" t="s">
         <v>102</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>44485</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -10277,7 +10303,7 @@
       <c r="T26" t="s">
         <v>397</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>45580</v>
       </c>
     </row>
@@ -10315,10 +10341,10 @@
       <c r="O27" t="s">
         <v>88</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45420</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -10330,7 +10356,7 @@
       <c r="T27" t="s">
         <v>398</v>
       </c>
-      <c r="U27" s="1">
+      <c r="U27" s="2">
         <v>45588</v>
       </c>
     </row>
@@ -10368,10 +10394,10 @@
       <c r="O28" t="s">
         <v>103</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>44369</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -10383,7 +10409,7 @@
       <c r="T28" t="s">
         <v>399</v>
       </c>
-      <c r="U28" s="1">
+      <c r="U28" s="2">
         <v>45831</v>
       </c>
     </row>
@@ -10421,10 +10447,10 @@
       <c r="O29" t="s">
         <v>100</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44652</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -10436,7 +10462,7 @@
       <c r="T29" t="s">
         <v>400</v>
       </c>
-      <c r="U29" s="1">
+      <c r="U29" s="2">
         <v>45734</v>
       </c>
     </row>
@@ -10468,7 +10494,7 @@
       <c r="T30" t="s">
         <v>401</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10500,7 +10526,7 @@
       <c r="T31" t="s">
         <v>402</v>
       </c>
-      <c r="U31" s="1">
+      <c r="U31" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10532,7 +10558,7 @@
       <c r="T32" t="s">
         <v>403</v>
       </c>
-      <c r="U32" s="1">
+      <c r="U32" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10570,10 +10596,10 @@
       <c r="O33" t="s">
         <v>92</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>43762</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -10585,7 +10611,7 @@
       <c r="T33" t="s">
         <v>382</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="2">
         <v>46037</v>
       </c>
     </row>
@@ -10623,16 +10649,16 @@
       <c r="O34" t="s">
         <v>355</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>40071</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>149</v>
       </c>
-      <c r="U34" s="1">
+      <c r="U34" s="2">
         <v>41023</v>
       </c>
     </row>
@@ -10664,10 +10690,10 @@
       <c r="O35" t="s">
         <v>89</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>44784</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -10676,7 +10702,7 @@
       <c r="S35" t="s">
         <v>149</v>
       </c>
-      <c r="U35" s="1">
+      <c r="U35" s="2">
         <v>45259</v>
       </c>
     </row>
@@ -10714,10 +10740,10 @@
       <c r="O36" t="s">
         <v>93</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45103</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -10726,7 +10752,7 @@
       <c r="S36" t="s">
         <v>149</v>
       </c>
-      <c r="U36" s="1">
+      <c r="U36" s="2">
         <v>46000</v>
       </c>
     </row>
@@ -10790,10 +10816,10 @@
       <c r="O38" t="s">
         <v>98</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>38511</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -10802,7 +10828,7 @@
       <c r="S38" t="s">
         <v>149</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="2">
         <v>39068</v>
       </c>
     </row>
@@ -10840,10 +10866,10 @@
       <c r="O39" t="s">
         <v>105</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>39006</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -10855,7 +10881,7 @@
       <c r="T39" t="s">
         <v>404</v>
       </c>
-      <c r="U39" s="1">
+      <c r="U39" s="2">
         <v>40568</v>
       </c>
     </row>
@@ -10887,10 +10913,10 @@
       <c r="O40" t="s">
         <v>102</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>40836</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -10902,7 +10928,7 @@
       <c r="T40" t="s">
         <v>405</v>
       </c>
-      <c r="U40" s="1">
+      <c r="U40" s="2">
         <v>42270</v>
       </c>
     </row>
@@ -10940,10 +10966,10 @@
       <c r="O41" t="s">
         <v>97</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P41" s="2">
         <v>42940</v>
       </c>
-      <c r="Q41" s="1">
+      <c r="Q41" s="2">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -10955,7 +10981,7 @@
       <c r="T41" t="s">
         <v>406</v>
       </c>
-      <c r="U41" s="1">
+      <c r="U41" s="2">
         <v>44148</v>
       </c>
     </row>
@@ -10993,10 +11019,10 @@
       <c r="O42" t="s">
         <v>84</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P42" s="2">
         <v>43696</v>
       </c>
-      <c r="Q42" s="1">
+      <c r="Q42" s="2">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -11008,7 +11034,7 @@
       <c r="T42" t="s">
         <v>407</v>
       </c>
-      <c r="U42" s="1">
+      <c r="U42" s="2">
         <v>43185</v>
       </c>
     </row>
@@ -11046,10 +11072,10 @@
       <c r="O43" t="s">
         <v>86</v>
       </c>
-      <c r="P43" s="1">
+      <c r="P43" s="2">
         <v>43544</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="Q43" s="2">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -11061,7 +11087,7 @@
       <c r="T43" t="s">
         <v>408</v>
       </c>
-      <c r="U43" s="1">
+      <c r="U43" s="2">
         <v>42850</v>
       </c>
     </row>
@@ -11099,10 +11125,10 @@
       <c r="O44" t="s">
         <v>99</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P44" s="2">
         <v>45076</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="Q44" s="2">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -11114,7 +11140,7 @@
       <c r="T44" t="s">
         <v>409</v>
       </c>
-      <c r="U44" s="1">
+      <c r="U44" s="2">
         <v>44404</v>
       </c>
     </row>
@@ -11152,10 +11178,10 @@
       <c r="O45" t="s">
         <v>83</v>
       </c>
-      <c r="P45" s="1">
+      <c r="P45" s="2">
         <v>42963</v>
       </c>
-      <c r="Q45" s="1">
+      <c r="Q45" s="2">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -11167,7 +11193,7 @@
       <c r="T45" t="s">
         <v>410</v>
       </c>
-      <c r="U45" s="1">
+      <c r="U45" s="2">
         <v>42698</v>
       </c>
     </row>
@@ -11205,10 +11231,10 @@
       <c r="O46" t="s">
         <v>90</v>
       </c>
-      <c r="P46" s="1">
+      <c r="P46" s="2">
         <v>45054</v>
       </c>
-      <c r="Q46" s="1">
+      <c r="Q46" s="2">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -11220,7 +11246,7 @@
       <c r="T46" t="s">
         <v>411</v>
       </c>
-      <c r="U46" s="1">
+      <c r="U46" s="2">
         <v>43941</v>
       </c>
     </row>
@@ -11235,25 +11261,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>416</v>
       </c>
     </row>
@@ -11927,22 +11953,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>422</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1427,16 +1427,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1452,7 +1444,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1460,30 +1452,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1783,70 +1757,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1887,10 +1861,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>41754</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1902,7 +1876,7 @@
       <c r="T2" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="1">
         <v>46170</v>
       </c>
     </row>
@@ -1943,10 +1917,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>44709</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1993,10 +1967,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>44348</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -2040,10 +2014,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>46059</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -2055,7 +2029,7 @@
       <c r="T5" t="s">
         <v>151</v>
       </c>
-      <c r="U5" s="2">
+      <c r="U5" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -2096,10 +2070,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>46149</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -2146,10 +2120,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>43731</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -2161,7 +2135,7 @@
       <c r="T7" t="s">
         <v>152</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U7" s="1">
         <v>43507</v>
       </c>
     </row>
@@ -2202,10 +2176,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45511</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2252,10 +2226,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45716</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2267,7 +2241,7 @@
       <c r="T9" t="s">
         <v>153</v>
       </c>
-      <c r="U9" s="2">
+      <c r="U9" s="1">
         <v>44665</v>
       </c>
     </row>
@@ -2308,10 +2282,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>45064</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2349,10 +2323,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>46135</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2364,7 +2338,7 @@
       <c r="T11" t="s">
         <v>154</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -2402,7 +2376,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2443,10 +2417,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>46199</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2493,10 +2467,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45667</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2508,7 +2482,7 @@
       <c r="T14" t="s">
         <v>155</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" s="1">
         <v>46072</v>
       </c>
     </row>
@@ -2549,10 +2523,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>46064</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="1">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2599,10 +2573,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>44285</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="1">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2614,7 +2588,7 @@
       <c r="T16" t="s">
         <v>156</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2655,10 +2629,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45922</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2705,10 +2679,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>45930</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2720,7 +2694,7 @@
       <c r="T18" t="s">
         <v>157</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" s="1">
         <v>46198</v>
       </c>
     </row>
@@ -2761,10 +2735,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45524</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2776,7 +2750,7 @@
       <c r="T19" t="s">
         <v>124</v>
       </c>
-      <c r="U19" s="2">
+      <c r="U19" s="1">
         <v>46153</v>
       </c>
     </row>
@@ -2817,10 +2791,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>45026</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2832,7 +2806,7 @@
       <c r="T20" t="s">
         <v>158</v>
       </c>
-      <c r="U20" s="2">
+      <c r="U20" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2873,10 +2847,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>45159</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2888,7 +2862,7 @@
       <c r="T21" t="s">
         <v>126</v>
       </c>
-      <c r="U21" s="2">
+      <c r="U21" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2929,10 +2903,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2944,7 +2918,7 @@
       <c r="T22" t="s">
         <v>159</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" s="1">
         <v>45995</v>
       </c>
     </row>
@@ -2982,10 +2956,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>45713</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -2994,7 +2968,7 @@
       <c r="S23" t="s">
         <v>149</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -3035,10 +3009,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>46062</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>46220</v>
       </c>
       <c r="R24" t="s">
@@ -3047,7 +3021,7 @@
       <c r="S24" t="s">
         <v>149</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -3088,10 +3062,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45079</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -3138,10 +3112,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>41346</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -3153,7 +3127,7 @@
       <c r="T26" t="s">
         <v>160</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>46150</v>
       </c>
     </row>
@@ -3194,10 +3168,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45579</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3244,10 +3218,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>46171</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3294,10 +3268,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44320</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3344,10 +3318,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="1">
         <v>42661</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="1">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3359,7 +3333,7 @@
       <c r="T30" t="s">
         <v>161</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>45358</v>
       </c>
     </row>
@@ -3400,10 +3374,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="1">
         <v>46220</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="1">
         <v>46220</v>
       </c>
       <c r="R31" t="s">
@@ -3450,10 +3424,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="1">
         <v>43797</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="1">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3500,10 +3474,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>42810</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3515,7 +3489,7 @@
       <c r="T33" t="s">
         <v>162</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>43802</v>
       </c>
     </row>
@@ -3556,10 +3530,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>45070</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>44910</v>
       </c>
       <c r="R34" t="s">
@@ -3606,10 +3580,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>43250</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3656,10 +3630,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45841</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3706,10 +3680,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="2">
+      <c r="P37" s="1">
         <v>45105</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="1">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3721,7 +3695,7 @@
       <c r="T37" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="2">
+      <c r="U37" s="1">
         <v>46184</v>
       </c>
     </row>
@@ -3762,10 +3736,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>45636</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>46219</v>
       </c>
       <c r="S38" t="s">
@@ -3774,7 +3748,7 @@
       <c r="T38" t="s">
         <v>164</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>45351</v>
       </c>
     </row>
@@ -3815,10 +3789,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>45831</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3862,10 +3836,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>44287</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3886,22 +3860,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>167</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>169</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>170</v>
       </c>
     </row>
@@ -8112,91 +8086,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>233</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>235</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>236</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>237</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>238</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>239</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>240</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>241</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>242</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>243</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>244</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>245</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>246</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>247</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>248</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>249</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>250</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>251</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>252</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>253</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>254</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>255</v>
       </c>
     </row>
@@ -8210,13 +8184,13 @@
       <c r="D2" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
         <v>261</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>45492</v>
       </c>
       <c r="H2" t="s">
@@ -8234,13 +8208,13 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45491</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="1">
         <v>45528</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="1">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
@@ -8278,13 +8252,13 @@
       <c r="D3" t="s">
         <v>259</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
         <v>261</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>45631</v>
       </c>
       <c r="H3" t="s">
@@ -8302,13 +8276,13 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45628</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>45632</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
@@ -8343,13 +8317,13 @@
       <c r="D4" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
         <v>261</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>45716</v>
       </c>
       <c r="H4" t="s">
@@ -8367,13 +8341,13 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45716</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <v>45722</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="1">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
@@ -8408,13 +8382,13 @@
       <c r="D5" t="s">
         <v>259</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
         <v>261</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>45728</v>
       </c>
       <c r="H5" t="s">
@@ -8432,13 +8406,13 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45722</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <v>45782</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="1">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
@@ -8476,13 +8450,13 @@
       <c r="D6" t="s">
         <v>259</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
         <v>261</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>45755</v>
       </c>
       <c r="H6" t="s">
@@ -8500,13 +8474,13 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45728</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="1">
         <v>45734</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="1">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
@@ -8544,7 +8518,7 @@
       <c r="D7" t="s">
         <v>260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
@@ -8565,10 +8539,10 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45772</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="1">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
@@ -8606,7 +8580,7 @@
       <c r="D8" t="s">
         <v>260</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
@@ -8627,10 +8601,10 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>45762</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="1">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
@@ -8668,7 +8642,7 @@
       <c r="D9" t="s">
         <v>260</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
@@ -8689,10 +8663,10 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45763</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="1">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
@@ -8730,13 +8704,13 @@
       <c r="D10" t="s">
         <v>259</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
         <v>261</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>45755</v>
       </c>
       <c r="H10" t="s">
@@ -8754,13 +8728,13 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45754</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="1">
         <v>45849</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="1">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
@@ -8795,13 +8769,13 @@
       <c r="D11" t="s">
         <v>259</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
         <v>261</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>44973</v>
       </c>
       <c r="H11" t="s">
@@ -8819,13 +8793,13 @@
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44973</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="1">
         <v>45687</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" s="1">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
@@ -8860,13 +8834,13 @@
       <c r="D12" t="s">
         <v>259</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
         <v>261</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>45358</v>
       </c>
       <c r="H12" t="s">
@@ -8884,13 +8858,13 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45358</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="1">
         <v>45517</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12" s="1">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
@@ -8925,13 +8899,13 @@
       <c r="D13" t="s">
         <v>259</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
         <v>261</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>45573</v>
       </c>
       <c r="H13" t="s">
@@ -8949,13 +8923,13 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45572</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="1">
         <v>45572</v>
       </c>
-      <c r="S13" s="2">
+      <c r="S13" s="1">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
@@ -8993,13 +8967,13 @@
       <c r="D14" t="s">
         <v>259</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
         <v>261</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>45747</v>
       </c>
       <c r="H14" t="s">
@@ -9017,13 +8991,13 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>45736</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" s="1">
         <v>46101</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14" s="1">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
@@ -9059,70 +9033,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9160,10 +9134,10 @@
       <c r="O2" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>45490</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -9207,10 +9181,10 @@
       <c r="O3" t="s">
         <v>83</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>45618</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -9254,10 +9228,10 @@
       <c r="O4" t="s">
         <v>99</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>45539</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -9301,10 +9275,10 @@
       <c r="O5" t="s">
         <v>100</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>45567</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -9348,10 +9322,10 @@
       <c r="O6" t="s">
         <v>97</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>45568</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -9395,10 +9369,10 @@
       <c r="O7" t="s">
         <v>85</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>45831</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -9442,10 +9416,10 @@
       <c r="O8" t="s">
         <v>105</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45601</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -9489,10 +9463,10 @@
       <c r="O9" t="s">
         <v>94</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45631</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -9536,10 +9510,10 @@
       <c r="O10" t="s">
         <v>91</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>43902</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -9583,10 +9557,10 @@
       <c r="O11" t="s">
         <v>101</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>44736</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -9630,10 +9604,10 @@
       <c r="O12" t="s">
         <v>84</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>45776</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -9677,10 +9651,10 @@
       <c r="O13" t="s">
         <v>82</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>45772</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -9724,10 +9698,10 @@
       <c r="O14" t="s">
         <v>102</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45000</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -9771,7 +9745,7 @@
       <c r="O15" t="s">
         <v>96</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -9812,7 +9786,7 @@
       <c r="O16" t="s">
         <v>92</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -9853,10 +9827,10 @@
       <c r="O17" t="s">
         <v>95</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45371</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -9900,10 +9874,10 @@
       <c r="O18" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>46001</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -9947,10 +9921,10 @@
       <c r="O19" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45436</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -9994,10 +9968,10 @@
       <c r="O20" t="s">
         <v>98</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>44372</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -10041,10 +10015,10 @@
       <c r="O21" t="s">
         <v>107</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>44362</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -10088,10 +10062,10 @@
       <c r="O22" t="s">
         <v>88</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -10129,10 +10103,10 @@
       <c r="O23" t="s">
         <v>354</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>40044</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -10144,7 +10118,7 @@
       <c r="T23" t="s">
         <v>394</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45775</v>
       </c>
     </row>
@@ -10182,10 +10156,10 @@
       <c r="O24" t="s">
         <v>82</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>43549</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -10197,7 +10171,7 @@
       <c r="T24" t="s">
         <v>395</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -10235,10 +10209,10 @@
       <c r="O25" t="s">
         <v>88</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45447</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -10250,7 +10224,7 @@
       <c r="T25" t="s">
         <v>396</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U25" s="1">
         <v>45937</v>
       </c>
     </row>
@@ -10288,10 +10262,10 @@
       <c r="O26" t="s">
         <v>102</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>44485</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -10303,7 +10277,7 @@
       <c r="T26" t="s">
         <v>397</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>45580</v>
       </c>
     </row>
@@ -10341,10 +10315,10 @@
       <c r="O27" t="s">
         <v>88</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45420</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -10356,7 +10330,7 @@
       <c r="T27" t="s">
         <v>398</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U27" s="1">
         <v>45588</v>
       </c>
     </row>
@@ -10394,10 +10368,10 @@
       <c r="O28" t="s">
         <v>103</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>44369</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -10409,7 +10383,7 @@
       <c r="T28" t="s">
         <v>399</v>
       </c>
-      <c r="U28" s="2">
+      <c r="U28" s="1">
         <v>45831</v>
       </c>
     </row>
@@ -10447,10 +10421,10 @@
       <c r="O29" t="s">
         <v>100</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44652</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -10462,7 +10436,7 @@
       <c r="T29" t="s">
         <v>400</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U29" s="1">
         <v>45734</v>
       </c>
     </row>
@@ -10494,7 +10468,7 @@
       <c r="T30" t="s">
         <v>401</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10526,7 +10500,7 @@
       <c r="T31" t="s">
         <v>402</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10558,7 +10532,7 @@
       <c r="T32" t="s">
         <v>403</v>
       </c>
-      <c r="U32" s="2">
+      <c r="U32" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10596,10 +10570,10 @@
       <c r="O33" t="s">
         <v>92</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>43762</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -10611,7 +10585,7 @@
       <c r="T33" t="s">
         <v>382</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>46037</v>
       </c>
     </row>
@@ -10649,16 +10623,16 @@
       <c r="O34" t="s">
         <v>355</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>40071</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>149</v>
       </c>
-      <c r="U34" s="2">
+      <c r="U34" s="1">
         <v>41023</v>
       </c>
     </row>
@@ -10690,10 +10664,10 @@
       <c r="O35" t="s">
         <v>89</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>44784</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -10702,7 +10676,7 @@
       <c r="S35" t="s">
         <v>149</v>
       </c>
-      <c r="U35" s="2">
+      <c r="U35" s="1">
         <v>45259</v>
       </c>
     </row>
@@ -10740,10 +10714,10 @@
       <c r="O36" t="s">
         <v>93</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45103</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -10752,7 +10726,7 @@
       <c r="S36" t="s">
         <v>149</v>
       </c>
-      <c r="U36" s="2">
+      <c r="U36" s="1">
         <v>46000</v>
       </c>
     </row>
@@ -10816,10 +10790,10 @@
       <c r="O38" t="s">
         <v>98</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>38511</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -10828,7 +10802,7 @@
       <c r="S38" t="s">
         <v>149</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>39068</v>
       </c>
     </row>
@@ -10866,10 +10840,10 @@
       <c r="O39" t="s">
         <v>105</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>39006</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -10881,7 +10855,7 @@
       <c r="T39" t="s">
         <v>404</v>
       </c>
-      <c r="U39" s="2">
+      <c r="U39" s="1">
         <v>40568</v>
       </c>
     </row>
@@ -10913,10 +10887,10 @@
       <c r="O40" t="s">
         <v>102</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>40836</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -10928,7 +10902,7 @@
       <c r="T40" t="s">
         <v>405</v>
       </c>
-      <c r="U40" s="2">
+      <c r="U40" s="1">
         <v>42270</v>
       </c>
     </row>
@@ -10966,10 +10940,10 @@
       <c r="O41" t="s">
         <v>97</v>
       </c>
-      <c r="P41" s="2">
+      <c r="P41" s="1">
         <v>42940</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="1">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -10981,7 +10955,7 @@
       <c r="T41" t="s">
         <v>406</v>
       </c>
-      <c r="U41" s="2">
+      <c r="U41" s="1">
         <v>44148</v>
       </c>
     </row>
@@ -11019,10 +10993,10 @@
       <c r="O42" t="s">
         <v>84</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="1">
         <v>43696</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="1">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -11034,7 +11008,7 @@
       <c r="T42" t="s">
         <v>407</v>
       </c>
-      <c r="U42" s="2">
+      <c r="U42" s="1">
         <v>43185</v>
       </c>
     </row>
@@ -11072,10 +11046,10 @@
       <c r="O43" t="s">
         <v>86</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="1">
         <v>43544</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="1">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -11087,7 +11061,7 @@
       <c r="T43" t="s">
         <v>408</v>
       </c>
-      <c r="U43" s="2">
+      <c r="U43" s="1">
         <v>42850</v>
       </c>
     </row>
@@ -11125,10 +11099,10 @@
       <c r="O44" t="s">
         <v>99</v>
       </c>
-      <c r="P44" s="2">
+      <c r="P44" s="1">
         <v>45076</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="1">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -11140,7 +11114,7 @@
       <c r="T44" t="s">
         <v>409</v>
       </c>
-      <c r="U44" s="2">
+      <c r="U44" s="1">
         <v>44404</v>
       </c>
     </row>
@@ -11178,10 +11152,10 @@
       <c r="O45" t="s">
         <v>83</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="1">
         <v>42963</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="1">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -11193,7 +11167,7 @@
       <c r="T45" t="s">
         <v>410</v>
       </c>
-      <c r="U45" s="2">
+      <c r="U45" s="1">
         <v>42698</v>
       </c>
     </row>
@@ -11231,10 +11205,10 @@
       <c r="O46" t="s">
         <v>90</v>
       </c>
-      <c r="P46" s="2">
+      <c r="P46" s="1">
         <v>45054</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="1">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -11246,7 +11220,7 @@
       <c r="T46" t="s">
         <v>411</v>
       </c>
-      <c r="U46" s="2">
+      <c r="U46" s="1">
         <v>43941</v>
       </c>
     </row>
@@ -11261,25 +11235,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>412</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>413</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>414</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>415</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>416</v>
       </c>
     </row>
@@ -11953,22 +11927,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>417</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>418</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>419</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>420</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>421</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>422</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -537,39 +537,39 @@
     <t>1.0</t>
   </si>
   <si>
+    <t>NÃO HÁ AT</t>
+  </si>
+  <si>
     <t>TBO</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>NÃO HÁ AT</t>
+    <t>17.3</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>HSI</t>
+  </si>
+  <si>
+    <t>16.3</t>
+  </si>
+  <si>
+    <t>34.2</t>
+  </si>
+  <si>
+    <t>22.0</t>
+  </si>
+  <si>
+    <t>27.1</t>
   </si>
   <si>
     <t>vazamento de oleo pelo flange</t>
   </si>
   <si>
-    <t>17.3</t>
-  </si>
-  <si>
-    <t>16.0</t>
-  </si>
-  <si>
-    <t>HSI</t>
-  </si>
-  <si>
-    <t>16.3</t>
-  </si>
-  <si>
-    <t>34.2</t>
-  </si>
-  <si>
-    <t>22.0</t>
-  </si>
-  <si>
-    <t>27.1</t>
-  </si>
-  <si>
     <t>HÁ AT</t>
   </si>
   <si>
@@ -591,34 +591,34 @@
     <t>2.726773384</t>
   </si>
   <si>
+    <t>57.1</t>
+  </si>
+  <si>
+    <t>47.0</t>
+  </si>
+  <si>
+    <t>4.906536528</t>
+  </si>
+  <si>
+    <t>#N/A</t>
+  </si>
+  <si>
+    <t>Rachadura na CT DISK, vai recolher</t>
+  </si>
+  <si>
+    <t>19.2</t>
+  </si>
+  <si>
+    <t>MOTOR EM HSI NO OPERADOR, 17/07/2026</t>
+  </si>
+  <si>
     <t>28.1</t>
   </si>
   <si>
     <t>27.0</t>
   </si>
   <si>
-    <t>9.574774775</t>
-  </si>
-  <si>
-    <t>#N/A</t>
-  </si>
-  <si>
-    <t>Rachadura na CT DISK, vai recolher</t>
-  </si>
-  <si>
-    <t>19.2</t>
-  </si>
-  <si>
-    <t>MOTOR EM HSI NO OPERADOR, 17/07/2026</t>
-  </si>
-  <si>
-    <t>57.1</t>
-  </si>
-  <si>
-    <t>47.0</t>
-  </si>
-  <si>
-    <t>4.906536528</t>
+    <t>12.68828829</t>
   </si>
   <si>
     <t>6.081238361</t>
@@ -660,7 +660,7 @@
     <t>17.63967357</t>
   </si>
   <si>
-    <t>22.94847203</t>
+    <t>22.95015112</t>
   </si>
   <si>
     <t>Motor novo, não atingiu performance (CAIXA DE ACESSÓRIOS PESADA) 27/05</t>
@@ -669,25 +669,19 @@
     <t>recolhido 23/04. adiantou o tbo</t>
   </si>
   <si>
-    <t>54.82962963</t>
+    <t>54.9</t>
   </si>
   <si>
     <t>30.17519472</t>
   </si>
   <si>
-    <t>AT 313000000805 extensão até 4200h TBO</t>
+    <t>AT 386000001002  500H
+Motor já está no GLOG-CO</t>
   </si>
   <si>
     <t>AT 313000000695
 4450H
 Motor substituto já em MN</t>
-  </si>
-  <si>
-    <t>AT 386000001002  500H
-Motor já está no GLOG-CO</t>
-  </si>
-  <si>
-    <t>Possui AT 313000000812 de 200H, porém foi encontrada  uma trinca e o housing será recolhido.</t>
   </si>
   <si>
     <t>Fez o 1° HSI COM 1941H, O PROX SERÁ COM 3441.
@@ -696,7 +690,13 @@
 motor POSSUI TSO DE 2.941:00H, RESTANDO 500:15H . vai casar exatamente com o HSI 3.441,25</t>
   </si>
   <si>
+    <t>AT 313000000805 extensão até 4200h TBO</t>
+  </si>
+  <si>
     <t>AT 685000002046, CONCEDEU MAIS 400H</t>
+  </si>
+  <si>
+    <t>Possui AT 313000000812 de 200H, porém foi encontrada  uma trinca e o housing será recolhido.</t>
   </si>
   <si>
     <t>PREVISÃO PARA O PRÓXIMO HSI COM 4665:30 TSO
@@ -2364,6 +2364,9 @@
       <c r="J12" t="s">
         <v>81</v>
       </c>
+      <c r="K12">
+        <v>100</v>
+      </c>
       <c r="L12">
         <v>7592.92</v>
       </c>
@@ -2404,6 +2407,9 @@
       </c>
       <c r="J13" t="s">
         <v>81</v>
+      </c>
+      <c r="K13">
+        <v>100</v>
       </c>
       <c r="L13">
         <v>4526.42</v>
@@ -3881,10 +3887,10 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B2">
-        <v>2736</v>
+        <v>2743</v>
       </c>
       <c r="C2">
         <v>2025</v>
@@ -3898,10 +3904,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B3">
-        <v>2736</v>
+        <v>2743</v>
       </c>
       <c r="C3">
         <v>2025</v>
@@ -3915,10 +3921,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B4">
-        <v>2736</v>
+        <v>2743</v>
       </c>
       <c r="C4">
         <v>2025</v>
@@ -3932,39 +3938,39 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B5">
-        <v>2736</v>
+        <v>2743</v>
       </c>
       <c r="C5">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>172</v>
       </c>
-      <c r="F5" t="s">
-        <v>218</v>
-      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" t="b">
-        <v>0</v>
+        <v>74</v>
+      </c>
+      <c r="B6">
+        <v>2743</v>
       </c>
       <c r="C6">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
         <v>173</v>
+      </c>
+      <c r="F6" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3978,10 +3984,10 @@
         <v>2025</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3995,10 +4001,10 @@
         <v>2025</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4012,10 +4018,10 @@
         <v>2025</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4029,10 +4035,10 @@
         <v>2025</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4046,7 +4052,7 @@
         <v>2025</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
         <v>174</v>
@@ -4060,47 +4066,47 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>172</v>
       </c>
-      <c r="F12" t="s">
-        <v>219</v>
-      </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13">
-        <v>2743</v>
+        <v>61</v>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="F13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B14">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="C14">
         <v>2025</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
         <v>171</v>
@@ -4108,16 +4114,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B15">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="C15">
         <v>2025</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="s">
         <v>171</v>
@@ -4125,104 +4131,104 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B16">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="C16">
         <v>2025</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B17">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="C17">
         <v>2026</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>172</v>
-      </c>
-      <c r="F17" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B18">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C18">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B19">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C19">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>173</v>
+        <v>177</v>
+      </c>
+      <c r="F19" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B20">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C20">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="B21">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C21">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E21" t="s">
         <v>173</v>
@@ -4230,220 +4236,217 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B22">
-        <v>2741</v>
+        <v>2709</v>
       </c>
       <c r="C22">
         <v>2025</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B23">
-        <v>2741</v>
+        <v>2709</v>
       </c>
       <c r="C23">
         <v>2025</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B24">
-        <v>2741</v>
+        <v>2709</v>
       </c>
       <c r="C24">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B25">
-        <v>2741</v>
+        <v>2709</v>
       </c>
       <c r="C25">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
         <v>172</v>
       </c>
-      <c r="F25" t="s">
-        <v>221</v>
-      </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B26">
-        <v>2740</v>
+        <v>2709</v>
       </c>
       <c r="C26">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B27">
-        <v>2740</v>
+        <v>2709</v>
       </c>
       <c r="C27">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B28">
-        <v>2740</v>
+        <v>2709</v>
       </c>
       <c r="C28">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B29">
-        <v>2740</v>
+        <v>2709</v>
       </c>
       <c r="C29">
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B30">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="C30">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B31">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="C31">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>178</v>
-      </c>
-      <c r="F31" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B32">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="C32">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B33">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="C33">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="F33" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B34">
-        <v>2709</v>
+        <v>2722</v>
       </c>
       <c r="C34">
         <v>2025</v>
@@ -4457,10 +4460,10 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B35">
-        <v>2709</v>
+        <v>2722</v>
       </c>
       <c r="C35">
         <v>2025</v>
@@ -4474,10 +4477,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B36">
-        <v>2709</v>
+        <v>2722</v>
       </c>
       <c r="C36">
         <v>2025</v>
@@ -4491,10 +4494,10 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B37">
-        <v>2709</v>
+        <v>2722</v>
       </c>
       <c r="C37">
         <v>2025</v>
@@ -4503,160 +4506,163 @@
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B38">
-        <v>2709</v>
+        <v>2722</v>
       </c>
       <c r="C38">
         <v>2026</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>180</v>
+        <v>173</v>
+      </c>
+      <c r="F38" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B39">
-        <v>2709</v>
+        <v>2741</v>
       </c>
       <c r="C39">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B40">
-        <v>2709</v>
+        <v>2741</v>
       </c>
       <c r="C40">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D40">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E40" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B41">
-        <v>2709</v>
+        <v>2741</v>
       </c>
       <c r="C41">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D41">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B42">
-        <v>2722</v>
+        <v>2741</v>
       </c>
       <c r="C42">
         <v>2025</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B43">
-        <v>2722</v>
+        <v>2741</v>
       </c>
       <c r="C43">
         <v>2025</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B44">
-        <v>2722</v>
+        <v>2741</v>
       </c>
       <c r="C44">
         <v>2025</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B45">
-        <v>2722</v>
+        <v>2741</v>
       </c>
       <c r="C45">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B46">
-        <v>2722</v>
+        <v>2741</v>
       </c>
       <c r="C46">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="D46">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" t="s">
         <v>223</v>
@@ -4832,7 +4838,7 @@
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -4900,7 +4906,7 @@
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F60" t="s">
         <v>225</v>
@@ -4920,7 +4926,7 @@
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -5022,15 +5028,15 @@
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B68">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="C68">
         <v>2025</v>
@@ -5039,15 +5045,15 @@
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B69">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="C69">
         <v>2025</v>
@@ -5056,15 +5062,15 @@
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B70">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="C70">
         <v>2025</v>
@@ -5073,126 +5079,126 @@
         <v>3</v>
       </c>
       <c r="E70" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B71">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="C71">
         <v>2025</v>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B72">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="C72">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D72">
         <v>5</v>
       </c>
       <c r="E72" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B73">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="C73">
         <v>2026</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E73" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B74">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="C74">
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E74" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B75">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="C75">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="D75">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E75" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>46</v>
-      </c>
-      <c r="B76">
-        <v>2742</v>
+        <v>64</v>
+      </c>
+      <c r="B76" t="b">
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="D76">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>46</v>
-      </c>
-      <c r="B77">
-        <v>2742</v>
+        <v>64</v>
+      </c>
+      <c r="B77" t="b">
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="D77">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -5206,7 +5212,7 @@
         <v>2025</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" t="s">
         <v>171</v>
@@ -5223,10 +5229,10 @@
         <v>2025</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -5240,10 +5246,10 @@
         <v>2025</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -5254,13 +5260,13 @@
         <v>0</v>
       </c>
       <c r="C81">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D81">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E81" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -5271,47 +5277,47 @@
         <v>0</v>
       </c>
       <c r="C82">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E82" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B83" t="b">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D83">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B84" t="b">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D84">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5325,7 +5331,7 @@
         <v>2025</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E85" t="s">
         <v>171</v>
@@ -5342,10 +5348,10 @@
         <v>2025</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E86" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5356,13 +5362,13 @@
         <v>0</v>
       </c>
       <c r="C87">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E87" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -5373,13 +5379,16 @@
         <v>0</v>
       </c>
       <c r="C88">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E88" t="s">
-        <v>174</v>
+        <v>177</v>
+      </c>
+      <c r="F88" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -5393,10 +5402,10 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E89" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -5410,183 +5419,180 @@
         <v>2026</v>
       </c>
       <c r="D90">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
-        <v>178</v>
-      </c>
-      <c r="F90" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>78</v>
-      </c>
-      <c r="B91" t="b">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="B91">
+        <v>2742</v>
       </c>
       <c r="C91">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D91">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>78</v>
-      </c>
-      <c r="B92" t="b">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="B92">
+        <v>2742</v>
       </c>
       <c r="C92">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D92">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E92" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B93">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C93">
         <v>2025</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E93" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B94">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C94">
         <v>2025</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B95">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C95">
         <v>2025</v>
       </c>
       <c r="D95">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E95" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B96">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C96">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E96" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B97">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C97">
         <v>2026</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E97" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B98">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C98">
         <v>2026</v>
       </c>
       <c r="D98">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E98" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B99">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C99">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="D99">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B100">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C100">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="D100">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -5654,7 +5660,7 @@
         <v>5</v>
       </c>
       <c r="E104" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5671,7 +5677,7 @@
         <v>8</v>
       </c>
       <c r="E105" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5688,7 +5694,7 @@
         <v>10</v>
       </c>
       <c r="E106" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5722,7 +5728,7 @@
         <v>7</v>
       </c>
       <c r="E108" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5790,7 +5796,7 @@
         <v>4</v>
       </c>
       <c r="E112" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5807,7 +5813,7 @@
         <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5824,7 +5830,7 @@
         <v>10</v>
       </c>
       <c r="E114" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5858,7 +5864,7 @@
         <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5926,7 +5932,7 @@
         <v>10</v>
       </c>
       <c r="E120" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5994,7 +6000,7 @@
         <v>1</v>
       </c>
       <c r="E124" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -6011,7 +6017,7 @@
         <v>4</v>
       </c>
       <c r="E125" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -6028,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -6045,7 +6051,7 @@
         <v>2</v>
       </c>
       <c r="E127" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -6062,7 +6068,7 @@
         <v>3</v>
       </c>
       <c r="E128" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -6079,7 +6085,7 @@
         <v>4</v>
       </c>
       <c r="E129" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -6096,7 +6102,7 @@
         <v>5</v>
       </c>
       <c r="E130" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -6147,7 +6153,7 @@
         <v>6</v>
       </c>
       <c r="E133" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -6269,7 +6275,7 @@
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F140" t="s">
         <v>228</v>
@@ -6289,7 +6295,7 @@
         <v>2</v>
       </c>
       <c r="E141" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6306,7 +6312,7 @@
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -6323,7 +6329,7 @@
         <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6340,7 +6346,7 @@
         <v>3</v>
       </c>
       <c r="E144" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -6357,7 +6363,7 @@
         <v>4</v>
       </c>
       <c r="E145" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -6374,7 +6380,7 @@
         <v>5</v>
       </c>
       <c r="E146" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -6391,7 +6397,7 @@
         <v>10</v>
       </c>
       <c r="E147" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -6425,7 +6431,7 @@
         <v>8</v>
       </c>
       <c r="E149" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -6493,7 +6499,7 @@
         <v>10</v>
       </c>
       <c r="E153" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -6561,7 +6567,7 @@
         <v>6</v>
       </c>
       <c r="E157" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -6578,7 +6584,7 @@
         <v>1</v>
       </c>
       <c r="E158" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -6595,7 +6601,7 @@
         <v>2</v>
       </c>
       <c r="E159" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -6612,7 +6618,7 @@
         <v>3</v>
       </c>
       <c r="E160" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -6629,7 +6635,7 @@
         <v>4</v>
       </c>
       <c r="E161" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -6646,7 +6652,7 @@
         <v>5</v>
       </c>
       <c r="E162" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -6680,7 +6686,7 @@
         <v>12</v>
       </c>
       <c r="E164" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -6697,7 +6703,7 @@
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -6731,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="E167" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -6748,7 +6754,7 @@
         <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -6765,7 +6771,7 @@
         <v>3</v>
       </c>
       <c r="E169" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -6782,7 +6788,7 @@
         <v>4</v>
       </c>
       <c r="E170" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -6799,7 +6805,7 @@
         <v>5</v>
       </c>
       <c r="E171" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -6816,7 +6822,7 @@
         <v>1</v>
       </c>
       <c r="E172" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -6833,7 +6839,7 @@
         <v>2</v>
       </c>
       <c r="E173" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -6850,7 +6856,7 @@
         <v>3</v>
       </c>
       <c r="E174" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -6867,7 +6873,7 @@
         <v>4</v>
       </c>
       <c r="E175" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -6884,7 +6890,7 @@
         <v>5</v>
       </c>
       <c r="E176" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -6952,7 +6958,7 @@
         <v>8</v>
       </c>
       <c r="E180" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F180" t="s">
         <v>229</v>
@@ -7006,7 +7012,7 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -7023,7 +7029,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -7040,7 +7046,7 @@
         <v>3</v>
       </c>
       <c r="E185" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -7057,7 +7063,7 @@
         <v>4</v>
       </c>
       <c r="E186" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -7074,7 +7080,7 @@
         <v>5</v>
       </c>
       <c r="E187" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -7108,7 +7114,7 @@
         <v>3</v>
       </c>
       <c r="E189" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -7125,7 +7131,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -7142,7 +7148,7 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -7159,7 +7165,7 @@
         <v>3</v>
       </c>
       <c r="E192" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -7176,7 +7182,7 @@
         <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -7193,7 +7199,7 @@
         <v>5</v>
       </c>
       <c r="E194" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -7210,7 +7216,7 @@
         <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -7227,7 +7233,7 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -7244,7 +7250,7 @@
         <v>3</v>
       </c>
       <c r="E197" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -7261,7 +7267,7 @@
         <v>4</v>
       </c>
       <c r="E198" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -7278,7 +7284,7 @@
         <v>5</v>
       </c>
       <c r="E199" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -7295,7 +7301,7 @@
         <v>8</v>
       </c>
       <c r="E200" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F200" t="s">
         <v>230</v>
@@ -7332,7 +7338,7 @@
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F202" t="s">
         <v>230</v>
@@ -7454,7 +7460,7 @@
         <v>8</v>
       </c>
       <c r="E209" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -7471,7 +7477,7 @@
         <v>9</v>
       </c>
       <c r="E210" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -7556,7 +7562,7 @@
         <v>2</v>
       </c>
       <c r="E215" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -7590,7 +7596,7 @@
         <v>8</v>
       </c>
       <c r="E217" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F217" t="s">
         <v>231</v>
@@ -7610,7 +7616,7 @@
         <v>9</v>
       </c>
       <c r="E218" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F218" t="s">
         <v>231</v>
@@ -7630,7 +7636,7 @@
         <v>1</v>
       </c>
       <c r="E219" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -7647,7 +7653,7 @@
         <v>2</v>
       </c>
       <c r="E220" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -7664,7 +7670,7 @@
         <v>3</v>
       </c>
       <c r="E221" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -7681,7 +7687,7 @@
         <v>4</v>
       </c>
       <c r="E222" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -7698,7 +7704,7 @@
         <v>5</v>
       </c>
       <c r="E223" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -7715,7 +7721,7 @@
         <v>1</v>
       </c>
       <c r="E224" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -7732,7 +7738,7 @@
         <v>2</v>
       </c>
       <c r="E225" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -7749,7 +7755,7 @@
         <v>3</v>
       </c>
       <c r="E226" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -7766,7 +7772,7 @@
         <v>4</v>
       </c>
       <c r="E227" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -7783,7 +7789,7 @@
         <v>5</v>
       </c>
       <c r="E228" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -7800,7 +7806,7 @@
         <v>10</v>
       </c>
       <c r="E229" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -7834,7 +7840,7 @@
         <v>10</v>
       </c>
       <c r="E231" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -7851,7 +7857,7 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -7868,7 +7874,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -7885,7 +7891,7 @@
         <v>3</v>
       </c>
       <c r="E234" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -7902,7 +7908,7 @@
         <v>4</v>
       </c>
       <c r="E235" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -7919,7 +7925,7 @@
         <v>5</v>
       </c>
       <c r="E236" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -7987,7 +7993,7 @@
         <v>10</v>
       </c>
       <c r="E240" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -8004,7 +8010,7 @@
         <v>1</v>
       </c>
       <c r="E241" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -8021,7 +8027,7 @@
         <v>2</v>
       </c>
       <c r="E242" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -8038,7 +8044,7 @@
         <v>3</v>
       </c>
       <c r="E243" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -8055,7 +8061,7 @@
         <v>4</v>
       </c>
       <c r="E244" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -8072,7 +8078,7 @@
         <v>5</v>
       </c>
       <c r="E245" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -11259,25 +11265,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B2">
-        <v>2736</v>
+        <v>2743</v>
       </c>
       <c r="C2">
-        <v>3992.33</v>
+        <v>4412.92</v>
       </c>
       <c r="D2">
-        <v>207.6666667</v>
+        <v>87.08333333</v>
       </c>
       <c r="E2">
-        <v>55.52851064</v>
+        <v>95.14042553</v>
       </c>
       <c r="F2">
-        <v>260.984</v>
+        <v>447.16</v>
       </c>
       <c r="G2">
-        <v>3.739820576</v>
+        <v>0.9153136834</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -11293,62 +11299,62 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B4">
-        <v>2743</v>
+        <v>2740</v>
       </c>
       <c r="C4">
-        <v>4412.92</v>
+        <v>3301.75</v>
       </c>
       <c r="D4">
-        <v>87.08333333</v>
+        <v>139.25</v>
       </c>
       <c r="E4">
-        <v>95.14042553</v>
+        <v>55.52851064</v>
       </c>
       <c r="F4">
-        <v>447.16</v>
+        <v>260.984</v>
       </c>
       <c r="G4">
-        <v>0.9153136834</v>
+        <v>2.50772078</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B5">
-        <v>2741</v>
+        <v>2709</v>
       </c>
       <c r="C5">
-        <v>3886.67</v>
+        <v>2755.25</v>
       </c>
       <c r="D5">
-        <v>313.3333333</v>
+        <v>147.75</v>
       </c>
       <c r="E5">
-        <v>55.52851064</v>
+        <v>51.37446809</v>
       </c>
       <c r="F5">
-        <v>260.984</v>
+        <v>241.46</v>
       </c>
       <c r="G5">
-        <v>5.642746937</v>
+        <v>2.875942185</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="B6">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="C6">
-        <v>3301.75</v>
+        <v>3992.33</v>
       </c>
       <c r="D6">
-        <v>139.25</v>
+        <v>207.6666667</v>
       </c>
       <c r="E6">
         <v>55.52851064</v>
@@ -11357,53 +11363,53 @@
         <v>260.984</v>
       </c>
       <c r="G6">
-        <v>2.50772078</v>
+        <v>3.739820576</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B7">
-        <v>2709</v>
+        <v>2722</v>
       </c>
       <c r="C7">
-        <v>2755.25</v>
+        <v>4158.42</v>
       </c>
       <c r="D7">
-        <v>147.75</v>
+        <v>241.5833333</v>
       </c>
       <c r="E7">
-        <v>51.37446809</v>
+        <v>59.24680851</v>
       </c>
       <c r="F7">
-        <v>241.46</v>
+        <v>278.46</v>
       </c>
       <c r="G7">
-        <v>2.875942185</v>
+        <v>4.077575475</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B8">
-        <v>2722</v>
+        <v>2741</v>
       </c>
       <c r="C8">
-        <v>4158.42</v>
+        <v>3886.67</v>
       </c>
       <c r="D8">
-        <v>241.5833333</v>
+        <v>313.3333333</v>
       </c>
       <c r="E8">
-        <v>59.24680851</v>
+        <v>55.52851064</v>
       </c>
       <c r="F8">
-        <v>278.46</v>
+        <v>260.984</v>
       </c>
       <c r="G8">
-        <v>4.077575475</v>
+        <v>5.642746937</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -11477,25 +11483,25 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B12">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="C12">
-        <v>790.42</v>
+        <v>1250.58</v>
       </c>
       <c r="D12">
-        <v>709.5833333</v>
+        <v>249.4166667</v>
       </c>
       <c r="E12">
-        <v>56.75531915</v>
+        <v>17.77163121</v>
       </c>
       <c r="F12">
-        <v>266.75</v>
+        <v>83.52666667</v>
       </c>
       <c r="G12">
-        <v>12.50249922</v>
+        <v>14.03453987</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -11522,25 +11528,25 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B15">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C15">
-        <v>1250.58</v>
+        <v>790.42</v>
       </c>
       <c r="D15">
-        <v>249.4166667</v>
+        <v>853.5833333</v>
       </c>
       <c r="E15">
-        <v>17.77163121</v>
+        <v>56.75531915</v>
       </c>
       <c r="F15">
-        <v>83.52666667</v>
+        <v>266.75</v>
       </c>
       <c r="G15">
-        <v>14.03453987</v>
+        <v>15.03970634</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -11707,8 +11713,11 @@
       <c r="B24">
         <v>2738</v>
       </c>
+      <c r="C24">
+        <v>100</v>
+      </c>
       <c r="D24">
-        <v>1399.916667</v>
+        <v>1400</v>
       </c>
       <c r="E24">
         <v>55.52851064</v>
@@ -11717,7 +11726,7 @@
         <v>260.984</v>
       </c>
       <c r="G24">
-        <v>25.21077282</v>
+        <v>25.21227355</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -11768,8 +11777,11 @@
       <c r="B29">
         <v>2727</v>
       </c>
+      <c r="C29">
+        <v>100</v>
+      </c>
       <c r="D29">
-        <v>1398.416667</v>
+        <v>1400</v>
       </c>
       <c r="E29">
         <v>35.05319149</v>
@@ -11778,7 +11790,7 @@
         <v>164.75</v>
       </c>
       <c r="G29">
-        <v>39.89413252</v>
+        <v>39.93930197</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -11913,7 +11925,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1427,8 +1427,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1444,7 +1452,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1452,12 +1460,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1757,70 +1783,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1861,10 +1887,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>41754</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1876,7 +1902,7 @@
       <c r="T2" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="1">
+      <c r="U2" s="2">
         <v>46170</v>
       </c>
     </row>
@@ -1917,10 +1943,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>44709</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1967,10 +1993,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>44348</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -2014,10 +2040,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>46059</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -2029,7 +2055,7 @@
       <c r="T5" t="s">
         <v>151</v>
       </c>
-      <c r="U5" s="1">
+      <c r="U5" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -2070,10 +2096,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>46149</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -2120,10 +2146,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>43731</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -2135,7 +2161,7 @@
       <c r="T7" t="s">
         <v>152</v>
       </c>
-      <c r="U7" s="1">
+      <c r="U7" s="2">
         <v>43507</v>
       </c>
     </row>
@@ -2176,10 +2202,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45511</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2226,10 +2252,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45716</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2241,7 +2267,7 @@
       <c r="T9" t="s">
         <v>153</v>
       </c>
-      <c r="U9" s="1">
+      <c r="U9" s="2">
         <v>44665</v>
       </c>
     </row>
@@ -2282,10 +2308,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>45064</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2323,10 +2349,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>46135</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2338,7 +2364,7 @@
       <c r="T11" t="s">
         <v>154</v>
       </c>
-      <c r="U11" s="1">
+      <c r="U11" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -2379,7 +2405,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2423,10 +2449,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>46199</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2473,10 +2499,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45667</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2488,7 +2514,7 @@
       <c r="T14" t="s">
         <v>155</v>
       </c>
-      <c r="U14" s="1">
+      <c r="U14" s="2">
         <v>46072</v>
       </c>
     </row>
@@ -2529,10 +2555,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>46064</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="Q15" s="2">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2579,10 +2605,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>44285</v>
       </c>
-      <c r="Q16" s="1">
+      <c r="Q16" s="2">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2594,7 +2620,7 @@
       <c r="T16" t="s">
         <v>156</v>
       </c>
-      <c r="U16" s="1">
+      <c r="U16" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2635,10 +2661,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45922</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2685,10 +2711,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>45930</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2700,7 +2726,7 @@
       <c r="T18" t="s">
         <v>157</v>
       </c>
-      <c r="U18" s="1">
+      <c r="U18" s="2">
         <v>46198</v>
       </c>
     </row>
@@ -2741,10 +2767,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45524</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2756,7 +2782,7 @@
       <c r="T19" t="s">
         <v>124</v>
       </c>
-      <c r="U19" s="1">
+      <c r="U19" s="2">
         <v>46153</v>
       </c>
     </row>
@@ -2797,10 +2823,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>45026</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2812,7 +2838,7 @@
       <c r="T20" t="s">
         <v>158</v>
       </c>
-      <c r="U20" s="1">
+      <c r="U20" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2853,10 +2879,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>45159</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2868,7 +2894,7 @@
       <c r="T21" t="s">
         <v>126</v>
       </c>
-      <c r="U21" s="1">
+      <c r="U21" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -2909,10 +2935,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2924,7 +2950,7 @@
       <c r="T22" t="s">
         <v>159</v>
       </c>
-      <c r="U22" s="1">
+      <c r="U22" s="2">
         <v>45995</v>
       </c>
     </row>
@@ -2962,10 +2988,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>45713</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -2974,7 +3000,7 @@
       <c r="S23" t="s">
         <v>149</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -3015,10 +3041,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>46062</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>46220</v>
       </c>
       <c r="R24" t="s">
@@ -3027,7 +3053,7 @@
       <c r="S24" t="s">
         <v>149</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -3068,10 +3094,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45079</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -3118,10 +3144,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>41346</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -3133,7 +3159,7 @@
       <c r="T26" t="s">
         <v>160</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>46150</v>
       </c>
     </row>
@@ -3174,10 +3200,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45579</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3224,10 +3250,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>46171</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3274,10 +3300,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44320</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3324,10 +3350,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="2">
         <v>42661</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="Q30" s="2">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3339,7 +3365,7 @@
       <c r="T30" t="s">
         <v>161</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="2">
         <v>45358</v>
       </c>
     </row>
@@ -3380,10 +3406,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="2">
         <v>46220</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="Q31" s="2">
         <v>46220</v>
       </c>
       <c r="R31" t="s">
@@ -3430,10 +3456,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="2">
         <v>43797</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="Q32" s="2">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3480,10 +3506,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>42810</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3495,7 +3521,7 @@
       <c r="T33" t="s">
         <v>162</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="2">
         <v>43802</v>
       </c>
     </row>
@@ -3536,10 +3562,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>45070</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>44910</v>
       </c>
       <c r="R34" t="s">
@@ -3586,10 +3612,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>43250</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3636,10 +3662,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45841</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3686,10 +3712,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="2">
         <v>45105</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="Q37" s="2">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3701,7 +3727,7 @@
       <c r="T37" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="1">
+      <c r="U37" s="2">
         <v>46184</v>
       </c>
     </row>
@@ -3742,10 +3768,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>45636</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>46219</v>
       </c>
       <c r="S38" t="s">
@@ -3754,7 +3780,7 @@
       <c r="T38" t="s">
         <v>164</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="2">
         <v>45351</v>
       </c>
     </row>
@@ -3795,10 +3821,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>45831</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3842,10 +3868,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>44287</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3866,22 +3892,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>170</v>
       </c>
     </row>
@@ -8092,91 +8118,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>255</v>
       </c>
     </row>
@@ -8190,13 +8216,13 @@
       <c r="D2" t="s">
         <v>258</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
         <v>261</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>45492</v>
       </c>
       <c r="H2" t="s">
@@ -8214,13 +8240,13 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45491</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="2">
         <v>45528</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="2">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
@@ -8258,13 +8284,13 @@
       <c r="D3" t="s">
         <v>259</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
         <v>261</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="2">
         <v>45631</v>
       </c>
       <c r="H3" t="s">
@@ -8282,13 +8308,13 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>45628</v>
       </c>
-      <c r="R3" s="1">
+      <c r="R3" s="2">
         <v>45632</v>
       </c>
-      <c r="S3" s="1">
+      <c r="S3" s="2">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
@@ -8323,13 +8349,13 @@
       <c r="D4" t="s">
         <v>259</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
         <v>261</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="2">
         <v>45716</v>
       </c>
       <c r="H4" t="s">
@@ -8347,13 +8373,13 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45716</v>
       </c>
-      <c r="R4" s="1">
+      <c r="R4" s="2">
         <v>45722</v>
       </c>
-      <c r="S4" s="1">
+      <c r="S4" s="2">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
@@ -8388,13 +8414,13 @@
       <c r="D5" t="s">
         <v>259</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
         <v>261</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <v>45728</v>
       </c>
       <c r="H5" t="s">
@@ -8412,13 +8438,13 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45722</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R5" s="2">
         <v>45782</v>
       </c>
-      <c r="S5" s="1">
+      <c r="S5" s="2">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
@@ -8456,13 +8482,13 @@
       <c r="D6" t="s">
         <v>259</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
         <v>261</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <v>45755</v>
       </c>
       <c r="H6" t="s">
@@ -8480,13 +8506,13 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45728</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R6" s="2">
         <v>45734</v>
       </c>
-      <c r="S6" s="1">
+      <c r="S6" s="2">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
@@ -8524,7 +8550,7 @@
       <c r="D7" t="s">
         <v>260</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
@@ -8545,10 +8571,10 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45772</v>
       </c>
-      <c r="R7" s="1">
+      <c r="R7" s="2">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
@@ -8586,7 +8612,7 @@
       <c r="D8" t="s">
         <v>260</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
@@ -8607,10 +8633,10 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>45762</v>
       </c>
-      <c r="R8" s="1">
+      <c r="R8" s="2">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
@@ -8648,7 +8674,7 @@
       <c r="D9" t="s">
         <v>260</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
@@ -8669,10 +8695,10 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45763</v>
       </c>
-      <c r="R9" s="1">
+      <c r="R9" s="2">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
@@ -8710,13 +8736,13 @@
       <c r="D10" t="s">
         <v>259</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
         <v>261</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="2">
         <v>45755</v>
       </c>
       <c r="H10" t="s">
@@ -8734,13 +8760,13 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45754</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R10" s="2">
         <v>45849</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S10" s="2">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
@@ -8775,13 +8801,13 @@
       <c r="D11" t="s">
         <v>259</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
         <v>261</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="2">
         <v>44973</v>
       </c>
       <c r="H11" t="s">
@@ -8799,13 +8825,13 @@
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44973</v>
       </c>
-      <c r="R11" s="1">
+      <c r="R11" s="2">
         <v>45687</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S11" s="2">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
@@ -8840,13 +8866,13 @@
       <c r="D12" t="s">
         <v>259</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
         <v>261</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="2">
         <v>45358</v>
       </c>
       <c r="H12" t="s">
@@ -8864,13 +8890,13 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45358</v>
       </c>
-      <c r="R12" s="1">
+      <c r="R12" s="2">
         <v>45517</v>
       </c>
-      <c r="S12" s="1">
+      <c r="S12" s="2">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
@@ -8905,13 +8931,13 @@
       <c r="D13" t="s">
         <v>259</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
         <v>261</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="2">
         <v>45573</v>
       </c>
       <c r="H13" t="s">
@@ -8929,13 +8955,13 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45572</v>
       </c>
-      <c r="R13" s="1">
+      <c r="R13" s="2">
         <v>45572</v>
       </c>
-      <c r="S13" s="1">
+      <c r="S13" s="2">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
@@ -8973,13 +8999,13 @@
       <c r="D14" t="s">
         <v>259</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
         <v>261</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="2">
         <v>45747</v>
       </c>
       <c r="H14" t="s">
@@ -8997,13 +9023,13 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>45736</v>
       </c>
-      <c r="R14" s="1">
+      <c r="R14" s="2">
         <v>46101</v>
       </c>
-      <c r="S14" s="1">
+      <c r="S14" s="2">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
@@ -9039,70 +9065,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9140,10 +9166,10 @@
       <c r="O2" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>45490</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -9187,10 +9213,10 @@
       <c r="O3" t="s">
         <v>83</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>45618</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -9234,10 +9260,10 @@
       <c r="O4" t="s">
         <v>99</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>45539</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -9281,10 +9307,10 @@
       <c r="O5" t="s">
         <v>100</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>45567</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -9328,10 +9354,10 @@
       <c r="O6" t="s">
         <v>97</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>45568</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -9375,10 +9401,10 @@
       <c r="O7" t="s">
         <v>85</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>45831</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -9422,10 +9448,10 @@
       <c r="O8" t="s">
         <v>105</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45601</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -9469,10 +9495,10 @@
       <c r="O9" t="s">
         <v>94</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45631</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -9516,10 +9542,10 @@
       <c r="O10" t="s">
         <v>91</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>43902</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -9563,10 +9589,10 @@
       <c r="O11" t="s">
         <v>101</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>44736</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -9610,10 +9636,10 @@
       <c r="O12" t="s">
         <v>84</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>45776</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -9657,10 +9683,10 @@
       <c r="O13" t="s">
         <v>82</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>45772</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -9704,10 +9730,10 @@
       <c r="O14" t="s">
         <v>102</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45000</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -9751,7 +9777,7 @@
       <c r="O15" t="s">
         <v>96</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -9792,7 +9818,7 @@
       <c r="O16" t="s">
         <v>92</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -9833,10 +9859,10 @@
       <c r="O17" t="s">
         <v>95</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45371</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -9880,10 +9906,10 @@
       <c r="O18" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>46001</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -9927,10 +9953,10 @@
       <c r="O19" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45436</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -9974,10 +10000,10 @@
       <c r="O20" t="s">
         <v>98</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>44372</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -10021,10 +10047,10 @@
       <c r="O21" t="s">
         <v>107</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>44362</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -10068,10 +10094,10 @@
       <c r="O22" t="s">
         <v>88</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -10109,10 +10135,10 @@
       <c r="O23" t="s">
         <v>354</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>40044</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -10124,7 +10150,7 @@
       <c r="T23" t="s">
         <v>394</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>45775</v>
       </c>
     </row>
@@ -10162,10 +10188,10 @@
       <c r="O24" t="s">
         <v>82</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>43549</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -10177,7 +10203,7 @@
       <c r="T24" t="s">
         <v>395</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -10215,10 +10241,10 @@
       <c r="O25" t="s">
         <v>88</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45447</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -10230,7 +10256,7 @@
       <c r="T25" t="s">
         <v>396</v>
       </c>
-      <c r="U25" s="1">
+      <c r="U25" s="2">
         <v>45937</v>
       </c>
     </row>
@@ -10268,10 +10294,10 @@
       <c r="O26" t="s">
         <v>102</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>44485</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -10283,7 +10309,7 @@
       <c r="T26" t="s">
         <v>397</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>45580</v>
       </c>
     </row>
@@ -10321,10 +10347,10 @@
       <c r="O27" t="s">
         <v>88</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45420</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -10336,7 +10362,7 @@
       <c r="T27" t="s">
         <v>398</v>
       </c>
-      <c r="U27" s="1">
+      <c r="U27" s="2">
         <v>45588</v>
       </c>
     </row>
@@ -10374,10 +10400,10 @@
       <c r="O28" t="s">
         <v>103</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>44369</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -10389,7 +10415,7 @@
       <c r="T28" t="s">
         <v>399</v>
       </c>
-      <c r="U28" s="1">
+      <c r="U28" s="2">
         <v>45831</v>
       </c>
     </row>
@@ -10427,10 +10453,10 @@
       <c r="O29" t="s">
         <v>100</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44652</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -10442,7 +10468,7 @@
       <c r="T29" t="s">
         <v>400</v>
       </c>
-      <c r="U29" s="1">
+      <c r="U29" s="2">
         <v>45734</v>
       </c>
     </row>
@@ -10474,7 +10500,7 @@
       <c r="T30" t="s">
         <v>401</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10506,7 +10532,7 @@
       <c r="T31" t="s">
         <v>402</v>
       </c>
-      <c r="U31" s="1">
+      <c r="U31" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10538,7 +10564,7 @@
       <c r="T32" t="s">
         <v>403</v>
       </c>
-      <c r="U32" s="1">
+      <c r="U32" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10576,10 +10602,10 @@
       <c r="O33" t="s">
         <v>92</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>43762</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -10591,7 +10617,7 @@
       <c r="T33" t="s">
         <v>382</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="2">
         <v>46037</v>
       </c>
     </row>
@@ -10629,16 +10655,16 @@
       <c r="O34" t="s">
         <v>355</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>40071</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>149</v>
       </c>
-      <c r="U34" s="1">
+      <c r="U34" s="2">
         <v>41023</v>
       </c>
     </row>
@@ -10670,10 +10696,10 @@
       <c r="O35" t="s">
         <v>89</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>44784</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -10682,7 +10708,7 @@
       <c r="S35" t="s">
         <v>149</v>
       </c>
-      <c r="U35" s="1">
+      <c r="U35" s="2">
         <v>45259</v>
       </c>
     </row>
@@ -10720,10 +10746,10 @@
       <c r="O36" t="s">
         <v>93</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45103</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -10732,7 +10758,7 @@
       <c r="S36" t="s">
         <v>149</v>
       </c>
-      <c r="U36" s="1">
+      <c r="U36" s="2">
         <v>46000</v>
       </c>
     </row>
@@ -10796,10 +10822,10 @@
       <c r="O38" t="s">
         <v>98</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>38511</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -10808,7 +10834,7 @@
       <c r="S38" t="s">
         <v>149</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="2">
         <v>39068</v>
       </c>
     </row>
@@ -10846,10 +10872,10 @@
       <c r="O39" t="s">
         <v>105</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>39006</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -10861,7 +10887,7 @@
       <c r="T39" t="s">
         <v>404</v>
       </c>
-      <c r="U39" s="1">
+      <c r="U39" s="2">
         <v>40568</v>
       </c>
     </row>
@@ -10893,10 +10919,10 @@
       <c r="O40" t="s">
         <v>102</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>40836</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -10908,7 +10934,7 @@
       <c r="T40" t="s">
         <v>405</v>
       </c>
-      <c r="U40" s="1">
+      <c r="U40" s="2">
         <v>42270</v>
       </c>
     </row>
@@ -10946,10 +10972,10 @@
       <c r="O41" t="s">
         <v>97</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P41" s="2">
         <v>42940</v>
       </c>
-      <c r="Q41" s="1">
+      <c r="Q41" s="2">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -10961,7 +10987,7 @@
       <c r="T41" t="s">
         <v>406</v>
       </c>
-      <c r="U41" s="1">
+      <c r="U41" s="2">
         <v>44148</v>
       </c>
     </row>
@@ -10999,10 +11025,10 @@
       <c r="O42" t="s">
         <v>84</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P42" s="2">
         <v>43696</v>
       </c>
-      <c r="Q42" s="1">
+      <c r="Q42" s="2">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -11014,7 +11040,7 @@
       <c r="T42" t="s">
         <v>407</v>
       </c>
-      <c r="U42" s="1">
+      <c r="U42" s="2">
         <v>43185</v>
       </c>
     </row>
@@ -11052,10 +11078,10 @@
       <c r="O43" t="s">
         <v>86</v>
       </c>
-      <c r="P43" s="1">
+      <c r="P43" s="2">
         <v>43544</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="Q43" s="2">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -11067,7 +11093,7 @@
       <c r="T43" t="s">
         <v>408</v>
       </c>
-      <c r="U43" s="1">
+      <c r="U43" s="2">
         <v>42850</v>
       </c>
     </row>
@@ -11105,10 +11131,10 @@
       <c r="O44" t="s">
         <v>99</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P44" s="2">
         <v>45076</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="Q44" s="2">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -11120,7 +11146,7 @@
       <c r="T44" t="s">
         <v>409</v>
       </c>
-      <c r="U44" s="1">
+      <c r="U44" s="2">
         <v>44404</v>
       </c>
     </row>
@@ -11158,10 +11184,10 @@
       <c r="O45" t="s">
         <v>83</v>
       </c>
-      <c r="P45" s="1">
+      <c r="P45" s="2">
         <v>42963</v>
       </c>
-      <c r="Q45" s="1">
+      <c r="Q45" s="2">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -11173,7 +11199,7 @@
       <c r="T45" t="s">
         <v>410</v>
       </c>
-      <c r="U45" s="1">
+      <c r="U45" s="2">
         <v>42698</v>
       </c>
     </row>
@@ -11211,10 +11237,10 @@
       <c r="O46" t="s">
         <v>90</v>
       </c>
-      <c r="P46" s="1">
+      <c r="P46" s="2">
         <v>45054</v>
       </c>
-      <c r="Q46" s="1">
+      <c r="Q46" s="2">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -11226,7 +11252,7 @@
       <c r="T46" t="s">
         <v>411</v>
       </c>
-      <c r="U46" s="1">
+      <c r="U46" s="2">
         <v>43941</v>
       </c>
     </row>
@@ -11241,25 +11267,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>416</v>
       </c>
     </row>
@@ -11939,22 +11965,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>422</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="463">
   <si>
     <t>om</t>
   </si>
@@ -619,6 +619,12 @@
   </si>
   <si>
     <t>12.68828829</t>
+  </si>
+  <si>
+    <t>1340h disp</t>
+  </si>
+  <si>
+    <t>3190h p tbo</t>
   </si>
   <si>
     <t>6.081238361</t>
@@ -1427,16 +1433,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1452,7 +1450,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1460,30 +1458,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1783,70 +1763,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1887,10 +1867,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>41754</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1902,7 +1882,7 @@
       <c r="T2" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="1">
         <v>46170</v>
       </c>
     </row>
@@ -1943,10 +1923,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>44709</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1993,10 +1973,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>44348</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -2040,10 +2020,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>46059</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -2055,7 +2035,7 @@
       <c r="T5" t="s">
         <v>151</v>
       </c>
-      <c r="U5" s="2">
+      <c r="U5" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -2096,10 +2076,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>46149</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -2146,10 +2126,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>43731</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -2161,7 +2141,7 @@
       <c r="T7" t="s">
         <v>152</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U7" s="1">
         <v>43507</v>
       </c>
     </row>
@@ -2202,10 +2182,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45511</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2252,10 +2232,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45716</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2267,7 +2247,7 @@
       <c r="T9" t="s">
         <v>153</v>
       </c>
-      <c r="U9" s="2">
+      <c r="U9" s="1">
         <v>44665</v>
       </c>
     </row>
@@ -2308,10 +2288,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>45064</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2349,10 +2329,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>46135</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2364,7 +2344,7 @@
       <c r="T11" t="s">
         <v>154</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -2405,7 +2385,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2449,10 +2429,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>46199</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2499,10 +2479,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45667</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2514,7 +2494,7 @@
       <c r="T14" t="s">
         <v>155</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" s="1">
         <v>46072</v>
       </c>
     </row>
@@ -2555,10 +2535,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>46064</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="1">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2605,10 +2585,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>44285</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="1">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2620,7 +2600,7 @@
       <c r="T16" t="s">
         <v>156</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2661,10 +2641,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45922</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2711,10 +2691,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>45930</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2726,7 +2706,7 @@
       <c r="T18" t="s">
         <v>157</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" s="1">
         <v>46198</v>
       </c>
     </row>
@@ -2767,10 +2747,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45524</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2782,7 +2762,7 @@
       <c r="T19" t="s">
         <v>124</v>
       </c>
-      <c r="U19" s="2">
+      <c r="U19" s="1">
         <v>46153</v>
       </c>
     </row>
@@ -2823,10 +2803,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>45026</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2838,7 +2818,7 @@
       <c r="T20" t="s">
         <v>158</v>
       </c>
-      <c r="U20" s="2">
+      <c r="U20" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2879,10 +2859,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>45159</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2894,7 +2874,7 @@
       <c r="T21" t="s">
         <v>126</v>
       </c>
-      <c r="U21" s="2">
+      <c r="U21" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2935,10 +2915,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2950,7 +2930,7 @@
       <c r="T22" t="s">
         <v>159</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" s="1">
         <v>45995</v>
       </c>
     </row>
@@ -2988,10 +2968,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>45713</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -3000,7 +2980,7 @@
       <c r="S23" t="s">
         <v>149</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -3041,10 +3021,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>46062</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>46220</v>
       </c>
       <c r="R24" t="s">
@@ -3053,7 +3033,7 @@
       <c r="S24" t="s">
         <v>149</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -3094,10 +3074,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45079</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -3144,10 +3124,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>41346</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -3159,7 +3139,7 @@
       <c r="T26" t="s">
         <v>160</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>46150</v>
       </c>
     </row>
@@ -3200,10 +3180,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45579</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3250,10 +3230,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>46171</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3300,10 +3280,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44320</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3350,10 +3330,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="1">
         <v>42661</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="1">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3365,7 +3345,7 @@
       <c r="T30" t="s">
         <v>161</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>45358</v>
       </c>
     </row>
@@ -3406,10 +3386,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="1">
         <v>46220</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="1">
         <v>46220</v>
       </c>
       <c r="R31" t="s">
@@ -3456,10 +3436,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="1">
         <v>43797</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="1">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3506,10 +3486,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>42810</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3521,7 +3501,7 @@
       <c r="T33" t="s">
         <v>162</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>43802</v>
       </c>
     </row>
@@ -3562,10 +3542,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>45070</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>44910</v>
       </c>
       <c r="R34" t="s">
@@ -3612,10 +3592,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>43250</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3662,10 +3642,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45841</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3712,10 +3692,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="2">
+      <c r="P37" s="1">
         <v>45105</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="1">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3727,7 +3707,7 @@
       <c r="T37" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="2">
+      <c r="U37" s="1">
         <v>46184</v>
       </c>
     </row>
@@ -3768,10 +3748,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>45636</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>46219</v>
       </c>
       <c r="S38" t="s">
@@ -3780,7 +3760,7 @@
       <c r="T38" t="s">
         <v>164</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>45351</v>
       </c>
     </row>
@@ -3821,10 +3801,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>45831</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3868,10 +3848,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>44287</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3888,26 +3868,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F245"/>
+  <dimension ref="A1:F247"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>167</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>169</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>170</v>
       </c>
     </row>
@@ -3996,7 +3976,7 @@
         <v>173</v>
       </c>
       <c r="F6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4118,7 +4098,7 @@
         <v>173</v>
       </c>
       <c r="F13" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4223,7 +4203,7 @@
         <v>177</v>
       </c>
       <c r="F19" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4464,7 +4444,7 @@
         <v>173</v>
       </c>
       <c r="F33" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4552,7 +4532,7 @@
         <v>173</v>
       </c>
       <c r="F38" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4691,7 +4671,7 @@
         <v>173</v>
       </c>
       <c r="F46" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4796,7 +4776,7 @@
         <v>185</v>
       </c>
       <c r="F52" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4935,7 +4915,7 @@
         <v>177</v>
       </c>
       <c r="F60" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -5414,7 +5394,7 @@
         <v>177</v>
       </c>
       <c r="F88" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -5595,13 +5575,13 @@
         <v>2742</v>
       </c>
       <c r="C99">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -5612,47 +5592,47 @@
         <v>2742</v>
       </c>
       <c r="C100">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D100">
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="B101">
-        <v>2704</v>
+        <v>2742</v>
       </c>
       <c r="C101">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D101">
         <v>1</v>
       </c>
       <c r="E101" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="B102">
-        <v>2704</v>
+        <v>2742</v>
       </c>
       <c r="C102">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5666,7 +5646,7 @@
         <v>2025</v>
       </c>
       <c r="D103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E103" t="s">
         <v>171</v>
@@ -5683,10 +5663,10 @@
         <v>2025</v>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E104" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5700,10 +5680,10 @@
         <v>2025</v>
       </c>
       <c r="D105">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E105" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5717,10 +5697,10 @@
         <v>2025</v>
       </c>
       <c r="D106">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E106" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5731,13 +5711,13 @@
         <v>2704</v>
       </c>
       <c r="C107">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D107">
         <v>8</v>
       </c>
       <c r="E107" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5748,47 +5728,47 @@
         <v>2704</v>
       </c>
       <c r="C108">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="D108">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E108" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B109">
-        <v>2720</v>
+        <v>2704</v>
       </c>
       <c r="C109">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E109" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B110">
-        <v>2720</v>
+        <v>2704</v>
       </c>
       <c r="C110">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E110" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5802,7 +5782,7 @@
         <v>2025</v>
       </c>
       <c r="D111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E111" t="s">
         <v>171</v>
@@ -5819,10 +5799,10 @@
         <v>2025</v>
       </c>
       <c r="D112">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5836,10 +5816,10 @@
         <v>2025</v>
       </c>
       <c r="D113">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E113" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5853,10 +5833,10 @@
         <v>2025</v>
       </c>
       <c r="D114">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E114" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5867,13 +5847,13 @@
         <v>2720</v>
       </c>
       <c r="C115">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D115">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E115" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -5884,47 +5864,47 @@
         <v>2720</v>
       </c>
       <c r="C116">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="D116">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E116" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B117">
-        <v>2708</v>
+        <v>2720</v>
       </c>
       <c r="C117">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E117" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B118">
-        <v>2708</v>
+        <v>2720</v>
       </c>
       <c r="C118">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D118">
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -5938,7 +5918,7 @@
         <v>2025</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E119" t="s">
         <v>171</v>
@@ -5955,10 +5935,10 @@
         <v>2025</v>
       </c>
       <c r="D120">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E120" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5969,13 +5949,13 @@
         <v>2708</v>
       </c>
       <c r="C121">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E121" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -5986,13 +5966,13 @@
         <v>2708</v>
       </c>
       <c r="C122">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D122">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -6006,7 +5986,7 @@
         <v>2026</v>
       </c>
       <c r="D123">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E123" t="s">
         <v>204</v>
@@ -6020,13 +6000,13 @@
         <v>2708</v>
       </c>
       <c r="C124">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E124" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -6037,47 +6017,47 @@
         <v>2708</v>
       </c>
       <c r="C125">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="D125">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E125" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B126">
-        <v>2737</v>
+        <v>2708</v>
       </c>
       <c r="C126">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D126">
         <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="B127">
-        <v>2737</v>
+        <v>2708</v>
       </c>
       <c r="C127">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E127" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -6091,7 +6071,7 @@
         <v>2025</v>
       </c>
       <c r="D128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E128" t="s">
         <v>174</v>
@@ -6108,7 +6088,7 @@
         <v>2025</v>
       </c>
       <c r="D129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E129" t="s">
         <v>174</v>
@@ -6125,7 +6105,7 @@
         <v>2025</v>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E130" t="s">
         <v>174</v>
@@ -6139,13 +6119,13 @@
         <v>2737</v>
       </c>
       <c r="C131">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D131">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E131" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -6156,13 +6136,13 @@
         <v>2737</v>
       </c>
       <c r="C132">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D132">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E132" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -6173,47 +6153,47 @@
         <v>2737</v>
       </c>
       <c r="C133">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D133">
         <v>6</v>
       </c>
       <c r="E133" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B134">
-        <v>2733</v>
+        <v>2737</v>
       </c>
       <c r="C134">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E134" t="s">
-        <v>171</v>
+        <v>208</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B135">
-        <v>2733</v>
+        <v>2737</v>
       </c>
       <c r="C135">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E135" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -6227,7 +6207,7 @@
         <v>2025</v>
       </c>
       <c r="D136">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E136" t="s">
         <v>171</v>
@@ -6244,10 +6224,10 @@
         <v>2025</v>
       </c>
       <c r="D137">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E137" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -6258,16 +6238,13 @@
         <v>2733</v>
       </c>
       <c r="C138">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D138">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E138" t="s">
-        <v>207</v>
-      </c>
-      <c r="F138" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -6278,13 +6255,13 @@
         <v>2733</v>
       </c>
       <c r="C139">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D139">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E139" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6295,67 +6272,70 @@
         <v>2733</v>
       </c>
       <c r="C140">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="D140">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E140" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="F140" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>45</v>
-      </c>
-      <c r="B141" t="b">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="B141">
+        <v>2733</v>
       </c>
       <c r="C141">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D141">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E141" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>58</v>
-      </c>
-      <c r="B142" t="b">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="B142">
+        <v>2733</v>
       </c>
       <c r="C142">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>174</v>
+        <v>173</v>
+      </c>
+      <c r="F142" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B143" t="b">
         <v>0</v>
       </c>
       <c r="C143">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D143">
         <v>2</v>
       </c>
       <c r="E143" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6369,7 +6349,7 @@
         <v>2025</v>
       </c>
       <c r="D144">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E144" t="s">
         <v>174</v>
@@ -6386,7 +6366,7 @@
         <v>2025</v>
       </c>
       <c r="D145">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E145" t="s">
         <v>174</v>
@@ -6403,7 +6383,7 @@
         <v>2025</v>
       </c>
       <c r="D146">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E146" t="s">
         <v>174</v>
@@ -6420,10 +6400,10 @@
         <v>2025</v>
       </c>
       <c r="D147">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E147" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -6434,13 +6414,13 @@
         <v>0</v>
       </c>
       <c r="C148">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E148" t="s">
-        <v>209</v>
+        <v>174</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -6451,47 +6431,47 @@
         <v>0</v>
       </c>
       <c r="C149">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="D149">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E149" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>68</v>
-      </c>
-      <c r="B150">
-        <v>2702</v>
+        <v>58</v>
+      </c>
+      <c r="B150" t="b">
+        <v>0</v>
       </c>
       <c r="C150">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E150" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>68</v>
-      </c>
-      <c r="B151">
-        <v>2702</v>
+        <v>58</v>
+      </c>
+      <c r="B151" t="b">
+        <v>0</v>
       </c>
       <c r="C151">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D151">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E151" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -6505,7 +6485,7 @@
         <v>2025</v>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E152" t="s">
         <v>171</v>
@@ -6522,10 +6502,10 @@
         <v>2025</v>
       </c>
       <c r="D153">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -6536,13 +6516,13 @@
         <v>2702</v>
       </c>
       <c r="C154">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E154" t="s">
-        <v>210</v>
+        <v>171</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -6553,13 +6533,13 @@
         <v>2702</v>
       </c>
       <c r="C155">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D155">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E155" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -6573,7 +6553,7 @@
         <v>2026</v>
       </c>
       <c r="D156">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E156" t="s">
         <v>212</v>
@@ -6587,47 +6567,47 @@
         <v>2702</v>
       </c>
       <c r="C157">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D157">
         <v>6</v>
       </c>
       <c r="E157" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B158">
-        <v>2738</v>
+        <v>2702</v>
       </c>
       <c r="C158">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D158">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E158" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B159">
-        <v>2738</v>
+        <v>2702</v>
       </c>
       <c r="C159">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E159" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -6641,7 +6621,7 @@
         <v>2025</v>
       </c>
       <c r="D160">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E160" t="s">
         <v>174</v>
@@ -6658,7 +6638,7 @@
         <v>2025</v>
       </c>
       <c r="D161">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E161" t="s">
         <v>174</v>
@@ -6675,7 +6655,7 @@
         <v>2025</v>
       </c>
       <c r="D162">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E162" t="s">
         <v>174</v>
@@ -6689,13 +6669,13 @@
         <v>2738</v>
       </c>
       <c r="C163">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D163">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E163" t="s">
-        <v>213</v>
+        <v>174</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -6706,13 +6686,13 @@
         <v>2738</v>
       </c>
       <c r="C164">
-        <v>2028</v>
+        <v>2025</v>
       </c>
       <c r="D164">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -6723,64 +6703,64 @@
         <v>2738</v>
       </c>
       <c r="C165">
-        <v>2029</v>
+        <v>2026</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E165" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>51</v>
-      </c>
-      <c r="B166" t="b">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="B166">
+        <v>2738</v>
       </c>
       <c r="C166">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="D166">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E166" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>47</v>
-      </c>
-      <c r="B167" t="b">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="B167">
+        <v>2738</v>
       </c>
       <c r="C167">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D167">
         <v>1</v>
       </c>
       <c r="E167" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B168" t="b">
         <v>0</v>
       </c>
       <c r="C168">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D168">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E168" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -6794,7 +6774,7 @@
         <v>2025</v>
       </c>
       <c r="D169">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E169" t="s">
         <v>174</v>
@@ -6811,7 +6791,7 @@
         <v>2025</v>
       </c>
       <c r="D170">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E170" t="s">
         <v>174</v>
@@ -6828,7 +6808,7 @@
         <v>2025</v>
       </c>
       <c r="D171">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E171" t="s">
         <v>174</v>
@@ -6836,7 +6816,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B172" t="b">
         <v>0</v>
@@ -6845,7 +6825,7 @@
         <v>2025</v>
       </c>
       <c r="D172">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E172" t="s">
         <v>174</v>
@@ -6853,7 +6833,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B173" t="b">
         <v>0</v>
@@ -6862,7 +6842,7 @@
         <v>2025</v>
       </c>
       <c r="D173">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E173" t="s">
         <v>174</v>
@@ -6879,7 +6859,7 @@
         <v>2025</v>
       </c>
       <c r="D174">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E174" t="s">
         <v>174</v>
@@ -6896,7 +6876,7 @@
         <v>2025</v>
       </c>
       <c r="D175">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E175" t="s">
         <v>174</v>
@@ -6913,7 +6893,7 @@
         <v>2025</v>
       </c>
       <c r="D176">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E176" t="s">
         <v>174</v>
@@ -6921,7 +6901,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B177" t="b">
         <v>0</v>
@@ -6930,15 +6910,15 @@
         <v>2025</v>
       </c>
       <c r="D177">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E177" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B178" t="b">
         <v>0</v>
@@ -6947,10 +6927,10 @@
         <v>2025</v>
       </c>
       <c r="D178">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E178" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -6964,7 +6944,7 @@
         <v>2025</v>
       </c>
       <c r="D179">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E179" t="s">
         <v>171</v>
@@ -6981,13 +6961,10 @@
         <v>2025</v>
       </c>
       <c r="D180">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E180" t="s">
-        <v>173</v>
-      </c>
-      <c r="F180" t="s">
-        <v>229</v>
+        <v>171</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -7001,10 +6978,10 @@
         <v>2025</v>
       </c>
       <c r="D181">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E181" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -7015,47 +6992,50 @@
         <v>0</v>
       </c>
       <c r="C182">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D182">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E182" t="s">
-        <v>215</v>
+        <v>173</v>
+      </c>
+      <c r="F182" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>52</v>
-      </c>
-      <c r="B183">
-        <v>2727</v>
+        <v>42</v>
+      </c>
+      <c r="B183" t="b">
+        <v>0</v>
       </c>
       <c r="C183">
         <v>2025</v>
       </c>
       <c r="D183">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E183" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>52</v>
-      </c>
-      <c r="B184">
-        <v>2727</v>
+        <v>42</v>
+      </c>
+      <c r="B184" t="b">
+        <v>0</v>
       </c>
       <c r="C184">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D184">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E184" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -7069,7 +7049,7 @@
         <v>2025</v>
       </c>
       <c r="D185">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E185" t="s">
         <v>174</v>
@@ -7086,7 +7066,7 @@
         <v>2025</v>
       </c>
       <c r="D186">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E186" t="s">
         <v>174</v>
@@ -7103,7 +7083,7 @@
         <v>2025</v>
       </c>
       <c r="D187">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E187" t="s">
         <v>174</v>
@@ -7117,13 +7097,13 @@
         <v>2727</v>
       </c>
       <c r="C188">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D188">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E188" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -7134,47 +7114,47 @@
         <v>2727</v>
       </c>
       <c r="C189">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="D189">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E189" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>56</v>
-      </c>
-      <c r="B190" t="b">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="B190">
+        <v>2727</v>
       </c>
       <c r="C190">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D190">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E190" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>56</v>
-      </c>
-      <c r="B191" t="b">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="B191">
+        <v>2727</v>
       </c>
       <c r="C191">
-        <v>2025</v>
+        <v>2029</v>
       </c>
       <c r="D191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E191" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -7188,7 +7168,7 @@
         <v>2025</v>
       </c>
       <c r="D192">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E192" t="s">
         <v>174</v>
@@ -7205,7 +7185,7 @@
         <v>2025</v>
       </c>
       <c r="D193">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E193" t="s">
         <v>174</v>
@@ -7222,7 +7202,7 @@
         <v>2025</v>
       </c>
       <c r="D194">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E194" t="s">
         <v>174</v>
@@ -7230,7 +7210,7 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B195" t="b">
         <v>0</v>
@@ -7239,7 +7219,7 @@
         <v>2025</v>
       </c>
       <c r="D195">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E195" t="s">
         <v>174</v>
@@ -7247,7 +7227,7 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B196" t="b">
         <v>0</v>
@@ -7256,7 +7236,7 @@
         <v>2025</v>
       </c>
       <c r="D196">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E196" t="s">
         <v>174</v>
@@ -7273,7 +7253,7 @@
         <v>2025</v>
       </c>
       <c r="D197">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E197" t="s">
         <v>174</v>
@@ -7290,7 +7270,7 @@
         <v>2025</v>
       </c>
       <c r="D198">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E198" t="s">
         <v>174</v>
@@ -7307,7 +7287,7 @@
         <v>2025</v>
       </c>
       <c r="D199">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E199" t="s">
         <v>174</v>
@@ -7324,13 +7304,10 @@
         <v>2025</v>
       </c>
       <c r="D200">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E200" t="s">
-        <v>173</v>
-      </c>
-      <c r="F200" t="s">
-        <v>230</v>
+        <v>174</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -7344,10 +7321,10 @@
         <v>2025</v>
       </c>
       <c r="D201">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E201" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -7358,21 +7335,21 @@
         <v>0</v>
       </c>
       <c r="C202">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E202" t="s">
         <v>173</v>
       </c>
       <c r="F202" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B203" t="b">
         <v>0</v>
@@ -7381,27 +7358,30 @@
         <v>2025</v>
       </c>
       <c r="D203">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E203" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B204" t="b">
         <v>0</v>
       </c>
       <c r="C204">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="F204" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -7415,7 +7395,7 @@
         <v>2025</v>
       </c>
       <c r="D205">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E205" t="s">
         <v>171</v>
@@ -7423,7 +7403,7 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B206" t="b">
         <v>0</v>
@@ -7432,7 +7412,7 @@
         <v>2025</v>
       </c>
       <c r="D206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E206" t="s">
         <v>171</v>
@@ -7440,7 +7420,7 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B207" t="b">
         <v>0</v>
@@ -7449,7 +7429,7 @@
         <v>2025</v>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E207" t="s">
         <v>171</v>
@@ -7466,7 +7446,7 @@
         <v>2025</v>
       </c>
       <c r="D208">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E208" t="s">
         <v>171</v>
@@ -7483,10 +7463,10 @@
         <v>2025</v>
       </c>
       <c r="D209">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -7500,15 +7480,15 @@
         <v>2025</v>
       </c>
       <c r="D210">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E210" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B211" t="b">
         <v>0</v>
@@ -7517,15 +7497,15 @@
         <v>2025</v>
       </c>
       <c r="D211">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E211" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B212" t="b">
         <v>0</v>
@@ -7534,10 +7514,10 @@
         <v>2025</v>
       </c>
       <c r="D212">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E212" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -7551,7 +7531,7 @@
         <v>2025</v>
       </c>
       <c r="D213">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E213" t="s">
         <v>171</v>
@@ -7559,7 +7539,7 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B214" t="b">
         <v>0</v>
@@ -7568,7 +7548,7 @@
         <v>2025</v>
       </c>
       <c r="D214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E214" t="s">
         <v>171</v>
@@ -7576,7 +7556,7 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B215" t="b">
         <v>0</v>
@@ -7585,10 +7565,10 @@
         <v>2025</v>
       </c>
       <c r="D215">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E215" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -7602,7 +7582,7 @@
         <v>2025</v>
       </c>
       <c r="D216">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E216" t="s">
         <v>171</v>
@@ -7619,13 +7599,10 @@
         <v>2025</v>
       </c>
       <c r="D217">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>173</v>
-      </c>
-      <c r="F217" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -7639,18 +7616,15 @@
         <v>2025</v>
       </c>
       <c r="D218">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E218" t="s">
-        <v>173</v>
-      </c>
-      <c r="F218" t="s">
-        <v>231</v>
+        <v>171</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B219" t="b">
         <v>0</v>
@@ -7659,15 +7633,18 @@
         <v>2025</v>
       </c>
       <c r="D219">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E219" t="s">
-        <v>174</v>
+        <v>173</v>
+      </c>
+      <c r="F219" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B220" t="b">
         <v>0</v>
@@ -7676,10 +7653,13 @@
         <v>2025</v>
       </c>
       <c r="D220">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E220" t="s">
-        <v>174</v>
+        <v>173</v>
+      </c>
+      <c r="F220" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -7693,7 +7673,7 @@
         <v>2025</v>
       </c>
       <c r="D221">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E221" t="s">
         <v>174</v>
@@ -7710,7 +7690,7 @@
         <v>2025</v>
       </c>
       <c r="D222">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E222" t="s">
         <v>174</v>
@@ -7727,7 +7707,7 @@
         <v>2025</v>
       </c>
       <c r="D223">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E223" t="s">
         <v>174</v>
@@ -7735,16 +7715,16 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>57</v>
-      </c>
-      <c r="B224">
-        <v>2731</v>
+        <v>70</v>
+      </c>
+      <c r="B224" t="b">
+        <v>0</v>
       </c>
       <c r="C224">
         <v>2025</v>
       </c>
       <c r="D224">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E224" t="s">
         <v>174</v>
@@ -7752,16 +7732,16 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>57</v>
-      </c>
-      <c r="B225">
-        <v>2731</v>
+        <v>70</v>
+      </c>
+      <c r="B225" t="b">
+        <v>0</v>
       </c>
       <c r="C225">
         <v>2025</v>
       </c>
       <c r="D225">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E225" t="s">
         <v>174</v>
@@ -7778,7 +7758,7 @@
         <v>2025</v>
       </c>
       <c r="D226">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E226" t="s">
         <v>174</v>
@@ -7795,7 +7775,7 @@
         <v>2025</v>
       </c>
       <c r="D227">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E227" t="s">
         <v>174</v>
@@ -7812,7 +7792,7 @@
         <v>2025</v>
       </c>
       <c r="D228">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E228" t="s">
         <v>174</v>
@@ -7829,10 +7809,10 @@
         <v>2025</v>
       </c>
       <c r="D229">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E229" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -7843,13 +7823,13 @@
         <v>2731</v>
       </c>
       <c r="C230">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D230">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E230" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -7860,47 +7840,47 @@
         <v>2731</v>
       </c>
       <c r="C231">
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="D231">
         <v>10</v>
       </c>
       <c r="E231" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" t="s">
-        <v>73</v>
-      </c>
-      <c r="B232" t="b">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="B232">
+        <v>2731</v>
       </c>
       <c r="C232">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E232" t="s">
-        <v>174</v>
+        <v>219</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" t="s">
-        <v>73</v>
-      </c>
-      <c r="B233" t="b">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="B233">
+        <v>2731</v>
       </c>
       <c r="C233">
-        <v>2025</v>
+        <v>2030</v>
       </c>
       <c r="D233">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E233" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -7914,7 +7894,7 @@
         <v>2025</v>
       </c>
       <c r="D234">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E234" t="s">
         <v>174</v>
@@ -7931,7 +7911,7 @@
         <v>2025</v>
       </c>
       <c r="D235">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E235" t="s">
         <v>174</v>
@@ -7948,7 +7928,7 @@
         <v>2025</v>
       </c>
       <c r="D236">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E236" t="s">
         <v>174</v>
@@ -7956,7 +7936,7 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B237" t="b">
         <v>0</v>
@@ -7965,15 +7945,15 @@
         <v>2025</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E237" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B238" t="b">
         <v>0</v>
@@ -7982,10 +7962,10 @@
         <v>2025</v>
       </c>
       <c r="D238">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E238" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -7999,7 +7979,7 @@
         <v>2025</v>
       </c>
       <c r="D239">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E239" t="s">
         <v>171</v>
@@ -8016,15 +7996,15 @@
         <v>2025</v>
       </c>
       <c r="D240">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E240" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B241" t="b">
         <v>0</v>
@@ -8033,15 +8013,15 @@
         <v>2025</v>
       </c>
       <c r="D241">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E241" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="B242" t="b">
         <v>0</v>
@@ -8050,10 +8030,10 @@
         <v>2025</v>
       </c>
       <c r="D242">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E242" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -8067,7 +8047,7 @@
         <v>2025</v>
       </c>
       <c r="D243">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E243" t="s">
         <v>174</v>
@@ -8084,7 +8064,7 @@
         <v>2025</v>
       </c>
       <c r="D244">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E244" t="s">
         <v>174</v>
@@ -8101,9 +8081,43 @@
         <v>2025</v>
       </c>
       <c r="D245">
+        <v>3</v>
+      </c>
+      <c r="E245" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" t="s">
+        <v>77</v>
+      </c>
+      <c r="B246" t="b">
+        <v>0</v>
+      </c>
+      <c r="C246">
+        <v>2025</v>
+      </c>
+      <c r="D246">
+        <v>4</v>
+      </c>
+      <c r="E246" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" t="s">
+        <v>77</v>
+      </c>
+      <c r="B247" t="b">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>2025</v>
+      </c>
+      <c r="D247">
         <v>5</v>
       </c>
-      <c r="E245" t="s">
+      <c r="E247" t="s">
         <v>174</v>
       </c>
     </row>
@@ -8118,92 +8132,92 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="I1" t="s">
+        <v>239</v>
+      </c>
+      <c r="J1" t="s">
+        <v>240</v>
+      </c>
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="M1" t="s">
         <v>241</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="N1" t="s">
         <v>242</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="O1" t="s">
         <v>243</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="P1" t="s">
         <v>244</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>245</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="R1" t="s">
         <v>246</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="S1" t="s">
         <v>247</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="T1" t="s">
         <v>248</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="U1" t="s">
         <v>249</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="V1" t="s">
         <v>250</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="W1" t="s">
         <v>251</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="X1" t="s">
         <v>252</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>253</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>254</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>255</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>256</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:29">
@@ -8211,18 +8225,18 @@
         <v>3810267428</v>
       </c>
       <c r="C2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E2" s="2">
+        <v>260</v>
+      </c>
+      <c r="E2" s="1">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G2" s="2">
+        <v>263</v>
+      </c>
+      <c r="G2" s="1">
         <v>45492</v>
       </c>
       <c r="H2" t="s">
@@ -8232,7 +8246,7 @@
         <v>198</v>
       </c>
       <c r="J2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K2" t="s">
         <v>60</v>
@@ -8240,38 +8254,38 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45491</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="1">
         <v>45528</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="1">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="V2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="W2" t="s">
         <v>22</v>
       </c>
       <c r="X2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Y2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Z2" t="s">
         <v>30</v>
       </c>
       <c r="AA2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AB2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -8279,18 +8293,18 @@
         <v>3810269967</v>
       </c>
       <c r="C3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E3" s="2">
+        <v>261</v>
+      </c>
+      <c r="E3" s="1">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G3" s="2">
+        <v>263</v>
+      </c>
+      <c r="G3" s="1">
         <v>45631</v>
       </c>
       <c r="H3" t="s">
@@ -8300,7 +8314,7 @@
         <v>198</v>
       </c>
       <c r="J3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K3" t="s">
         <v>77</v>
@@ -8308,35 +8322,35 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45628</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>45632</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W3" t="s">
         <v>22</v>
       </c>
       <c r="X3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Y3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Z3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AA3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AB3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -8344,18 +8358,18 @@
         <v>3810271134</v>
       </c>
       <c r="C4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D4" t="s">
-        <v>259</v>
-      </c>
-      <c r="E4" s="2">
+        <v>261</v>
+      </c>
+      <c r="E4" s="1">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G4" s="2">
+        <v>263</v>
+      </c>
+      <c r="G4" s="1">
         <v>45716</v>
       </c>
       <c r="H4" t="s">
@@ -8365,7 +8379,7 @@
         <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K4" t="s">
         <v>56</v>
@@ -8373,35 +8387,35 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45716</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <v>45722</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="1">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W4" t="s">
         <v>22</v>
       </c>
       <c r="X4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Y4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Z4" t="s">
         <v>30</v>
       </c>
       <c r="AA4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AB4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -8409,18 +8423,18 @@
         <v>3810271161</v>
       </c>
       <c r="C5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D5" t="s">
-        <v>259</v>
-      </c>
-      <c r="E5" s="2">
+        <v>261</v>
+      </c>
+      <c r="E5" s="1">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
-        <v>261</v>
-      </c>
-      <c r="G5" s="2">
+        <v>263</v>
+      </c>
+      <c r="G5" s="1">
         <v>45728</v>
       </c>
       <c r="H5" t="s">
@@ -8430,7 +8444,7 @@
         <v>198</v>
       </c>
       <c r="J5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K5" t="s">
         <v>46</v>
@@ -8438,35 +8452,35 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45722</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <v>45782</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="1">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W5" t="s">
         <v>22</v>
       </c>
       <c r="X5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Y5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Z5" t="s">
         <v>30</v>
       </c>
       <c r="AA5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AB5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -8477,18 +8491,18 @@
         <v>3810271161</v>
       </c>
       <c r="C6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D6" t="s">
-        <v>259</v>
-      </c>
-      <c r="E6" s="2">
+        <v>261</v>
+      </c>
+      <c r="E6" s="1">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
-        <v>261</v>
-      </c>
-      <c r="G6" s="2">
+        <v>263</v>
+      </c>
+      <c r="G6" s="1">
         <v>45755</v>
       </c>
       <c r="H6" t="s">
@@ -8498,7 +8512,7 @@
         <v>198</v>
       </c>
       <c r="J6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K6" t="s">
         <v>46</v>
@@ -8506,35 +8520,35 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45728</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="1">
         <v>45734</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="1">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W6" t="s">
         <v>22</v>
       </c>
       <c r="X6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Y6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Z6" t="s">
         <v>22</v>
       </c>
       <c r="AA6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AB6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -8545,16 +8559,16 @@
         <v>3810272114</v>
       </c>
       <c r="C7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E7" s="2">
+        <v>262</v>
+      </c>
+      <c r="E7" s="1">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H7" t="s">
         <v>38</v>
@@ -8563,7 +8577,7 @@
         <v>198</v>
       </c>
       <c r="J7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K7" t="s">
         <v>46</v>
@@ -8571,32 +8585,32 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45772</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="1">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W7" t="s">
         <v>22</v>
       </c>
       <c r="X7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Y7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Z7" t="s">
         <v>22</v>
       </c>
       <c r="AA7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AB7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -8607,16 +8621,16 @@
         <v>3810272114</v>
       </c>
       <c r="C8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D8" t="s">
-        <v>260</v>
-      </c>
-      <c r="E8" s="2">
+        <v>262</v>
+      </c>
+      <c r="E8" s="1">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H8" t="s">
         <v>38</v>
@@ -8625,7 +8639,7 @@
         <v>198</v>
       </c>
       <c r="J8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K8" t="s">
         <v>46</v>
@@ -8633,32 +8647,32 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>45762</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="1">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W8" t="s">
         <v>22</v>
       </c>
       <c r="X8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Y8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Z8" t="s">
         <v>22</v>
       </c>
       <c r="AA8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AB8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -8669,16 +8683,16 @@
         <v>3810272114</v>
       </c>
       <c r="C9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D9" t="s">
-        <v>260</v>
-      </c>
-      <c r="E9" s="2">
+        <v>262</v>
+      </c>
+      <c r="E9" s="1">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H9" t="s">
         <v>38</v>
@@ -8687,7 +8701,7 @@
         <v>198</v>
       </c>
       <c r="J9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K9" t="s">
         <v>46</v>
@@ -8695,32 +8709,32 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45763</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="1">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W9" t="s">
         <v>22</v>
       </c>
       <c r="X9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Y9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Z9" t="s">
         <v>22</v>
       </c>
       <c r="AA9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AB9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -8731,18 +8745,18 @@
         <v>3810271161</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D10" t="s">
-        <v>259</v>
-      </c>
-      <c r="E10" s="2">
+        <v>261</v>
+      </c>
+      <c r="E10" s="1">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
-        <v>261</v>
-      </c>
-      <c r="G10" s="2">
+        <v>263</v>
+      </c>
+      <c r="G10" s="1">
         <v>45755</v>
       </c>
       <c r="H10" t="s">
@@ -8752,7 +8766,7 @@
         <v>198</v>
       </c>
       <c r="J10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K10" t="s">
         <v>46</v>
@@ -8760,35 +8774,35 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45754</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="1">
         <v>45849</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="1">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W10" t="s">
         <v>22</v>
       </c>
       <c r="X10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Y10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Z10" t="s">
         <v>22</v>
       </c>
       <c r="AA10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AB10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -8796,18 +8810,18 @@
         <v>3810255268</v>
       </c>
       <c r="C11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>259</v>
-      </c>
-      <c r="E11" s="2">
+        <v>261</v>
+      </c>
+      <c r="E11" s="1">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
-        <v>261</v>
-      </c>
-      <c r="G11" s="2">
+        <v>263</v>
+      </c>
+      <c r="G11" s="1">
         <v>44973</v>
       </c>
       <c r="H11" t="s">
@@ -8817,43 +8831,43 @@
         <v>198</v>
       </c>
       <c r="J11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44973</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="1">
         <v>45687</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" s="1">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W11" t="s">
         <v>22</v>
       </c>
       <c r="X11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Y11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Z11" t="s">
         <v>22</v>
       </c>
       <c r="AA11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AB11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -8861,18 +8875,18 @@
         <v>3810264674</v>
       </c>
       <c r="C12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>259</v>
-      </c>
-      <c r="E12" s="2">
+        <v>261</v>
+      </c>
+      <c r="E12" s="1">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
-        <v>261</v>
-      </c>
-      <c r="G12" s="2">
+        <v>263</v>
+      </c>
+      <c r="G12" s="1">
         <v>45358</v>
       </c>
       <c r="H12" t="s">
@@ -8882,7 +8896,7 @@
         <v>198</v>
       </c>
       <c r="J12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K12" t="s">
         <v>70</v>
@@ -8890,35 +8904,35 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45358</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="1">
         <v>45517</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12" s="1">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W12" t="s">
         <v>22</v>
       </c>
       <c r="X12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Y12" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Z12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AA12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AB12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -8926,18 +8940,18 @@
         <v>3810268863</v>
       </c>
       <c r="C13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>259</v>
-      </c>
-      <c r="E13" s="2">
+        <v>261</v>
+      </c>
+      <c r="E13" s="1">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
-        <v>261</v>
-      </c>
-      <c r="G13" s="2">
+        <v>263</v>
+      </c>
+      <c r="G13" s="1">
         <v>45573</v>
       </c>
       <c r="H13" t="s">
@@ -8947,7 +8961,7 @@
         <v>198</v>
       </c>
       <c r="J13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K13" t="s">
         <v>57</v>
@@ -8955,38 +8969,38 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45572</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="1">
         <v>45572</v>
       </c>
-      <c r="S13" s="2">
+      <c r="S13" s="1">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="V13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="W13" t="s">
         <v>22</v>
       </c>
       <c r="X13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Y13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Z13" t="s">
         <v>22</v>
       </c>
       <c r="AA13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AB13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -8994,18 +9008,18 @@
         <v>3810271550</v>
       </c>
       <c r="C14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>259</v>
-      </c>
-      <c r="E14" s="2">
+        <v>261</v>
+      </c>
+      <c r="E14" s="1">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
-        <v>261</v>
-      </c>
-      <c r="G14" s="2">
+        <v>263</v>
+      </c>
+      <c r="G14" s="1">
         <v>45747</v>
       </c>
       <c r="H14" t="s">
@@ -9015,7 +9029,7 @@
         <v>198</v>
       </c>
       <c r="J14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K14" t="s">
         <v>55</v>
@@ -9023,35 +9037,35 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>45736</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" s="1">
         <v>46101</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14" s="1">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="W14" t="s">
         <v>22</v>
       </c>
       <c r="X14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Y14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Z14" t="s">
         <v>22</v>
       </c>
       <c r="AA14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AB14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -9065,70 +9079,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9140,13 +9154,13 @@
         <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J2" t="s">
         <v>81</v>
@@ -9166,14 +9180,14 @@
       <c r="O2" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>45490</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="S2" t="s">
         <v>145</v>
@@ -9181,19 +9195,19 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B3" t="s">
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J3" t="s">
         <v>81</v>
@@ -9213,14 +9227,14 @@
       <c r="O3" t="s">
         <v>83</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>45618</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="S3" t="s">
         <v>145</v>
@@ -9234,13 +9248,13 @@
         <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J4" t="s">
         <v>81</v>
@@ -9260,14 +9274,14 @@
       <c r="O4" t="s">
         <v>99</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>45539</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="S4" t="s">
         <v>145</v>
@@ -9281,13 +9295,13 @@
         <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J5" t="s">
         <v>81</v>
@@ -9307,14 +9321,14 @@
       <c r="O5" t="s">
         <v>100</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>45567</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="S5" t="s">
         <v>145</v>
@@ -9328,13 +9342,13 @@
         <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J6" t="s">
         <v>81</v>
@@ -9354,14 +9368,14 @@
       <c r="O6" t="s">
         <v>97</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>45568</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="S6" t="s">
         <v>145</v>
@@ -9375,13 +9389,13 @@
         <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E7" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J7" t="s">
         <v>81</v>
@@ -9401,14 +9415,14 @@
       <c r="O7" t="s">
         <v>85</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>45831</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="S7" t="s">
         <v>145</v>
@@ -9422,13 +9436,13 @@
         <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E8" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J8" t="s">
         <v>81</v>
@@ -9448,14 +9462,14 @@
       <c r="O8" t="s">
         <v>105</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45601</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="S8" t="s">
         <v>145</v>
@@ -9469,13 +9483,13 @@
         <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J9" t="s">
         <v>81</v>
@@ -9495,14 +9509,14 @@
       <c r="O9" t="s">
         <v>94</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45631</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="S9" t="s">
         <v>145</v>
@@ -9516,13 +9530,13 @@
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J10" t="s">
         <v>81</v>
@@ -9542,14 +9556,14 @@
       <c r="O10" t="s">
         <v>91</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>43902</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="S10" t="s">
         <v>145</v>
@@ -9557,19 +9571,19 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B11" t="s">
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J11" t="s">
         <v>81</v>
@@ -9589,14 +9603,14 @@
       <c r="O11" t="s">
         <v>101</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>44736</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="S11" t="s">
         <v>145</v>
@@ -9610,13 +9624,13 @@
         <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E12" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J12" t="s">
         <v>81</v>
@@ -9636,14 +9650,14 @@
       <c r="O12" t="s">
         <v>84</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>45776</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="S12" t="s">
         <v>145</v>
@@ -9651,19 +9665,19 @@
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B13" t="s">
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J13" t="s">
         <v>81</v>
@@ -9683,14 +9697,14 @@
       <c r="O13" t="s">
         <v>82</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>45772</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="S13" t="s">
         <v>145</v>
@@ -9704,13 +9718,13 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J14" t="s">
         <v>81</v>
@@ -9730,14 +9744,14 @@
       <c r="O14" t="s">
         <v>102</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45000</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="S14" t="s">
         <v>145</v>
@@ -9751,13 +9765,13 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E15" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J15" t="s">
         <v>81</v>
@@ -9777,7 +9791,7 @@
       <c r="O15" t="s">
         <v>96</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -9792,13 +9806,13 @@
         <v>36</v>
       </c>
       <c r="C16" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E16" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I16" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J16" t="s">
         <v>81</v>
@@ -9818,7 +9832,7 @@
       <c r="O16" t="s">
         <v>92</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -9833,13 +9847,13 @@
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E17" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I17" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J17" t="s">
         <v>81</v>
@@ -9859,14 +9873,14 @@
       <c r="O17" t="s">
         <v>95</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45371</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="S17" t="s">
         <v>145</v>
@@ -9880,13 +9894,13 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E18" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I18" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J18" t="s">
         <v>81</v>
@@ -9906,14 +9920,14 @@
       <c r="O18" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>46001</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="S18" t="s">
         <v>145</v>
@@ -9927,13 +9941,13 @@
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E19" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J19" t="s">
         <v>81</v>
@@ -9953,14 +9967,14 @@
       <c r="O19" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45436</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="S19" t="s">
         <v>145</v>
@@ -9974,13 +9988,13 @@
         <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E20" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I20" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J20" t="s">
         <v>81</v>
@@ -10000,14 +10014,14 @@
       <c r="O20" t="s">
         <v>98</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>44372</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="S20" t="s">
         <v>145</v>
@@ -10021,13 +10035,13 @@
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E21" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I21" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J21" t="s">
         <v>81</v>
@@ -10047,14 +10061,14 @@
       <c r="O21" t="s">
         <v>107</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>44362</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="S21" t="s">
         <v>145</v>
@@ -10068,13 +10082,13 @@
         <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E22" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I22" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J22" t="s">
         <v>81</v>
@@ -10094,14 +10108,14 @@
       <c r="O22" t="s">
         <v>88</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="S22" t="s">
         <v>145</v>
@@ -10115,13 +10129,13 @@
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J23" t="s">
         <v>81</v>
@@ -10133,24 +10147,24 @@
         <v>4000</v>
       </c>
       <c r="O23" t="s">
-        <v>354</v>
-      </c>
-      <c r="P23" s="2">
+        <v>356</v>
+      </c>
+      <c r="P23" s="1">
         <v>40044</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="S23" t="s">
         <v>144</v>
       </c>
       <c r="T23" t="s">
-        <v>394</v>
-      </c>
-      <c r="U23" s="2">
+        <v>396</v>
+      </c>
+      <c r="U23" s="1">
         <v>45775</v>
       </c>
     </row>
@@ -10162,13 +10176,13 @@
         <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I24" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J24" t="s">
         <v>81</v>
@@ -10188,22 +10202,22 @@
       <c r="O24" t="s">
         <v>82</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>43549</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="S24" t="s">
         <v>144</v>
       </c>
       <c r="T24" t="s">
-        <v>395</v>
-      </c>
-      <c r="U24" s="2">
+        <v>397</v>
+      </c>
+      <c r="U24" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -10215,13 +10229,13 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E25" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I25" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J25" t="s">
         <v>81</v>
@@ -10241,22 +10255,22 @@
       <c r="O25" t="s">
         <v>88</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45447</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="S25" t="s">
         <v>144</v>
       </c>
       <c r="T25" t="s">
-        <v>396</v>
-      </c>
-      <c r="U25" s="2">
+        <v>398</v>
+      </c>
+      <c r="U25" s="1">
         <v>45937</v>
       </c>
     </row>
@@ -10268,13 +10282,13 @@
         <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E26" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I26" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J26" t="s">
         <v>81</v>
@@ -10294,22 +10308,22 @@
       <c r="O26" t="s">
         <v>102</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>44485</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="S26" t="s">
         <v>144</v>
       </c>
       <c r="T26" t="s">
-        <v>397</v>
-      </c>
-      <c r="U26" s="2">
+        <v>399</v>
+      </c>
+      <c r="U26" s="1">
         <v>45580</v>
       </c>
     </row>
@@ -10321,13 +10335,13 @@
         <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E27" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I27" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J27" t="s">
         <v>81</v>
@@ -10347,22 +10361,22 @@
       <c r="O27" t="s">
         <v>88</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45420</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="S27" t="s">
         <v>144</v>
       </c>
       <c r="T27" t="s">
-        <v>398</v>
-      </c>
-      <c r="U27" s="2">
+        <v>400</v>
+      </c>
+      <c r="U27" s="1">
         <v>45588</v>
       </c>
     </row>
@@ -10374,13 +10388,13 @@
         <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E28" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I28" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J28" t="s">
         <v>81</v>
@@ -10400,22 +10414,22 @@
       <c r="O28" t="s">
         <v>103</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>44369</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="S28" t="s">
         <v>144</v>
       </c>
       <c r="T28" t="s">
-        <v>399</v>
-      </c>
-      <c r="U28" s="2">
+        <v>401</v>
+      </c>
+      <c r="U28" s="1">
         <v>45831</v>
       </c>
     </row>
@@ -10427,13 +10441,13 @@
         <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E29" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I29" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J29" t="s">
         <v>81</v>
@@ -10453,22 +10467,22 @@
       <c r="O29" t="s">
         <v>100</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44652</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="S29" t="s">
         <v>144</v>
       </c>
       <c r="T29" t="s">
-        <v>400</v>
-      </c>
-      <c r="U29" s="2">
+        <v>402</v>
+      </c>
+      <c r="U29" s="1">
         <v>45734</v>
       </c>
     </row>
@@ -10480,13 +10494,13 @@
         <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E30" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I30" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J30" t="s">
         <v>81</v>
@@ -10498,9 +10512,9 @@
         <v>144</v>
       </c>
       <c r="T30" t="s">
-        <v>401</v>
-      </c>
-      <c r="U30" s="2">
+        <v>403</v>
+      </c>
+      <c r="U30" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10512,13 +10526,13 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E31" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I31" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J31" t="s">
         <v>81</v>
@@ -10530,9 +10544,9 @@
         <v>144</v>
       </c>
       <c r="T31" t="s">
-        <v>402</v>
-      </c>
-      <c r="U31" s="2">
+        <v>404</v>
+      </c>
+      <c r="U31" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10544,13 +10558,13 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E32" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I32" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J32" t="s">
         <v>81</v>
@@ -10562,9 +10576,9 @@
         <v>144</v>
       </c>
       <c r="T32" t="s">
-        <v>403</v>
-      </c>
-      <c r="U32" s="2">
+        <v>405</v>
+      </c>
+      <c r="U32" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10576,13 +10590,13 @@
         <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E33" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I33" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J33" t="s">
         <v>81</v>
@@ -10602,22 +10616,22 @@
       <c r="O33" t="s">
         <v>92</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>43762</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="S33" t="s">
         <v>148</v>
       </c>
       <c r="T33" t="s">
-        <v>382</v>
-      </c>
-      <c r="U33" s="2">
+        <v>384</v>
+      </c>
+      <c r="U33" s="1">
         <v>46037</v>
       </c>
     </row>
@@ -10629,13 +10643,13 @@
         <v>36</v>
       </c>
       <c r="C34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E34" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I34" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J34" t="s">
         <v>81</v>
@@ -10653,36 +10667,36 @@
         <v>4000</v>
       </c>
       <c r="O34" t="s">
-        <v>355</v>
-      </c>
-      <c r="P34" s="2">
+        <v>357</v>
+      </c>
+      <c r="P34" s="1">
         <v>40071</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>149</v>
       </c>
-      <c r="U34" s="2">
+      <c r="U34" s="1">
         <v>41023</v>
       </c>
     </row>
     <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s">
         <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E35" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I35" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J35" t="s">
         <v>81</v>
@@ -10696,19 +10710,19 @@
       <c r="O35" t="s">
         <v>89</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>44784</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="S35" t="s">
         <v>149</v>
       </c>
-      <c r="U35" s="2">
+      <c r="U35" s="1">
         <v>45259</v>
       </c>
     </row>
@@ -10720,13 +10734,13 @@
         <v>36</v>
       </c>
       <c r="C36" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E36" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J36" t="s">
         <v>81</v>
@@ -10746,19 +10760,19 @@
       <c r="O36" t="s">
         <v>93</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45103</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="S36" t="s">
         <v>149</v>
       </c>
-      <c r="U36" s="2">
+      <c r="U36" s="1">
         <v>46000</v>
       </c>
     </row>
@@ -10770,13 +10784,13 @@
         <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E37" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I37" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J37" t="s">
         <v>81</v>
@@ -10796,13 +10810,13 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E38" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I38" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J38" t="s">
         <v>81</v>
@@ -10822,19 +10836,19 @@
       <c r="O38" t="s">
         <v>98</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>38511</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="S38" t="s">
         <v>149</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>39068</v>
       </c>
     </row>
@@ -10846,13 +10860,13 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E39" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I39" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J39" t="s">
         <v>81</v>
@@ -10872,22 +10886,22 @@
       <c r="O39" t="s">
         <v>105</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>39006</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="S39" t="s">
         <v>149</v>
       </c>
       <c r="T39" t="s">
-        <v>404</v>
-      </c>
-      <c r="U39" s="2">
+        <v>406</v>
+      </c>
+      <c r="U39" s="1">
         <v>40568</v>
       </c>
     </row>
@@ -10899,13 +10913,13 @@
         <v>36</v>
       </c>
       <c r="C40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E40" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I40" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J40" t="s">
         <v>81</v>
@@ -10919,22 +10933,22 @@
       <c r="O40" t="s">
         <v>102</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>40836</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="S40" t="s">
         <v>149</v>
       </c>
       <c r="T40" t="s">
-        <v>405</v>
-      </c>
-      <c r="U40" s="2">
+        <v>407</v>
+      </c>
+      <c r="U40" s="1">
         <v>42270</v>
       </c>
     </row>
@@ -10946,13 +10960,13 @@
         <v>36</v>
       </c>
       <c r="C41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I41" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J41" t="s">
         <v>81</v>
@@ -10972,22 +10986,22 @@
       <c r="O41" t="s">
         <v>97</v>
       </c>
-      <c r="P41" s="2">
+      <c r="P41" s="1">
         <v>42940</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="1">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="S41" t="s">
         <v>146</v>
       </c>
       <c r="T41" t="s">
-        <v>406</v>
-      </c>
-      <c r="U41" s="2">
+        <v>408</v>
+      </c>
+      <c r="U41" s="1">
         <v>44148</v>
       </c>
     </row>
@@ -10999,13 +11013,13 @@
         <v>36</v>
       </c>
       <c r="C42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E42" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I42" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J42" t="s">
         <v>81</v>
@@ -11025,22 +11039,22 @@
       <c r="O42" t="s">
         <v>84</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="1">
         <v>43696</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="1">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="S42" t="s">
         <v>146</v>
       </c>
       <c r="T42" t="s">
-        <v>407</v>
-      </c>
-      <c r="U42" s="2">
+        <v>409</v>
+      </c>
+      <c r="U42" s="1">
         <v>43185</v>
       </c>
     </row>
@@ -11052,13 +11066,13 @@
         <v>36</v>
       </c>
       <c r="C43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E43" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I43" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J43" t="s">
         <v>81</v>
@@ -11078,22 +11092,22 @@
       <c r="O43" t="s">
         <v>86</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="1">
         <v>43544</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="1">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="S43" t="s">
         <v>146</v>
       </c>
       <c r="T43" t="s">
-        <v>408</v>
-      </c>
-      <c r="U43" s="2">
+        <v>410</v>
+      </c>
+      <c r="U43" s="1">
         <v>42850</v>
       </c>
     </row>
@@ -11105,13 +11119,13 @@
         <v>36</v>
       </c>
       <c r="C44" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E44" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I44" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J44" t="s">
         <v>81</v>
@@ -11131,22 +11145,22 @@
       <c r="O44" t="s">
         <v>99</v>
       </c>
-      <c r="P44" s="2">
+      <c r="P44" s="1">
         <v>45076</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="1">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="S44" t="s">
         <v>146</v>
       </c>
       <c r="T44" t="s">
-        <v>409</v>
-      </c>
-      <c r="U44" s="2">
+        <v>411</v>
+      </c>
+      <c r="U44" s="1">
         <v>44404</v>
       </c>
     </row>
@@ -11158,13 +11172,13 @@
         <v>36</v>
       </c>
       <c r="C45" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I45" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J45" t="s">
         <v>81</v>
@@ -11184,22 +11198,22 @@
       <c r="O45" t="s">
         <v>83</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="1">
         <v>42963</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="1">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="S45" t="s">
         <v>146</v>
       </c>
       <c r="T45" t="s">
-        <v>410</v>
-      </c>
-      <c r="U45" s="2">
+        <v>412</v>
+      </c>
+      <c r="U45" s="1">
         <v>42698</v>
       </c>
     </row>
@@ -11211,13 +11225,13 @@
         <v>36</v>
       </c>
       <c r="C46" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I46" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J46" t="s">
         <v>81</v>
@@ -11237,22 +11251,22 @@
       <c r="O46" t="s">
         <v>90</v>
       </c>
-      <c r="P46" s="2">
+      <c r="P46" s="1">
         <v>45054</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="1">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="S46" t="s">
         <v>146</v>
       </c>
       <c r="T46" t="s">
-        <v>411</v>
-      </c>
-      <c r="U46" s="2">
+        <v>413</v>
+      </c>
+      <c r="U46" s="1">
         <v>43941</v>
       </c>
     </row>
@@ -11267,26 +11281,26 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" t="s">
         <v>414</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" t="s">
         <v>415</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E1" t="s">
         <v>416</v>
+      </c>
+      <c r="F1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G1" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -11965,40 +11979,40 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" t="s">
         <v>419</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" t="s">
         <v>420</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" t="s">
         <v>421</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" t="s">
         <v>422</v>
+      </c>
+      <c r="E1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F1" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F2">
         <v>200000</v>
@@ -12006,19 +12020,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F3">
         <v>700000</v>
@@ -12026,19 +12040,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F4">
         <v>800000</v>
@@ -12046,19 +12060,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B5" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D5" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E5" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F5">
         <v>400000</v>
@@ -12066,19 +12080,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F6">
         <v>400000</v>
@@ -12086,19 +12100,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F7">
         <v>400000</v>
@@ -12106,19 +12120,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D8" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F8">
         <v>1000000</v>
@@ -12126,19 +12140,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D9" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E9" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F9">
         <v>1000000</v>
@@ -12146,19 +12160,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D10" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F10">
         <v>1000000</v>
@@ -12166,19 +12180,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B11" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C11" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E11" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F11">
         <v>563000</v>
@@ -12186,19 +12200,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B12" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C12" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D12" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E12" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F12">
         <v>320000</v>
@@ -12206,19 +12220,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B13" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E13" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F13">
         <v>120000</v>
@@ -12226,19 +12240,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C14" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D14" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E14" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F14">
         <v>120000</v>
@@ -12246,19 +12260,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B15" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C15" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D15" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E15" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F15">
         <v>80000</v>
@@ -12266,19 +12280,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B16" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C16" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D16" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E16" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F16">
         <v>80000</v>
@@ -12286,19 +12300,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B17" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C17" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D17" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E17" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F17">
         <v>3800000</v>
@@ -12306,19 +12320,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B18" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C18" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D18" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E18" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F18">
         <v>3800000</v>
@@ -12326,19 +12340,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B19" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C19" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D19" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E19" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F19">
         <v>3800000</v>
@@ -12346,19 +12360,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B20" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C20" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D20" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E20" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F20">
         <v>3800000</v>
@@ -12366,19 +12380,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B21" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C21" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D21" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E21" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F21">
         <v>3800000</v>
@@ -12386,19 +12400,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B22" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C22" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D22" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E22" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F22">
         <v>3800000</v>
@@ -12406,19 +12420,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B23" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C23" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D23" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E23" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F23">
         <v>430000</v>
@@ -12426,19 +12440,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B24" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C24" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D24" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E24" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F24">
         <v>430000</v>
@@ -12446,19 +12460,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B25" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C25" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D25" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E25" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F25">
         <v>425000</v>
@@ -12466,19 +12480,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B26" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C26" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D26" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E26" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F26">
         <v>60000</v>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1433,8 +1433,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1450,7 +1458,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1458,12 +1466,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1763,70 +1789,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1867,10 +1893,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>41754</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1882,7 +1908,7 @@
       <c r="T2" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="1">
+      <c r="U2" s="2">
         <v>46170</v>
       </c>
     </row>
@@ -1923,10 +1949,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>44709</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1973,10 +1999,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>44348</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -2020,10 +2046,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>46059</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -2035,7 +2061,7 @@
       <c r="T5" t="s">
         <v>151</v>
       </c>
-      <c r="U5" s="1">
+      <c r="U5" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -2076,10 +2102,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>46149</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -2126,10 +2152,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>43731</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -2141,7 +2167,7 @@
       <c r="T7" t="s">
         <v>152</v>
       </c>
-      <c r="U7" s="1">
+      <c r="U7" s="2">
         <v>43507</v>
       </c>
     </row>
@@ -2182,10 +2208,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45511</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2232,10 +2258,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45716</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2247,7 +2273,7 @@
       <c r="T9" t="s">
         <v>153</v>
       </c>
-      <c r="U9" s="1">
+      <c r="U9" s="2">
         <v>44665</v>
       </c>
     </row>
@@ -2288,10 +2314,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>45064</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2329,10 +2355,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>46135</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2344,7 +2370,7 @@
       <c r="T11" t="s">
         <v>154</v>
       </c>
-      <c r="U11" s="1">
+      <c r="U11" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -2385,7 +2411,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2429,10 +2455,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>46199</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2479,10 +2505,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45667</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2494,7 +2520,7 @@
       <c r="T14" t="s">
         <v>155</v>
       </c>
-      <c r="U14" s="1">
+      <c r="U14" s="2">
         <v>46072</v>
       </c>
     </row>
@@ -2535,10 +2561,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>46064</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="Q15" s="2">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2585,10 +2611,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>44285</v>
       </c>
-      <c r="Q16" s="1">
+      <c r="Q16" s="2">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2600,7 +2626,7 @@
       <c r="T16" t="s">
         <v>156</v>
       </c>
-      <c r="U16" s="1">
+      <c r="U16" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2641,10 +2667,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45922</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2691,10 +2717,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>45930</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2706,7 +2732,7 @@
       <c r="T18" t="s">
         <v>157</v>
       </c>
-      <c r="U18" s="1">
+      <c r="U18" s="2">
         <v>46198</v>
       </c>
     </row>
@@ -2747,10 +2773,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45524</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2762,7 +2788,7 @@
       <c r="T19" t="s">
         <v>124</v>
       </c>
-      <c r="U19" s="1">
+      <c r="U19" s="2">
         <v>46153</v>
       </c>
     </row>
@@ -2803,10 +2829,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>45026</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2818,7 +2844,7 @@
       <c r="T20" t="s">
         <v>158</v>
       </c>
-      <c r="U20" s="1">
+      <c r="U20" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2859,10 +2885,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>45159</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2874,7 +2900,7 @@
       <c r="T21" t="s">
         <v>126</v>
       </c>
-      <c r="U21" s="1">
+      <c r="U21" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -2915,10 +2941,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2930,7 +2956,7 @@
       <c r="T22" t="s">
         <v>159</v>
       </c>
-      <c r="U22" s="1">
+      <c r="U22" s="2">
         <v>45995</v>
       </c>
     </row>
@@ -2968,10 +2994,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>45713</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -2980,7 +3006,7 @@
       <c r="S23" t="s">
         <v>149</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -3021,10 +3047,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>46062</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>46220</v>
       </c>
       <c r="R24" t="s">
@@ -3033,7 +3059,7 @@
       <c r="S24" t="s">
         <v>149</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24" s="2">
         <v>46220</v>
       </c>
     </row>
@@ -3074,10 +3100,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45079</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -3124,10 +3150,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>41346</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -3139,7 +3165,7 @@
       <c r="T26" t="s">
         <v>160</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>46150</v>
       </c>
     </row>
@@ -3180,10 +3206,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45579</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3230,10 +3256,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>46171</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3280,10 +3306,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44320</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3330,10 +3356,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="2">
         <v>42661</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="Q30" s="2">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3345,7 +3371,7 @@
       <c r="T30" t="s">
         <v>161</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="2">
         <v>45358</v>
       </c>
     </row>
@@ -3386,10 +3412,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="2">
         <v>46220</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="Q31" s="2">
         <v>46220</v>
       </c>
       <c r="R31" t="s">
@@ -3436,10 +3462,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="2">
         <v>43797</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="Q32" s="2">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3486,10 +3512,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>42810</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3501,7 +3527,7 @@
       <c r="T33" t="s">
         <v>162</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="2">
         <v>43802</v>
       </c>
     </row>
@@ -3542,10 +3568,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>45070</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>44910</v>
       </c>
       <c r="R34" t="s">
@@ -3592,10 +3618,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>43250</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3642,10 +3668,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45841</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3692,10 +3718,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="2">
         <v>45105</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="Q37" s="2">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3707,7 +3733,7 @@
       <c r="T37" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="1">
+      <c r="U37" s="2">
         <v>46184</v>
       </c>
     </row>
@@ -3748,10 +3774,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>45636</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>46219</v>
       </c>
       <c r="S38" t="s">
@@ -3760,7 +3786,7 @@
       <c r="T38" t="s">
         <v>164</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="2">
         <v>45351</v>
       </c>
     </row>
@@ -3801,10 +3827,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>45831</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3848,10 +3874,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>44287</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3872,22 +3898,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>170</v>
       </c>
     </row>
@@ -8132,91 +8158,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>257</v>
       </c>
     </row>
@@ -8230,13 +8256,13 @@
       <c r="D2" t="s">
         <v>260</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
         <v>263</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="2">
         <v>45492</v>
       </c>
       <c r="H2" t="s">
@@ -8254,13 +8280,13 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45491</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="2">
         <v>45528</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="2">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
@@ -8298,13 +8324,13 @@
       <c r="D3" t="s">
         <v>261</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
         <v>263</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="2">
         <v>45631</v>
       </c>
       <c r="H3" t="s">
@@ -8322,13 +8348,13 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>45628</v>
       </c>
-      <c r="R3" s="1">
+      <c r="R3" s="2">
         <v>45632</v>
       </c>
-      <c r="S3" s="1">
+      <c r="S3" s="2">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
@@ -8363,13 +8389,13 @@
       <c r="D4" t="s">
         <v>261</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
         <v>263</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="2">
         <v>45716</v>
       </c>
       <c r="H4" t="s">
@@ -8387,13 +8413,13 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45716</v>
       </c>
-      <c r="R4" s="1">
+      <c r="R4" s="2">
         <v>45722</v>
       </c>
-      <c r="S4" s="1">
+      <c r="S4" s="2">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
@@ -8428,13 +8454,13 @@
       <c r="D5" t="s">
         <v>261</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
         <v>263</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="2">
         <v>45728</v>
       </c>
       <c r="H5" t="s">
@@ -8452,13 +8478,13 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45722</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R5" s="2">
         <v>45782</v>
       </c>
-      <c r="S5" s="1">
+      <c r="S5" s="2">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
@@ -8496,13 +8522,13 @@
       <c r="D6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
         <v>263</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="2">
         <v>45755</v>
       </c>
       <c r="H6" t="s">
@@ -8520,13 +8546,13 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45728</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R6" s="2">
         <v>45734</v>
       </c>
-      <c r="S6" s="1">
+      <c r="S6" s="2">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
@@ -8564,7 +8590,7 @@
       <c r="D7" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
@@ -8585,10 +8611,10 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45772</v>
       </c>
-      <c r="R7" s="1">
+      <c r="R7" s="2">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
@@ -8626,7 +8652,7 @@
       <c r="D8" t="s">
         <v>262</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
@@ -8647,10 +8673,10 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>45762</v>
       </c>
-      <c r="R8" s="1">
+      <c r="R8" s="2">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
@@ -8688,7 +8714,7 @@
       <c r="D9" t="s">
         <v>262</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
@@ -8709,10 +8735,10 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45763</v>
       </c>
-      <c r="R9" s="1">
+      <c r="R9" s="2">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
@@ -8750,13 +8776,13 @@
       <c r="D10" t="s">
         <v>261</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="2">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
         <v>263</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="2">
         <v>45755</v>
       </c>
       <c r="H10" t="s">
@@ -8774,13 +8800,13 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45754</v>
       </c>
-      <c r="R10" s="1">
+      <c r="R10" s="2">
         <v>45849</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S10" s="2">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
@@ -8815,13 +8841,13 @@
       <c r="D11" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
         <v>263</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="2">
         <v>44973</v>
       </c>
       <c r="H11" t="s">
@@ -8839,13 +8865,13 @@
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44973</v>
       </c>
-      <c r="R11" s="1">
+      <c r="R11" s="2">
         <v>45687</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S11" s="2">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
@@ -8880,13 +8906,13 @@
       <c r="D12" t="s">
         <v>261</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
         <v>263</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="2">
         <v>45358</v>
       </c>
       <c r="H12" t="s">
@@ -8904,13 +8930,13 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45358</v>
       </c>
-      <c r="R12" s="1">
+      <c r="R12" s="2">
         <v>45517</v>
       </c>
-      <c r="S12" s="1">
+      <c r="S12" s="2">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
@@ -8945,13 +8971,13 @@
       <c r="D13" t="s">
         <v>261</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
         <v>263</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="2">
         <v>45573</v>
       </c>
       <c r="H13" t="s">
@@ -8969,13 +8995,13 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45572</v>
       </c>
-      <c r="R13" s="1">
+      <c r="R13" s="2">
         <v>45572</v>
       </c>
-      <c r="S13" s="1">
+      <c r="S13" s="2">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
@@ -9013,13 +9039,13 @@
       <c r="D14" t="s">
         <v>261</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
         <v>263</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="2">
         <v>45747</v>
       </c>
       <c r="H14" t="s">
@@ -9037,13 +9063,13 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>45736</v>
       </c>
-      <c r="R14" s="1">
+      <c r="R14" s="2">
         <v>46101</v>
       </c>
-      <c r="S14" s="1">
+      <c r="S14" s="2">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
@@ -9079,70 +9105,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9180,10 +9206,10 @@
       <c r="O2" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>45490</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -9227,10 +9253,10 @@
       <c r="O3" t="s">
         <v>83</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>45618</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -9274,10 +9300,10 @@
       <c r="O4" t="s">
         <v>99</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>45539</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -9321,10 +9347,10 @@
       <c r="O5" t="s">
         <v>100</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>45567</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -9368,10 +9394,10 @@
       <c r="O6" t="s">
         <v>97</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>45568</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -9415,10 +9441,10 @@
       <c r="O7" t="s">
         <v>85</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>45831</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -9462,10 +9488,10 @@
       <c r="O8" t="s">
         <v>105</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45601</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -9509,10 +9535,10 @@
       <c r="O9" t="s">
         <v>94</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45631</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -9556,10 +9582,10 @@
       <c r="O10" t="s">
         <v>91</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>43902</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -9603,10 +9629,10 @@
       <c r="O11" t="s">
         <v>101</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>44736</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -9650,10 +9676,10 @@
       <c r="O12" t="s">
         <v>84</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>45776</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -9697,10 +9723,10 @@
       <c r="O13" t="s">
         <v>82</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>45772</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -9744,10 +9770,10 @@
       <c r="O14" t="s">
         <v>102</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45000</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -9791,7 +9817,7 @@
       <c r="O15" t="s">
         <v>96</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -9832,7 +9858,7 @@
       <c r="O16" t="s">
         <v>92</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -9873,10 +9899,10 @@
       <c r="O17" t="s">
         <v>95</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45371</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -9920,10 +9946,10 @@
       <c r="O18" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>46001</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -9967,10 +9993,10 @@
       <c r="O19" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45436</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -10014,10 +10040,10 @@
       <c r="O20" t="s">
         <v>98</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>44372</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -10061,10 +10087,10 @@
       <c r="O21" t="s">
         <v>107</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>44362</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -10108,10 +10134,10 @@
       <c r="O22" t="s">
         <v>88</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -10149,10 +10175,10 @@
       <c r="O23" t="s">
         <v>356</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>40044</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -10164,7 +10190,7 @@
       <c r="T23" t="s">
         <v>396</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>45775</v>
       </c>
     </row>
@@ -10202,10 +10228,10 @@
       <c r="O24" t="s">
         <v>82</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>43549</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -10217,7 +10243,7 @@
       <c r="T24" t="s">
         <v>397</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -10255,10 +10281,10 @@
       <c r="O25" t="s">
         <v>88</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45447</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -10270,7 +10296,7 @@
       <c r="T25" t="s">
         <v>398</v>
       </c>
-      <c r="U25" s="1">
+      <c r="U25" s="2">
         <v>45937</v>
       </c>
     </row>
@@ -10308,10 +10334,10 @@
       <c r="O26" t="s">
         <v>102</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>44485</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -10323,7 +10349,7 @@
       <c r="T26" t="s">
         <v>399</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>45580</v>
       </c>
     </row>
@@ -10361,10 +10387,10 @@
       <c r="O27" t="s">
         <v>88</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45420</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -10376,7 +10402,7 @@
       <c r="T27" t="s">
         <v>400</v>
       </c>
-      <c r="U27" s="1">
+      <c r="U27" s="2">
         <v>45588</v>
       </c>
     </row>
@@ -10414,10 +10440,10 @@
       <c r="O28" t="s">
         <v>103</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>44369</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -10429,7 +10455,7 @@
       <c r="T28" t="s">
         <v>401</v>
       </c>
-      <c r="U28" s="1">
+      <c r="U28" s="2">
         <v>45831</v>
       </c>
     </row>
@@ -10467,10 +10493,10 @@
       <c r="O29" t="s">
         <v>100</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44652</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -10482,7 +10508,7 @@
       <c r="T29" t="s">
         <v>402</v>
       </c>
-      <c r="U29" s="1">
+      <c r="U29" s="2">
         <v>45734</v>
       </c>
     </row>
@@ -10514,7 +10540,7 @@
       <c r="T30" t="s">
         <v>403</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10546,7 +10572,7 @@
       <c r="T31" t="s">
         <v>404</v>
       </c>
-      <c r="U31" s="1">
+      <c r="U31" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10578,7 +10604,7 @@
       <c r="T32" t="s">
         <v>405</v>
       </c>
-      <c r="U32" s="1">
+      <c r="U32" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -10616,10 +10642,10 @@
       <c r="O33" t="s">
         <v>92</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>43762</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -10631,7 +10657,7 @@
       <c r="T33" t="s">
         <v>384</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="2">
         <v>46037</v>
       </c>
     </row>
@@ -10669,16 +10695,16 @@
       <c r="O34" t="s">
         <v>357</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>40071</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>149</v>
       </c>
-      <c r="U34" s="1">
+      <c r="U34" s="2">
         <v>41023</v>
       </c>
     </row>
@@ -10710,10 +10736,10 @@
       <c r="O35" t="s">
         <v>89</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>44784</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -10722,7 +10748,7 @@
       <c r="S35" t="s">
         <v>149</v>
       </c>
-      <c r="U35" s="1">
+      <c r="U35" s="2">
         <v>45259</v>
       </c>
     </row>
@@ -10760,10 +10786,10 @@
       <c r="O36" t="s">
         <v>93</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45103</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -10772,7 +10798,7 @@
       <c r="S36" t="s">
         <v>149</v>
       </c>
-      <c r="U36" s="1">
+      <c r="U36" s="2">
         <v>46000</v>
       </c>
     </row>
@@ -10836,10 +10862,10 @@
       <c r="O38" t="s">
         <v>98</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>38511</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -10848,7 +10874,7 @@
       <c r="S38" t="s">
         <v>149</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="2">
         <v>39068</v>
       </c>
     </row>
@@ -10886,10 +10912,10 @@
       <c r="O39" t="s">
         <v>105</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>39006</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -10901,7 +10927,7 @@
       <c r="T39" t="s">
         <v>406</v>
       </c>
-      <c r="U39" s="1">
+      <c r="U39" s="2">
         <v>40568</v>
       </c>
     </row>
@@ -10933,10 +10959,10 @@
       <c r="O40" t="s">
         <v>102</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>40836</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -10948,7 +10974,7 @@
       <c r="T40" t="s">
         <v>407</v>
       </c>
-      <c r="U40" s="1">
+      <c r="U40" s="2">
         <v>42270</v>
       </c>
     </row>
@@ -10986,10 +11012,10 @@
       <c r="O41" t="s">
         <v>97</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P41" s="2">
         <v>42940</v>
       </c>
-      <c r="Q41" s="1">
+      <c r="Q41" s="2">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -11001,7 +11027,7 @@
       <c r="T41" t="s">
         <v>408</v>
       </c>
-      <c r="U41" s="1">
+      <c r="U41" s="2">
         <v>44148</v>
       </c>
     </row>
@@ -11039,10 +11065,10 @@
       <c r="O42" t="s">
         <v>84</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P42" s="2">
         <v>43696</v>
       </c>
-      <c r="Q42" s="1">
+      <c r="Q42" s="2">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -11054,7 +11080,7 @@
       <c r="T42" t="s">
         <v>409</v>
       </c>
-      <c r="U42" s="1">
+      <c r="U42" s="2">
         <v>43185</v>
       </c>
     </row>
@@ -11092,10 +11118,10 @@
       <c r="O43" t="s">
         <v>86</v>
       </c>
-      <c r="P43" s="1">
+      <c r="P43" s="2">
         <v>43544</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="Q43" s="2">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -11107,7 +11133,7 @@
       <c r="T43" t="s">
         <v>410</v>
       </c>
-      <c r="U43" s="1">
+      <c r="U43" s="2">
         <v>42850</v>
       </c>
     </row>
@@ -11145,10 +11171,10 @@
       <c r="O44" t="s">
         <v>99</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P44" s="2">
         <v>45076</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="Q44" s="2">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -11160,7 +11186,7 @@
       <c r="T44" t="s">
         <v>411</v>
       </c>
-      <c r="U44" s="1">
+      <c r="U44" s="2">
         <v>44404</v>
       </c>
     </row>
@@ -11198,10 +11224,10 @@
       <c r="O45" t="s">
         <v>83</v>
       </c>
-      <c r="P45" s="1">
+      <c r="P45" s="2">
         <v>42963</v>
       </c>
-      <c r="Q45" s="1">
+      <c r="Q45" s="2">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -11213,7 +11239,7 @@
       <c r="T45" t="s">
         <v>412</v>
       </c>
-      <c r="U45" s="1">
+      <c r="U45" s="2">
         <v>42698</v>
       </c>
     </row>
@@ -11251,10 +11277,10 @@
       <c r="O46" t="s">
         <v>90</v>
       </c>
-      <c r="P46" s="1">
+      <c r="P46" s="2">
         <v>45054</v>
       </c>
-      <c r="Q46" s="1">
+      <c r="Q46" s="2">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -11266,7 +11292,7 @@
       <c r="T46" t="s">
         <v>413</v>
       </c>
-      <c r="U46" s="1">
+      <c r="U46" s="2">
         <v>43941</v>
       </c>
     </row>
@@ -11281,25 +11307,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>418</v>
       </c>
     </row>
@@ -11979,22 +12005,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>424</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1433,16 +1433,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1458,7 +1450,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1466,30 +1458,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1789,70 +1763,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1893,10 +1867,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>41754</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1908,7 +1882,7 @@
       <c r="T2" t="s">
         <v>150</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="1">
         <v>46170</v>
       </c>
     </row>
@@ -1949,10 +1923,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>44709</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1999,10 +1973,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>44348</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -2046,10 +2020,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>46059</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -2061,7 +2035,7 @@
       <c r="T5" t="s">
         <v>151</v>
       </c>
-      <c r="U5" s="2">
+      <c r="U5" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -2102,10 +2076,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>46149</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -2152,10 +2126,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>43731</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -2167,7 +2141,7 @@
       <c r="T7" t="s">
         <v>152</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U7" s="1">
         <v>43507</v>
       </c>
     </row>
@@ -2208,10 +2182,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45511</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2258,10 +2232,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45716</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2273,7 +2247,7 @@
       <c r="T9" t="s">
         <v>153</v>
       </c>
-      <c r="U9" s="2">
+      <c r="U9" s="1">
         <v>44665</v>
       </c>
     </row>
@@ -2314,10 +2288,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>45064</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2355,10 +2329,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>46135</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2370,7 +2344,7 @@
       <c r="T11" t="s">
         <v>154</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -2411,7 +2385,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2455,10 +2429,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>46199</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2505,10 +2479,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45667</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2520,7 +2494,7 @@
       <c r="T14" t="s">
         <v>155</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" s="1">
         <v>46072</v>
       </c>
     </row>
@@ -2561,10 +2535,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>46064</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="1">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2611,10 +2585,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>44285</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="1">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2626,7 +2600,7 @@
       <c r="T16" t="s">
         <v>156</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2667,10 +2641,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45922</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2717,10 +2691,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>45930</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2732,7 +2706,7 @@
       <c r="T18" t="s">
         <v>157</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" s="1">
         <v>46198</v>
       </c>
     </row>
@@ -2773,10 +2747,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45524</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2788,7 +2762,7 @@
       <c r="T19" t="s">
         <v>124</v>
       </c>
-      <c r="U19" s="2">
+      <c r="U19" s="1">
         <v>46153</v>
       </c>
     </row>
@@ -2829,10 +2803,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>45026</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2844,7 +2818,7 @@
       <c r="T20" t="s">
         <v>158</v>
       </c>
-      <c r="U20" s="2">
+      <c r="U20" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2885,10 +2859,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>45159</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2900,7 +2874,7 @@
       <c r="T21" t="s">
         <v>126</v>
       </c>
-      <c r="U21" s="2">
+      <c r="U21" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2941,10 +2915,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2956,7 +2930,7 @@
       <c r="T22" t="s">
         <v>159</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" s="1">
         <v>45995</v>
       </c>
     </row>
@@ -2994,10 +2968,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>45713</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -3006,7 +2980,7 @@
       <c r="S23" t="s">
         <v>149</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -3047,10 +3021,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>46062</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>46220</v>
       </c>
       <c r="R24" t="s">
@@ -3059,7 +3033,7 @@
       <c r="S24" t="s">
         <v>149</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="1">
         <v>46220</v>
       </c>
     </row>
@@ -3100,10 +3074,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45079</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -3150,10 +3124,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>41346</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -3165,7 +3139,7 @@
       <c r="T26" t="s">
         <v>160</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>46150</v>
       </c>
     </row>
@@ -3206,10 +3180,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45579</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3256,10 +3230,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>46171</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3306,10 +3280,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44320</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3356,10 +3330,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="1">
         <v>42661</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="1">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3371,7 +3345,7 @@
       <c r="T30" t="s">
         <v>161</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>45358</v>
       </c>
     </row>
@@ -3412,10 +3386,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="1">
         <v>46220</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="1">
         <v>46220</v>
       </c>
       <c r="R31" t="s">
@@ -3462,10 +3436,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="1">
         <v>43797</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="1">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3512,10 +3486,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>42810</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3527,7 +3501,7 @@
       <c r="T33" t="s">
         <v>162</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>43802</v>
       </c>
     </row>
@@ -3568,10 +3542,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>45070</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>44910</v>
       </c>
       <c r="R34" t="s">
@@ -3618,10 +3592,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>43250</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3668,10 +3642,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45841</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3718,10 +3692,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="2">
+      <c r="P37" s="1">
         <v>45105</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="1">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3733,7 +3707,7 @@
       <c r="T37" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="2">
+      <c r="U37" s="1">
         <v>46184</v>
       </c>
     </row>
@@ -3774,10 +3748,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>45636</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>46219</v>
       </c>
       <c r="S38" t="s">
@@ -3786,7 +3760,7 @@
       <c r="T38" t="s">
         <v>164</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>45351</v>
       </c>
     </row>
@@ -3827,10 +3801,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>45831</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3874,10 +3848,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>44287</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3898,22 +3872,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>167</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>169</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>170</v>
       </c>
     </row>
@@ -8158,91 +8132,91 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>234</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>235</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>236</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>237</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>238</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>239</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>240</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>241</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>242</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>243</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>244</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>245</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>246</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>247</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>248</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>249</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>250</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>251</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>252</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>253</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>254</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>255</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>256</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>257</v>
       </c>
     </row>
@@ -8256,13 +8230,13 @@
       <c r="D2" t="s">
         <v>260</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>45686</v>
       </c>
       <c r="F2" t="s">
         <v>263</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>45492</v>
       </c>
       <c r="H2" t="s">
@@ -8280,13 +8254,13 @@
       <c r="P2">
         <v>1</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45491</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="1">
         <v>45528</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="1">
         <v>45492</v>
       </c>
       <c r="U2" t="s">
@@ -8324,13 +8298,13 @@
       <c r="D3" t="s">
         <v>261</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>45728</v>
       </c>
       <c r="F3" t="s">
         <v>263</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>45631</v>
       </c>
       <c r="H3" t="s">
@@ -8348,13 +8322,13 @@
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45628</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>45632</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <v>45631</v>
       </c>
       <c r="U3" t="s">
@@ -8389,13 +8363,13 @@
       <c r="D4" t="s">
         <v>261</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>45716</v>
       </c>
       <c r="F4" t="s">
         <v>263</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>45716</v>
       </c>
       <c r="H4" t="s">
@@ -8413,13 +8387,13 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45716</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <v>45722</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="1">
         <v>45716</v>
       </c>
       <c r="U4" t="s">
@@ -8454,13 +8428,13 @@
       <c r="D5" t="s">
         <v>261</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>45728</v>
       </c>
       <c r="F5" t="s">
         <v>263</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>45728</v>
       </c>
       <c r="H5" t="s">
@@ -8478,13 +8452,13 @@
       <c r="P5">
         <v>1</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45722</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <v>45782</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="1">
         <v>45728</v>
       </c>
       <c r="U5" t="s">
@@ -8522,13 +8496,13 @@
       <c r="D6" t="s">
         <v>261</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>45755</v>
       </c>
       <c r="F6" t="s">
         <v>263</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>45755</v>
       </c>
       <c r="H6" t="s">
@@ -8546,13 +8520,13 @@
       <c r="P6">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45728</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="1">
         <v>45734</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="1">
         <v>45755</v>
       </c>
       <c r="U6" t="s">
@@ -8590,7 +8564,7 @@
       <c r="D7" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>45772</v>
       </c>
       <c r="F7" t="s">
@@ -8611,10 +8585,10 @@
       <c r="P7">
         <v>1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45772</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="1">
         <v>45775</v>
       </c>
       <c r="U7" t="s">
@@ -8652,7 +8626,7 @@
       <c r="D8" t="s">
         <v>262</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>45762</v>
       </c>
       <c r="F8" t="s">
@@ -8673,10 +8647,10 @@
       <c r="P8">
         <v>1</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>45762</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="1">
         <v>45770</v>
       </c>
       <c r="U8" t="s">
@@ -8714,7 +8688,7 @@
       <c r="D9" t="s">
         <v>262</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>45763</v>
       </c>
       <c r="F9" t="s">
@@ -8735,10 +8709,10 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45763</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="1">
         <v>45777</v>
       </c>
       <c r="U9" t="s">
@@ -8776,13 +8750,13 @@
       <c r="D10" t="s">
         <v>261</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>45755</v>
       </c>
       <c r="F10" t="s">
         <v>263</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>45755</v>
       </c>
       <c r="H10" t="s">
@@ -8800,13 +8774,13 @@
       <c r="P10">
         <v>1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45754</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="1">
         <v>45849</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="1">
         <v>45754</v>
       </c>
       <c r="U10" t="s">
@@ -8841,13 +8815,13 @@
       <c r="D11" t="s">
         <v>261</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>44973</v>
       </c>
       <c r="F11" t="s">
         <v>263</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <v>44973</v>
       </c>
       <c r="H11" t="s">
@@ -8865,13 +8839,13 @@
       <c r="P11">
         <v>1</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44973</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="1">
         <v>45687</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" s="1">
         <v>44973</v>
       </c>
       <c r="U11" t="s">
@@ -8906,13 +8880,13 @@
       <c r="D12" t="s">
         <v>261</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>45358</v>
       </c>
       <c r="F12" t="s">
         <v>263</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>45358</v>
       </c>
       <c r="H12" t="s">
@@ -8930,13 +8904,13 @@
       <c r="P12">
         <v>1</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45358</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="1">
         <v>45517</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12" s="1">
         <v>45358</v>
       </c>
       <c r="U12" t="s">
@@ -8971,13 +8945,13 @@
       <c r="D13" t="s">
         <v>261</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>45573</v>
       </c>
       <c r="F13" t="s">
         <v>263</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>45573</v>
       </c>
       <c r="H13" t="s">
@@ -8995,13 +8969,13 @@
       <c r="P13">
         <v>1</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45572</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="1">
         <v>45572</v>
       </c>
-      <c r="S13" s="2">
+      <c r="S13" s="1">
         <v>45573</v>
       </c>
       <c r="U13" t="s">
@@ -9039,13 +9013,13 @@
       <c r="D14" t="s">
         <v>261</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>45747</v>
       </c>
       <c r="F14" t="s">
         <v>263</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="1">
         <v>45747</v>
       </c>
       <c r="H14" t="s">
@@ -9063,13 +9037,13 @@
       <c r="P14">
         <v>1</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>45736</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" s="1">
         <v>46101</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14" s="1">
         <v>45747</v>
       </c>
       <c r="U14" t="s">
@@ -9105,70 +9079,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -9206,10 +9180,10 @@
       <c r="O2" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>45490</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -9253,10 +9227,10 @@
       <c r="O3" t="s">
         <v>83</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>45618</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -9300,10 +9274,10 @@
       <c r="O4" t="s">
         <v>99</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>45539</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -9347,10 +9321,10 @@
       <c r="O5" t="s">
         <v>100</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>45567</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -9394,10 +9368,10 @@
       <c r="O6" t="s">
         <v>97</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>45568</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -9441,10 +9415,10 @@
       <c r="O7" t="s">
         <v>85</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>45831</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -9488,10 +9462,10 @@
       <c r="O8" t="s">
         <v>105</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45601</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -9535,10 +9509,10 @@
       <c r="O9" t="s">
         <v>94</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45631</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -9582,10 +9556,10 @@
       <c r="O10" t="s">
         <v>91</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>43902</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -9629,10 +9603,10 @@
       <c r="O11" t="s">
         <v>101</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>44736</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -9676,10 +9650,10 @@
       <c r="O12" t="s">
         <v>84</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>45776</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -9723,10 +9697,10 @@
       <c r="O13" t="s">
         <v>82</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>45772</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -9770,10 +9744,10 @@
       <c r="O14" t="s">
         <v>102</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45000</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -9817,7 +9791,7 @@
       <c r="O15" t="s">
         <v>96</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -9858,7 +9832,7 @@
       <c r="O16" t="s">
         <v>92</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -9899,10 +9873,10 @@
       <c r="O17" t="s">
         <v>95</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45371</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -9946,10 +9920,10 @@
       <c r="O18" t="s">
         <v>93</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>46001</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -9993,10 +9967,10 @@
       <c r="O19" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45436</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -10040,10 +10014,10 @@
       <c r="O20" t="s">
         <v>98</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>44372</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -10087,10 +10061,10 @@
       <c r="O21" t="s">
         <v>107</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>44362</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -10134,10 +10108,10 @@
       <c r="O22" t="s">
         <v>88</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -10175,10 +10149,10 @@
       <c r="O23" t="s">
         <v>356</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>40044</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -10190,7 +10164,7 @@
       <c r="T23" t="s">
         <v>396</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45775</v>
       </c>
     </row>
@@ -10228,10 +10202,10 @@
       <c r="O24" t="s">
         <v>82</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>43549</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -10243,7 +10217,7 @@
       <c r="T24" t="s">
         <v>397</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -10281,10 +10255,10 @@
       <c r="O25" t="s">
         <v>88</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45447</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -10296,7 +10270,7 @@
       <c r="T25" t="s">
         <v>398</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U25" s="1">
         <v>45937</v>
       </c>
     </row>
@@ -10334,10 +10308,10 @@
       <c r="O26" t="s">
         <v>102</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>44485</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -10349,7 +10323,7 @@
       <c r="T26" t="s">
         <v>399</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>45580</v>
       </c>
     </row>
@@ -10387,10 +10361,10 @@
       <c r="O27" t="s">
         <v>88</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45420</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -10402,7 +10376,7 @@
       <c r="T27" t="s">
         <v>400</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U27" s="1">
         <v>45588</v>
       </c>
     </row>
@@ -10440,10 +10414,10 @@
       <c r="O28" t="s">
         <v>103</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>44369</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -10455,7 +10429,7 @@
       <c r="T28" t="s">
         <v>401</v>
       </c>
-      <c r="U28" s="2">
+      <c r="U28" s="1">
         <v>45831</v>
       </c>
     </row>
@@ -10493,10 +10467,10 @@
       <c r="O29" t="s">
         <v>100</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44652</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -10508,7 +10482,7 @@
       <c r="T29" t="s">
         <v>402</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U29" s="1">
         <v>45734</v>
       </c>
     </row>
@@ -10540,7 +10514,7 @@
       <c r="T30" t="s">
         <v>403</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10572,7 +10546,7 @@
       <c r="T31" t="s">
         <v>404</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10604,7 +10578,7 @@
       <c r="T32" t="s">
         <v>405</v>
       </c>
-      <c r="U32" s="2">
+      <c r="U32" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -10642,10 +10616,10 @@
       <c r="O33" t="s">
         <v>92</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>43762</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -10657,7 +10631,7 @@
       <c r="T33" t="s">
         <v>384</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>46037</v>
       </c>
     </row>
@@ -10695,16 +10669,16 @@
       <c r="O34" t="s">
         <v>357</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>40071</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>149</v>
       </c>
-      <c r="U34" s="2">
+      <c r="U34" s="1">
         <v>41023</v>
       </c>
     </row>
@@ -10736,10 +10710,10 @@
       <c r="O35" t="s">
         <v>89</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>44784</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -10748,7 +10722,7 @@
       <c r="S35" t="s">
         <v>149</v>
       </c>
-      <c r="U35" s="2">
+      <c r="U35" s="1">
         <v>45259</v>
       </c>
     </row>
@@ -10786,10 +10760,10 @@
       <c r="O36" t="s">
         <v>93</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45103</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -10798,7 +10772,7 @@
       <c r="S36" t="s">
         <v>149</v>
       </c>
-      <c r="U36" s="2">
+      <c r="U36" s="1">
         <v>46000</v>
       </c>
     </row>
@@ -10862,10 +10836,10 @@
       <c r="O38" t="s">
         <v>98</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>38511</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -10874,7 +10848,7 @@
       <c r="S38" t="s">
         <v>149</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>39068</v>
       </c>
     </row>
@@ -10912,10 +10886,10 @@
       <c r="O39" t="s">
         <v>105</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>39006</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -10927,7 +10901,7 @@
       <c r="T39" t="s">
         <v>406</v>
       </c>
-      <c r="U39" s="2">
+      <c r="U39" s="1">
         <v>40568</v>
       </c>
     </row>
@@ -10959,10 +10933,10 @@
       <c r="O40" t="s">
         <v>102</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>40836</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -10974,7 +10948,7 @@
       <c r="T40" t="s">
         <v>407</v>
       </c>
-      <c r="U40" s="2">
+      <c r="U40" s="1">
         <v>42270</v>
       </c>
     </row>
@@ -11012,10 +10986,10 @@
       <c r="O41" t="s">
         <v>97</v>
       </c>
-      <c r="P41" s="2">
+      <c r="P41" s="1">
         <v>42940</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="1">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -11027,7 +11001,7 @@
       <c r="T41" t="s">
         <v>408</v>
       </c>
-      <c r="U41" s="2">
+      <c r="U41" s="1">
         <v>44148</v>
       </c>
     </row>
@@ -11065,10 +11039,10 @@
       <c r="O42" t="s">
         <v>84</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="1">
         <v>43696</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="1">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -11080,7 +11054,7 @@
       <c r="T42" t="s">
         <v>409</v>
       </c>
-      <c r="U42" s="2">
+      <c r="U42" s="1">
         <v>43185</v>
       </c>
     </row>
@@ -11118,10 +11092,10 @@
       <c r="O43" t="s">
         <v>86</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="1">
         <v>43544</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="1">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -11133,7 +11107,7 @@
       <c r="T43" t="s">
         <v>410</v>
       </c>
-      <c r="U43" s="2">
+      <c r="U43" s="1">
         <v>42850</v>
       </c>
     </row>
@@ -11171,10 +11145,10 @@
       <c r="O44" t="s">
         <v>99</v>
       </c>
-      <c r="P44" s="2">
+      <c r="P44" s="1">
         <v>45076</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="1">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -11186,7 +11160,7 @@
       <c r="T44" t="s">
         <v>411</v>
       </c>
-      <c r="U44" s="2">
+      <c r="U44" s="1">
         <v>44404</v>
       </c>
     </row>
@@ -11224,10 +11198,10 @@
       <c r="O45" t="s">
         <v>83</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="1">
         <v>42963</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="1">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -11239,7 +11213,7 @@
       <c r="T45" t="s">
         <v>412</v>
       </c>
-      <c r="U45" s="2">
+      <c r="U45" s="1">
         <v>42698</v>
       </c>
     </row>
@@ -11277,10 +11251,10 @@
       <c r="O46" t="s">
         <v>90</v>
       </c>
-      <c r="P46" s="2">
+      <c r="P46" s="1">
         <v>45054</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="1">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -11292,7 +11266,7 @@
       <c r="T46" t="s">
         <v>413</v>
       </c>
-      <c r="U46" s="2">
+      <c r="U46" s="1">
         <v>43941</v>
       </c>
     </row>
@@ -11307,25 +11281,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>414</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>415</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>416</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>417</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>418</v>
       </c>
     </row>
@@ -12005,22 +11979,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>419</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>420</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>421</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>422</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>423</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>424</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -9,17 +9,16 @@
   <sheets>
     <sheet name="Situacao" sheetId="1" r:id="rId1"/>
     <sheet name="Diagonal" sheetId="2" r:id="rId2"/>
-    <sheet name="OS" sheetId="3" r:id="rId3"/>
-    <sheet name="Helice" sheetId="4" r:id="rId4"/>
-    <sheet name="DiagonalMeta" sheetId="5" r:id="rId5"/>
-    <sheet name="Financeiro" sheetId="6" r:id="rId6"/>
+    <sheet name="Helice" sheetId="3" r:id="rId3"/>
+    <sheet name="DiagonalMeta" sheetId="4" r:id="rId4"/>
+    <sheet name="Financeiro" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="395">
   <si>
     <t>om</t>
   </si>
@@ -739,220 +738,16 @@
 Essa aeronave vai para o Rumba para voar com estagiário e vai aumentar o consumo de Hr. AT vai até 5360h</t>
   </si>
   <si>
-    <t>os</t>
-  </si>
-  <si>
-    <t>os_origem</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>data_status</t>
-  </si>
-  <si>
-    <t>data_recebimento</t>
-  </si>
-  <si>
-    <t>cff</t>
-  </si>
-  <si>
-    <t>nomenclatura</t>
-  </si>
-  <si>
-    <t>lote</t>
-  </si>
-  <si>
-    <t>item_nao_listado</t>
-  </si>
-  <si>
-    <t>solicitante</t>
-  </si>
-  <si>
-    <t>quantidade</t>
-  </si>
-  <si>
-    <t>data_inicio_prev</t>
-  </si>
-  <si>
-    <t>data_fim_prev</t>
-  </si>
-  <si>
-    <t>data_inicio_real</t>
-  </si>
-  <si>
-    <t>data_fim_real</t>
-  </si>
-  <si>
-    <t>prioridade</t>
-  </si>
-  <si>
-    <t>emergencia</t>
-  </si>
-  <si>
-    <t>unidade_exec</t>
-  </si>
-  <si>
-    <t>setor_exec</t>
-  </si>
-  <si>
-    <t>solicitacao</t>
-  </si>
-  <si>
-    <t>unidade_solic</t>
-  </si>
-  <si>
-    <t>setor_solic</t>
-  </si>
-  <si>
-    <t>pessoa_solicitante</t>
-  </si>
-  <si>
-    <t>comentarios</t>
-  </si>
-  <si>
-    <t>NÃO PROGRAMADA</t>
-  </si>
-  <si>
-    <t>EXTERNA</t>
-  </si>
-  <si>
-    <t>INT</t>
-  </si>
-  <si>
-    <t>REC</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <t>ENGINE PT6A-114A</t>
-  </si>
-  <si>
-    <t>PCE-PC1428</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>313240015920</t>
-  </si>
-  <si>
-    <t>313240016031</t>
-  </si>
-  <si>
-    <t>S4J</t>
-  </si>
-  <si>
-    <t>TMAM</t>
-  </si>
-  <si>
-    <t>TMBT</t>
-  </si>
-  <si>
-    <t>SEP</t>
-  </si>
-  <si>
-    <t>3810496453</t>
-  </si>
-  <si>
-    <t>3810499719</t>
-  </si>
-  <si>
-    <t>3810500784</t>
-  </si>
-  <si>
-    <t>3810501279</t>
-  </si>
-  <si>
-    <t>3810502614</t>
-  </si>
-  <si>
-    <t>3810504268</t>
-  </si>
-  <si>
-    <t>3810504159</t>
-  </si>
-  <si>
-    <t>3810504182</t>
-  </si>
-  <si>
-    <t>3810503807</t>
-  </si>
-  <si>
-    <t>3810481813</t>
-  </si>
-  <si>
-    <t>3810492521</t>
-  </si>
-  <si>
-    <t>3810499557</t>
-  </si>
-  <si>
-    <t>3810499086</t>
+    <t>EEAR</t>
+  </si>
+  <si>
+    <t>BABV</t>
+  </si>
+  <si>
+    <t>EPCAR</t>
   </si>
   <si>
     <t>BABE</t>
-  </si>
-  <si>
-    <t>BABV</t>
-  </si>
-  <si>
-    <t>SMPR</t>
-  </si>
-  <si>
-    <t>GLOGTEC</t>
-  </si>
-  <si>
-    <t>SMNT</t>
-  </si>
-  <si>
-    <t>TM6A</t>
-  </si>
-  <si>
-    <t>CMOT</t>
-  </si>
-  <si>
-    <t>1S PAULO SERGIO</t>
-  </si>
-  <si>
-    <t>SO GABRIEL</t>
-  </si>
-  <si>
-    <t>2S ABNER ROSA</t>
-  </si>
-  <si>
-    <t>SO ISAMU</t>
-  </si>
-  <si>
-    <t>2S ROBERTO</t>
-  </si>
-  <si>
-    <t>2S NATANAEL</t>
-  </si>
-  <si>
-    <t>3S SANTIAGO</t>
-  </si>
-  <si>
-    <t>1S CARLOS LIMA</t>
-  </si>
-  <si>
-    <t>SO MARCELO</t>
-  </si>
-  <si>
-    <t>3S MIGUEL</t>
-  </si>
-  <si>
-    <t>EEAR</t>
-  </si>
-  <si>
-    <t>EPCAR</t>
   </si>
   <si>
     <t>P7036368-01</t>
@@ -8128,944 +7923,2199 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K2">
+        <v>797.33</v>
+      </c>
+      <c r="L2">
+        <v>6156.92</v>
+      </c>
+      <c r="M2">
+        <v>19.93</v>
+      </c>
+      <c r="N2">
+        <v>4000</v>
+      </c>
+      <c r="O2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="1">
+        <v>45490</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>45015</v>
+      </c>
+      <c r="R2" t="s">
+        <v>290</v>
+      </c>
+      <c r="S2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" t="s">
         <v>234</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" t="s">
+        <v>242</v>
+      </c>
+      <c r="I3" t="s">
+        <v>245</v>
+      </c>
+      <c r="J3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K3">
+        <v>1001.83</v>
+      </c>
+      <c r="L3">
+        <v>8226.17</v>
+      </c>
+      <c r="M3">
+        <v>25.05</v>
+      </c>
+      <c r="N3">
+        <v>4000</v>
+      </c>
+      <c r="O3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" s="1">
+        <v>45618</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>45614</v>
+      </c>
+      <c r="R3" t="s">
+        <v>291</v>
+      </c>
+      <c r="S3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" t="s">
+        <v>242</v>
+      </c>
+      <c r="I4" t="s">
+        <v>246</v>
+      </c>
+      <c r="J4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4">
+        <v>2813.92</v>
+      </c>
+      <c r="L4">
+        <v>6291.75</v>
+      </c>
+      <c r="M4">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="N4">
+        <v>4000</v>
+      </c>
+      <c r="O4" t="s">
+        <v>99</v>
+      </c>
+      <c r="P4" s="1">
+        <v>45539</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>45539</v>
+      </c>
+      <c r="R4" t="s">
+        <v>292</v>
+      </c>
+      <c r="S4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" t="s">
+        <v>242</v>
+      </c>
+      <c r="I5" t="s">
+        <v>247</v>
+      </c>
+      <c r="J5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5">
+        <v>1258.5</v>
+      </c>
+      <c r="L5">
+        <v>5428.67</v>
+      </c>
+      <c r="M5">
+        <v>31.46</v>
+      </c>
+      <c r="N5">
+        <v>4000</v>
+      </c>
+      <c r="O5" t="s">
+        <v>100</v>
+      </c>
+      <c r="P5" s="1">
+        <v>45567</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>45490</v>
+      </c>
+      <c r="R5" t="s">
+        <v>293</v>
+      </c>
+      <c r="S5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" t="s">
+        <v>242</v>
+      </c>
+      <c r="I6" t="s">
+        <v>248</v>
+      </c>
+      <c r="J6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6">
+        <v>708.33</v>
+      </c>
+      <c r="L6">
+        <v>6401.42</v>
+      </c>
+      <c r="M6">
+        <v>17.71</v>
+      </c>
+      <c r="N6">
+        <v>4000</v>
+      </c>
+      <c r="O6" t="s">
+        <v>97</v>
+      </c>
+      <c r="P6" s="1">
+        <v>45568</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>45526</v>
+      </c>
+      <c r="R6" t="s">
+        <v>294</v>
+      </c>
+      <c r="S6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" t="s">
+        <v>242</v>
+      </c>
+      <c r="I7" t="s">
+        <v>249</v>
+      </c>
+      <c r="J7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7">
+        <v>133.42</v>
+      </c>
+      <c r="L7">
+        <v>9321</v>
+      </c>
+      <c r="M7">
+        <v>3.34</v>
+      </c>
+      <c r="N7">
+        <v>4000</v>
+      </c>
+      <c r="O7" t="s">
+        <v>85</v>
+      </c>
+      <c r="P7" s="1">
+        <v>45831</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>45352</v>
+      </c>
+      <c r="R7" t="s">
+        <v>295</v>
+      </c>
+      <c r="S7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E8" t="s">
+        <v>242</v>
+      </c>
+      <c r="I8" t="s">
+        <v>250</v>
+      </c>
+      <c r="J8" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8">
+        <v>224.08</v>
+      </c>
+      <c r="L8">
+        <v>4042.75</v>
+      </c>
+      <c r="M8">
+        <v>5.6</v>
+      </c>
+      <c r="N8">
+        <v>4000</v>
+      </c>
+      <c r="O8" t="s">
+        <v>105</v>
+      </c>
+      <c r="P8" s="1">
+        <v>45601</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>44704</v>
+      </c>
+      <c r="R8" t="s">
+        <v>296</v>
+      </c>
+      <c r="S8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" t="s">
+        <v>242</v>
+      </c>
+      <c r="I9" t="s">
+        <v>251</v>
+      </c>
+      <c r="J9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9">
+        <v>783.42</v>
+      </c>
+      <c r="L9">
+        <v>5242.33</v>
+      </c>
+      <c r="M9">
+        <v>19.59</v>
+      </c>
+      <c r="N9">
+        <v>4000</v>
+      </c>
+      <c r="O9" t="s">
+        <v>94</v>
+      </c>
+      <c r="P9" s="1">
+        <v>45631</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>45628</v>
+      </c>
+      <c r="R9" t="s">
+        <v>297</v>
+      </c>
+      <c r="S9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>238</v>
+      </c>
+      <c r="E10" t="s">
+        <v>242</v>
+      </c>
+      <c r="I10" t="s">
+        <v>252</v>
+      </c>
+      <c r="J10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10">
+        <v>2718.58</v>
+      </c>
+      <c r="L10">
+        <v>9682.42</v>
+      </c>
+      <c r="M10">
+        <v>67.95999999999999</v>
+      </c>
+      <c r="N10">
+        <v>4000</v>
+      </c>
+      <c r="O10" t="s">
+        <v>91</v>
+      </c>
+      <c r="P10" s="1">
+        <v>43902</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>43549</v>
+      </c>
+      <c r="R10" t="s">
+        <v>298</v>
+      </c>
+      <c r="S10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11" t="s">
         <v>235</v>
       </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E11" t="s">
+        <v>242</v>
+      </c>
+      <c r="I11" t="s">
+        <v>253</v>
+      </c>
+      <c r="J11" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11">
+        <v>3603.17</v>
+      </c>
+      <c r="L11">
+        <v>6330.08</v>
+      </c>
+      <c r="M11">
+        <v>90.08</v>
+      </c>
+      <c r="N11">
+        <v>4000</v>
+      </c>
+      <c r="O11" t="s">
+        <v>101</v>
+      </c>
+      <c r="P11" s="1">
+        <v>44736</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>44735</v>
+      </c>
+      <c r="R11" t="s">
+        <v>299</v>
+      </c>
+      <c r="S11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>239</v>
+      </c>
+      <c r="E12" t="s">
+        <v>242</v>
+      </c>
+      <c r="I12" t="s">
+        <v>254</v>
+      </c>
+      <c r="J12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12">
+        <v>2298.67</v>
+      </c>
+      <c r="L12">
+        <v>4857.58</v>
+      </c>
+      <c r="M12">
+        <v>57.47</v>
+      </c>
+      <c r="N12">
+        <v>4000</v>
+      </c>
+      <c r="O12" t="s">
+        <v>84</v>
+      </c>
+      <c r="P12" s="1">
+        <v>45776</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>45776</v>
+      </c>
+      <c r="R12" t="s">
+        <v>300</v>
+      </c>
+      <c r="S12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13" t="s">
         <v>236</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" t="s">
+        <v>242</v>
+      </c>
+      <c r="I13" t="s">
+        <v>255</v>
+      </c>
+      <c r="J13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13">
+        <v>2132.08</v>
+      </c>
+      <c r="L13">
+        <v>5063.58</v>
+      </c>
+      <c r="M13">
+        <v>53.3</v>
+      </c>
+      <c r="N13">
+        <v>4000</v>
+      </c>
+      <c r="O13" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13" s="1">
+        <v>45772</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>45600</v>
+      </c>
+      <c r="R13" t="s">
+        <v>301</v>
+      </c>
+      <c r="S13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" t="s">
+        <v>242</v>
+      </c>
+      <c r="I14" t="s">
+        <v>256</v>
+      </c>
+      <c r="J14" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14">
+        <v>1013.92</v>
+      </c>
+      <c r="L14">
+        <v>5211.33</v>
+      </c>
+      <c r="M14">
+        <v>25.35</v>
+      </c>
+      <c r="N14">
+        <v>4000</v>
+      </c>
+      <c r="O14" t="s">
+        <v>102</v>
+      </c>
+      <c r="P14" s="1">
+        <v>45000</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>44630</v>
+      </c>
+      <c r="R14" t="s">
+        <v>302</v>
+      </c>
+      <c r="S14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" t="s">
+        <v>242</v>
+      </c>
+      <c r="I15" t="s">
+        <v>257</v>
+      </c>
+      <c r="J15" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15">
+        <v>209.92</v>
+      </c>
+      <c r="L15">
+        <v>209.92</v>
+      </c>
+      <c r="M15">
+        <v>5.25</v>
+      </c>
+      <c r="N15">
+        <v>4000</v>
+      </c>
+      <c r="O15" t="s">
+        <v>96</v>
+      </c>
+      <c r="P15" s="1">
+        <v>45930</v>
+      </c>
+      <c r="S15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" t="s">
+        <v>242</v>
+      </c>
+      <c r="I16" t="s">
+        <v>258</v>
+      </c>
+      <c r="J16" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16">
+        <v>49.33</v>
+      </c>
+      <c r="L16">
+        <v>49.33</v>
+      </c>
+      <c r="M16">
+        <v>1.23</v>
+      </c>
+      <c r="N16">
+        <v>4000</v>
+      </c>
+      <c r="O16" t="s">
+        <v>92</v>
+      </c>
+      <c r="P16" s="1">
+        <v>46035</v>
+      </c>
+      <c r="S16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" t="s">
+        <v>242</v>
+      </c>
+      <c r="I17" t="s">
+        <v>259</v>
+      </c>
+      <c r="J17" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17">
+        <v>923.83</v>
+      </c>
+      <c r="L17">
+        <v>19483.33</v>
+      </c>
+      <c r="M17">
+        <v>23.1</v>
+      </c>
+      <c r="N17">
+        <v>4000</v>
+      </c>
+      <c r="O17" t="s">
+        <v>95</v>
+      </c>
+      <c r="P17" s="1">
+        <v>45371</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>45026</v>
+      </c>
+      <c r="R17" t="s">
+        <v>303</v>
+      </c>
+      <c r="S17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" t="s">
+        <v>242</v>
+      </c>
+      <c r="I18" t="s">
+        <v>260</v>
+      </c>
+      <c r="J18" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18">
+        <v>112.33</v>
+      </c>
+      <c r="L18">
+        <v>4746.08</v>
+      </c>
+      <c r="M18">
+        <v>2.81</v>
+      </c>
+      <c r="N18">
+        <v>4000</v>
+      </c>
+      <c r="O18" t="s">
+        <v>93</v>
+      </c>
+      <c r="P18" s="1">
+        <v>46001</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>45371</v>
+      </c>
+      <c r="R18" t="s">
+        <v>304</v>
+      </c>
+      <c r="S18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>238</v>
+      </c>
+      <c r="E19" t="s">
+        <v>242</v>
+      </c>
+      <c r="I19" t="s">
+        <v>261</v>
+      </c>
+      <c r="J19" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19">
+        <v>598</v>
+      </c>
+      <c r="L19">
+        <v>17238.58</v>
+      </c>
+      <c r="M19">
+        <v>14.95</v>
+      </c>
+      <c r="N19">
+        <v>4000</v>
+      </c>
+      <c r="O19" t="s">
+        <v>106</v>
+      </c>
+      <c r="P19" s="1">
+        <v>45436</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>45294</v>
+      </c>
+      <c r="R19" t="s">
+        <v>305</v>
+      </c>
+      <c r="S19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" t="s">
+        <v>242</v>
+      </c>
+      <c r="I20" t="s">
+        <v>262</v>
+      </c>
+      <c r="J20" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20">
+        <v>779.67</v>
+      </c>
+      <c r="L20">
+        <v>9284.25</v>
+      </c>
+      <c r="M20">
+        <v>19.49</v>
+      </c>
+      <c r="N20">
+        <v>4000</v>
+      </c>
+      <c r="O20" t="s">
+        <v>98</v>
+      </c>
+      <c r="P20" s="1">
+        <v>44372</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>44369</v>
+      </c>
+      <c r="R20" t="s">
+        <v>306</v>
+      </c>
+      <c r="S20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>238</v>
+      </c>
+      <c r="E21" t="s">
+        <v>242</v>
+      </c>
+      <c r="I21" t="s">
+        <v>263</v>
+      </c>
+      <c r="J21" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21">
+        <v>1685.25</v>
+      </c>
+      <c r="L21">
+        <v>5853.58</v>
+      </c>
+      <c r="M21">
+        <v>42.13</v>
+      </c>
+      <c r="N21">
+        <v>4000</v>
+      </c>
+      <c r="O21" t="s">
+        <v>107</v>
+      </c>
+      <c r="P21" s="1">
+        <v>44362</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>43894</v>
+      </c>
+      <c r="R21" t="s">
+        <v>307</v>
+      </c>
+      <c r="S21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22" t="s">
+        <v>242</v>
+      </c>
+      <c r="I22" t="s">
+        <v>264</v>
+      </c>
+      <c r="J22" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22">
+        <v>1926.58</v>
+      </c>
+      <c r="L22">
+        <v>11035.33</v>
+      </c>
+      <c r="M22">
+        <v>48.16</v>
+      </c>
+      <c r="N22">
+        <v>4000</v>
+      </c>
+      <c r="O22" t="s">
+        <v>88</v>
+      </c>
+      <c r="P22" s="1">
+        <v>45511</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>45509</v>
+      </c>
+      <c r="R22" t="s">
+        <v>308</v>
+      </c>
+      <c r="S22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" t="s">
+        <v>238</v>
+      </c>
+      <c r="E23" t="s">
+        <v>242</v>
+      </c>
+      <c r="I23" t="s">
+        <v>265</v>
+      </c>
+      <c r="J23" t="s">
+        <v>81</v>
+      </c>
+      <c r="L23">
+        <v>2562.83</v>
+      </c>
+      <c r="N23">
+        <v>4000</v>
+      </c>
+      <c r="O23" t="s">
+        <v>288</v>
+      </c>
+      <c r="P23" s="1">
+        <v>40044</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>40126</v>
+      </c>
+      <c r="R23" t="s">
+        <v>309</v>
+      </c>
+      <c r="S23" t="s">
+        <v>144</v>
+      </c>
+      <c r="T23" t="s">
+        <v>328</v>
+      </c>
+      <c r="U23" s="1">
+        <v>45775</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>238</v>
+      </c>
+      <c r="E24" t="s">
+        <v>242</v>
+      </c>
+      <c r="I24" t="s">
+        <v>266</v>
+      </c>
+      <c r="J24" t="s">
+        <v>81</v>
+      </c>
+      <c r="K24">
+        <v>1903.17</v>
+      </c>
+      <c r="L24">
+        <v>4373</v>
+      </c>
+      <c r="M24">
+        <v>47.58</v>
+      </c>
+      <c r="N24">
+        <v>4000</v>
+      </c>
+      <c r="O24" t="s">
+        <v>82</v>
+      </c>
+      <c r="P24" s="1">
+        <v>43549</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>45772</v>
+      </c>
+      <c r="R24" t="s">
+        <v>310</v>
+      </c>
+      <c r="S24" t="s">
+        <v>144</v>
+      </c>
+      <c r="T24" t="s">
+        <v>329</v>
+      </c>
+      <c r="U24" s="1">
+        <v>45810</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>238</v>
+      </c>
+      <c r="E25" t="s">
+        <v>242</v>
+      </c>
+      <c r="I25" t="s">
+        <v>267</v>
+      </c>
+      <c r="J25" t="s">
+        <v>81</v>
+      </c>
+      <c r="K25">
+        <v>835.42</v>
+      </c>
+      <c r="L25">
+        <v>5559.92</v>
+      </c>
+      <c r="M25">
+        <v>20.89</v>
+      </c>
+      <c r="N25">
+        <v>4000</v>
+      </c>
+      <c r="O25" t="s">
+        <v>88</v>
+      </c>
+      <c r="P25" s="1">
+        <v>45447</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>45510</v>
+      </c>
+      <c r="R25" t="s">
+        <v>311</v>
+      </c>
+      <c r="S25" t="s">
+        <v>144</v>
+      </c>
+      <c r="T25" t="s">
+        <v>330</v>
+      </c>
+      <c r="U25" s="1">
+        <v>45937</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
+        <v>239</v>
+      </c>
+      <c r="E26" t="s">
+        <v>242</v>
+      </c>
+      <c r="I26" t="s">
+        <v>268</v>
+      </c>
+      <c r="J26" t="s">
+        <v>81</v>
+      </c>
+      <c r="K26">
+        <v>1657.42</v>
+      </c>
+      <c r="L26">
+        <v>4769.83</v>
+      </c>
+      <c r="M26">
+        <v>41.44</v>
+      </c>
+      <c r="N26">
+        <v>4000</v>
+      </c>
+      <c r="O26" t="s">
+        <v>102</v>
+      </c>
+      <c r="P26" s="1">
+        <v>44485</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>44959</v>
+      </c>
+      <c r="R26" t="s">
+        <v>312</v>
+      </c>
+      <c r="S26" t="s">
+        <v>144</v>
+      </c>
+      <c r="T26" t="s">
+        <v>331</v>
+      </c>
+      <c r="U26" s="1">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>238</v>
+      </c>
+      <c r="E27" t="s">
+        <v>242</v>
+      </c>
+      <c r="I27" t="s">
+        <v>269</v>
+      </c>
+      <c r="J27" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27">
+        <v>39.92</v>
+      </c>
+      <c r="L27">
+        <v>3843.83</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>4000</v>
+      </c>
+      <c r="O27" t="s">
+        <v>88</v>
+      </c>
+      <c r="P27" s="1">
+        <v>45420</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>45446</v>
+      </c>
+      <c r="R27" t="s">
+        <v>313</v>
+      </c>
+      <c r="S27" t="s">
+        <v>144</v>
+      </c>
+      <c r="T27" t="s">
+        <v>332</v>
+      </c>
+      <c r="U27" s="1">
+        <v>45588</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>238</v>
+      </c>
+      <c r="E28" t="s">
+        <v>242</v>
+      </c>
+      <c r="I28" t="s">
+        <v>270</v>
+      </c>
+      <c r="J28" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28">
+        <v>4204.25</v>
+      </c>
+      <c r="L28">
+        <v>15636.58</v>
+      </c>
+      <c r="M28">
+        <v>105.11</v>
+      </c>
+      <c r="N28">
+        <v>4000</v>
+      </c>
+      <c r="O28" t="s">
+        <v>103</v>
+      </c>
+      <c r="P28" s="1">
+        <v>44369</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>45824</v>
+      </c>
+      <c r="R28" t="s">
+        <v>314</v>
+      </c>
+      <c r="S28" t="s">
+        <v>144</v>
+      </c>
+      <c r="T28" t="s">
+        <v>333</v>
+      </c>
+      <c r="U28" s="1">
+        <v>45831</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>239</v>
+      </c>
+      <c r="E29" t="s">
+        <v>242</v>
+      </c>
+      <c r="I29" t="s">
+        <v>271</v>
+      </c>
+      <c r="J29" t="s">
+        <v>81</v>
+      </c>
+      <c r="K29">
+        <v>1891.33</v>
+      </c>
+      <c r="L29">
+        <v>5276.25</v>
+      </c>
+      <c r="M29">
+        <v>47.28</v>
+      </c>
+      <c r="N29">
+        <v>4000</v>
+      </c>
+      <c r="O29" t="s">
+        <v>100</v>
+      </c>
+      <c r="P29" s="1">
+        <v>44652</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>45567</v>
+      </c>
+      <c r="R29" t="s">
+        <v>315</v>
+      </c>
+      <c r="S29" t="s">
+        <v>144</v>
+      </c>
+      <c r="T29" t="s">
+        <v>334</v>
+      </c>
+      <c r="U29" s="1">
+        <v>45734</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E30" t="s">
+        <v>242</v>
+      </c>
+      <c r="I30" t="s">
+        <v>272</v>
+      </c>
+      <c r="J30" t="s">
+        <v>81</v>
+      </c>
+      <c r="N30">
+        <v>4000</v>
+      </c>
+      <c r="S30" t="s">
+        <v>144</v>
+      </c>
+      <c r="T30" t="s">
+        <v>335</v>
+      </c>
+      <c r="U30" s="1">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" t="s">
+        <v>238</v>
+      </c>
+      <c r="E31" t="s">
+        <v>242</v>
+      </c>
+      <c r="I31" t="s">
+        <v>273</v>
+      </c>
+      <c r="J31" t="s">
+        <v>81</v>
+      </c>
+      <c r="N31">
+        <v>4000</v>
+      </c>
+      <c r="S31" t="s">
+        <v>144</v>
+      </c>
+      <c r="T31" t="s">
+        <v>336</v>
+      </c>
+      <c r="U31" s="1">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>238</v>
+      </c>
+      <c r="E32" t="s">
+        <v>242</v>
+      </c>
+      <c r="I32" t="s">
+        <v>274</v>
+      </c>
+      <c r="J32" t="s">
+        <v>81</v>
+      </c>
+      <c r="N32">
+        <v>4000</v>
+      </c>
+      <c r="S32" t="s">
+        <v>144</v>
+      </c>
+      <c r="T32" t="s">
+        <v>337</v>
+      </c>
+      <c r="U32" s="1">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>239</v>
+      </c>
+      <c r="E33" t="s">
+        <v>242</v>
+      </c>
+      <c r="I33" t="s">
+        <v>275</v>
+      </c>
+      <c r="J33" t="s">
+        <v>81</v>
+      </c>
+      <c r="K33">
+        <v>3238.83</v>
+      </c>
+      <c r="L33">
+        <v>6794.67</v>
+      </c>
+      <c r="M33">
+        <v>80.97</v>
+      </c>
+      <c r="N33">
+        <v>4000</v>
+      </c>
+      <c r="O33" t="s">
+        <v>92</v>
+      </c>
+      <c r="P33" s="1">
+        <v>43762</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>46031</v>
+      </c>
+      <c r="R33" t="s">
+        <v>316</v>
+      </c>
+      <c r="S33" t="s">
+        <v>148</v>
+      </c>
+      <c r="T33" t="s">
+        <v>316</v>
+      </c>
+      <c r="U33" s="1">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" t="s">
+        <v>239</v>
+      </c>
+      <c r="E34" t="s">
+        <v>242</v>
+      </c>
+      <c r="I34" t="s">
+        <v>276</v>
+      </c>
+      <c r="J34" t="s">
+        <v>81</v>
+      </c>
+      <c r="K34">
+        <v>833.58</v>
+      </c>
+      <c r="L34">
+        <v>833.58</v>
+      </c>
+      <c r="M34">
+        <v>20.84</v>
+      </c>
+      <c r="N34">
+        <v>4000</v>
+      </c>
+      <c r="O34" t="s">
+        <v>289</v>
+      </c>
+      <c r="P34" s="1">
+        <v>40071</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>41023</v>
+      </c>
+      <c r="S34" t="s">
+        <v>149</v>
+      </c>
+      <c r="U34" s="1">
+        <v>41023</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" t="s">
         <v>237</v>
       </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" t="s">
         <v>238</v>
       </c>
-      <c r="H1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="E35" t="s">
+        <v>242</v>
+      </c>
+      <c r="I35" t="s">
+        <v>277</v>
+      </c>
+      <c r="J35" t="s">
+        <v>81</v>
+      </c>
+      <c r="L35">
+        <v>6168.75</v>
+      </c>
+      <c r="N35">
+        <v>4000</v>
+      </c>
+      <c r="O35" t="s">
+        <v>89</v>
+      </c>
+      <c r="P35" s="1">
+        <v>44784</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>45259</v>
+      </c>
+      <c r="R35" t="s">
+        <v>317</v>
+      </c>
+      <c r="S35" t="s">
+        <v>149</v>
+      </c>
+      <c r="U35" s="1">
+        <v>45259</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
+      <c r="A36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" t="s">
+        <v>238</v>
+      </c>
+      <c r="E36" t="s">
+        <v>242</v>
+      </c>
+      <c r="I36" t="s">
+        <v>278</v>
+      </c>
+      <c r="J36" t="s">
+        <v>81</v>
+      </c>
+      <c r="K36">
+        <v>2184.17</v>
+      </c>
+      <c r="L36">
+        <v>13647.17</v>
+      </c>
+      <c r="M36">
+        <v>54.6</v>
+      </c>
+      <c r="N36">
+        <v>4000</v>
+      </c>
+      <c r="O36" t="s">
+        <v>93</v>
+      </c>
+      <c r="P36" s="1">
+        <v>45103</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>46000</v>
+      </c>
+      <c r="R36" t="s">
+        <v>318</v>
+      </c>
+      <c r="S36" t="s">
+        <v>149</v>
+      </c>
+      <c r="U36" s="1">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" t="s">
+        <v>240</v>
+      </c>
+      <c r="E37" t="s">
+        <v>242</v>
+      </c>
+      <c r="I37" t="s">
+        <v>261</v>
+      </c>
+      <c r="J37" t="s">
+        <v>81</v>
+      </c>
+      <c r="N37">
+        <v>4000</v>
+      </c>
+      <c r="S37" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
+      <c r="A38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" t="s">
+        <v>238</v>
+      </c>
+      <c r="E38" t="s">
+        <v>242</v>
+      </c>
+      <c r="I38" t="s">
+        <v>279</v>
+      </c>
+      <c r="J38" t="s">
+        <v>81</v>
+      </c>
+      <c r="K38">
+        <v>553.17</v>
+      </c>
+      <c r="L38">
+        <v>553.17</v>
+      </c>
+      <c r="M38">
+        <v>13.83</v>
+      </c>
+      <c r="N38">
+        <v>4000</v>
+      </c>
+      <c r="O38" t="s">
+        <v>98</v>
+      </c>
+      <c r="P38" s="1">
+        <v>38511</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>39068</v>
+      </c>
+      <c r="R38" t="s">
+        <v>319</v>
+      </c>
+      <c r="S38" t="s">
+        <v>149</v>
+      </c>
+      <c r="U38" s="1">
+        <v>39068</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" t="s">
+        <v>238</v>
+      </c>
+      <c r="E39" t="s">
+        <v>242</v>
+      </c>
+      <c r="I39" t="s">
+        <v>280</v>
+      </c>
+      <c r="J39" t="s">
+        <v>81</v>
+      </c>
+      <c r="K39">
+        <v>85.58</v>
+      </c>
+      <c r="L39">
+        <v>2007.17</v>
+      </c>
+      <c r="M39">
+        <v>2.14</v>
+      </c>
+      <c r="N39">
+        <v>4000</v>
+      </c>
+      <c r="O39" t="s">
+        <v>105</v>
+      </c>
+      <c r="P39" s="1">
+        <v>39006</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>40568</v>
+      </c>
+      <c r="R39" t="s">
+        <v>320</v>
+      </c>
+      <c r="S39" t="s">
+        <v>149</v>
+      </c>
+      <c r="T39" t="s">
+        <v>338</v>
+      </c>
+      <c r="U39" s="1">
+        <v>40568</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" t="s">
+        <v>243</v>
+      </c>
+      <c r="I40" t="s">
+        <v>281</v>
+      </c>
+      <c r="J40" t="s">
+        <v>81</v>
+      </c>
+      <c r="K40">
+        <v>796.67</v>
+      </c>
+      <c r="L40">
+        <v>3739.5</v>
+      </c>
+      <c r="O40" t="s">
+        <v>102</v>
+      </c>
+      <c r="P40" s="1">
+        <v>40836</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>42270</v>
+      </c>
+      <c r="R40" t="s">
+        <v>321</v>
+      </c>
+      <c r="S40" t="s">
+        <v>149</v>
+      </c>
+      <c r="T40" t="s">
+        <v>339</v>
+      </c>
+      <c r="U40" s="1">
+        <v>42270</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>238</v>
+      </c>
+      <c r="E41" t="s">
+        <v>242</v>
+      </c>
+      <c r="I41" t="s">
+        <v>282</v>
+      </c>
+      <c r="J41" t="s">
+        <v>81</v>
+      </c>
+      <c r="K41">
+        <v>981.58</v>
+      </c>
+      <c r="L41">
+        <v>7558.67</v>
+      </c>
+      <c r="M41">
+        <v>24.54</v>
+      </c>
+      <c r="N41">
+        <v>4000</v>
+      </c>
+      <c r="O41" t="s">
+        <v>97</v>
+      </c>
+      <c r="P41" s="1">
+        <v>42940</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>43494</v>
+      </c>
+      <c r="R41" t="s">
+        <v>322</v>
+      </c>
+      <c r="S41" t="s">
+        <v>146</v>
+      </c>
+      <c r="T41" t="s">
+        <v>340</v>
+      </c>
+      <c r="U41" s="1">
+        <v>44148</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
+      <c r="A42" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" t="s">
         <v>239</v>
       </c>
-      <c r="J1" t="s">
-        <v>240</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>241</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="E42" t="s">
         <v>242</v>
       </c>
-      <c r="O1" t="s">
-        <v>243</v>
-      </c>
-      <c r="P1" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>245</v>
-      </c>
-      <c r="R1" t="s">
-        <v>246</v>
-      </c>
-      <c r="S1" t="s">
-        <v>247</v>
-      </c>
-      <c r="T1" t="s">
-        <v>248</v>
-      </c>
-      <c r="U1" t="s">
-        <v>249</v>
-      </c>
-      <c r="V1" t="s">
-        <v>250</v>
-      </c>
-      <c r="W1" t="s">
-        <v>251</v>
-      </c>
-      <c r="X1" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>253</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>254</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>255</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>256</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29">
-      <c r="A2">
-        <v>3810267428</v>
-      </c>
-      <c r="C2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E2" s="1">
-        <v>45686</v>
-      </c>
-      <c r="F2" t="s">
-        <v>263</v>
-      </c>
-      <c r="G2" s="1">
-        <v>45492</v>
-      </c>
-      <c r="H2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2">
-        <v>198</v>
-      </c>
-      <c r="J2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>45491</v>
-      </c>
-      <c r="R2" s="1">
-        <v>45528</v>
-      </c>
-      <c r="S2" s="1">
-        <v>45492</v>
-      </c>
-      <c r="U2" t="s">
-        <v>266</v>
-      </c>
-      <c r="V2" t="s">
-        <v>268</v>
-      </c>
-      <c r="W2" t="s">
-        <v>22</v>
-      </c>
-      <c r="X2" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29">
-      <c r="A3">
-        <v>3810269967</v>
-      </c>
-      <c r="C3" t="s">
-        <v>258</v>
-      </c>
-      <c r="D3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E3" s="1">
-        <v>45728</v>
-      </c>
-      <c r="F3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G3" s="1">
-        <v>45631</v>
-      </c>
-      <c r="H3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3">
-        <v>198</v>
-      </c>
-      <c r="J3" t="s">
-        <v>264</v>
-      </c>
-      <c r="K3" t="s">
-        <v>77</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>45628</v>
-      </c>
-      <c r="R3" s="1">
-        <v>45632</v>
-      </c>
-      <c r="S3" s="1">
-        <v>45631</v>
-      </c>
-      <c r="U3" t="s">
-        <v>267</v>
-      </c>
-      <c r="W3" t="s">
-        <v>22</v>
-      </c>
-      <c r="X3" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>275</v>
-      </c>
-      <c r="Z3" t="s">
+      <c r="I42" t="s">
+        <v>283</v>
+      </c>
+      <c r="J42" t="s">
+        <v>81</v>
+      </c>
+      <c r="K42">
+        <v>3152</v>
+      </c>
+      <c r="L42">
+        <v>6001.67</v>
+      </c>
+      <c r="M42">
+        <v>78.8</v>
+      </c>
+      <c r="N42">
+        <v>4000</v>
+      </c>
+      <c r="O42" t="s">
+        <v>84</v>
+      </c>
+      <c r="P42" s="1">
+        <v>43696</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>45776</v>
+      </c>
+      <c r="R42" t="s">
+        <v>323</v>
+      </c>
+      <c r="S42" t="s">
+        <v>146</v>
+      </c>
+      <c r="T42" t="s">
+        <v>341</v>
+      </c>
+      <c r="U42" s="1">
+        <v>43185</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
+      <c r="A43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" t="s">
+        <v>239</v>
+      </c>
+      <c r="E43" t="s">
+        <v>242</v>
+      </c>
+      <c r="I43" t="s">
+        <v>284</v>
+      </c>
+      <c r="J43" t="s">
+        <v>81</v>
+      </c>
+      <c r="K43">
+        <v>2787.25</v>
+      </c>
+      <c r="L43">
+        <v>4761.25</v>
+      </c>
+      <c r="M43">
+        <v>69.68000000000001</v>
+      </c>
+      <c r="N43">
+        <v>4000</v>
+      </c>
+      <c r="O43" t="s">
+        <v>86</v>
+      </c>
+      <c r="P43" s="1">
+        <v>43544</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>45916</v>
+      </c>
+      <c r="R43" t="s">
+        <v>324</v>
+      </c>
+      <c r="S43" t="s">
+        <v>146</v>
+      </c>
+      <c r="T43" t="s">
+        <v>342</v>
+      </c>
+      <c r="U43" s="1">
+        <v>42850</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
+      <c r="A44" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" t="s">
+        <v>239</v>
+      </c>
+      <c r="E44" t="s">
+        <v>242</v>
+      </c>
+      <c r="I44" t="s">
+        <v>285</v>
+      </c>
+      <c r="J44" t="s">
+        <v>81</v>
+      </c>
+      <c r="K44">
+        <v>2413.42</v>
+      </c>
+      <c r="L44">
+        <v>4307.92</v>
+      </c>
+      <c r="M44">
+        <v>60.34</v>
+      </c>
+      <c r="N44">
+        <v>4000</v>
+      </c>
+      <c r="O44" t="s">
+        <v>99</v>
+      </c>
+      <c r="P44" s="1">
+        <v>45076</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>45539</v>
+      </c>
+      <c r="R44" t="s">
+        <v>325</v>
+      </c>
+      <c r="S44" t="s">
+        <v>146</v>
+      </c>
+      <c r="T44" t="s">
+        <v>343</v>
+      </c>
+      <c r="U44" s="1">
+        <v>44404</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
+      <c r="A45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" t="s">
+        <v>242</v>
+      </c>
+      <c r="I45" t="s">
+        <v>286</v>
+      </c>
+      <c r="J45" t="s">
+        <v>81</v>
+      </c>
+      <c r="K45">
+        <v>2266.5</v>
+      </c>
+      <c r="L45">
+        <v>4852</v>
+      </c>
+      <c r="M45">
+        <v>56.66</v>
+      </c>
+      <c r="N45">
+        <v>4000</v>
+      </c>
+      <c r="O45" t="s">
+        <v>83</v>
+      </c>
+      <c r="P45" s="1">
+        <v>42963</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>45239</v>
+      </c>
+      <c r="R45" t="s">
+        <v>326</v>
+      </c>
+      <c r="S45" t="s">
+        <v>146</v>
+      </c>
+      <c r="T45" t="s">
+        <v>344</v>
+      </c>
+      <c r="U45" s="1">
+        <v>42698</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
+      <c r="A46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" t="s">
+        <v>238</v>
+      </c>
+      <c r="E46" t="s">
+        <v>242</v>
+      </c>
+      <c r="I46" t="s">
         <v>287</v>
       </c>
-      <c r="AA3" t="s">
-        <v>290</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29">
-      <c r="A4">
-        <v>3810271134</v>
-      </c>
-      <c r="C4" t="s">
-        <v>258</v>
-      </c>
-      <c r="D4" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4" s="1">
-        <v>45716</v>
-      </c>
-      <c r="F4" t="s">
-        <v>263</v>
-      </c>
-      <c r="G4" s="1">
-        <v>45716</v>
-      </c>
-      <c r="H4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I4">
-        <v>198</v>
-      </c>
-      <c r="J4" t="s">
-        <v>264</v>
-      </c>
-      <c r="K4" t="s">
-        <v>56</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>45716</v>
-      </c>
-      <c r="R4" s="1">
-        <v>45722</v>
-      </c>
-      <c r="S4" s="1">
-        <v>45716</v>
-      </c>
-      <c r="U4" t="s">
-        <v>267</v>
-      </c>
-      <c r="W4" t="s">
-        <v>22</v>
-      </c>
-      <c r="X4" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>276</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>291</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29">
-      <c r="A5">
-        <v>3810271161</v>
-      </c>
-      <c r="C5" t="s">
-        <v>258</v>
-      </c>
-      <c r="D5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E5" s="1">
-        <v>45728</v>
-      </c>
-      <c r="F5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G5" s="1">
-        <v>45728</v>
-      </c>
-      <c r="H5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5">
-        <v>198</v>
-      </c>
-      <c r="J5" t="s">
-        <v>264</v>
-      </c>
-      <c r="K5" t="s">
-        <v>46</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>45722</v>
-      </c>
-      <c r="R5" s="1">
-        <v>45782</v>
-      </c>
-      <c r="S5" s="1">
-        <v>45728</v>
-      </c>
-      <c r="U5" t="s">
-        <v>267</v>
-      </c>
-      <c r="W5" t="s">
-        <v>22</v>
-      </c>
-      <c r="X5" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>277</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>289</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
-      <c r="A6">
-        <v>3810271238</v>
-      </c>
-      <c r="B6">
-        <v>3810271161</v>
-      </c>
-      <c r="C6" t="s">
-        <v>258</v>
-      </c>
-      <c r="D6" t="s">
-        <v>261</v>
-      </c>
-      <c r="E6" s="1">
-        <v>45755</v>
-      </c>
-      <c r="F6" t="s">
-        <v>263</v>
-      </c>
-      <c r="G6" s="1">
-        <v>45755</v>
-      </c>
-      <c r="H6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6">
-        <v>198</v>
-      </c>
-      <c r="J6" t="s">
-        <v>264</v>
-      </c>
-      <c r="K6" t="s">
-        <v>46</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>45728</v>
-      </c>
-      <c r="R6" s="1">
-        <v>45734</v>
-      </c>
-      <c r="S6" s="1">
-        <v>45755</v>
-      </c>
-      <c r="U6" t="s">
-        <v>267</v>
-      </c>
-      <c r="W6" t="s">
-        <v>22</v>
-      </c>
-      <c r="X6" t="s">
-        <v>271</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>270</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29">
-      <c r="A7">
-        <v>3810272417</v>
-      </c>
-      <c r="B7">
-        <v>3810272114</v>
-      </c>
-      <c r="C7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E7" s="1">
-        <v>45772</v>
-      </c>
-      <c r="F7" t="s">
-        <v>263</v>
-      </c>
-      <c r="H7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7">
-        <v>198</v>
-      </c>
-      <c r="J7" t="s">
-        <v>264</v>
-      </c>
-      <c r="K7" t="s">
-        <v>46</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>45772</v>
-      </c>
-      <c r="R7" s="1">
-        <v>45775</v>
-      </c>
-      <c r="U7" t="s">
-        <v>267</v>
-      </c>
-      <c r="W7" t="s">
-        <v>22</v>
-      </c>
-      <c r="X7" t="s">
-        <v>271</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>279</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29">
-      <c r="A8">
-        <v>3810272291</v>
-      </c>
-      <c r="B8">
-        <v>3810272114</v>
-      </c>
-      <c r="C8" t="s">
-        <v>258</v>
-      </c>
-      <c r="D8" t="s">
-        <v>262</v>
-      </c>
-      <c r="E8" s="1">
-        <v>45762</v>
-      </c>
-      <c r="F8" t="s">
-        <v>263</v>
-      </c>
-      <c r="H8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8">
-        <v>198</v>
-      </c>
-      <c r="J8" t="s">
-        <v>264</v>
-      </c>
-      <c r="K8" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>45762</v>
-      </c>
-      <c r="R8" s="1">
-        <v>45770</v>
-      </c>
-      <c r="U8" t="s">
-        <v>267</v>
-      </c>
-      <c r="W8" t="s">
-        <v>22</v>
-      </c>
-      <c r="X8" t="s">
-        <v>271</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>280</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>272</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29">
-      <c r="A9">
-        <v>3810272339</v>
-      </c>
-      <c r="B9">
-        <v>3810272114</v>
-      </c>
-      <c r="C9" t="s">
-        <v>258</v>
-      </c>
-      <c r="D9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E9" s="1">
-        <v>45763</v>
-      </c>
-      <c r="F9" t="s">
-        <v>263</v>
-      </c>
-      <c r="H9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9">
-        <v>198</v>
-      </c>
-      <c r="J9" t="s">
-        <v>264</v>
-      </c>
-      <c r="K9" t="s">
-        <v>46</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>45763</v>
-      </c>
-      <c r="R9" s="1">
-        <v>45777</v>
-      </c>
-      <c r="U9" t="s">
-        <v>267</v>
-      </c>
-      <c r="W9" t="s">
-        <v>22</v>
-      </c>
-      <c r="X9" t="s">
-        <v>271</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>281</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>272</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29">
-      <c r="A10">
-        <v>3810272114</v>
-      </c>
-      <c r="B10">
-        <v>3810271161</v>
-      </c>
-      <c r="C10" t="s">
-        <v>258</v>
-      </c>
-      <c r="D10" t="s">
-        <v>261</v>
-      </c>
-      <c r="E10" s="1">
-        <v>45755</v>
-      </c>
-      <c r="F10" t="s">
-        <v>263</v>
-      </c>
-      <c r="G10" s="1">
-        <v>45755</v>
-      </c>
-      <c r="H10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10">
-        <v>198</v>
-      </c>
-      <c r="J10" t="s">
-        <v>264</v>
-      </c>
-      <c r="K10" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>45754</v>
-      </c>
-      <c r="R10" s="1">
-        <v>45849</v>
-      </c>
-      <c r="S10" s="1">
-        <v>45754</v>
-      </c>
-      <c r="U10" t="s">
-        <v>267</v>
-      </c>
-      <c r="W10" t="s">
-        <v>22</v>
-      </c>
-      <c r="X10" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>282</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>292</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29">
-      <c r="A11">
-        <v>3810255268</v>
-      </c>
-      <c r="C11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D11" t="s">
-        <v>261</v>
-      </c>
-      <c r="E11" s="1">
-        <v>44973</v>
-      </c>
-      <c r="F11" t="s">
-        <v>263</v>
-      </c>
-      <c r="G11" s="1">
-        <v>44973</v>
-      </c>
-      <c r="H11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11">
-        <v>198</v>
-      </c>
-      <c r="J11" t="s">
-        <v>264</v>
-      </c>
-      <c r="K11" t="s">
-        <v>265</v>
-      </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>44973</v>
-      </c>
-      <c r="R11" s="1">
-        <v>45687</v>
-      </c>
-      <c r="S11" s="1">
-        <v>44973</v>
-      </c>
-      <c r="U11" t="s">
-        <v>267</v>
-      </c>
-      <c r="W11" t="s">
-        <v>22</v>
-      </c>
-      <c r="X11" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>270</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29">
-      <c r="A12">
-        <v>3810264674</v>
-      </c>
-      <c r="C12" t="s">
-        <v>259</v>
-      </c>
-      <c r="D12" t="s">
-        <v>261</v>
-      </c>
-      <c r="E12" s="1">
-        <v>45358</v>
-      </c>
-      <c r="F12" t="s">
-        <v>263</v>
-      </c>
-      <c r="G12" s="1">
-        <v>45358</v>
-      </c>
-      <c r="H12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12">
-        <v>198</v>
-      </c>
-      <c r="J12" t="s">
-        <v>264</v>
-      </c>
-      <c r="K12" t="s">
-        <v>70</v>
-      </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>45358</v>
-      </c>
-      <c r="R12" s="1">
-        <v>45517</v>
-      </c>
-      <c r="S12" s="1">
-        <v>45358</v>
-      </c>
-      <c r="U12" t="s">
-        <v>267</v>
-      </c>
-      <c r="W12" t="s">
-        <v>22</v>
-      </c>
-      <c r="X12" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>284</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>288</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>293</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29">
-      <c r="A13">
-        <v>3810268863</v>
-      </c>
-      <c r="C13" t="s">
-        <v>259</v>
-      </c>
-      <c r="D13" t="s">
-        <v>261</v>
-      </c>
-      <c r="E13" s="1">
-        <v>45573</v>
-      </c>
-      <c r="F13" t="s">
-        <v>263</v>
-      </c>
-      <c r="G13" s="1">
-        <v>45573</v>
-      </c>
-      <c r="H13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I13">
-        <v>198</v>
-      </c>
-      <c r="J13" t="s">
-        <v>264</v>
-      </c>
-      <c r="K13" t="s">
-        <v>57</v>
-      </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>45572</v>
-      </c>
-      <c r="R13" s="1">
-        <v>45572</v>
-      </c>
-      <c r="S13" s="1">
-        <v>45573</v>
-      </c>
-      <c r="U13" t="s">
-        <v>266</v>
-      </c>
-      <c r="V13" t="s">
-        <v>269</v>
-      </c>
-      <c r="W13" t="s">
-        <v>22</v>
-      </c>
-      <c r="X13" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>285</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>270</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29">
-      <c r="A14">
-        <v>3810271550</v>
-      </c>
-      <c r="C14" t="s">
-        <v>259</v>
-      </c>
-      <c r="D14" t="s">
-        <v>261</v>
-      </c>
-      <c r="E14" s="1">
-        <v>45747</v>
-      </c>
-      <c r="F14" t="s">
-        <v>263</v>
-      </c>
-      <c r="G14" s="1">
-        <v>45747</v>
-      </c>
-      <c r="H14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14">
-        <v>198</v>
-      </c>
-      <c r="J14" t="s">
-        <v>264</v>
-      </c>
-      <c r="K14" t="s">
-        <v>55</v>
-      </c>
-      <c r="P14">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>45736</v>
-      </c>
-      <c r="R14" s="1">
-        <v>46101</v>
-      </c>
-      <c r="S14" s="1">
-        <v>45747</v>
-      </c>
-      <c r="U14" t="s">
-        <v>267</v>
-      </c>
-      <c r="W14" t="s">
-        <v>22</v>
-      </c>
-      <c r="X14" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>286</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>270</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>303</v>
+      <c r="J46" t="s">
+        <v>81</v>
+      </c>
+      <c r="K46">
+        <v>545.75</v>
+      </c>
+      <c r="L46">
+        <v>5774.25</v>
+      </c>
+      <c r="M46">
+        <v>13.64</v>
+      </c>
+      <c r="N46">
+        <v>4000</v>
+      </c>
+      <c r="O46" t="s">
+        <v>90</v>
+      </c>
+      <c r="P46" s="1">
+        <v>45054</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>45586</v>
+      </c>
+      <c r="R46" t="s">
+        <v>327</v>
+      </c>
+      <c r="S46" t="s">
+        <v>146</v>
+      </c>
+      <c r="T46" t="s">
+        <v>345</v>
+      </c>
+      <c r="U46" s="1">
+        <v>43941</v>
       </c>
     </row>
   </sheetData>
@@ -9075,2199 +10125,695 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2">
+        <v>2743</v>
+      </c>
+      <c r="C2">
+        <v>4412.92</v>
+      </c>
+      <c r="D2">
+        <v>87.08333333</v>
+      </c>
+      <c r="E2">
+        <v>95.14042553</v>
+      </c>
+      <c r="F2">
+        <v>447.16</v>
+      </c>
+      <c r="G2">
+        <v>0.9153136834</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3">
+        <v>4449.92</v>
+      </c>
+      <c r="D3">
+        <v>0.08333333333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4">
+        <v>2740</v>
+      </c>
+      <c r="C4">
+        <v>3301.75</v>
+      </c>
+      <c r="D4">
+        <v>139.25</v>
+      </c>
+      <c r="E4">
+        <v>55.52851064</v>
+      </c>
+      <c r="F4">
+        <v>260.984</v>
+      </c>
+      <c r="G4">
+        <v>2.50772078</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5">
+        <v>2709</v>
+      </c>
+      <c r="C5">
+        <v>2755.25</v>
+      </c>
+      <c r="D5">
+        <v>147.75</v>
+      </c>
+      <c r="E5">
+        <v>51.37446809</v>
+      </c>
+      <c r="F5">
+        <v>241.46</v>
+      </c>
+      <c r="G5">
+        <v>2.875942185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6">
+        <v>2736</v>
+      </c>
+      <c r="C6">
+        <v>3992.33</v>
+      </c>
+      <c r="D6">
+        <v>207.6666667</v>
+      </c>
+      <c r="E6">
+        <v>55.52851064</v>
+      </c>
+      <c r="F6">
+        <v>260.984</v>
+      </c>
+      <c r="G6">
+        <v>3.739820576</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7">
+        <v>2722</v>
+      </c>
+      <c r="C7">
+        <v>4158.42</v>
+      </c>
+      <c r="D7">
+        <v>241.5833333</v>
+      </c>
+      <c r="E7">
+        <v>59.24680851</v>
+      </c>
+      <c r="F7">
+        <v>278.46</v>
+      </c>
+      <c r="G7">
+        <v>4.077575475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8">
+        <v>2741</v>
+      </c>
+      <c r="C8">
+        <v>3886.67</v>
+      </c>
+      <c r="D8">
+        <v>313.3333333</v>
+      </c>
+      <c r="E8">
+        <v>55.52851064</v>
+      </c>
+      <c r="F8">
+        <v>260.984</v>
+      </c>
+      <c r="G8">
+        <v>5.642746937</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9">
+        <v>2719</v>
+      </c>
+      <c r="C9">
+        <v>4342.92</v>
+      </c>
+      <c r="D9">
+        <v>357.0833333</v>
+      </c>
+      <c r="E9">
+        <v>59.24680851</v>
+      </c>
+      <c r="F9">
+        <v>278.46</v>
+      </c>
+      <c r="G9">
+        <v>6.027047571</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10">
+        <v>2723</v>
+      </c>
+      <c r="C10">
+        <v>2830.67</v>
+      </c>
+      <c r="D10">
+        <v>408.3333333</v>
+      </c>
+      <c r="E10">
+        <v>61.24042553</v>
+      </c>
+      <c r="F10">
+        <v>287.83</v>
+      </c>
+      <c r="G10">
+        <v>6.667708949</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11">
+        <v>2703</v>
+      </c>
+      <c r="C11">
+        <v>4186.33</v>
+      </c>
+      <c r="D11">
+        <v>313.6666667</v>
+      </c>
+      <c r="E11">
+        <v>42.09219858</v>
+      </c>
+      <c r="F11">
+        <v>197.8333333</v>
+      </c>
+      <c r="G11">
+        <v>7.451895535</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12">
+        <v>2739</v>
+      </c>
+      <c r="C12">
+        <v>1250.58</v>
+      </c>
+      <c r="D12">
+        <v>249.4166667</v>
+      </c>
+      <c r="E12">
+        <v>17.77163121</v>
+      </c>
+      <c r="F12">
+        <v>83.52666667</v>
+      </c>
+      <c r="G12">
+        <v>14.03453987</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13">
+        <v>3095.33</v>
+      </c>
+      <c r="D13">
+        <v>904.6666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14">
+        <v>2832.83</v>
+      </c>
+      <c r="D14">
+        <v>1167.166667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15">
+        <v>2742</v>
+      </c>
+      <c r="C15">
+        <v>790.42</v>
+      </c>
+      <c r="D15">
+        <v>853.5833333</v>
+      </c>
+      <c r="E15">
+        <v>56.75531915</v>
+      </c>
+      <c r="F15">
+        <v>266.75</v>
+      </c>
+      <c r="G15">
+        <v>15.03970634</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16">
+        <v>2704</v>
+      </c>
+      <c r="C16">
+        <v>4873.67</v>
+      </c>
+      <c r="D16">
+        <v>126.3333333</v>
+      </c>
+      <c r="E16">
+        <v>8.351063829999999</v>
+      </c>
+      <c r="F16">
+        <v>39.25</v>
+      </c>
+      <c r="G16">
+        <v>15.12781316</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17">
+        <v>2720</v>
+      </c>
+      <c r="C17">
+        <v>3209.33</v>
+      </c>
+      <c r="D17">
+        <v>790.6666667</v>
+      </c>
+      <c r="E17">
+        <v>51.37446809</v>
+      </c>
+      <c r="F17">
+        <v>241.46</v>
+      </c>
+      <c r="G17">
+        <v>15.39026478</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18">
+        <v>2708</v>
+      </c>
+      <c r="C18">
+        <v>2295.75</v>
+      </c>
+      <c r="D18">
+        <v>704.25</v>
+      </c>
+      <c r="E18">
+        <v>42.09219858</v>
+      </c>
+      <c r="F18">
+        <v>197.8333333</v>
+      </c>
+      <c r="G18">
+        <v>16.7311289</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19">
+        <v>2737</v>
+      </c>
+      <c r="C19">
+        <v>377.25</v>
+      </c>
+      <c r="D19">
+        <v>1122.75</v>
+      </c>
+      <c r="E19">
+        <v>55.52851064</v>
+      </c>
+      <c r="F19">
+        <v>260.984</v>
+      </c>
+      <c r="G19">
+        <v>20.21934295</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20">
+        <v>2733</v>
+      </c>
+      <c r="C20">
+        <v>4135.92</v>
+      </c>
+      <c r="D20">
+        <v>364.0833333</v>
+      </c>
+      <c r="E20">
+        <v>17.77163121</v>
+      </c>
+      <c r="F20">
+        <v>83.52666667</v>
+      </c>
+      <c r="G20">
+        <v>20.48677069</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21">
+        <v>1440.833333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22">
+        <v>267.17</v>
+      </c>
+      <c r="D22">
+        <v>1232.833333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23">
+        <v>2702</v>
+      </c>
+      <c r="C23">
+        <v>552.83</v>
+      </c>
+      <c r="D23">
+        <v>947.1666667</v>
+      </c>
+      <c r="E23">
+        <v>42.09219858</v>
+      </c>
+      <c r="F23">
+        <v>197.8333333</v>
+      </c>
+      <c r="G23">
+        <v>22.5021904</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24">
+        <v>2738</v>
+      </c>
+      <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
+        <v>1400</v>
+      </c>
+      <c r="E24">
+        <v>55.52851064</v>
+      </c>
+      <c r="F24">
+        <v>260.984</v>
+      </c>
+      <c r="G24">
+        <v>25.21227355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26">
+        <v>4997</v>
+      </c>
+      <c r="D26">
+        <v>-997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27">
+        <v>2889.42</v>
+      </c>
+      <c r="D27">
+        <v>110.5833333</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28">
+        <v>5139.25</v>
+      </c>
+      <c r="D28">
+        <v>110.75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29">
+        <v>2727</v>
+      </c>
+      <c r="C29">
+        <v>100</v>
+      </c>
+      <c r="D29">
+        <v>1400</v>
+      </c>
+      <c r="E29">
+        <v>35.05319149</v>
+      </c>
+      <c r="F29">
+        <v>164.75</v>
+      </c>
+      <c r="G29">
+        <v>39.93930197</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30">
+        <v>4479.58</v>
+      </c>
+      <c r="D30">
+        <v>-479.5833333</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32">
+        <v>4832.42</v>
+      </c>
+      <c r="D32">
+        <v>-832.4166667</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33">
+        <v>4629.83</v>
+      </c>
+      <c r="D33">
+        <v>-629.8333333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E2" t="s">
-        <v>310</v>
-      </c>
-      <c r="I2" t="s">
-        <v>312</v>
-      </c>
-      <c r="J2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K2">
-        <v>797.33</v>
-      </c>
-      <c r="L2">
-        <v>6156.92</v>
-      </c>
-      <c r="M2">
-        <v>19.93</v>
-      </c>
-      <c r="N2">
-        <v>4000</v>
-      </c>
-      <c r="O2" t="s">
-        <v>104</v>
-      </c>
-      <c r="P2" s="1">
-        <v>45490</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>45015</v>
-      </c>
-      <c r="R2" t="s">
-        <v>358</v>
-      </c>
-      <c r="S2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E3" t="s">
-        <v>310</v>
-      </c>
-      <c r="I3" t="s">
-        <v>313</v>
-      </c>
-      <c r="J3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3">
-        <v>1001.83</v>
-      </c>
-      <c r="L3">
-        <v>8226.17</v>
-      </c>
-      <c r="M3">
-        <v>25.05</v>
-      </c>
-      <c r="N3">
-        <v>4000</v>
-      </c>
-      <c r="O3" t="s">
-        <v>83</v>
-      </c>
-      <c r="P3" s="1">
-        <v>45618</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>45614</v>
-      </c>
-      <c r="R3" t="s">
-        <v>359</v>
-      </c>
-      <c r="S3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>306</v>
-      </c>
-      <c r="E4" t="s">
-        <v>310</v>
-      </c>
-      <c r="I4" t="s">
-        <v>314</v>
-      </c>
-      <c r="J4" t="s">
-        <v>81</v>
-      </c>
-      <c r="K4">
-        <v>2813.92</v>
-      </c>
-      <c r="L4">
-        <v>6291.75</v>
-      </c>
-      <c r="M4">
-        <v>70.34999999999999</v>
-      </c>
-      <c r="N4">
-        <v>4000</v>
-      </c>
-      <c r="O4" t="s">
-        <v>99</v>
-      </c>
-      <c r="P4" s="1">
-        <v>45539</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>45539</v>
-      </c>
-      <c r="R4" t="s">
-        <v>360</v>
-      </c>
-      <c r="S4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E5" t="s">
-        <v>310</v>
-      </c>
-      <c r="I5" t="s">
-        <v>315</v>
-      </c>
-      <c r="J5" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5">
-        <v>1258.5</v>
-      </c>
-      <c r="L5">
-        <v>5428.67</v>
-      </c>
-      <c r="M5">
-        <v>31.46</v>
-      </c>
-      <c r="N5">
-        <v>4000</v>
-      </c>
-      <c r="O5" t="s">
-        <v>100</v>
-      </c>
-      <c r="P5" s="1">
-        <v>45567</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>45490</v>
-      </c>
-      <c r="R5" t="s">
-        <v>361</v>
-      </c>
-      <c r="S5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E6" t="s">
-        <v>310</v>
-      </c>
-      <c r="I6" t="s">
-        <v>316</v>
-      </c>
-      <c r="J6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K6">
-        <v>708.33</v>
-      </c>
-      <c r="L6">
-        <v>6401.42</v>
-      </c>
-      <c r="M6">
-        <v>17.71</v>
-      </c>
-      <c r="N6">
-        <v>4000</v>
-      </c>
-      <c r="O6" t="s">
-        <v>97</v>
-      </c>
-      <c r="P6" s="1">
-        <v>45568</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>45526</v>
-      </c>
-      <c r="R6" t="s">
-        <v>362</v>
-      </c>
-      <c r="S6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>306</v>
-      </c>
-      <c r="E7" t="s">
-        <v>310</v>
-      </c>
-      <c r="I7" t="s">
-        <v>317</v>
-      </c>
-      <c r="J7" t="s">
-        <v>81</v>
-      </c>
-      <c r="K7">
-        <v>133.42</v>
-      </c>
-      <c r="L7">
-        <v>9321</v>
-      </c>
-      <c r="M7">
-        <v>3.34</v>
-      </c>
-      <c r="N7">
-        <v>4000</v>
-      </c>
-      <c r="O7" t="s">
-        <v>85</v>
-      </c>
-      <c r="P7" s="1">
-        <v>45831</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>45352</v>
-      </c>
-      <c r="R7" t="s">
-        <v>363</v>
-      </c>
-      <c r="S7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>306</v>
-      </c>
-      <c r="E8" t="s">
-        <v>310</v>
-      </c>
-      <c r="I8" t="s">
-        <v>318</v>
-      </c>
-      <c r="J8" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8">
-        <v>224.08</v>
-      </c>
-      <c r="L8">
-        <v>4042.75</v>
-      </c>
-      <c r="M8">
-        <v>5.6</v>
-      </c>
-      <c r="N8">
-        <v>4000</v>
-      </c>
-      <c r="O8" t="s">
-        <v>105</v>
-      </c>
-      <c r="P8" s="1">
-        <v>45601</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>44704</v>
-      </c>
-      <c r="R8" t="s">
-        <v>364</v>
-      </c>
-      <c r="S8" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>307</v>
-      </c>
-      <c r="E9" t="s">
-        <v>310</v>
-      </c>
-      <c r="I9" t="s">
-        <v>319</v>
-      </c>
-      <c r="J9" t="s">
-        <v>81</v>
-      </c>
-      <c r="K9">
-        <v>783.42</v>
-      </c>
-      <c r="L9">
-        <v>5242.33</v>
-      </c>
-      <c r="M9">
-        <v>19.59</v>
-      </c>
-      <c r="N9">
-        <v>4000</v>
-      </c>
-      <c r="O9" t="s">
-        <v>94</v>
-      </c>
-      <c r="P9" s="1">
-        <v>45631</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>45628</v>
-      </c>
-      <c r="R9" t="s">
-        <v>365</v>
-      </c>
-      <c r="S9" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" t="s">
-        <v>306</v>
-      </c>
-      <c r="E10" t="s">
-        <v>310</v>
-      </c>
-      <c r="I10" t="s">
-        <v>320</v>
-      </c>
-      <c r="J10" t="s">
-        <v>81</v>
-      </c>
-      <c r="K10">
-        <v>2718.58</v>
-      </c>
-      <c r="L10">
-        <v>9682.42</v>
-      </c>
-      <c r="M10">
-        <v>67.95999999999999</v>
-      </c>
-      <c r="N10">
-        <v>4000</v>
-      </c>
-      <c r="O10" t="s">
-        <v>91</v>
-      </c>
-      <c r="P10" s="1">
-        <v>43902</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>43549</v>
-      </c>
-      <c r="R10" t="s">
-        <v>366</v>
-      </c>
-      <c r="S10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>307</v>
-      </c>
-      <c r="E11" t="s">
-        <v>310</v>
-      </c>
-      <c r="I11" t="s">
-        <v>321</v>
-      </c>
-      <c r="J11" t="s">
-        <v>81</v>
-      </c>
-      <c r="K11">
-        <v>3603.17</v>
-      </c>
-      <c r="L11">
-        <v>6330.08</v>
-      </c>
-      <c r="M11">
-        <v>90.08</v>
-      </c>
-      <c r="N11">
-        <v>4000</v>
-      </c>
-      <c r="O11" t="s">
-        <v>101</v>
-      </c>
-      <c r="P11" s="1">
-        <v>44736</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>44735</v>
-      </c>
-      <c r="R11" t="s">
-        <v>367</v>
-      </c>
-      <c r="S11" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>307</v>
-      </c>
-      <c r="E12" t="s">
-        <v>310</v>
-      </c>
-      <c r="I12" t="s">
-        <v>322</v>
-      </c>
-      <c r="J12" t="s">
-        <v>81</v>
-      </c>
-      <c r="K12">
-        <v>2298.67</v>
-      </c>
-      <c r="L12">
-        <v>4857.58</v>
-      </c>
-      <c r="M12">
-        <v>57.47</v>
-      </c>
-      <c r="N12">
-        <v>4000</v>
-      </c>
-      <c r="O12" t="s">
-        <v>84</v>
-      </c>
-      <c r="P12" s="1">
-        <v>45776</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>45776</v>
-      </c>
-      <c r="R12" t="s">
-        <v>368</v>
-      </c>
-      <c r="S12" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
-      <c r="A13" t="s">
-        <v>305</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>307</v>
-      </c>
-      <c r="E13" t="s">
-        <v>310</v>
-      </c>
-      <c r="I13" t="s">
-        <v>323</v>
-      </c>
-      <c r="J13" t="s">
-        <v>81</v>
-      </c>
-      <c r="K13">
-        <v>2132.08</v>
-      </c>
-      <c r="L13">
-        <v>5063.58</v>
-      </c>
-      <c r="M13">
-        <v>53.3</v>
-      </c>
-      <c r="N13">
-        <v>4000</v>
-      </c>
-      <c r="O13" t="s">
-        <v>82</v>
-      </c>
-      <c r="P13" s="1">
-        <v>45772</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>45600</v>
-      </c>
-      <c r="R13" t="s">
-        <v>369</v>
-      </c>
-      <c r="S13" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>307</v>
-      </c>
-      <c r="E14" t="s">
-        <v>310</v>
-      </c>
-      <c r="I14" t="s">
-        <v>324</v>
-      </c>
-      <c r="J14" t="s">
-        <v>81</v>
-      </c>
-      <c r="K14">
-        <v>1013.92</v>
-      </c>
-      <c r="L14">
-        <v>5211.33</v>
-      </c>
-      <c r="M14">
-        <v>25.35</v>
-      </c>
-      <c r="N14">
-        <v>4000</v>
-      </c>
-      <c r="O14" t="s">
-        <v>102</v>
-      </c>
-      <c r="P14" s="1">
-        <v>45000</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>44630</v>
-      </c>
-      <c r="R14" t="s">
-        <v>370</v>
-      </c>
-      <c r="S14" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" t="s">
-        <v>306</v>
-      </c>
-      <c r="E15" t="s">
-        <v>310</v>
-      </c>
-      <c r="I15" t="s">
-        <v>325</v>
-      </c>
-      <c r="J15" t="s">
-        <v>81</v>
-      </c>
-      <c r="K15">
-        <v>209.92</v>
-      </c>
-      <c r="L15">
-        <v>209.92</v>
-      </c>
-      <c r="M15">
-        <v>5.25</v>
-      </c>
-      <c r="N15">
-        <v>4000</v>
-      </c>
-      <c r="O15" t="s">
-        <v>96</v>
-      </c>
-      <c r="P15" s="1">
-        <v>45930</v>
-      </c>
-      <c r="S15" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>306</v>
-      </c>
-      <c r="E16" t="s">
-        <v>310</v>
-      </c>
-      <c r="I16" t="s">
-        <v>326</v>
-      </c>
-      <c r="J16" t="s">
-        <v>81</v>
-      </c>
-      <c r="K16">
-        <v>49.33</v>
-      </c>
-      <c r="L16">
-        <v>49.33</v>
-      </c>
-      <c r="M16">
-        <v>1.23</v>
-      </c>
-      <c r="N16">
-        <v>4000</v>
-      </c>
-      <c r="O16" t="s">
-        <v>92</v>
-      </c>
-      <c r="P16" s="1">
-        <v>46035</v>
-      </c>
-      <c r="S16" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" t="s">
-        <v>306</v>
-      </c>
-      <c r="E17" t="s">
-        <v>310</v>
-      </c>
-      <c r="I17" t="s">
-        <v>327</v>
-      </c>
-      <c r="J17" t="s">
-        <v>81</v>
-      </c>
-      <c r="K17">
-        <v>923.83</v>
-      </c>
-      <c r="L17">
-        <v>19483.33</v>
-      </c>
-      <c r="M17">
-        <v>23.1</v>
-      </c>
-      <c r="N17">
-        <v>4000</v>
-      </c>
-      <c r="O17" t="s">
-        <v>95</v>
-      </c>
-      <c r="P17" s="1">
-        <v>45371</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>45026</v>
-      </c>
-      <c r="R17" t="s">
-        <v>371</v>
-      </c>
-      <c r="S17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>306</v>
-      </c>
-      <c r="E18" t="s">
-        <v>310</v>
-      </c>
-      <c r="I18" t="s">
-        <v>328</v>
-      </c>
-      <c r="J18" t="s">
-        <v>81</v>
-      </c>
-      <c r="K18">
-        <v>112.33</v>
-      </c>
-      <c r="L18">
-        <v>4746.08</v>
-      </c>
-      <c r="M18">
-        <v>2.81</v>
-      </c>
-      <c r="N18">
-        <v>4000</v>
-      </c>
-      <c r="O18" t="s">
-        <v>93</v>
-      </c>
-      <c r="P18" s="1">
-        <v>46001</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>45371</v>
-      </c>
-      <c r="R18" t="s">
-        <v>372</v>
-      </c>
-      <c r="S18" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>306</v>
-      </c>
-      <c r="E19" t="s">
-        <v>310</v>
-      </c>
-      <c r="I19" t="s">
-        <v>329</v>
-      </c>
-      <c r="J19" t="s">
-        <v>81</v>
-      </c>
-      <c r="K19">
-        <v>598</v>
-      </c>
-      <c r="L19">
-        <v>17238.58</v>
-      </c>
-      <c r="M19">
-        <v>14.95</v>
-      </c>
-      <c r="N19">
-        <v>4000</v>
-      </c>
-      <c r="O19" t="s">
-        <v>106</v>
-      </c>
-      <c r="P19" s="1">
-        <v>45436</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>45294</v>
-      </c>
-      <c r="R19" t="s">
-        <v>373</v>
-      </c>
-      <c r="S19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21">
-      <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" t="s">
-        <v>310</v>
-      </c>
-      <c r="I20" t="s">
-        <v>330</v>
-      </c>
-      <c r="J20" t="s">
-        <v>81</v>
-      </c>
-      <c r="K20">
-        <v>779.67</v>
-      </c>
-      <c r="L20">
-        <v>9284.25</v>
-      </c>
-      <c r="M20">
-        <v>19.49</v>
-      </c>
-      <c r="N20">
-        <v>4000</v>
-      </c>
-      <c r="O20" t="s">
-        <v>98</v>
-      </c>
-      <c r="P20" s="1">
-        <v>44372</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>44369</v>
-      </c>
-      <c r="R20" t="s">
-        <v>374</v>
-      </c>
-      <c r="S20" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>306</v>
-      </c>
-      <c r="E21" t="s">
-        <v>310</v>
-      </c>
-      <c r="I21" t="s">
-        <v>331</v>
-      </c>
-      <c r="J21" t="s">
-        <v>81</v>
-      </c>
-      <c r="K21">
-        <v>1685.25</v>
-      </c>
-      <c r="L21">
-        <v>5853.58</v>
-      </c>
-      <c r="M21">
-        <v>42.13</v>
-      </c>
-      <c r="N21">
-        <v>4000</v>
-      </c>
-      <c r="O21" t="s">
-        <v>107</v>
-      </c>
-      <c r="P21" s="1">
-        <v>44362</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>43894</v>
-      </c>
-      <c r="R21" t="s">
-        <v>375</v>
-      </c>
-      <c r="S21" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" t="s">
-        <v>306</v>
-      </c>
-      <c r="E22" t="s">
-        <v>310</v>
-      </c>
-      <c r="I22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J22" t="s">
-        <v>81</v>
-      </c>
-      <c r="K22">
-        <v>1926.58</v>
-      </c>
-      <c r="L22">
-        <v>11035.33</v>
-      </c>
-      <c r="M22">
-        <v>48.16</v>
-      </c>
-      <c r="N22">
-        <v>4000</v>
-      </c>
-      <c r="O22" t="s">
-        <v>88</v>
-      </c>
-      <c r="P22" s="1">
-        <v>45511</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>45509</v>
-      </c>
-      <c r="R22" t="s">
-        <v>376</v>
-      </c>
-      <c r="S22" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" t="s">
-        <v>306</v>
-      </c>
-      <c r="E23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I23" t="s">
-        <v>333</v>
-      </c>
-      <c r="J23" t="s">
-        <v>81</v>
-      </c>
-      <c r="L23">
-        <v>2562.83</v>
-      </c>
-      <c r="N23">
-        <v>4000</v>
-      </c>
-      <c r="O23" t="s">
-        <v>356</v>
-      </c>
-      <c r="P23" s="1">
-        <v>40044</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>40126</v>
-      </c>
-      <c r="R23" t="s">
-        <v>377</v>
-      </c>
-      <c r="S23" t="s">
-        <v>144</v>
-      </c>
-      <c r="T23" t="s">
-        <v>396</v>
-      </c>
-      <c r="U23" s="1">
-        <v>45775</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21">
-      <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" t="s">
-        <v>306</v>
-      </c>
-      <c r="E24" t="s">
-        <v>310</v>
-      </c>
-      <c r="I24" t="s">
-        <v>334</v>
-      </c>
-      <c r="J24" t="s">
-        <v>81</v>
-      </c>
-      <c r="K24">
-        <v>1903.17</v>
-      </c>
-      <c r="L24">
-        <v>4373</v>
-      </c>
-      <c r="M24">
-        <v>47.58</v>
-      </c>
-      <c r="N24">
-        <v>4000</v>
-      </c>
-      <c r="O24" t="s">
-        <v>82</v>
-      </c>
-      <c r="P24" s="1">
-        <v>43549</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>45772</v>
-      </c>
-      <c r="R24" t="s">
-        <v>378</v>
-      </c>
-      <c r="S24" t="s">
-        <v>144</v>
-      </c>
-      <c r="T24" t="s">
-        <v>397</v>
-      </c>
-      <c r="U24" s="1">
-        <v>45810</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21">
-      <c r="A25" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" t="s">
-        <v>306</v>
-      </c>
-      <c r="E25" t="s">
-        <v>310</v>
-      </c>
-      <c r="I25" t="s">
-        <v>335</v>
-      </c>
-      <c r="J25" t="s">
-        <v>81</v>
-      </c>
-      <c r="K25">
-        <v>835.42</v>
-      </c>
-      <c r="L25">
-        <v>5559.92</v>
-      </c>
-      <c r="M25">
-        <v>20.89</v>
-      </c>
-      <c r="N25">
-        <v>4000</v>
-      </c>
-      <c r="O25" t="s">
-        <v>88</v>
-      </c>
-      <c r="P25" s="1">
-        <v>45447</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>45510</v>
-      </c>
-      <c r="R25" t="s">
-        <v>379</v>
-      </c>
-      <c r="S25" t="s">
-        <v>144</v>
-      </c>
-      <c r="T25" t="s">
-        <v>398</v>
-      </c>
-      <c r="U25" s="1">
-        <v>45937</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21">
-      <c r="A26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" t="s">
-        <v>307</v>
-      </c>
-      <c r="E26" t="s">
-        <v>310</v>
-      </c>
-      <c r="I26" t="s">
-        <v>336</v>
-      </c>
-      <c r="J26" t="s">
-        <v>81</v>
-      </c>
-      <c r="K26">
-        <v>1657.42</v>
-      </c>
-      <c r="L26">
-        <v>4769.83</v>
-      </c>
-      <c r="M26">
-        <v>41.44</v>
-      </c>
-      <c r="N26">
-        <v>4000</v>
-      </c>
-      <c r="O26" t="s">
-        <v>102</v>
-      </c>
-      <c r="P26" s="1">
-        <v>44485</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>44959</v>
-      </c>
-      <c r="R26" t="s">
-        <v>380</v>
-      </c>
-      <c r="S26" t="s">
-        <v>144</v>
-      </c>
-      <c r="T26" t="s">
-        <v>399</v>
-      </c>
-      <c r="U26" s="1">
-        <v>45580</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21">
-      <c r="A27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" t="s">
-        <v>306</v>
-      </c>
-      <c r="E27" t="s">
-        <v>310</v>
-      </c>
-      <c r="I27" t="s">
-        <v>337</v>
-      </c>
-      <c r="J27" t="s">
-        <v>81</v>
-      </c>
-      <c r="K27">
-        <v>39.92</v>
-      </c>
-      <c r="L27">
-        <v>3843.83</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>4000</v>
-      </c>
-      <c r="O27" t="s">
-        <v>88</v>
-      </c>
-      <c r="P27" s="1">
-        <v>45420</v>
-      </c>
-      <c r="Q27" s="1">
-        <v>45446</v>
-      </c>
-      <c r="R27" t="s">
-        <v>381</v>
-      </c>
-      <c r="S27" t="s">
-        <v>144</v>
-      </c>
-      <c r="T27" t="s">
-        <v>400</v>
-      </c>
-      <c r="U27" s="1">
-        <v>45588</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" t="s">
-        <v>306</v>
-      </c>
-      <c r="E28" t="s">
-        <v>310</v>
-      </c>
-      <c r="I28" t="s">
-        <v>338</v>
-      </c>
-      <c r="J28" t="s">
-        <v>81</v>
-      </c>
-      <c r="K28">
-        <v>4204.25</v>
-      </c>
-      <c r="L28">
-        <v>15636.58</v>
-      </c>
-      <c r="M28">
-        <v>105.11</v>
-      </c>
-      <c r="N28">
-        <v>4000</v>
-      </c>
-      <c r="O28" t="s">
-        <v>103</v>
-      </c>
-      <c r="P28" s="1">
-        <v>44369</v>
-      </c>
-      <c r="Q28" s="1">
-        <v>45824</v>
-      </c>
-      <c r="R28" t="s">
-        <v>382</v>
-      </c>
-      <c r="S28" t="s">
-        <v>144</v>
-      </c>
-      <c r="T28" t="s">
-        <v>401</v>
-      </c>
-      <c r="U28" s="1">
-        <v>45831</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21">
-      <c r="A29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" t="s">
-        <v>307</v>
-      </c>
-      <c r="E29" t="s">
-        <v>310</v>
-      </c>
-      <c r="I29" t="s">
-        <v>339</v>
-      </c>
-      <c r="J29" t="s">
-        <v>81</v>
-      </c>
-      <c r="K29">
-        <v>1891.33</v>
-      </c>
-      <c r="L29">
-        <v>5276.25</v>
-      </c>
-      <c r="M29">
-        <v>47.28</v>
-      </c>
-      <c r="N29">
-        <v>4000</v>
-      </c>
-      <c r="O29" t="s">
-        <v>100</v>
-      </c>
-      <c r="P29" s="1">
-        <v>44652</v>
-      </c>
-      <c r="Q29" s="1">
-        <v>45567</v>
-      </c>
-      <c r="R29" t="s">
-        <v>383</v>
-      </c>
-      <c r="S29" t="s">
-        <v>144</v>
-      </c>
-      <c r="T29" t="s">
-        <v>402</v>
-      </c>
-      <c r="U29" s="1">
-        <v>45734</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21">
-      <c r="A30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" t="s">
-        <v>306</v>
-      </c>
-      <c r="E30" t="s">
-        <v>310</v>
-      </c>
-      <c r="I30" t="s">
-        <v>340</v>
-      </c>
-      <c r="J30" t="s">
-        <v>81</v>
-      </c>
-      <c r="N30">
-        <v>4000</v>
-      </c>
-      <c r="S30" t="s">
-        <v>144</v>
-      </c>
-      <c r="T30" t="s">
-        <v>403</v>
-      </c>
-      <c r="U30" s="1">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" t="s">
-        <v>306</v>
-      </c>
-      <c r="E31" t="s">
-        <v>310</v>
-      </c>
-      <c r="I31" t="s">
-        <v>341</v>
-      </c>
-      <c r="J31" t="s">
-        <v>81</v>
-      </c>
-      <c r="N31">
-        <v>4000</v>
-      </c>
-      <c r="S31" t="s">
-        <v>144</v>
-      </c>
-      <c r="T31" t="s">
-        <v>404</v>
-      </c>
-      <c r="U31" s="1">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" t="s">
-        <v>306</v>
-      </c>
-      <c r="E32" t="s">
-        <v>310</v>
-      </c>
-      <c r="I32" t="s">
-        <v>342</v>
-      </c>
-      <c r="J32" t="s">
-        <v>81</v>
-      </c>
-      <c r="N32">
-        <v>4000</v>
-      </c>
-      <c r="S32" t="s">
-        <v>144</v>
-      </c>
-      <c r="T32" t="s">
-        <v>405</v>
-      </c>
-      <c r="U32" s="1">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21">
-      <c r="A33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" t="s">
-        <v>307</v>
-      </c>
-      <c r="E33" t="s">
-        <v>310</v>
-      </c>
-      <c r="I33" t="s">
-        <v>343</v>
-      </c>
-      <c r="J33" t="s">
-        <v>81</v>
-      </c>
-      <c r="K33">
-        <v>3238.83</v>
-      </c>
-      <c r="L33">
-        <v>6794.67</v>
-      </c>
-      <c r="M33">
-        <v>80.97</v>
-      </c>
-      <c r="N33">
-        <v>4000</v>
-      </c>
-      <c r="O33" t="s">
-        <v>92</v>
-      </c>
-      <c r="P33" s="1">
-        <v>43762</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>46031</v>
-      </c>
-      <c r="R33" t="s">
-        <v>384</v>
-      </c>
-      <c r="S33" t="s">
-        <v>148</v>
-      </c>
-      <c r="T33" t="s">
-        <v>384</v>
-      </c>
-      <c r="U33" s="1">
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21">
-      <c r="A34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" t="s">
-        <v>307</v>
-      </c>
-      <c r="E34" t="s">
-        <v>310</v>
-      </c>
-      <c r="I34" t="s">
-        <v>344</v>
-      </c>
-      <c r="J34" t="s">
-        <v>81</v>
-      </c>
-      <c r="K34">
-        <v>833.58</v>
-      </c>
-      <c r="L34">
-        <v>833.58</v>
-      </c>
-      <c r="M34">
-        <v>20.84</v>
-      </c>
-      <c r="N34">
-        <v>4000</v>
-      </c>
-      <c r="O34" t="s">
-        <v>357</v>
-      </c>
-      <c r="P34" s="1">
-        <v>40071</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>41023</v>
-      </c>
-      <c r="S34" t="s">
-        <v>149</v>
-      </c>
-      <c r="U34" s="1">
-        <v>41023</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21">
+      <c r="D34">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>287</v>
-      </c>
-      <c r="B35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" t="s">
-        <v>306</v>
-      </c>
-      <c r="E35" t="s">
-        <v>310</v>
-      </c>
-      <c r="I35" t="s">
-        <v>345</v>
-      </c>
-      <c r="J35" t="s">
-        <v>81</v>
-      </c>
-      <c r="L35">
-        <v>6168.75</v>
-      </c>
-      <c r="N35">
-        <v>4000</v>
-      </c>
-      <c r="O35" t="s">
-        <v>89</v>
-      </c>
-      <c r="P35" s="1">
-        <v>44784</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>45259</v>
-      </c>
-      <c r="R35" t="s">
-        <v>385</v>
-      </c>
-      <c r="S35" t="s">
-        <v>149</v>
-      </c>
-      <c r="U35" s="1">
-        <v>45259</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21">
+        <v>66</v>
+      </c>
+      <c r="C35">
+        <v>5348.58</v>
+      </c>
+      <c r="D35">
+        <v>-1348.583333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" t="s">
-        <v>306</v>
-      </c>
-      <c r="E36" t="s">
-        <v>310</v>
-      </c>
-      <c r="I36" t="s">
-        <v>346</v>
-      </c>
-      <c r="J36" t="s">
-        <v>81</v>
-      </c>
-      <c r="K36">
-        <v>2184.17</v>
-      </c>
-      <c r="L36">
-        <v>13647.17</v>
-      </c>
-      <c r="M36">
-        <v>54.6</v>
-      </c>
-      <c r="N36">
-        <v>4000</v>
-      </c>
-      <c r="O36" t="s">
-        <v>93</v>
-      </c>
-      <c r="P36" s="1">
-        <v>45103</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>46000</v>
-      </c>
-      <c r="R36" t="s">
-        <v>386</v>
-      </c>
-      <c r="S36" t="s">
-        <v>149</v>
-      </c>
-      <c r="U36" s="1">
-        <v>46000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21">
+        <v>70</v>
+      </c>
+      <c r="C36">
+        <v>3346.92</v>
+      </c>
+      <c r="D36">
+        <v>653.0833333</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" t="s">
-        <v>308</v>
-      </c>
-      <c r="E37" t="s">
-        <v>310</v>
-      </c>
-      <c r="I37" t="s">
-        <v>329</v>
-      </c>
-      <c r="J37" t="s">
-        <v>81</v>
-      </c>
-      <c r="N37">
-        <v>4000</v>
-      </c>
-      <c r="S37" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21">
+        <v>57</v>
+      </c>
+      <c r="B37">
+        <v>2731</v>
+      </c>
+      <c r="C37">
+        <v>396.25</v>
+      </c>
+      <c r="D37">
+        <v>1103.75</v>
+      </c>
+      <c r="E37">
+        <v>17.77163121</v>
+      </c>
+      <c r="F37">
+        <v>83.52666667</v>
+      </c>
+      <c r="G37">
+        <v>62.10741081</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" t="s">
-        <v>306</v>
-      </c>
-      <c r="E38" t="s">
-        <v>310</v>
-      </c>
-      <c r="I38" t="s">
-        <v>347</v>
-      </c>
-      <c r="J38" t="s">
-        <v>81</v>
-      </c>
-      <c r="K38">
-        <v>553.17</v>
-      </c>
-      <c r="L38">
-        <v>553.17</v>
-      </c>
-      <c r="M38">
-        <v>13.83</v>
-      </c>
-      <c r="N38">
-        <v>4000</v>
-      </c>
-      <c r="O38" t="s">
-        <v>98</v>
-      </c>
-      <c r="P38" s="1">
-        <v>38511</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>39068</v>
-      </c>
-      <c r="R38" t="s">
-        <v>387</v>
-      </c>
-      <c r="S38" t="s">
-        <v>149</v>
-      </c>
-      <c r="U38" s="1">
-        <v>39068</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21">
+        <v>73</v>
+      </c>
+      <c r="C38">
+        <v>482.08</v>
+      </c>
+      <c r="D38">
+        <v>1017.916667</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39" t="s">
-        <v>306</v>
-      </c>
-      <c r="E39" t="s">
-        <v>310</v>
-      </c>
-      <c r="I39" t="s">
-        <v>348</v>
-      </c>
-      <c r="J39" t="s">
-        <v>81</v>
-      </c>
-      <c r="K39">
-        <v>85.58</v>
-      </c>
-      <c r="L39">
-        <v>2007.17</v>
-      </c>
-      <c r="M39">
-        <v>2.14</v>
-      </c>
-      <c r="N39">
-        <v>4000</v>
-      </c>
-      <c r="O39" t="s">
-        <v>105</v>
-      </c>
-      <c r="P39" s="1">
-        <v>39006</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>40568</v>
-      </c>
-      <c r="R39" t="s">
-        <v>388</v>
-      </c>
-      <c r="S39" t="s">
-        <v>149</v>
-      </c>
-      <c r="T39" t="s">
-        <v>406</v>
-      </c>
-      <c r="U39" s="1">
-        <v>40568</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21">
+        <v>54</v>
+      </c>
+      <c r="C39">
+        <v>142.92</v>
+      </c>
+      <c r="D39">
+        <v>1357.083333</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" t="s">
-        <v>309</v>
-      </c>
-      <c r="E40" t="s">
-        <v>311</v>
-      </c>
-      <c r="I40" t="s">
-        <v>349</v>
-      </c>
-      <c r="J40" t="s">
-        <v>81</v>
-      </c>
-      <c r="K40">
-        <v>796.67</v>
-      </c>
-      <c r="L40">
-        <v>3739.5</v>
-      </c>
-      <c r="O40" t="s">
-        <v>102</v>
-      </c>
-      <c r="P40" s="1">
-        <v>40836</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>42270</v>
-      </c>
-      <c r="R40" t="s">
-        <v>389</v>
-      </c>
-      <c r="S40" t="s">
-        <v>149</v>
-      </c>
-      <c r="T40" t="s">
-        <v>407</v>
-      </c>
-      <c r="U40" s="1">
-        <v>42270</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21">
+        <v>77</v>
+      </c>
+      <c r="C40">
+        <v>1818.92</v>
+      </c>
+      <c r="D40">
+        <v>1181.083333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" t="s">
-        <v>306</v>
-      </c>
-      <c r="E41" t="s">
-        <v>310</v>
-      </c>
-      <c r="I41" t="s">
-        <v>350</v>
-      </c>
-      <c r="J41" t="s">
-        <v>81</v>
-      </c>
-      <c r="K41">
-        <v>981.58</v>
-      </c>
-      <c r="L41">
-        <v>7558.67</v>
-      </c>
-      <c r="M41">
-        <v>24.54</v>
-      </c>
-      <c r="N41">
-        <v>4000</v>
-      </c>
-      <c r="O41" t="s">
-        <v>97</v>
-      </c>
-      <c r="P41" s="1">
-        <v>42940</v>
-      </c>
-      <c r="Q41" s="1">
-        <v>43494</v>
-      </c>
-      <c r="R41" t="s">
-        <v>390</v>
-      </c>
-      <c r="S41" t="s">
-        <v>146</v>
-      </c>
-      <c r="T41" t="s">
-        <v>408</v>
-      </c>
-      <c r="U41" s="1">
-        <v>44148</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21">
-      <c r="A42" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" t="s">
-        <v>36</v>
-      </c>
-      <c r="C42" t="s">
-        <v>307</v>
-      </c>
-      <c r="E42" t="s">
-        <v>310</v>
-      </c>
-      <c r="I42" t="s">
-        <v>351</v>
-      </c>
-      <c r="J42" t="s">
-        <v>81</v>
-      </c>
-      <c r="K42">
-        <v>3152</v>
-      </c>
-      <c r="L42">
-        <v>6001.67</v>
-      </c>
-      <c r="M42">
-        <v>78.8</v>
-      </c>
-      <c r="N42">
-        <v>4000</v>
-      </c>
-      <c r="O42" t="s">
-        <v>84</v>
-      </c>
-      <c r="P42" s="1">
-        <v>43696</v>
-      </c>
-      <c r="Q42" s="1">
-        <v>45776</v>
-      </c>
-      <c r="R42" t="s">
-        <v>391</v>
-      </c>
-      <c r="S42" t="s">
-        <v>146</v>
-      </c>
-      <c r="T42" t="s">
-        <v>409</v>
-      </c>
-      <c r="U42" s="1">
-        <v>43185</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21">
-      <c r="A43" t="s">
-        <v>32</v>
-      </c>
-      <c r="B43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43" t="s">
-        <v>307</v>
-      </c>
-      <c r="E43" t="s">
-        <v>310</v>
-      </c>
-      <c r="I43" t="s">
-        <v>352</v>
-      </c>
-      <c r="J43" t="s">
-        <v>81</v>
-      </c>
-      <c r="K43">
-        <v>2787.25</v>
-      </c>
-      <c r="L43">
-        <v>4761.25</v>
-      </c>
-      <c r="M43">
-        <v>69.68000000000001</v>
-      </c>
-      <c r="N43">
-        <v>4000</v>
-      </c>
-      <c r="O43" t="s">
-        <v>86</v>
-      </c>
-      <c r="P43" s="1">
-        <v>43544</v>
-      </c>
-      <c r="Q43" s="1">
-        <v>45916</v>
-      </c>
-      <c r="R43" t="s">
-        <v>392</v>
-      </c>
-      <c r="S43" t="s">
-        <v>146</v>
-      </c>
-      <c r="T43" t="s">
-        <v>410</v>
-      </c>
-      <c r="U43" s="1">
-        <v>42850</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21">
-      <c r="A44" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" t="s">
-        <v>307</v>
-      </c>
-      <c r="E44" t="s">
-        <v>310</v>
-      </c>
-      <c r="I44" t="s">
-        <v>353</v>
-      </c>
-      <c r="J44" t="s">
-        <v>81</v>
-      </c>
-      <c r="K44">
-        <v>2413.42</v>
-      </c>
-      <c r="L44">
-        <v>4307.92</v>
-      </c>
-      <c r="M44">
-        <v>60.34</v>
-      </c>
-      <c r="N44">
-        <v>4000</v>
-      </c>
-      <c r="O44" t="s">
-        <v>99</v>
-      </c>
-      <c r="P44" s="1">
-        <v>45076</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>45539</v>
-      </c>
-      <c r="R44" t="s">
-        <v>393</v>
-      </c>
-      <c r="S44" t="s">
-        <v>146</v>
-      </c>
-      <c r="T44" t="s">
-        <v>411</v>
-      </c>
-      <c r="U44" s="1">
-        <v>44404</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21">
-      <c r="A45" t="s">
-        <v>32</v>
-      </c>
-      <c r="B45" t="s">
-        <v>36</v>
-      </c>
-      <c r="C45" t="s">
-        <v>307</v>
-      </c>
-      <c r="E45" t="s">
-        <v>310</v>
-      </c>
-      <c r="I45" t="s">
-        <v>354</v>
-      </c>
-      <c r="J45" t="s">
-        <v>81</v>
-      </c>
-      <c r="K45">
-        <v>2266.5</v>
-      </c>
-      <c r="L45">
-        <v>4852</v>
-      </c>
-      <c r="M45">
-        <v>56.66</v>
-      </c>
-      <c r="N45">
-        <v>4000</v>
-      </c>
-      <c r="O45" t="s">
-        <v>83</v>
-      </c>
-      <c r="P45" s="1">
-        <v>42963</v>
-      </c>
-      <c r="Q45" s="1">
-        <v>45239</v>
-      </c>
-      <c r="R45" t="s">
-        <v>394</v>
-      </c>
-      <c r="S45" t="s">
-        <v>146</v>
-      </c>
-      <c r="T45" t="s">
-        <v>412</v>
-      </c>
-      <c r="U45" s="1">
-        <v>42698</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21">
-      <c r="A46" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" t="s">
-        <v>36</v>
-      </c>
-      <c r="C46" t="s">
-        <v>306</v>
-      </c>
-      <c r="E46" t="s">
-        <v>310</v>
-      </c>
-      <c r="I46" t="s">
-        <v>355</v>
-      </c>
-      <c r="J46" t="s">
-        <v>81</v>
-      </c>
-      <c r="K46">
-        <v>545.75</v>
-      </c>
-      <c r="L46">
-        <v>5774.25</v>
-      </c>
-      <c r="M46">
-        <v>13.64</v>
-      </c>
-      <c r="N46">
-        <v>4000</v>
-      </c>
-      <c r="O46" t="s">
-        <v>90</v>
-      </c>
-      <c r="P46" s="1">
-        <v>45054</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>45586</v>
-      </c>
-      <c r="R46" t="s">
-        <v>395</v>
-      </c>
-      <c r="S46" t="s">
-        <v>146</v>
-      </c>
-      <c r="T46" t="s">
-        <v>413</v>
-      </c>
-      <c r="U46" s="1">
-        <v>43941</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -11277,742 +10823,44 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D1" t="s">
-        <v>415</v>
-      </c>
-      <c r="E1" t="s">
-        <v>416</v>
-      </c>
-      <c r="F1" t="s">
-        <v>417</v>
-      </c>
-      <c r="G1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2">
-        <v>2743</v>
-      </c>
-      <c r="C2">
-        <v>4412.92</v>
-      </c>
-      <c r="D2">
-        <v>87.08333333</v>
-      </c>
-      <c r="E2">
-        <v>95.14042553</v>
-      </c>
-      <c r="F2">
-        <v>447.16</v>
-      </c>
-      <c r="G2">
-        <v>0.9153136834</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3">
-        <v>4449.92</v>
-      </c>
-      <c r="D3">
-        <v>0.08333333333</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4">
-        <v>2740</v>
-      </c>
-      <c r="C4">
-        <v>3301.75</v>
-      </c>
-      <c r="D4">
-        <v>139.25</v>
-      </c>
-      <c r="E4">
-        <v>55.52851064</v>
-      </c>
-      <c r="F4">
-        <v>260.984</v>
-      </c>
-      <c r="G4">
-        <v>2.50772078</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5">
-        <v>2709</v>
-      </c>
-      <c r="C5">
-        <v>2755.25</v>
-      </c>
-      <c r="D5">
-        <v>147.75</v>
-      </c>
-      <c r="E5">
-        <v>51.37446809</v>
-      </c>
-      <c r="F5">
-        <v>241.46</v>
-      </c>
-      <c r="G5">
-        <v>2.875942185</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6">
-        <v>2736</v>
-      </c>
-      <c r="C6">
-        <v>3992.33</v>
-      </c>
-      <c r="D6">
-        <v>207.6666667</v>
-      </c>
-      <c r="E6">
-        <v>55.52851064</v>
-      </c>
-      <c r="F6">
-        <v>260.984</v>
-      </c>
-      <c r="G6">
-        <v>3.739820576</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7">
-        <v>2722</v>
-      </c>
-      <c r="C7">
-        <v>4158.42</v>
-      </c>
-      <c r="D7">
-        <v>241.5833333</v>
-      </c>
-      <c r="E7">
-        <v>59.24680851</v>
-      </c>
-      <c r="F7">
-        <v>278.46</v>
-      </c>
-      <c r="G7">
-        <v>4.077575475</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8">
-        <v>2741</v>
-      </c>
-      <c r="C8">
-        <v>3886.67</v>
-      </c>
-      <c r="D8">
-        <v>313.3333333</v>
-      </c>
-      <c r="E8">
-        <v>55.52851064</v>
-      </c>
-      <c r="F8">
-        <v>260.984</v>
-      </c>
-      <c r="G8">
-        <v>5.642746937</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9">
-        <v>2719</v>
-      </c>
-      <c r="C9">
-        <v>4342.92</v>
-      </c>
-      <c r="D9">
-        <v>357.0833333</v>
-      </c>
-      <c r="E9">
-        <v>59.24680851</v>
-      </c>
-      <c r="F9">
-        <v>278.46</v>
-      </c>
-      <c r="G9">
-        <v>6.027047571</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10">
-        <v>2723</v>
-      </c>
-      <c r="C10">
-        <v>2830.67</v>
-      </c>
-      <c r="D10">
-        <v>408.3333333</v>
-      </c>
-      <c r="E10">
-        <v>61.24042553</v>
-      </c>
-      <c r="F10">
-        <v>287.83</v>
-      </c>
-      <c r="G10">
-        <v>6.667708949</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11">
-        <v>2703</v>
-      </c>
-      <c r="C11">
-        <v>4186.33</v>
-      </c>
-      <c r="D11">
-        <v>313.6666667</v>
-      </c>
-      <c r="E11">
-        <v>42.09219858</v>
-      </c>
-      <c r="F11">
-        <v>197.8333333</v>
-      </c>
-      <c r="G11">
-        <v>7.451895535</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12">
-        <v>2739</v>
-      </c>
-      <c r="C12">
-        <v>1250.58</v>
-      </c>
-      <c r="D12">
-        <v>249.4166667</v>
-      </c>
-      <c r="E12">
-        <v>17.77163121</v>
-      </c>
-      <c r="F12">
-        <v>83.52666667</v>
-      </c>
-      <c r="G12">
-        <v>14.03453987</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13">
-        <v>3095.33</v>
-      </c>
-      <c r="D13">
-        <v>904.6666667</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14">
-        <v>2832.83</v>
-      </c>
-      <c r="D14">
-        <v>1167.166667</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15">
-        <v>2742</v>
-      </c>
-      <c r="C15">
-        <v>790.42</v>
-      </c>
-      <c r="D15">
-        <v>853.5833333</v>
-      </c>
-      <c r="E15">
-        <v>56.75531915</v>
-      </c>
-      <c r="F15">
-        <v>266.75</v>
-      </c>
-      <c r="G15">
-        <v>15.03970634</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16">
-        <v>2704</v>
-      </c>
-      <c r="C16">
-        <v>4873.67</v>
-      </c>
-      <c r="D16">
-        <v>126.3333333</v>
-      </c>
-      <c r="E16">
-        <v>8.351063829999999</v>
-      </c>
-      <c r="F16">
-        <v>39.25</v>
-      </c>
-      <c r="G16">
-        <v>15.12781316</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17">
-        <v>2720</v>
-      </c>
-      <c r="C17">
-        <v>3209.33</v>
-      </c>
-      <c r="D17">
-        <v>790.6666667</v>
-      </c>
-      <c r="E17">
-        <v>51.37446809</v>
-      </c>
-      <c r="F17">
-        <v>241.46</v>
-      </c>
-      <c r="G17">
-        <v>15.39026478</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18">
-        <v>2708</v>
-      </c>
-      <c r="C18">
-        <v>2295.75</v>
-      </c>
-      <c r="D18">
-        <v>704.25</v>
-      </c>
-      <c r="E18">
-        <v>42.09219858</v>
-      </c>
-      <c r="F18">
-        <v>197.8333333</v>
-      </c>
-      <c r="G18">
-        <v>16.7311289</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19">
-        <v>2737</v>
-      </c>
-      <c r="C19">
-        <v>377.25</v>
-      </c>
-      <c r="D19">
-        <v>1122.75</v>
-      </c>
-      <c r="E19">
-        <v>55.52851064</v>
-      </c>
-      <c r="F19">
-        <v>260.984</v>
-      </c>
-      <c r="G19">
-        <v>20.21934295</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20">
-        <v>2733</v>
-      </c>
-      <c r="C20">
-        <v>4135.92</v>
-      </c>
-      <c r="D20">
-        <v>364.0833333</v>
-      </c>
-      <c r="E20">
-        <v>17.77163121</v>
-      </c>
-      <c r="F20">
-        <v>83.52666667</v>
-      </c>
-      <c r="G20">
-        <v>20.48677069</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21">
-        <v>1440.833333</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22">
-        <v>267.17</v>
-      </c>
-      <c r="D22">
-        <v>1232.833333</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23">
-        <v>2702</v>
-      </c>
-      <c r="C23">
-        <v>552.83</v>
-      </c>
-      <c r="D23">
-        <v>947.1666667</v>
-      </c>
-      <c r="E23">
-        <v>42.09219858</v>
-      </c>
-      <c r="F23">
-        <v>197.8333333</v>
-      </c>
-      <c r="G23">
-        <v>22.5021904</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24">
-        <v>2738</v>
-      </c>
-      <c r="C24">
-        <v>100</v>
-      </c>
-      <c r="D24">
-        <v>1400</v>
-      </c>
-      <c r="E24">
-        <v>55.52851064</v>
-      </c>
-      <c r="F24">
-        <v>260.984</v>
-      </c>
-      <c r="G24">
-        <v>25.21227355</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26">
-        <v>4997</v>
-      </c>
-      <c r="D26">
-        <v>-997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27">
-        <v>2889.42</v>
-      </c>
-      <c r="D27">
-        <v>110.5833333</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28">
-        <v>5139.25</v>
-      </c>
-      <c r="D28">
-        <v>110.75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29">
-        <v>2727</v>
-      </c>
-      <c r="C29">
-        <v>100</v>
-      </c>
-      <c r="D29">
-        <v>1400</v>
-      </c>
-      <c r="E29">
-        <v>35.05319149</v>
-      </c>
-      <c r="F29">
-        <v>164.75</v>
-      </c>
-      <c r="G29">
-        <v>39.93930197</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30">
-        <v>4479.58</v>
-      </c>
-      <c r="D30">
-        <v>-479.5833333</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31">
-        <v>5200</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32">
-        <v>4832.42</v>
-      </c>
-      <c r="D32">
-        <v>-832.4166667</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33">
-        <v>4629.83</v>
-      </c>
-      <c r="D33">
-        <v>-629.8333333</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35">
-        <v>5348.58</v>
-      </c>
-      <c r="D35">
-        <v>-1348.583333</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36">
-        <v>3346.92</v>
-      </c>
-      <c r="D36">
-        <v>653.0833333</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37">
-        <v>2731</v>
-      </c>
-      <c r="C37">
-        <v>396.25</v>
-      </c>
-      <c r="D37">
-        <v>1103.75</v>
-      </c>
-      <c r="E37">
-        <v>17.77163121</v>
-      </c>
-      <c r="F37">
-        <v>83.52666667</v>
-      </c>
-      <c r="G37">
-        <v>62.10741081</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38">
-        <v>482.08</v>
-      </c>
-      <c r="D38">
-        <v>1017.916667</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39">
-        <v>142.92</v>
-      </c>
-      <c r="D39">
-        <v>1357.083333</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40">
-        <v>1818.92</v>
-      </c>
-      <c r="D40">
-        <v>1181.083333</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" t="s">
-        <v>173</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>419</v>
+        <v>351</v>
       </c>
       <c r="B1" t="s">
-        <v>420</v>
+        <v>352</v>
       </c>
       <c r="C1" t="s">
-        <v>421</v>
+        <v>353</v>
       </c>
       <c r="D1" t="s">
-        <v>422</v>
+        <v>354</v>
       </c>
       <c r="E1" t="s">
-        <v>423</v>
+        <v>355</v>
       </c>
       <c r="F1" t="s">
-        <v>424</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B2" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C2" t="s">
-        <v>430</v>
+        <v>362</v>
       </c>
       <c r="D2" t="s">
-        <v>437</v>
+        <v>369</v>
       </c>
       <c r="E2" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F2">
         <v>200000</v>
@@ -12020,19 +10868,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B3" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C3" t="s">
-        <v>431</v>
+        <v>363</v>
       </c>
       <c r="D3" t="s">
-        <v>438</v>
+        <v>370</v>
       </c>
       <c r="E3" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F3">
         <v>700000</v>
@@ -12040,19 +10888,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>426</v>
+        <v>358</v>
       </c>
       <c r="B4" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C4" t="s">
-        <v>431</v>
+        <v>363</v>
       </c>
       <c r="D4" t="s">
-        <v>439</v>
+        <v>371</v>
       </c>
       <c r="E4" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F4">
         <v>800000</v>
@@ -12060,19 +10908,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B5" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>364</v>
       </c>
       <c r="D5" t="s">
-        <v>440</v>
+        <v>372</v>
       </c>
       <c r="E5" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F5">
         <v>400000</v>
@@ -12080,19 +10928,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B6" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>364</v>
       </c>
       <c r="D6" t="s">
-        <v>441</v>
+        <v>373</v>
       </c>
       <c r="E6" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F6">
         <v>400000</v>
@@ -12100,19 +10948,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B7" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C7" t="s">
-        <v>432</v>
+        <v>364</v>
       </c>
       <c r="D7" t="s">
-        <v>442</v>
+        <v>374</v>
       </c>
       <c r="E7" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F7">
         <v>400000</v>
@@ -12120,19 +10968,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B8" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>433</v>
+        <v>365</v>
       </c>
       <c r="D8" t="s">
-        <v>443</v>
+        <v>375</v>
       </c>
       <c r="E8" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F8">
         <v>1000000</v>
@@ -12140,19 +10988,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>426</v>
+        <v>358</v>
       </c>
       <c r="B9" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C9" t="s">
-        <v>433</v>
+        <v>365</v>
       </c>
       <c r="D9" t="s">
-        <v>444</v>
+        <v>376</v>
       </c>
       <c r="E9" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F9">
         <v>1000000</v>
@@ -12160,19 +11008,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>426</v>
+        <v>358</v>
       </c>
       <c r="B10" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C10" t="s">
-        <v>433</v>
+        <v>365</v>
       </c>
       <c r="D10" t="s">
-        <v>445</v>
+        <v>377</v>
       </c>
       <c r="E10" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F10">
         <v>1000000</v>
@@ -12180,19 +11028,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B11" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C11" t="s">
-        <v>430</v>
+        <v>362</v>
       </c>
       <c r="D11" t="s">
-        <v>446</v>
+        <v>378</v>
       </c>
       <c r="E11" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F11">
         <v>563000</v>
@@ -12200,19 +11048,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B12" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C12" t="s">
-        <v>430</v>
+        <v>362</v>
       </c>
       <c r="D12" t="s">
-        <v>447</v>
+        <v>379</v>
       </c>
       <c r="E12" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F12">
         <v>320000</v>
@@ -12220,19 +11068,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B13" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C13" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="D13" t="s">
-        <v>448</v>
+        <v>380</v>
       </c>
       <c r="E13" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F13">
         <v>120000</v>
@@ -12240,19 +11088,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>427</v>
+        <v>359</v>
       </c>
       <c r="B14" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C14" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="D14" t="s">
-        <v>449</v>
+        <v>381</v>
       </c>
       <c r="E14" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F14">
         <v>120000</v>
@@ -12260,19 +11108,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B15" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C15" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="D15" t="s">
-        <v>450</v>
+        <v>382</v>
       </c>
       <c r="E15" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F15">
         <v>80000</v>
@@ -12280,19 +11128,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>427</v>
+        <v>359</v>
       </c>
       <c r="B16" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C16" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="D16" t="s">
-        <v>451</v>
+        <v>383</v>
       </c>
       <c r="E16" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F16">
         <v>80000</v>
@@ -12300,19 +11148,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>428</v>
+        <v>360</v>
       </c>
       <c r="B17" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C17" t="s">
-        <v>435</v>
+        <v>367</v>
       </c>
       <c r="D17" t="s">
-        <v>452</v>
+        <v>384</v>
       </c>
       <c r="E17" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F17">
         <v>3800000</v>
@@ -12320,19 +11168,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>428</v>
+        <v>360</v>
       </c>
       <c r="B18" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C18" t="s">
-        <v>435</v>
+        <v>367</v>
       </c>
       <c r="D18" t="s">
-        <v>453</v>
+        <v>385</v>
       </c>
       <c r="E18" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F18">
         <v>3800000</v>
@@ -12340,19 +11188,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B19" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C19" t="s">
-        <v>435</v>
+        <v>367</v>
       </c>
       <c r="D19" t="s">
-        <v>454</v>
+        <v>386</v>
       </c>
       <c r="E19" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F19">
         <v>3800000</v>
@@ -12360,19 +11208,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B20" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C20" t="s">
-        <v>436</v>
+        <v>368</v>
       </c>
       <c r="D20" t="s">
-        <v>455</v>
+        <v>387</v>
       </c>
       <c r="E20" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F20">
         <v>3800000</v>
@@ -12380,19 +11228,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>426</v>
+        <v>358</v>
       </c>
       <c r="B21" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C21" t="s">
-        <v>436</v>
+        <v>368</v>
       </c>
       <c r="D21" t="s">
-        <v>456</v>
+        <v>388</v>
       </c>
       <c r="E21" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F21">
         <v>3800000</v>
@@ -12400,19 +11248,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>426</v>
+        <v>358</v>
       </c>
       <c r="B22" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C22" t="s">
-        <v>436</v>
+        <v>368</v>
       </c>
       <c r="D22" t="s">
-        <v>457</v>
+        <v>389</v>
       </c>
       <c r="E22" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F22">
         <v>3800000</v>
@@ -12420,19 +11268,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B23" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C23" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="D23" t="s">
-        <v>458</v>
+        <v>390</v>
       </c>
       <c r="E23" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F23">
         <v>430000</v>
@@ -12440,19 +11288,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B24" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C24" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="D24" t="s">
-        <v>459</v>
+        <v>391</v>
       </c>
       <c r="E24" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F24">
         <v>430000</v>
@@ -12460,19 +11308,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B25" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C25" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="D25" t="s">
-        <v>460</v>
+        <v>392</v>
       </c>
       <c r="E25" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F25">
         <v>425000</v>
@@ -12480,19 +11328,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>425</v>
+        <v>357</v>
       </c>
       <c r="B26" t="s">
-        <v>429</v>
+        <v>361</v>
       </c>
       <c r="C26" t="s">
-        <v>434</v>
+        <v>366</v>
       </c>
       <c r="D26" t="s">
-        <v>461</v>
+        <v>393</v>
       </c>
       <c r="E26" t="s">
-        <v>462</v>
+        <v>394</v>
       </c>
       <c r="F26">
         <v>60000</v>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1237,8 +1237,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1254,7 +1262,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1262,12 +1270,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1567,70 +1593,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1671,10 +1697,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>41754</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1686,7 +1712,7 @@
       <c r="T2" t="s">
         <v>149</v>
       </c>
-      <c r="U2" s="1">
+      <c r="U2" s="2">
         <v>46170</v>
       </c>
     </row>
@@ -1727,10 +1753,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>44709</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1777,10 +1803,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>44348</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -1827,10 +1853,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>46059</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -1842,7 +1868,7 @@
       <c r="T5" t="s">
         <v>150</v>
       </c>
-      <c r="U5" s="1">
+      <c r="U5" s="2">
         <v>46210</v>
       </c>
     </row>
@@ -1883,10 +1909,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>46149</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -1933,10 +1959,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>43731</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -1948,7 +1974,7 @@
       <c r="T7" t="s">
         <v>151</v>
       </c>
-      <c r="U7" s="1">
+      <c r="U7" s="2">
         <v>43507</v>
       </c>
     </row>
@@ -1989,10 +2015,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45511</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2039,10 +2065,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45716</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2054,7 +2080,7 @@
       <c r="T9" t="s">
         <v>152</v>
       </c>
-      <c r="U9" s="1">
+      <c r="U9" s="2">
         <v>44665</v>
       </c>
     </row>
@@ -2095,10 +2121,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>45064</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2139,10 +2165,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>46135</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2154,7 +2180,7 @@
       <c r="T11" t="s">
         <v>153</v>
       </c>
-      <c r="U11" s="1">
+      <c r="U11" s="2">
         <v>46227</v>
       </c>
     </row>
@@ -2195,7 +2221,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2239,10 +2265,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>46199</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2289,10 +2315,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45667</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2304,7 +2330,7 @@
       <c r="T14" t="s">
         <v>154</v>
       </c>
-      <c r="U14" s="1">
+      <c r="U14" s="2">
         <v>46072</v>
       </c>
     </row>
@@ -2345,10 +2371,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>46064</v>
       </c>
-      <c r="Q15" s="1">
+      <c r="Q15" s="2">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2395,10 +2421,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>44285</v>
       </c>
-      <c r="Q16" s="1">
+      <c r="Q16" s="2">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2410,7 +2436,7 @@
       <c r="T16" t="s">
         <v>155</v>
       </c>
-      <c r="U16" s="1">
+      <c r="U16" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2451,10 +2477,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45922</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2501,10 +2527,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>45930</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2516,7 +2542,7 @@
       <c r="T18" t="s">
         <v>156</v>
       </c>
-      <c r="U18" s="1">
+      <c r="U18" s="2">
         <v>46198</v>
       </c>
     </row>
@@ -2557,10 +2583,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45524</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2572,7 +2598,7 @@
       <c r="T19" t="s">
         <v>157</v>
       </c>
-      <c r="U19" s="1">
+      <c r="U19" s="2">
         <v>46258</v>
       </c>
     </row>
@@ -2613,10 +2639,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>45026</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2628,7 +2654,7 @@
       <c r="T20" t="s">
         <v>158</v>
       </c>
-      <c r="U20" s="1">
+      <c r="U20" s="2">
         <v>46157</v>
       </c>
     </row>
@@ -2669,10 +2695,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>45159</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2684,7 +2710,7 @@
       <c r="T21" t="s">
         <v>125</v>
       </c>
-      <c r="U21" s="1">
+      <c r="U21" s="2">
         <v>46209</v>
       </c>
     </row>
@@ -2722,10 +2748,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2737,7 +2763,7 @@
       <c r="T22" t="s">
         <v>159</v>
       </c>
-      <c r="U22" s="1">
+      <c r="U22" s="2">
         <v>45995</v>
       </c>
     </row>
@@ -2775,10 +2801,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>45713</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -2787,7 +2813,7 @@
       <c r="S23" t="s">
         <v>148</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -2828,10 +2854,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>46062</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>46220</v>
       </c>
       <c r="R24" t="s">
@@ -2843,7 +2869,7 @@
       <c r="T24" t="s">
         <v>160</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24" s="2">
         <v>46253</v>
       </c>
     </row>
@@ -2884,10 +2910,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45079</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -2934,10 +2960,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>41346</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -2949,7 +2975,7 @@
       <c r="T26" t="s">
         <v>161</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>46150</v>
       </c>
     </row>
@@ -2990,10 +3016,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45579</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3040,10 +3066,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>46171</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3090,10 +3116,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44320</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3140,10 +3166,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="2">
         <v>42661</v>
       </c>
-      <c r="Q30" s="1">
+      <c r="Q30" s="2">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3155,7 +3181,7 @@
       <c r="T30" t="s">
         <v>162</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="2">
         <v>45358</v>
       </c>
     </row>
@@ -3196,10 +3222,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="2">
         <v>46220</v>
       </c>
-      <c r="Q31" s="1">
+      <c r="Q31" s="2">
         <v>46253</v>
       </c>
       <c r="R31" t="s">
@@ -3211,7 +3237,7 @@
       <c r="T31" t="s">
         <v>163</v>
       </c>
-      <c r="U31" s="1">
+      <c r="U31" s="2">
         <v>46252</v>
       </c>
     </row>
@@ -3252,10 +3278,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="2">
         <v>43797</v>
       </c>
-      <c r="Q32" s="1">
+      <c r="Q32" s="2">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3302,10 +3328,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>42810</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3317,7 +3343,7 @@
       <c r="T33" t="s">
         <v>164</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="2">
         <v>43802</v>
       </c>
     </row>
@@ -3358,10 +3384,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>45070</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>46258</v>
       </c>
       <c r="R34" t="s">
@@ -3373,7 +3399,7 @@
       <c r="T34" t="s">
         <v>165</v>
       </c>
-      <c r="U34" s="1">
+      <c r="U34" s="2">
         <v>46258</v>
       </c>
     </row>
@@ -3414,10 +3440,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>43250</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3464,10 +3490,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45841</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3514,10 +3540,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="2">
         <v>45105</v>
       </c>
-      <c r="Q37" s="1">
+      <c r="Q37" s="2">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3529,7 +3555,7 @@
       <c r="T37" t="s">
         <v>166</v>
       </c>
-      <c r="U37" s="1">
+      <c r="U37" s="2">
         <v>46184</v>
       </c>
     </row>
@@ -3570,10 +3596,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>45636</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>46219</v>
       </c>
       <c r="S38" t="s">
@@ -3582,7 +3608,7 @@
       <c r="T38" t="s">
         <v>167</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="2">
         <v>45351</v>
       </c>
     </row>
@@ -3623,10 +3649,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>45831</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3670,10 +3696,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>44287</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3694,22 +3720,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -7957,70 +7983,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8058,10 +8084,10 @@
       <c r="O2" t="s">
         <v>103</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="2">
         <v>45490</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="2">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -8105,10 +8131,10 @@
       <c r="O3" t="s">
         <v>82</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="2">
         <v>45618</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3" s="2">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -8152,10 +8178,10 @@
       <c r="O4" t="s">
         <v>98</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="2">
         <v>45539</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="2">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -8199,10 +8225,10 @@
       <c r="O5" t="s">
         <v>99</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>45567</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -8246,10 +8272,10 @@
       <c r="O6" t="s">
         <v>96</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>45568</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -8293,10 +8319,10 @@
       <c r="O7" t="s">
         <v>84</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>45831</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -8340,10 +8366,10 @@
       <c r="O8" t="s">
         <v>104</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>45601</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -8387,10 +8413,10 @@
       <c r="O9" t="s">
         <v>93</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>45631</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -8434,10 +8460,10 @@
       <c r="O10" t="s">
         <v>90</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>43902</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -8481,10 +8507,10 @@
       <c r="O11" t="s">
         <v>100</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="2">
         <v>44736</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -8528,10 +8554,10 @@
       <c r="O12" t="s">
         <v>83</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="2">
         <v>45776</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="2">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -8575,10 +8601,10 @@
       <c r="O13" t="s">
         <v>81</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="2">
         <v>45772</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="2">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -8622,10 +8648,10 @@
       <c r="O14" t="s">
         <v>101</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="2">
         <v>45000</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="2">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -8669,7 +8695,7 @@
       <c r="O15" t="s">
         <v>95</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="2">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -8710,7 +8736,7 @@
       <c r="O16" t="s">
         <v>91</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="2">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -8751,10 +8777,10 @@
       <c r="O17" t="s">
         <v>94</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="2">
         <v>45371</v>
       </c>
-      <c r="Q17" s="1">
+      <c r="Q17" s="2">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -8798,10 +8824,10 @@
       <c r="O18" t="s">
         <v>92</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="2">
         <v>46001</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="Q18" s="2">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -8845,10 +8871,10 @@
       <c r="O19" t="s">
         <v>105</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="2">
         <v>45436</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q19" s="2">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -8892,10 +8918,10 @@
       <c r="O20" t="s">
         <v>97</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="2">
         <v>44372</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="Q20" s="2">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -8939,10 +8965,10 @@
       <c r="O21" t="s">
         <v>106</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="2">
         <v>44362</v>
       </c>
-      <c r="Q21" s="1">
+      <c r="Q21" s="2">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -8986,10 +9012,10 @@
       <c r="O22" t="s">
         <v>87</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="2">
         <v>45511</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="Q22" s="2">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -9027,10 +9053,10 @@
       <c r="O23" t="s">
         <v>291</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="2">
         <v>40044</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q23" s="2">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -9042,7 +9068,7 @@
       <c r="T23" t="s">
         <v>331</v>
       </c>
-      <c r="U23" s="1">
+      <c r="U23" s="2">
         <v>45775</v>
       </c>
     </row>
@@ -9080,10 +9106,10 @@
       <c r="O24" t="s">
         <v>81</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="2">
         <v>43549</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="Q24" s="2">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -9095,7 +9121,7 @@
       <c r="T24" t="s">
         <v>332</v>
       </c>
-      <c r="U24" s="1">
+      <c r="U24" s="2">
         <v>45810</v>
       </c>
     </row>
@@ -9133,10 +9159,10 @@
       <c r="O25" t="s">
         <v>87</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="2">
         <v>45447</v>
       </c>
-      <c r="Q25" s="1">
+      <c r="Q25" s="2">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -9148,7 +9174,7 @@
       <c r="T25" t="s">
         <v>333</v>
       </c>
-      <c r="U25" s="1">
+      <c r="U25" s="2">
         <v>45937</v>
       </c>
     </row>
@@ -9186,10 +9212,10 @@
       <c r="O26" t="s">
         <v>101</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="2">
         <v>44485</v>
       </c>
-      <c r="Q26" s="1">
+      <c r="Q26" s="2">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -9201,7 +9227,7 @@
       <c r="T26" t="s">
         <v>334</v>
       </c>
-      <c r="U26" s="1">
+      <c r="U26" s="2">
         <v>45580</v>
       </c>
     </row>
@@ -9239,10 +9265,10 @@
       <c r="O27" t="s">
         <v>87</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="2">
         <v>45420</v>
       </c>
-      <c r="Q27" s="1">
+      <c r="Q27" s="2">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -9254,7 +9280,7 @@
       <c r="T27" t="s">
         <v>335</v>
       </c>
-      <c r="U27" s="1">
+      <c r="U27" s="2">
         <v>45588</v>
       </c>
     </row>
@@ -9292,10 +9318,10 @@
       <c r="O28" t="s">
         <v>102</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="2">
         <v>44369</v>
       </c>
-      <c r="Q28" s="1">
+      <c r="Q28" s="2">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -9307,7 +9333,7 @@
       <c r="T28" t="s">
         <v>336</v>
       </c>
-      <c r="U28" s="1">
+      <c r="U28" s="2">
         <v>45831</v>
       </c>
     </row>
@@ -9345,10 +9371,10 @@
       <c r="O29" t="s">
         <v>99</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="2">
         <v>44652</v>
       </c>
-      <c r="Q29" s="1">
+      <c r="Q29" s="2">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -9360,7 +9386,7 @@
       <c r="T29" t="s">
         <v>337</v>
       </c>
-      <c r="U29" s="1">
+      <c r="U29" s="2">
         <v>45734</v>
       </c>
     </row>
@@ -9392,7 +9418,7 @@
       <c r="T30" t="s">
         <v>338</v>
       </c>
-      <c r="U30" s="1">
+      <c r="U30" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -9424,7 +9450,7 @@
       <c r="T31" t="s">
         <v>339</v>
       </c>
-      <c r="U31" s="1">
+      <c r="U31" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -9456,7 +9482,7 @@
       <c r="T32" t="s">
         <v>340</v>
       </c>
-      <c r="U32" s="1">
+      <c r="U32" s="2">
         <v>46001</v>
       </c>
     </row>
@@ -9494,10 +9520,10 @@
       <c r="O33" t="s">
         <v>91</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="2">
         <v>43762</v>
       </c>
-      <c r="Q33" s="1">
+      <c r="Q33" s="2">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -9509,7 +9535,7 @@
       <c r="T33" t="s">
         <v>319</v>
       </c>
-      <c r="U33" s="1">
+      <c r="U33" s="2">
         <v>46037</v>
       </c>
     </row>
@@ -9547,16 +9573,16 @@
       <c r="O34" t="s">
         <v>292</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="2">
         <v>40071</v>
       </c>
-      <c r="Q34" s="1">
+      <c r="Q34" s="2">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>148</v>
       </c>
-      <c r="U34" s="1">
+      <c r="U34" s="2">
         <v>41023</v>
       </c>
     </row>
@@ -9588,10 +9614,10 @@
       <c r="O35" t="s">
         <v>88</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="2">
         <v>44784</v>
       </c>
-      <c r="Q35" s="1">
+      <c r="Q35" s="2">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -9600,7 +9626,7 @@
       <c r="S35" t="s">
         <v>148</v>
       </c>
-      <c r="U35" s="1">
+      <c r="U35" s="2">
         <v>45259</v>
       </c>
     </row>
@@ -9638,10 +9664,10 @@
       <c r="O36" t="s">
         <v>92</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="2">
         <v>45103</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="Q36" s="2">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -9650,7 +9676,7 @@
       <c r="S36" t="s">
         <v>148</v>
       </c>
-      <c r="U36" s="1">
+      <c r="U36" s="2">
         <v>46000</v>
       </c>
     </row>
@@ -9714,10 +9740,10 @@
       <c r="O38" t="s">
         <v>97</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="2">
         <v>38511</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="Q38" s="2">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -9726,7 +9752,7 @@
       <c r="S38" t="s">
         <v>148</v>
       </c>
-      <c r="U38" s="1">
+      <c r="U38" s="2">
         <v>39068</v>
       </c>
     </row>
@@ -9764,10 +9790,10 @@
       <c r="O39" t="s">
         <v>104</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="2">
         <v>39006</v>
       </c>
-      <c r="Q39" s="1">
+      <c r="Q39" s="2">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -9779,7 +9805,7 @@
       <c r="T39" t="s">
         <v>341</v>
       </c>
-      <c r="U39" s="1">
+      <c r="U39" s="2">
         <v>40568</v>
       </c>
     </row>
@@ -9811,10 +9837,10 @@
       <c r="O40" t="s">
         <v>101</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="2">
         <v>40836</v>
       </c>
-      <c r="Q40" s="1">
+      <c r="Q40" s="2">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -9826,7 +9852,7 @@
       <c r="T40" t="s">
         <v>342</v>
       </c>
-      <c r="U40" s="1">
+      <c r="U40" s="2">
         <v>42270</v>
       </c>
     </row>
@@ -9864,10 +9890,10 @@
       <c r="O41" t="s">
         <v>96</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P41" s="2">
         <v>42940</v>
       </c>
-      <c r="Q41" s="1">
+      <c r="Q41" s="2">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -9879,7 +9905,7 @@
       <c r="T41" t="s">
         <v>343</v>
       </c>
-      <c r="U41" s="1">
+      <c r="U41" s="2">
         <v>44148</v>
       </c>
     </row>
@@ -9917,10 +9943,10 @@
       <c r="O42" t="s">
         <v>83</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P42" s="2">
         <v>43696</v>
       </c>
-      <c r="Q42" s="1">
+      <c r="Q42" s="2">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -9932,7 +9958,7 @@
       <c r="T42" t="s">
         <v>344</v>
       </c>
-      <c r="U42" s="1">
+      <c r="U42" s="2">
         <v>43185</v>
       </c>
     </row>
@@ -9970,10 +9996,10 @@
       <c r="O43" t="s">
         <v>85</v>
       </c>
-      <c r="P43" s="1">
+      <c r="P43" s="2">
         <v>43544</v>
       </c>
-      <c r="Q43" s="1">
+      <c r="Q43" s="2">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -9985,7 +10011,7 @@
       <c r="T43" t="s">
         <v>345</v>
       </c>
-      <c r="U43" s="1">
+      <c r="U43" s="2">
         <v>42850</v>
       </c>
     </row>
@@ -10023,10 +10049,10 @@
       <c r="O44" t="s">
         <v>98</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P44" s="2">
         <v>45076</v>
       </c>
-      <c r="Q44" s="1">
+      <c r="Q44" s="2">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -10038,7 +10064,7 @@
       <c r="T44" t="s">
         <v>346</v>
       </c>
-      <c r="U44" s="1">
+      <c r="U44" s="2">
         <v>44404</v>
       </c>
     </row>
@@ -10076,10 +10102,10 @@
       <c r="O45" t="s">
         <v>82</v>
       </c>
-      <c r="P45" s="1">
+      <c r="P45" s="2">
         <v>42963</v>
       </c>
-      <c r="Q45" s="1">
+      <c r="Q45" s="2">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -10091,7 +10117,7 @@
       <c r="T45" t="s">
         <v>347</v>
       </c>
-      <c r="U45" s="1">
+      <c r="U45" s="2">
         <v>42698</v>
       </c>
     </row>
@@ -10129,10 +10155,10 @@
       <c r="O46" t="s">
         <v>89</v>
       </c>
-      <c r="P46" s="1">
+      <c r="P46" s="2">
         <v>45054</v>
       </c>
-      <c r="Q46" s="1">
+      <c r="Q46" s="2">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -10144,7 +10170,7 @@
       <c r="T46" t="s">
         <v>348</v>
       </c>
-      <c r="U46" s="1">
+      <c r="U46" s="2">
         <v>43941</v>
       </c>
     </row>
@@ -10159,25 +10185,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>353</v>
       </c>
     </row>
@@ -10839,22 +10865,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>359</v>
       </c>
     </row>

--- a/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_motores_tratada.xlsx
@@ -1237,16 +1237,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1262,7 +1254,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1270,30 +1262,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1593,70 +1567,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1697,10 +1671,10 @@
       <c r="O2">
         <v>4000</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>41754</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>46134</v>
       </c>
       <c r="R2" t="s">
@@ -1712,7 +1686,7 @@
       <c r="T2" t="s">
         <v>149</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="1">
         <v>46170</v>
       </c>
     </row>
@@ -1753,10 +1727,10 @@
       <c r="O3">
         <v>4000</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>44709</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>44652</v>
       </c>
       <c r="R3" t="s">
@@ -1803,10 +1777,10 @@
       <c r="O4">
         <v>4000</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>44348</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>44348</v>
       </c>
       <c r="R4" t="s">
@@ -1853,10 +1827,10 @@
       <c r="O5">
         <v>4000</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>46059</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>46203</v>
       </c>
       <c r="R5" t="s">
@@ -1868,7 +1842,7 @@
       <c r="T5" t="s">
         <v>150</v>
       </c>
-      <c r="U5" s="2">
+      <c r="U5" s="1">
         <v>46210</v>
       </c>
     </row>
@@ -1909,10 +1883,10 @@
       <c r="O6">
         <v>4000</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>46149</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45510</v>
       </c>
       <c r="R6" t="s">
@@ -1959,10 +1933,10 @@
       <c r="O7">
         <v>4000</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>43731</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45301</v>
       </c>
       <c r="R7" t="s">
@@ -1974,7 +1948,7 @@
       <c r="T7" t="s">
         <v>151</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U7" s="1">
         <v>43507</v>
       </c>
     </row>
@@ -2015,10 +1989,10 @@
       <c r="O8">
         <v>4000</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45511</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>43725</v>
       </c>
       <c r="R8" t="s">
@@ -2065,10 +2039,10 @@
       <c r="O9">
         <v>4000</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45716</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45716</v>
       </c>
       <c r="R9" t="s">
@@ -2080,7 +2054,7 @@
       <c r="T9" t="s">
         <v>152</v>
       </c>
-      <c r="U9" s="2">
+      <c r="U9" s="1">
         <v>44665</v>
       </c>
     </row>
@@ -2121,10 +2095,10 @@
       <c r="O10">
         <v>4000</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>45064</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>45048</v>
       </c>
       <c r="R10" t="s">
@@ -2165,10 +2139,10 @@
       <c r="O11">
         <v>4000</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>46135</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>46169</v>
       </c>
       <c r="R11" t="s">
@@ -2180,7 +2154,7 @@
       <c r="T11" t="s">
         <v>153</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="1">
         <v>46227</v>
       </c>
     </row>
@@ -2221,7 +2195,7 @@
       <c r="O12">
         <v>4000</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>46125</v>
       </c>
       <c r="S12" t="s">
@@ -2265,10 +2239,10 @@
       <c r="O13">
         <v>4000</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>46199</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>41861</v>
       </c>
       <c r="R13" t="s">
@@ -2315,10 +2289,10 @@
       <c r="O14">
         <v>4000</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45667</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>46059</v>
       </c>
       <c r="R14" t="s">
@@ -2330,7 +2304,7 @@
       <c r="T14" t="s">
         <v>154</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" s="1">
         <v>46072</v>
       </c>
     </row>
@@ -2371,10 +2345,10 @@
       <c r="O15">
         <v>4000</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>46064</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="1">
         <v>43592</v>
       </c>
       <c r="R15" t="s">
@@ -2421,10 +2395,10 @@
       <c r="O16">
         <v>4000</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>44285</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="1">
         <v>45524</v>
       </c>
       <c r="R16" t="s">
@@ -2436,7 +2410,7 @@
       <c r="T16" t="s">
         <v>155</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2477,10 +2451,10 @@
       <c r="O17">
         <v>4000</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45922</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45061</v>
       </c>
       <c r="R17" t="s">
@@ -2527,10 +2501,10 @@
       <c r="O18">
         <v>4000</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>45930</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>46184</v>
       </c>
       <c r="R18" t="s">
@@ -2542,7 +2516,7 @@
       <c r="T18" t="s">
         <v>156</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" s="1">
         <v>46198</v>
       </c>
     </row>
@@ -2583,10 +2557,10 @@
       <c r="O19">
         <v>4000</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45524</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>46014</v>
       </c>
       <c r="R19" t="s">
@@ -2598,7 +2572,7 @@
       <c r="T19" t="s">
         <v>157</v>
       </c>
-      <c r="U19" s="2">
+      <c r="U19" s="1">
         <v>46258</v>
       </c>
     </row>
@@ -2639,10 +2613,10 @@
       <c r="O20">
         <v>4000</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>45026</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>45446</v>
       </c>
       <c r="R20" t="s">
@@ -2654,7 +2628,7 @@
       <c r="T20" t="s">
         <v>158</v>
       </c>
-      <c r="U20" s="2">
+      <c r="U20" s="1">
         <v>46157</v>
       </c>
     </row>
@@ -2695,10 +2669,10 @@
       <c r="O21">
         <v>4000</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>45159</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>46199</v>
       </c>
       <c r="R21" t="s">
@@ -2710,7 +2684,7 @@
       <c r="T21" t="s">
         <v>125</v>
       </c>
-      <c r="U21" s="2">
+      <c r="U21" s="1">
         <v>46209</v>
       </c>
     </row>
@@ -2748,10 +2722,10 @@
       <c r="O22">
         <v>4000</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45922</v>
       </c>
       <c r="R22" t="s">
@@ -2763,7 +2737,7 @@
       <c r="T22" t="s">
         <v>159</v>
       </c>
-      <c r="U22" s="2">
+      <c r="U22" s="1">
         <v>45995</v>
       </c>
     </row>
@@ -2801,10 +2775,10 @@
       <c r="O23">
         <v>4000</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>45713</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>45810</v>
       </c>
       <c r="R23" t="s">
@@ -2813,7 +2787,7 @@
       <c r="S23" t="s">
         <v>148</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -2854,10 +2828,10 @@
       <c r="O24">
         <v>4000</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>46062</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>46220</v>
       </c>
       <c r="R24" t="s">
@@ -2869,7 +2843,7 @@
       <c r="T24" t="s">
         <v>160</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="1">
         <v>46253</v>
       </c>
     </row>
@@ -2910,10 +2884,10 @@
       <c r="O25">
         <v>4000</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45079</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45062</v>
       </c>
       <c r="R25" t="s">
@@ -2960,10 +2934,10 @@
       <c r="O26">
         <v>4000</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>41346</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>45916</v>
       </c>
       <c r="R26" t="s">
@@ -2975,7 +2949,7 @@
       <c r="T26" t="s">
         <v>161</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>46150</v>
       </c>
     </row>
@@ -3016,10 +2990,10 @@
       <c r="O27">
         <v>4000</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45579</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45579</v>
       </c>
       <c r="R27" t="s">
@@ -3066,10 +3040,10 @@
       <c r="O28">
         <v>4000</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>46171</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>46149</v>
       </c>
       <c r="R28" t="s">
@@ -3116,10 +3090,10 @@
       <c r="O29">
         <v>4000</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44320</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>44320</v>
       </c>
       <c r="R29" t="s">
@@ -3166,10 +3140,10 @@
       <c r="O30">
         <v>4000</v>
       </c>
-      <c r="P30" s="2">
+      <c r="P30" s="1">
         <v>42661</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="1">
         <v>45252</v>
       </c>
       <c r="R30" t="s">
@@ -3181,7 +3155,7 @@
       <c r="T30" t="s">
         <v>162</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>45358</v>
       </c>
     </row>
@@ -3222,10 +3196,10 @@
       <c r="O31">
         <v>4000</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="1">
         <v>46220</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="1">
         <v>46253</v>
       </c>
       <c r="R31" t="s">
@@ -3237,7 +3211,7 @@
       <c r="T31" t="s">
         <v>163</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" s="1">
         <v>46252</v>
       </c>
     </row>
@@ -3278,10 +3252,10 @@
       <c r="O32">
         <v>4000</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="1">
         <v>43797</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="1">
         <v>43725</v>
       </c>
       <c r="R32" t="s">
@@ -3328,10 +3302,10 @@
       <c r="O33">
         <v>4000</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>42810</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>43159</v>
       </c>
       <c r="R33" t="s">
@@ -3343,7 +3317,7 @@
       <c r="T33" t="s">
         <v>164</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>43802</v>
       </c>
     </row>
@@ -3384,10 +3358,10 @@
       <c r="O34">
         <v>4000</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>45070</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>46258</v>
       </c>
       <c r="R34" t="s">
@@ -3399,7 +3373,7 @@
       <c r="T34" t="s">
         <v>165</v>
       </c>
-      <c r="U34" s="2">
+      <c r="U34" s="1">
         <v>46258</v>
       </c>
     </row>
@@ -3440,10 +3414,10 @@
       <c r="O35">
         <v>4000</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>43250</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>41149</v>
       </c>
       <c r="R35" t="s">
@@ -3490,10 +3464,10 @@
       <c r="O36">
         <v>4000</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45841</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>45754</v>
       </c>
       <c r="R36" t="s">
@@ -3540,10 +3514,10 @@
       <c r="O37">
         <v>4000</v>
       </c>
-      <c r="P37" s="2">
+      <c r="P37" s="1">
         <v>45105</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="1">
         <v>45509</v>
       </c>
       <c r="R37" t="s">
@@ -3555,7 +3529,7 @@
       <c r="T37" t="s">
         <v>166</v>
       </c>
-      <c r="U37" s="2">
+      <c r="U37" s="1">
         <v>46184</v>
       </c>
     </row>
@@ -3596,10 +3570,10 @@
       <c r="O38">
         <v>4000</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>45636</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>46219</v>
       </c>
       <c r="S38" t="s">
@@ -3608,7 +3582,7 @@
       <c r="T38" t="s">
         <v>167</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>45351</v>
       </c>
     </row>
@@ -3649,10 +3623,10 @@
       <c r="O39">
         <v>4000</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>45831</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>45740</v>
       </c>
       <c r="S39" t="s">
@@ -3696,10 +3670,10 @@
       <c r="O40">
         <v>4000</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>44287</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>44114</v>
       </c>
       <c r="R40" t="s">
@@ -3720,22 +3694,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>170</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>171</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>172</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>173</v>
       </c>
     </row>
@@ -7983,70 +7957,70 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
@@ -8084,10 +8058,10 @@
       <c r="O2" t="s">
         <v>103</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="1">
         <v>45490</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="1">
         <v>45015</v>
       </c>
       <c r="R2" t="s">
@@ -8131,10 +8105,10 @@
       <c r="O3" t="s">
         <v>82</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>45618</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>45614</v>
       </c>
       <c r="R3" t="s">
@@ -8178,10 +8152,10 @@
       <c r="O4" t="s">
         <v>98</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="1">
         <v>45539</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>45539</v>
       </c>
       <c r="R4" t="s">
@@ -8225,10 +8199,10 @@
       <c r="O5" t="s">
         <v>99</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="1">
         <v>45567</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>45490</v>
       </c>
       <c r="R5" t="s">
@@ -8272,10 +8246,10 @@
       <c r="O6" t="s">
         <v>96</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="1">
         <v>45568</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>45526</v>
       </c>
       <c r="R6" t="s">
@@ -8319,10 +8293,10 @@
       <c r="O7" t="s">
         <v>84</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
         <v>45831</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>45352</v>
       </c>
       <c r="R7" t="s">
@@ -8366,10 +8340,10 @@
       <c r="O8" t="s">
         <v>104</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
         <v>45601</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>44704</v>
       </c>
       <c r="R8" t="s">
@@ -8413,10 +8387,10 @@
       <c r="O9" t="s">
         <v>93</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
         <v>45631</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>45628</v>
       </c>
       <c r="R9" t="s">
@@ -8460,10 +8434,10 @@
       <c r="O10" t="s">
         <v>90</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="1">
         <v>43902</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>43549</v>
       </c>
       <c r="R10" t="s">
@@ -8507,10 +8481,10 @@
       <c r="O11" t="s">
         <v>100</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="1">
         <v>44736</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <v>44735</v>
       </c>
       <c r="R11" t="s">
@@ -8554,10 +8528,10 @@
       <c r="O12" t="s">
         <v>83</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>45776</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <v>45776</v>
       </c>
       <c r="R12" t="s">
@@ -8601,10 +8575,10 @@
       <c r="O13" t="s">
         <v>81</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="1">
         <v>45772</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="1">
         <v>45600</v>
       </c>
       <c r="R13" t="s">
@@ -8648,10 +8622,10 @@
       <c r="O14" t="s">
         <v>101</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="1">
         <v>45000</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="1">
         <v>44630</v>
       </c>
       <c r="R14" t="s">
@@ -8695,7 +8669,7 @@
       <c r="O15" t="s">
         <v>95</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="1">
         <v>45930</v>
       </c>
       <c r="S15" t="s">
@@ -8736,7 +8710,7 @@
       <c r="O16" t="s">
         <v>91</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="1">
         <v>46035</v>
       </c>
       <c r="S16" t="s">
@@ -8777,10 +8751,10 @@
       <c r="O17" t="s">
         <v>94</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="1">
         <v>45371</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="1">
         <v>45026</v>
       </c>
       <c r="R17" t="s">
@@ -8824,10 +8798,10 @@
       <c r="O18" t="s">
         <v>92</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="1">
         <v>46001</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
         <v>45371</v>
       </c>
       <c r="R18" t="s">
@@ -8871,10 +8845,10 @@
       <c r="O19" t="s">
         <v>105</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="1">
         <v>45436</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>45294</v>
       </c>
       <c r="R19" t="s">
@@ -8918,10 +8892,10 @@
       <c r="O20" t="s">
         <v>97</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>44372</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>44369</v>
       </c>
       <c r="R20" t="s">
@@ -8965,10 +8939,10 @@
       <c r="O21" t="s">
         <v>106</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="1">
         <v>44362</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>43894</v>
       </c>
       <c r="R21" t="s">
@@ -9012,10 +8986,10 @@
       <c r="O22" t="s">
         <v>87</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>45511</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>45509</v>
       </c>
       <c r="R22" t="s">
@@ -9053,10 +9027,10 @@
       <c r="O23" t="s">
         <v>291</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>40044</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>40126</v>
       </c>
       <c r="R23" t="s">
@@ -9068,7 +9042,7 @@
       <c r="T23" t="s">
         <v>331</v>
       </c>
-      <c r="U23" s="2">
+      <c r="U23" s="1">
         <v>45775</v>
       </c>
     </row>
@@ -9106,10 +9080,10 @@
       <c r="O24" t="s">
         <v>81</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="1">
         <v>43549</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>45772</v>
       </c>
       <c r="R24" t="s">
@@ -9121,7 +9095,7 @@
       <c r="T24" t="s">
         <v>332</v>
       </c>
-      <c r="U24" s="2">
+      <c r="U24" s="1">
         <v>45810</v>
       </c>
     </row>
@@ -9159,10 +9133,10 @@
       <c r="O25" t="s">
         <v>87</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="1">
         <v>45447</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>45510</v>
       </c>
       <c r="R25" t="s">
@@ -9174,7 +9148,7 @@
       <c r="T25" t="s">
         <v>333</v>
       </c>
-      <c r="U25" s="2">
+      <c r="U25" s="1">
         <v>45937</v>
       </c>
     </row>
@@ -9212,10 +9186,10 @@
       <c r="O26" t="s">
         <v>101</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="1">
         <v>44485</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>44959</v>
       </c>
       <c r="R26" t="s">
@@ -9227,7 +9201,7 @@
       <c r="T26" t="s">
         <v>334</v>
       </c>
-      <c r="U26" s="2">
+      <c r="U26" s="1">
         <v>45580</v>
       </c>
     </row>
@@ -9265,10 +9239,10 @@
       <c r="O27" t="s">
         <v>87</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="1">
         <v>45420</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <v>45446</v>
       </c>
       <c r="R27" t="s">
@@ -9280,7 +9254,7 @@
       <c r="T27" t="s">
         <v>335</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U27" s="1">
         <v>45588</v>
       </c>
     </row>
@@ -9318,10 +9292,10 @@
       <c r="O28" t="s">
         <v>102</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="1">
         <v>44369</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <v>45824</v>
       </c>
       <c r="R28" t="s">
@@ -9333,7 +9307,7 @@
       <c r="T28" t="s">
         <v>336</v>
       </c>
-      <c r="U28" s="2">
+      <c r="U28" s="1">
         <v>45831</v>
       </c>
     </row>
@@ -9371,10 +9345,10 @@
       <c r="O29" t="s">
         <v>99</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="1">
         <v>44652</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
         <v>45567</v>
       </c>
       <c r="R29" t="s">
@@ -9386,7 +9360,7 @@
       <c r="T29" t="s">
         <v>337</v>
       </c>
-      <c r="U29" s="2">
+      <c r="U29" s="1">
         <v>45734</v>
       </c>
     </row>
@@ -9418,7 +9392,7 @@
       <c r="T30" t="s">
         <v>338</v>
       </c>
-      <c r="U30" s="2">
+      <c r="U30" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -9450,7 +9424,7 @@
       <c r="T31" t="s">
         <v>339</v>
       </c>
-      <c r="U31" s="2">
+      <c r="U31" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -9482,7 +9456,7 @@
       <c r="T32" t="s">
         <v>340</v>
       </c>
-      <c r="U32" s="2">
+      <c r="U32" s="1">
         <v>46001</v>
       </c>
     </row>
@@ -9520,10 +9494,10 @@
       <c r="O33" t="s">
         <v>91</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
         <v>43762</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
         <v>46031</v>
       </c>
       <c r="R33" t="s">
@@ -9535,7 +9509,7 @@
       <c r="T33" t="s">
         <v>319</v>
       </c>
-      <c r="U33" s="2">
+      <c r="U33" s="1">
         <v>46037</v>
       </c>
     </row>
@@ -9573,16 +9547,16 @@
       <c r="O34" t="s">
         <v>292</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
         <v>40071</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="1">
         <v>41023</v>
       </c>
       <c r="S34" t="s">
         <v>148</v>
       </c>
-      <c r="U34" s="2">
+      <c r="U34" s="1">
         <v>41023</v>
       </c>
     </row>
@@ -9614,10 +9588,10 @@
       <c r="O35" t="s">
         <v>88</v>
       </c>
-      <c r="P35" s="2">
+      <c r="P35" s="1">
         <v>44784</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>45259</v>
       </c>
       <c r="R35" t="s">
@@ -9626,7 +9600,7 @@
       <c r="S35" t="s">
         <v>148</v>
       </c>
-      <c r="U35" s="2">
+      <c r="U35" s="1">
         <v>45259</v>
       </c>
     </row>
@@ -9664,10 +9638,10 @@
       <c r="O36" t="s">
         <v>92</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="1">
         <v>45103</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>46000</v>
       </c>
       <c r="R36" t="s">
@@ -9676,7 +9650,7 @@
       <c r="S36" t="s">
         <v>148</v>
       </c>
-      <c r="U36" s="2">
+      <c r="U36" s="1">
         <v>46000</v>
       </c>
     </row>
@@ -9740,10 +9714,10 @@
       <c r="O38" t="s">
         <v>97</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="1">
         <v>38511</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>39068</v>
       </c>
       <c r="R38" t="s">
@@ -9752,7 +9726,7 @@
       <c r="S38" t="s">
         <v>148</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="1">
         <v>39068</v>
       </c>
     </row>
@@ -9790,10 +9764,10 @@
       <c r="O39" t="s">
         <v>104</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="1">
         <v>39006</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>40568</v>
       </c>
       <c r="R39" t="s">
@@ -9805,7 +9779,7 @@
       <c r="T39" t="s">
         <v>341</v>
       </c>
-      <c r="U39" s="2">
+      <c r="U39" s="1">
         <v>40568</v>
       </c>
     </row>
@@ -9837,10 +9811,10 @@
       <c r="O40" t="s">
         <v>101</v>
       </c>
-      <c r="P40" s="2">
+      <c r="P40" s="1">
         <v>40836</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>42270</v>
       </c>
       <c r="R40" t="s">
@@ -9852,7 +9826,7 @@
       <c r="T40" t="s">
         <v>342</v>
       </c>
-      <c r="U40" s="2">
+      <c r="U40" s="1">
         <v>42270</v>
       </c>
     </row>
@@ -9890,10 +9864,10 @@
       <c r="O41" t="s">
         <v>96</v>
       </c>
-      <c r="P41" s="2">
+      <c r="P41" s="1">
         <v>42940</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="1">
         <v>43494</v>
       </c>
       <c r="R41" t="s">
@@ -9905,7 +9879,7 @@
       <c r="T41" t="s">
         <v>343</v>
       </c>
-      <c r="U41" s="2">
+      <c r="U41" s="1">
         <v>44148</v>
       </c>
     </row>
@@ -9943,10 +9917,10 @@
       <c r="O42" t="s">
         <v>83</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="1">
         <v>43696</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="1">
         <v>45776</v>
       </c>
       <c r="R42" t="s">
@@ -9958,7 +9932,7 @@
       <c r="T42" t="s">
         <v>344</v>
       </c>
-      <c r="U42" s="2">
+      <c r="U42" s="1">
         <v>43185</v>
       </c>
     </row>
@@ -9996,10 +9970,10 @@
       <c r="O43" t="s">
         <v>85</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="1">
         <v>43544</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="1">
         <v>45916</v>
       </c>
       <c r="R43" t="s">
@@ -10011,7 +9985,7 @@
       <c r="T43" t="s">
         <v>345</v>
       </c>
-      <c r="U43" s="2">
+      <c r="U43" s="1">
         <v>42850</v>
       </c>
     </row>
@@ -10049,10 +10023,10 @@
       <c r="O44" t="s">
         <v>98</v>
       </c>
-      <c r="P44" s="2">
+      <c r="P44" s="1">
         <v>45076</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="1">
         <v>45539</v>
       </c>
       <c r="R44" t="s">
@@ -10064,7 +10038,7 @@
       <c r="T44" t="s">
         <v>346</v>
       </c>
-      <c r="U44" s="2">
+      <c r="U44" s="1">
         <v>44404</v>
       </c>
     </row>
@@ -10102,10 +10076,10 @@
       <c r="O45" t="s">
         <v>82</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="1">
         <v>42963</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="1">
         <v>45239</v>
       </c>
       <c r="R45" t="s">
@@ -10117,7 +10091,7 @@
       <c r="T45" t="s">
         <v>347</v>
       </c>
-      <c r="U45" s="2">
+      <c r="U45" s="1">
         <v>42698</v>
       </c>
     </row>
@@ -10155,10 +10129,10 @@
       <c r="O46" t="s">
         <v>89</v>
       </c>
-      <c r="P46" s="2">
+      <c r="P46" s="1">
         <v>45054</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="1">
         <v>45586</v>
       </c>
       <c r="R46" t="s">
@@ -10170,7 +10144,7 @@
       <c r="T46" t="s">
         <v>348</v>
       </c>
-      <c r="U46" s="2">
+      <c r="U46" s="1">
         <v>43941</v>
       </c>
     </row>
@@ -10185,25 +10159,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>349</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>350</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>351</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>352</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>353</v>
       </c>
     </row>
@@ -10865,22 +10839,22 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>354</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>355</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>356</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>357</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>358</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>359</v>
       </c>
     </row>
